--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="723">
   <si>
     <t>IDSocio</t>
   </si>
@@ -109,112 +109,148 @@
     <t>144658</t>
   </si>
   <si>
+    <t>118108</t>
+  </si>
+  <si>
+    <t>183590</t>
+  </si>
+  <si>
     <t>134792</t>
   </si>
   <si>
     <t>75553</t>
   </si>
   <si>
-    <t>183590</t>
-  </si>
-  <si>
     <t>322246</t>
   </si>
   <si>
+    <t>340035</t>
+  </si>
+  <si>
+    <t>340108</t>
+  </si>
+  <si>
+    <t>340183</t>
+  </si>
+  <si>
+    <t>340181</t>
+  </si>
+  <si>
+    <t>340334</t>
+  </si>
+  <si>
+    <t>340231</t>
+  </si>
+  <si>
+    <t>340750</t>
+  </si>
+  <si>
+    <t>338245</t>
+  </si>
+  <si>
+    <t>340441</t>
+  </si>
+  <si>
+    <t>340564</t>
+  </si>
+  <si>
+    <t>340899</t>
+  </si>
+  <si>
+    <t>341159</t>
+  </si>
+  <si>
     <t>339095</t>
   </si>
   <si>
+    <t>339521</t>
+  </si>
+  <si>
+    <t>339898</t>
+  </si>
+  <si>
+    <t>341189</t>
+  </si>
+  <si>
+    <t>340249</t>
+  </si>
+  <si>
     <t>339800</t>
   </si>
   <si>
-    <t>339521</t>
-  </si>
-  <si>
-    <t>339898</t>
-  </si>
-  <si>
-    <t>340183</t>
-  </si>
-  <si>
-    <t>340231</t>
-  </si>
-  <si>
-    <t>340035</t>
-  </si>
-  <si>
-    <t>340108</t>
-  </si>
-  <si>
     <t>339895</t>
   </si>
   <si>
     <t>339961</t>
   </si>
   <si>
-    <t>340181</t>
-  </si>
-  <si>
-    <t>340334</t>
-  </si>
-  <si>
-    <t>340441</t>
-  </si>
-  <si>
-    <t>340249</t>
-  </si>
-  <si>
     <t>340472</t>
   </si>
   <si>
-    <t>340750</t>
-  </si>
-  <si>
-    <t>340564</t>
-  </si>
-  <si>
-    <t>341189</t>
-  </si>
-  <si>
-    <t>341159</t>
-  </si>
-  <si>
-    <t>340899</t>
+    <t>342293</t>
+  </si>
+  <si>
+    <t>341056</t>
   </si>
   <si>
     <t>341295</t>
   </si>
   <si>
-    <t>341056</t>
+    <t>342573</t>
+  </si>
+  <si>
+    <t>342676</t>
+  </si>
+  <si>
+    <t>342142</t>
+  </si>
+  <si>
+    <t>342495</t>
+  </si>
+  <si>
+    <t>343240</t>
+  </si>
+  <si>
+    <t>342853</t>
+  </si>
+  <si>
+    <t>343007</t>
+  </si>
+  <si>
+    <t>343391</t>
+  </si>
+  <si>
+    <t>343394</t>
   </si>
   <si>
     <t>341297</t>
   </si>
   <si>
-    <t>342142</t>
-  </si>
-  <si>
     <t>341467</t>
   </si>
   <si>
-    <t>342293</t>
-  </si>
-  <si>
-    <t>342495</t>
-  </si>
-  <si>
-    <t>342676</t>
-  </si>
-  <si>
-    <t>342573</t>
-  </si>
-  <si>
-    <t>342853</t>
-  </si>
-  <si>
     <t>342494</t>
   </si>
   <si>
-    <t>343007</t>
+    <t>342851</t>
+  </si>
+  <si>
+    <t>343969</t>
+  </si>
+  <si>
+    <t>344019</t>
+  </si>
+  <si>
+    <t>343968</t>
+  </si>
+  <si>
+    <t>344075</t>
+  </si>
+  <si>
+    <t>344087</t>
+  </si>
+  <si>
+    <t>343401</t>
   </si>
   <si>
     <t>342843</t>
@@ -223,19 +259,13 @@
     <t>342857</t>
   </si>
   <si>
-    <t>342851</t>
-  </si>
-  <si>
-    <t>343391</t>
-  </si>
-  <si>
-    <t>343394</t>
-  </si>
-  <si>
-    <t>343240</t>
-  </si>
-  <si>
-    <t>343401</t>
+    <t>343975</t>
+  </si>
+  <si>
+    <t>343982</t>
+  </si>
+  <si>
+    <t>344362</t>
   </si>
   <si>
     <t>46373</t>
@@ -244,112 +274,148 @@
     <t>42252</t>
   </si>
   <si>
+    <t>15820</t>
+  </si>
+  <si>
+    <t>81097</t>
+  </si>
+  <si>
     <t>32440</t>
   </si>
   <si>
     <t>73366</t>
   </si>
   <si>
-    <t>81097</t>
-  </si>
-  <si>
     <t>19185</t>
   </si>
   <si>
+    <t>17853</t>
+  </si>
+  <si>
+    <t>17926</t>
+  </si>
+  <si>
+    <t>18001</t>
+  </si>
+  <si>
+    <t>17999</t>
+  </si>
+  <si>
+    <t>18152</t>
+  </si>
+  <si>
+    <t>18049</t>
+  </si>
+  <si>
+    <t>18568</t>
+  </si>
+  <si>
+    <t>16063</t>
+  </si>
+  <si>
+    <t>18259</t>
+  </si>
+  <si>
+    <t>18382</t>
+  </si>
+  <si>
+    <t>18717</t>
+  </si>
+  <si>
+    <t>18977</t>
+  </si>
+  <si>
     <t>16913</t>
   </si>
   <si>
+    <t>17339</t>
+  </si>
+  <si>
+    <t>17716</t>
+  </si>
+  <si>
+    <t>19007</t>
+  </si>
+  <si>
+    <t>18067</t>
+  </si>
+  <si>
     <t>17618</t>
   </si>
   <si>
-    <t>17339</t>
-  </si>
-  <si>
-    <t>17716</t>
-  </si>
-  <si>
-    <t>18001</t>
-  </si>
-  <si>
-    <t>18049</t>
-  </si>
-  <si>
-    <t>17853</t>
-  </si>
-  <si>
-    <t>17926</t>
-  </si>
-  <si>
     <t>17713</t>
   </si>
   <si>
     <t>17779</t>
   </si>
   <si>
-    <t>17999</t>
-  </si>
-  <si>
-    <t>18152</t>
-  </si>
-  <si>
-    <t>18259</t>
-  </si>
-  <si>
-    <t>18067</t>
-  </si>
-  <si>
     <t>18290</t>
   </si>
   <si>
-    <t>18568</t>
-  </si>
-  <si>
-    <t>18382</t>
-  </si>
-  <si>
-    <t>19007</t>
-  </si>
-  <si>
-    <t>18977</t>
-  </si>
-  <si>
-    <t>18717</t>
+    <t>20111</t>
+  </si>
+  <si>
+    <t>18874</t>
   </si>
   <si>
     <t>19113</t>
   </si>
   <si>
-    <t>18874</t>
+    <t>20390</t>
+  </si>
+  <si>
+    <t>20493</t>
+  </si>
+  <si>
+    <t>19960</t>
+  </si>
+  <si>
+    <t>20312</t>
+  </si>
+  <si>
+    <t>21057</t>
+  </si>
+  <si>
+    <t>20670</t>
+  </si>
+  <si>
+    <t>20824</t>
+  </si>
+  <si>
+    <t>21208</t>
+  </si>
+  <si>
+    <t>21211</t>
   </si>
   <si>
     <t>19115</t>
   </si>
   <si>
-    <t>19960</t>
-  </si>
-  <si>
     <t>19285</t>
   </si>
   <si>
-    <t>20111</t>
-  </si>
-  <si>
-    <t>20312</t>
-  </si>
-  <si>
-    <t>20493</t>
-  </si>
-  <si>
-    <t>20390</t>
-  </si>
-  <si>
-    <t>20670</t>
-  </si>
-  <si>
     <t>20311</t>
   </si>
   <si>
-    <t>20824</t>
+    <t>20668</t>
+  </si>
+  <si>
+    <t>21786</t>
+  </si>
+  <si>
+    <t>21836</t>
+  </si>
+  <si>
+    <t>21785</t>
+  </si>
+  <si>
+    <t>21892</t>
+  </si>
+  <si>
+    <t>21904</t>
+  </si>
+  <si>
+    <t>21218</t>
   </si>
   <si>
     <t>20660</t>
@@ -358,19 +424,13 @@
     <t>20674</t>
   </si>
   <si>
-    <t>20668</t>
-  </si>
-  <si>
-    <t>21208</t>
-  </si>
-  <si>
-    <t>21211</t>
-  </si>
-  <si>
-    <t>21057</t>
-  </si>
-  <si>
-    <t>21218</t>
+    <t>21792</t>
+  </si>
+  <si>
+    <t>21799</t>
+  </si>
+  <si>
+    <t>22179</t>
   </si>
   <si>
     <t>VILLAS DEL REY</t>
@@ -382,112 +442,148 @@
     <t>KARLA DENNIS</t>
   </si>
   <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRIAN </t>
+  </si>
+  <si>
     <t xml:space="preserve">FRANCISCO ALEXANDER </t>
   </si>
   <si>
     <t>DANIEL ALEJANDRO</t>
   </si>
   <si>
-    <t xml:space="preserve">BRIAN </t>
-  </si>
-  <si>
     <t>ZAIRA RAMIREZ CASTRO</t>
   </si>
   <si>
+    <t>KITZIA AILIME</t>
+  </si>
+  <si>
+    <t>CHRISTIAN</t>
+  </si>
+  <si>
+    <t>LEYLANI MIRANDA</t>
+  </si>
+  <si>
+    <t>SAHIRA YOMAHIRA</t>
+  </si>
+  <si>
+    <t>EMILY SOFIA</t>
+  </si>
+  <si>
+    <t>ELLIOT SAMUEL</t>
+  </si>
+  <si>
+    <t>ARMANDO</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>LUIS FERNANDO</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YORLENI </t>
+  </si>
+  <si>
+    <t>DAVID ERNESTO</t>
+  </si>
+  <si>
     <t>KARLA ELDA</t>
   </si>
   <si>
+    <t>LIZY NAILY</t>
+  </si>
+  <si>
+    <t>NAYLA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANABEL </t>
+  </si>
+  <si>
     <t>BRIAN MIGUEL</t>
   </si>
   <si>
-    <t>LIZY NAILY</t>
-  </si>
-  <si>
-    <t>NAYLA ALEJANDRA</t>
-  </si>
-  <si>
-    <t>LEYLANI MIRANDA</t>
-  </si>
-  <si>
-    <t>ELLIOT SAMUEL</t>
-  </si>
-  <si>
-    <t>KITZIA AILIME</t>
-  </si>
-  <si>
-    <t>CHRISTIAN</t>
-  </si>
-  <si>
     <t>JULIO ALEJANDRO</t>
   </si>
   <si>
     <t>CELINA</t>
   </si>
   <si>
-    <t>SAHIRA YOMAHIRA</t>
-  </si>
-  <si>
-    <t>EMILY SOFIA</t>
-  </si>
-  <si>
-    <t>LUIS FERNANDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANABEL </t>
-  </si>
-  <si>
     <t xml:space="preserve">ELIZABETH </t>
   </si>
   <si>
-    <t>ARMANDO</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>DAVID ERNESTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YORLENI </t>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMMANUEL </t>
   </si>
   <si>
     <t>FERNANDA</t>
   </si>
   <si>
-    <t xml:space="preserve">EMMANUEL </t>
+    <t>LOURDES RENE</t>
+  </si>
+  <si>
+    <t>VIVIAN DENIISSE</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NELSON </t>
+  </si>
+  <si>
+    <t>HECTOR EDUARDO</t>
+  </si>
+  <si>
+    <t>DAMARIS KATHELEEN</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>JOSE ENRIQUE</t>
+  </si>
+  <si>
+    <t>BRIANA NAOMI</t>
   </si>
   <si>
     <t>NATALIE</t>
   </si>
   <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
     <t>ADOLFO</t>
   </si>
   <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NELSON </t>
-  </si>
-  <si>
-    <t>VIVIAN DENIISSE</t>
-  </si>
-  <si>
-    <t>LOURDES RENE</t>
-  </si>
-  <si>
-    <t>DAMARIS KATHELEEN</t>
-  </si>
-  <si>
     <t>MIGUEL ANGEL</t>
   </si>
   <si>
-    <t>SERGIO</t>
+    <t xml:space="preserve">JOSE JAVIE </t>
+  </si>
+  <si>
+    <t>LUIS ALBERTO</t>
+  </si>
+  <si>
+    <t>ABRHAM ISACC</t>
+  </si>
+  <si>
+    <t>ALEXIS ABRAHAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GABRIELA </t>
+  </si>
+  <si>
+    <t>ROSARIO GUADALUPE</t>
+  </si>
+  <si>
+    <t>CARLOS ALBERTO</t>
   </si>
   <si>
     <t xml:space="preserve">CARLOS </t>
@@ -496,19 +592,13 @@
     <t>JORGE</t>
   </si>
   <si>
-    <t xml:space="preserve">JOSE JAVIE </t>
-  </si>
-  <si>
-    <t>JOSE ENRIQUE</t>
-  </si>
-  <si>
-    <t>BRIANA NAOMI</t>
-  </si>
-  <si>
-    <t>HECTOR EDUARDO</t>
-  </si>
-  <si>
-    <t>CARLOS ALBERTO</t>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JENNIFER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREA MICHELL </t>
   </si>
   <si>
     <t>VALENZUELA</t>
@@ -517,97 +607,127 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">SOTO </t>
   </si>
   <si>
     <t xml:space="preserve">ROMERO </t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>MAGALLON</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAJO </t>
+  </si>
+  <si>
+    <t>ARRIAGA</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORTIZ </t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>FELIX</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>ARIZMENDI</t>
   </si>
   <si>
+    <t>BRICEÑO</t>
+  </si>
+  <si>
+    <t>COTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGUEZ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEARA </t>
+  </si>
+  <si>
     <t>AISPURO</t>
   </si>
   <si>
-    <t>BRICEÑO</t>
-  </si>
-  <si>
-    <t>COTA</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>MAGALLON</t>
-  </si>
-  <si>
     <t>BEJARANO</t>
   </si>
   <si>
     <t xml:space="preserve">REYES </t>
   </si>
   <si>
-    <t xml:space="preserve">BAJO </t>
-  </si>
-  <si>
-    <t>ARRIAGA</t>
-  </si>
-  <si>
-    <t>FELIX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEARA </t>
-  </si>
-  <si>
     <t xml:space="preserve">MORALES </t>
   </si>
   <si>
-    <t xml:space="preserve">ORTIZ </t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RODRIGUEZ </t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>MACIAS</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>CANALES</t>
+  </si>
+  <si>
+    <t>SALGADO</t>
+  </si>
+  <si>
+    <t>VILLARREAL</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>MACIAS</t>
-  </si>
-  <si>
     <t>ALBISO</t>
   </si>
   <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>SALGADO</t>
-  </si>
-  <si>
     <t>TEJADA</t>
   </si>
   <si>
-    <t>VILLARREAL</t>
+    <t>ALCARAZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAMOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TORRES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZEPEDA </t>
   </si>
   <si>
     <t>ORTIZ</t>
@@ -616,16 +736,13 @@
     <t xml:space="preserve">JIMENEZ </t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>CANALES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZEPEDA </t>
+    <t>PEREYDA</t>
+  </si>
+  <si>
+    <t>FAVELA</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
   </si>
   <si>
     <t>BALLESTEROS</t>
@@ -634,85 +751,106 @@
     <t>DAVALOS</t>
   </si>
   <si>
+    <t>CARDENAS</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>VILLAMAN</t>
   </si>
   <si>
     <t>QUIJADA</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>BARRERA</t>
+  </si>
+  <si>
+    <t>PIZANO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>COSSIO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>REA</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARCOS </t>
+  </si>
+  <si>
     <t>CORTEZ</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>PIZANO</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>BARRERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARCOS </t>
-  </si>
-  <si>
     <t xml:space="preserve">VALENZUELA </t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>REA</t>
-  </si>
-  <si>
-    <t>MORENO</t>
+    <t>CORREA</t>
+  </si>
+  <si>
+    <t>MELERO</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
+    <t>MARISCAL</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>CAMACHO</t>
+  </si>
+  <si>
     <t>BARAJAS</t>
   </si>
   <si>
-    <t>CORREA</t>
-  </si>
-  <si>
-    <t>MARISCAL</t>
-  </si>
-  <si>
-    <t>MELERO</t>
-  </si>
-  <si>
     <t>HURTADO</t>
   </si>
   <si>
-    <t>ZEPEDA</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>KETCHUL</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>BACA</t>
+  </si>
+  <si>
+    <t>OCHOA</t>
   </si>
   <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
+    <t>URIBE</t>
   </si>
   <si>
     <t>52</t>
@@ -727,112 +865,148 @@
     <t>6862153682</t>
   </si>
   <si>
+    <t>6865298916</t>
+  </si>
+  <si>
+    <t>6864295199</t>
+  </si>
+  <si>
     <t>6863847095</t>
   </si>
   <si>
     <t>6863466296</t>
   </si>
   <si>
-    <t>6864295199</t>
-  </si>
-  <si>
     <t>6861234537</t>
   </si>
   <si>
+    <t>6862541870</t>
+  </si>
+  <si>
+    <t>6866740223</t>
+  </si>
+  <si>
+    <t>6863558685</t>
+  </si>
+  <si>
+    <t>6862091543</t>
+  </si>
+  <si>
+    <t>6864702297</t>
+  </si>
+  <si>
+    <t>6866507552</t>
+  </si>
+  <si>
+    <t>6863928150</t>
+  </si>
+  <si>
+    <t>6862641454</t>
+  </si>
+  <si>
+    <t>6674121912</t>
+  </si>
+  <si>
+    <t>6865860740</t>
+  </si>
+  <si>
+    <t>6863226816</t>
+  </si>
+  <si>
+    <t>6863409250</t>
+  </si>
+  <si>
     <t>6862168895</t>
   </si>
   <si>
+    <t>6863079480</t>
+  </si>
+  <si>
+    <t>6864739006</t>
+  </si>
+  <si>
+    <t>6861965073</t>
+  </si>
+  <si>
+    <t>6863957626</t>
+  </si>
+  <si>
     <t>6862643137</t>
   </si>
   <si>
-    <t>6863079480</t>
-  </si>
-  <si>
-    <t>6864739006</t>
-  </si>
-  <si>
-    <t>6863558685</t>
-  </si>
-  <si>
-    <t>6866507552</t>
-  </si>
-  <si>
-    <t>6862541870</t>
-  </si>
-  <si>
-    <t>6866740223</t>
-  </si>
-  <si>
     <t>6867371621</t>
   </si>
   <si>
     <t>6864237570</t>
   </si>
   <si>
-    <t>6862091543</t>
-  </si>
-  <si>
-    <t>6864702297</t>
-  </si>
-  <si>
-    <t>6674121912</t>
-  </si>
-  <si>
-    <t>6863957626</t>
-  </si>
-  <si>
     <t>6861256955</t>
   </si>
   <si>
-    <t>6863928150</t>
-  </si>
-  <si>
-    <t>6865860740</t>
-  </si>
-  <si>
-    <t>6861965073</t>
-  </si>
-  <si>
-    <t>6863409250</t>
-  </si>
-  <si>
-    <t>6863226816</t>
+    <t>6864214771</t>
+  </si>
+  <si>
+    <t>6862034611</t>
   </si>
   <si>
     <t>6865781520</t>
   </si>
   <si>
-    <t>6862034611</t>
+    <t>6864162086</t>
+  </si>
+  <si>
+    <t>6644940465</t>
+  </si>
+  <si>
+    <t>6869453269</t>
+  </si>
+  <si>
+    <t>6861420567</t>
+  </si>
+  <si>
+    <t>7602343861</t>
+  </si>
+  <si>
+    <t>6861330533</t>
+  </si>
+  <si>
+    <t>6864644967</t>
+  </si>
+  <si>
+    <t>6861914185</t>
+  </si>
+  <si>
+    <t>6867481654</t>
   </si>
   <si>
     <t>6861344365</t>
   </si>
   <si>
-    <t>6869453269</t>
-  </si>
-  <si>
     <t>6862300377</t>
   </si>
   <si>
-    <t>6864214771</t>
-  </si>
-  <si>
-    <t>6861420567</t>
-  </si>
-  <si>
-    <t>6644940465</t>
-  </si>
-  <si>
-    <t>6864162086</t>
-  </si>
-  <si>
-    <t>6861330533</t>
-  </si>
-  <si>
     <t>6867291381</t>
   </si>
   <si>
-    <t>6864644967</t>
+    <t>6863023309</t>
+  </si>
+  <si>
+    <t>6462016615</t>
+  </si>
+  <si>
+    <t>6861255888</t>
+  </si>
+  <si>
+    <t>6864284152</t>
+  </si>
+  <si>
+    <t>6681446837</t>
+  </si>
+  <si>
+    <t>6863182471</t>
+  </si>
+  <si>
+    <t>6862110739</t>
   </si>
   <si>
     <t>6862437298</t>
@@ -841,19 +1015,13 @@
     <t>6861387777</t>
   </si>
   <si>
-    <t>6863023309</t>
-  </si>
-  <si>
-    <t>6861914185</t>
-  </si>
-  <si>
-    <t>6867481654</t>
-  </si>
-  <si>
-    <t>7602343861</t>
-  </si>
-  <si>
-    <t>6862110739</t>
+    <t>6861945257</t>
+  </si>
+  <si>
+    <t>6863626144</t>
+  </si>
+  <si>
+    <t>6863837971</t>
   </si>
   <si>
     <t xml:space="preserve">PASEO DEL REAL 438 </t>
@@ -862,64 +1030,82 @@
     <t>PINTADO ALTO 1960</t>
   </si>
   <si>
+    <t>HACIENDA SAN ROQUE</t>
+  </si>
+  <si>
+    <t>GALATEA 245</t>
+  </si>
+  <si>
     <t>AV. PINILLO 2898</t>
   </si>
   <si>
     <t>NERVA 118</t>
   </si>
   <si>
-    <t>GALATEA 245</t>
-  </si>
-  <si>
     <t xml:space="preserve">LA BARRERA 323 </t>
   </si>
   <si>
+    <t>CASA</t>
+  </si>
+  <si>
+    <t>PORTALES</t>
+  </si>
+  <si>
+    <t>CASTILLEJA 1818</t>
+  </si>
+  <si>
+    <t>AV RIOJA 160</t>
+  </si>
+  <si>
+    <t>AV GOLETA 1807</t>
+  </si>
+  <si>
+    <t>PRIVADA DUGAN DALI1129</t>
+  </si>
+  <si>
     <t>CALLE JAEN ESTE 1637</t>
   </si>
   <si>
-    <t>PORTALES</t>
-  </si>
-  <si>
     <t>CORULLON 193</t>
   </si>
   <si>
-    <t>AV GOLETA 1807</t>
-  </si>
-  <si>
-    <t>CASA</t>
-  </si>
-  <si>
-    <t>CASTILLEJA 1818</t>
-  </si>
-  <si>
-    <t>AV RIOJA 160</t>
+    <t>1RA MORELOS 19</t>
   </si>
   <si>
     <t>BONIFACIO AVILES 3133</t>
   </si>
   <si>
-    <t>1RA MORELOS 19</t>
-  </si>
-  <si>
-    <t>PRIVADA DUGAN DALI1129</t>
-  </si>
-  <si>
     <t>POTALES</t>
   </si>
   <si>
+    <t>LAGO PAZCUARO SN</t>
+  </si>
+  <si>
+    <t>C PASEO DEL AGUA 456</t>
+  </si>
+  <si>
+    <t>DE LAS ESPADAS 61</t>
+  </si>
+  <si>
     <t xml:space="preserve">PORTALES </t>
   </si>
   <si>
     <t>NORUEGA 2636</t>
   </si>
   <si>
-    <t>LAGO PAZCUARO SN</t>
-  </si>
-  <si>
-    <t>DE LAS ESPADAS 61</t>
-  </si>
-  <si>
-    <t>C PASEO DEL AGUA 456</t>
+    <t>PRIV AUDACIA 2134</t>
+  </si>
+  <si>
+    <t>AV BURGUETE 41</t>
+  </si>
+  <si>
+    <t>CALLE GILAS1892</t>
+  </si>
+  <si>
+    <t>AVENIDA MONTES DE LEON 2027</t>
+  </si>
+  <si>
+    <t>HERENCIA 2338</t>
   </si>
   <si>
     <t>Femenino</t>
@@ -934,112 +1120,148 @@
     <t>03-11-2000</t>
   </si>
   <si>
+    <t>03-07-1996</t>
+  </si>
+  <si>
+    <t>18-12-1993</t>
+  </si>
+  <si>
     <t>26-06-2003</t>
   </si>
   <si>
     <t>25-06-2003</t>
   </si>
   <si>
-    <t>18-12-1993</t>
-  </si>
-  <si>
     <t>07-10-1997</t>
   </si>
   <si>
+    <t>17-03-2003</t>
+  </si>
+  <si>
+    <t>11-02-2010</t>
+  </si>
+  <si>
+    <t>03-11-2011</t>
+  </si>
+  <si>
+    <t>13-04-2003</t>
+  </si>
+  <si>
+    <t>02-02-2006</t>
+  </si>
+  <si>
+    <t>09-08-1998</t>
+  </si>
+  <si>
+    <t>23-02-1988</t>
+  </si>
+  <si>
+    <t>28-07-1999</t>
+  </si>
+  <si>
+    <t>07-10-2003</t>
+  </si>
+  <si>
+    <t>27-12-1976</t>
+  </si>
+  <si>
+    <t>09-11-2000</t>
+  </si>
+  <si>
+    <t>28-08-2011</t>
+  </si>
+  <si>
     <t>01-08-1984</t>
   </si>
   <si>
+    <t>19-10-2002</t>
+  </si>
+  <si>
+    <t>29-08-2004</t>
+  </si>
+  <si>
+    <t>22-09-2000</t>
+  </si>
+  <si>
+    <t>26-01-1995</t>
+  </si>
+  <si>
     <t>13-12-1998</t>
   </si>
   <si>
-    <t>19-10-2002</t>
-  </si>
-  <si>
-    <t>29-08-2004</t>
-  </si>
-  <si>
-    <t>03-11-2011</t>
-  </si>
-  <si>
-    <t>09-08-1998</t>
-  </si>
-  <si>
-    <t>17-03-2003</t>
-  </si>
-  <si>
-    <t>11-02-2010</t>
-  </si>
-  <si>
     <t>04-09-2001</t>
   </si>
   <si>
     <t>25-06-1996</t>
   </si>
   <si>
-    <t>13-04-2003</t>
-  </si>
-  <si>
-    <t>02-02-2006</t>
-  </si>
-  <si>
-    <t>07-10-2003</t>
-  </si>
-  <si>
-    <t>26-01-1995</t>
-  </si>
-  <si>
     <t>16-05-1978</t>
   </si>
   <si>
-    <t>23-02-1988</t>
-  </si>
-  <si>
-    <t>27-12-1976</t>
-  </si>
-  <si>
-    <t>22-09-2000</t>
-  </si>
-  <si>
-    <t>28-08-2011</t>
-  </si>
-  <si>
-    <t>09-11-2000</t>
+    <t>10-08-2003</t>
+  </si>
+  <si>
+    <t>03-09-2005</t>
   </si>
   <si>
     <t>13-10-2006</t>
   </si>
   <si>
-    <t>03-09-2005</t>
+    <t>21-09-1988</t>
+  </si>
+  <si>
+    <t>19-06-1981</t>
+  </si>
+  <si>
+    <t>19-04-2008</t>
+  </si>
+  <si>
+    <t>28-10-1996</t>
+  </si>
+  <si>
+    <t>05-02-1997</t>
+  </si>
+  <si>
+    <t>26-02-2007</t>
+  </si>
+  <si>
+    <t>11-10-2001</t>
+  </si>
+  <si>
+    <t>02-01-2004</t>
+  </si>
+  <si>
+    <t>05-02-2011</t>
   </si>
   <si>
     <t>26-11-2004</t>
   </si>
   <si>
-    <t>19-04-2008</t>
-  </si>
-  <si>
     <t>12-11-1996</t>
   </si>
   <si>
-    <t>10-08-2003</t>
-  </si>
-  <si>
-    <t>28-10-1996</t>
-  </si>
-  <si>
-    <t>19-06-1981</t>
-  </si>
-  <si>
-    <t>21-09-1988</t>
-  </si>
-  <si>
-    <t>26-02-2007</t>
-  </si>
-  <si>
     <t>20-06-2005</t>
   </si>
   <si>
-    <t>11-10-2001</t>
+    <t>22-08-2003</t>
+  </si>
+  <si>
+    <t>05-11-2009</t>
+  </si>
+  <si>
+    <t>12-07-1992</t>
+  </si>
+  <si>
+    <t>17-11-2005</t>
+  </si>
+  <si>
+    <t>04-11-1987</t>
+  </si>
+  <si>
+    <t>06-10-1991</t>
+  </si>
+  <si>
+    <t>06-08-1987</t>
   </si>
   <si>
     <t>01-09-1989</t>
@@ -1048,19 +1270,13 @@
     <t>14-08-1972</t>
   </si>
   <si>
-    <t>22-08-2003</t>
-  </si>
-  <si>
-    <t>02-01-2004</t>
-  </si>
-  <si>
-    <t>05-02-2011</t>
-  </si>
-  <si>
-    <t>05-02-1997</t>
-  </si>
-  <si>
-    <t>06-08-1987</t>
+    <t>24-08-1995</t>
+  </si>
+  <si>
+    <t>11-12-2001</t>
+  </si>
+  <si>
+    <t>15-08-2000</t>
   </si>
   <si>
     <t>PSICOLOGOGEMAVALENZUELA@OUTLOOK.COM</t>
@@ -1069,109 +1285,145 @@
     <t>DAVALOSDENNIS19@GMAIL.COM</t>
   </si>
   <si>
+    <t>J.ANTONIO.CRUZ.CARDENAS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>BRIAN.GONZALEZ@UABC.EDU.MX</t>
+  </si>
+  <si>
     <t>ALEXANDERVILLAMAN@HOTMAIL.COM</t>
   </si>
   <si>
     <t>DANIELQUIJADA2532@GMAIL.COM</t>
   </si>
   <si>
-    <t>BRIAN.GONZALEZ@UABC.EDU.MX</t>
-  </si>
-  <si>
     <t>ZAIRA071097@HOTMAIL.COM</t>
   </si>
   <si>
+    <t>KITZIAMAGALON@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>HIELO12CV@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CUARTO.SAJIRA@ICLOUD.COM</t>
+  </si>
+  <si>
+    <t>EMILY.ARRIAGA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ELLIOT.MORA@UABC.COM.MX</t>
+  </si>
+  <si>
+    <t>MENTECUERPOYNUTRICION@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>FM7098082@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>FELIZLUISFERNANDO3@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>REA1628JOSE@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>YORPEREZ073@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>DAVID.ERNESTO@GMAIL.COM</t>
+  </si>
+  <si>
     <t>KARIZMENDI2902@GMAIL.COM</t>
   </si>
   <si>
+    <t>LIZY.NAILY@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>NAYLITACOTA.CHAVEZ@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>IVAN.RODRIGUEZ@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ANABELDEARA260195@GMAIL.COM</t>
+  </si>
+  <si>
     <t>PAISPURO1948@GMAIL.COM</t>
   </si>
   <si>
-    <t>LIZY.NAILY@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>NAYLITACOTA.CHAVEZ@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ELLIOT.MORA@UABC.COM.MX</t>
-  </si>
-  <si>
-    <t>KITZIAMAGALON@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>HIELO12CV@GMAIL.COM</t>
-  </si>
-  <si>
     <t>BEJARANOJULIO10@GMAIL.COM</t>
   </si>
   <si>
     <t>EYLECELENA25@GMAIL.COM</t>
   </si>
   <si>
-    <t>CUARTO.SAJIRA@ICLOUD.COM</t>
-  </si>
-  <si>
-    <t>EMILY.ARRIAGA@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>FELIZLUISFERNANDO3@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ANABELDEARA260195@GMAIL.COM</t>
-  </si>
-  <si>
     <t>ELYMORALESVALENZUELA@GMAIL.COM</t>
   </si>
   <si>
-    <t>MENTECUERPOYNUTRICION@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>REA1628JOSE@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>IVAN.RODRIGUEZ@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>DAVID.ERNESTO@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>YORPEREZ073@GMAIL.COM</t>
+    <t>MORAERNESTO741@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>EMMANUEL.PEREZ@GMAIL.COM</t>
   </si>
   <si>
     <t>FR65671@GMAIL.COM</t>
   </si>
   <si>
-    <t>EMMANUEL.PEREZ@GMAIL.COM</t>
+    <t>CAMPOSLULY0@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VIVIANDEFELIX@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VALMACIASSA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>NELSON.1028@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>HECTORCANALESLEYVA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>DAMARISK.SLOPEZ@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ZEPEDA111001@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JG747801@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>NAOMIDOM2011@ICLOUD.COM</t>
   </si>
   <si>
     <t>NATALIE.RODRIGUEZ@UABC.EDU.MX</t>
   </si>
   <si>
-    <t>VALMACIASSA@GMAIL.COM</t>
-  </si>
-  <si>
     <t>ADOLFO_19962016@HOTMAIL.COM</t>
   </si>
   <si>
-    <t>MORAERNESTO741@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>NELSON.1028@HOTMAIL.COM</t>
-  </si>
-  <si>
-    <t>VIVIANDEFELIX@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>CAMPOSLULY0@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>DAMARISK.SLOPEZ@GMAIL.COM</t>
-  </si>
-  <si>
     <t>MIGUELTEJADA317@ICLOUD.COM</t>
   </si>
   <si>
-    <t>ZEPEDA111001@GMAIL.COM</t>
+    <t>JV220803@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>AR7481660@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ABRAHAM.SKET1@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ALEXISARP15@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>GABYISA.0104@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>GARCIAGUADALUPE7414@HOTMAIL.COM</t>
+  </si>
+  <si>
+    <t>ZEPEDACOTAC@GMAIL.COM</t>
   </si>
   <si>
     <t>ERREDOS8@GMAIL.COM</t>
@@ -1180,19 +1432,13 @@
     <t>JORGEJIMENEZSOTO1994@GMAIL.COM</t>
   </si>
   <si>
-    <t>JV220803@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>JG747801@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>NAOMIDOM2011@ICLOUD.COM</t>
-  </si>
-  <si>
-    <t>HECTORCANALESLEYVA@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>ZEPEDACOTAC@GMAIL.COM</t>
+    <t>ISABELPEREYDA24@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>FAVELAPEREZVZ11@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ANDREAESTRADA1218@ICLOUD.COM</t>
   </si>
   <si>
     <t>13-09-2021 05:15:39</t>
@@ -1201,112 +1447,148 @@
     <t>13-01-2023 20:11:37</t>
   </si>
   <si>
+    <t>23-08-2022 19:27:05</t>
+  </si>
+  <si>
+    <t>11-07-2023 17:00:27</t>
+  </si>
+  <si>
     <t>14-11-2022 21:53:57</t>
   </si>
   <si>
     <t>28-02-2022 17:04:02</t>
   </si>
   <si>
-    <t>11-07-2023 17:00:27</t>
-  </si>
-  <si>
     <t>05-11-2025 16:07:36</t>
   </si>
   <si>
+    <t>02-02-2026 10:57:19</t>
+  </si>
+  <si>
+    <t>02-02-2026 12:53:45</t>
+  </si>
+  <si>
+    <t>02-02-2026 14:41:17</t>
+  </si>
+  <si>
+    <t>02-02-2026 14:35:58</t>
+  </si>
+  <si>
+    <t>02-02-2026 18:06:05</t>
+  </si>
+  <si>
+    <t>02-02-2026 15:50:44</t>
+  </si>
+  <si>
+    <t>03-02-2026 17:50:24</t>
+  </si>
+  <si>
+    <t>27-01-2026 05:22:15</t>
+  </si>
+  <si>
+    <t>03-02-2026 07:13:43</t>
+  </si>
+  <si>
+    <t>03-02-2026 13:24:47</t>
+  </si>
+  <si>
+    <t>04-02-2026 08:51:30</t>
+  </si>
+  <si>
+    <t>04-02-2026 19:08:30</t>
+  </si>
+  <si>
     <t>29-01-2026 17:00:05</t>
   </si>
   <si>
+    <t>30-01-2026 20:49:36</t>
+  </si>
+  <si>
+    <t>02-02-2026 08:07:50</t>
+  </si>
+  <si>
+    <t>04-02-2026 20:27:47</t>
+  </si>
+  <si>
+    <t>02-02-2026 16:10:16</t>
+  </si>
+  <si>
     <t>01-02-2026 12:02:45</t>
   </si>
   <si>
-    <t>30-01-2026 20:49:36</t>
-  </si>
-  <si>
-    <t>02-02-2026 08:07:50</t>
-  </si>
-  <si>
-    <t>02-02-2026 14:41:17</t>
-  </si>
-  <si>
-    <t>02-02-2026 15:50:44</t>
-  </si>
-  <si>
-    <t>02-02-2026 10:57:19</t>
-  </si>
-  <si>
-    <t>02-02-2026 12:53:45</t>
-  </si>
-  <si>
     <t>02-02-2026 08:04:32</t>
   </si>
   <si>
     <t>02-02-2026 09:30:33</t>
   </si>
   <si>
-    <t>02-02-2026 14:35:58</t>
-  </si>
-  <si>
-    <t>02-02-2026 18:06:05</t>
-  </si>
-  <si>
-    <t>03-02-2026 07:13:43</t>
-  </si>
-  <si>
-    <t>02-02-2026 16:10:16</t>
-  </si>
-  <si>
     <t>03-02-2026 08:35:58</t>
   </si>
   <si>
-    <t>03-02-2026 17:50:24</t>
-  </si>
-  <si>
-    <t>03-02-2026 13:24:47</t>
-  </si>
-  <si>
-    <t>04-02-2026 20:27:47</t>
-  </si>
-  <si>
-    <t>04-02-2026 19:08:30</t>
-  </si>
-  <si>
-    <t>04-02-2026 08:51:30</t>
+    <t>09-02-2026 16:57:09</t>
+  </si>
+  <si>
+    <t>04-02-2026 15:54:17</t>
   </si>
   <si>
     <t>05-02-2026 12:58:08</t>
   </si>
   <si>
-    <t>04-02-2026 15:54:17</t>
+    <t>10-02-2026 10:01:09</t>
+  </si>
+  <si>
+    <t>10-02-2026 15:37:05</t>
+  </si>
+  <si>
+    <t>09-02-2026 12:49:49</t>
+  </si>
+  <si>
+    <t>09-02-2026 21:04:58</t>
+  </si>
+  <si>
+    <t>12-02-2026 12:48:03</t>
+  </si>
+  <si>
+    <t>10-02-2026 19:51:12</t>
+  </si>
+  <si>
+    <t>11-02-2026 15:16:45</t>
+  </si>
+  <si>
+    <t>12-02-2026 19:39:05</t>
+  </si>
+  <si>
+    <t>12-02-2026 20:07:03</t>
   </si>
   <si>
     <t>05-02-2026 13:00:16</t>
   </si>
   <si>
-    <t>09-02-2026 12:49:49</t>
-  </si>
-  <si>
     <t>05-02-2026 21:05:50</t>
   </si>
   <si>
-    <t>09-02-2026 16:57:09</t>
-  </si>
-  <si>
-    <t>09-02-2026 21:04:58</t>
-  </si>
-  <si>
-    <t>10-02-2026 15:37:05</t>
-  </si>
-  <si>
-    <t>10-02-2026 10:01:09</t>
-  </si>
-  <si>
-    <t>10-02-2026 19:51:12</t>
-  </si>
-  <si>
     <t>09-02-2026 20:58:55</t>
   </si>
   <si>
-    <t>11-02-2026 15:16:45</t>
+    <t>10-02-2026 19:47:49</t>
+  </si>
+  <si>
+    <t>16-02-2026 08:36:28</t>
+  </si>
+  <si>
+    <t>16-02-2026 11:31:00</t>
+  </si>
+  <si>
+    <t>16-02-2026 08:36:23</t>
+  </si>
+  <si>
+    <t>16-02-2026 13:40:14</t>
+  </si>
+  <si>
+    <t>16-02-2026 14:05:34</t>
+  </si>
+  <si>
+    <t>12-02-2026 21:09:33</t>
   </si>
   <si>
     <t>10-02-2026 19:36:54</t>
@@ -1315,24 +1597,21 @@
     <t>10-02-2026 19:59:00</t>
   </si>
   <si>
-    <t>10-02-2026 19:47:49</t>
-  </si>
-  <si>
-    <t>12-02-2026 19:39:05</t>
-  </si>
-  <si>
-    <t>12-02-2026 20:07:03</t>
-  </si>
-  <si>
-    <t>12-02-2026 12:48:03</t>
-  </si>
-  <si>
-    <t>12-02-2026 21:09:33</t>
+    <t>16-02-2026 08:43:39</t>
+  </si>
+  <si>
+    <t>16-02-2026 09:07:20</t>
+  </si>
+  <si>
+    <t>16-02-2026 21:04:29</t>
   </si>
   <si>
     <t>Tarifas 2026 LE</t>
   </si>
   <si>
+    <t>inscripcion promo 199</t>
+  </si>
+  <si>
     <t>Sin contrato</t>
   </si>
   <si>
@@ -1351,15 +1630,15 @@
     <t>RECURRENTE $649 LE</t>
   </si>
   <si>
+    <t>3 MESES $1,899</t>
+  </si>
+  <si>
+    <t>CONVENIOS $549</t>
+  </si>
+  <si>
     <t>PROMO ENERO 12 MESES</t>
   </si>
   <si>
-    <t>CONVENIOS $549</t>
-  </si>
-  <si>
-    <t>3 MESES $1,899</t>
-  </si>
-  <si>
     <t>899</t>
   </si>
   <si>
@@ -1369,124 +1648,160 @@
     <t>649</t>
   </si>
   <si>
+    <t>633</t>
+  </si>
+  <si>
     <t>549</t>
   </si>
   <si>
-    <t>633</t>
-  </si>
-  <si>
     <t>03-02-2026 08:00:08</t>
   </si>
   <si>
     <t>02-02-2026 20:22:53</t>
   </si>
   <si>
+    <t>17-02-2026 14:14:53</t>
+  </si>
+  <si>
+    <t>02-02-2026 15:48:32</t>
+  </si>
+  <si>
     <t>10-02-2026 16:48:07</t>
   </si>
   <si>
     <t>02-02-2026 14:23:09</t>
   </si>
   <si>
-    <t>02-02-2026 15:48:32</t>
-  </si>
-  <si>
     <t>02-02-2026 17:50:01</t>
   </si>
   <si>
+    <t>02-02-2026 11:00:49</t>
+  </si>
+  <si>
+    <t>04-02-2026 13:54:22</t>
+  </si>
+  <si>
+    <t>02-02-2026 14:46:51</t>
+  </si>
+  <si>
+    <t>02-02-2026 14:42:26</t>
+  </si>
+  <si>
+    <t>05-02-2026 18:50:09</t>
+  </si>
+  <si>
+    <t>02-02-2026 15:56:47</t>
+  </si>
+  <si>
+    <t>03-02-2026 17:52:56</t>
+  </si>
+  <si>
+    <t>17-02-2026 05:01:55</t>
+  </si>
+  <si>
+    <t>03-02-2026 07:19:00</t>
+  </si>
+  <si>
+    <t>03-02-2026 13:26:26</t>
+  </si>
+  <si>
+    <t>04-02-2026 08:59:01</t>
+  </si>
+  <si>
+    <t>04-02-2026 19:10:17</t>
+  </si>
+  <si>
     <t>02-02-2026 11:21:22</t>
   </si>
   <si>
+    <t>02-02-2026 20:17:46</t>
+  </si>
+  <si>
+    <t>03-02-2026 07:26:19</t>
+  </si>
+  <si>
+    <t>04-02-2026 20:33:43</t>
+  </si>
+  <si>
+    <t>02-02-2026 16:15:39</t>
+  </si>
+  <si>
     <t>01-02-2026 12:08:41</t>
   </si>
   <si>
-    <t>02-02-2026 20:17:46</t>
-  </si>
-  <si>
-    <t>03-02-2026 07:26:19</t>
-  </si>
-  <si>
-    <t>02-02-2026 14:46:51</t>
-  </si>
-  <si>
-    <t>02-02-2026 15:56:47</t>
-  </si>
-  <si>
-    <t>02-02-2026 11:00:49</t>
-  </si>
-  <si>
-    <t>04-02-2026 13:54:22</t>
-  </si>
-  <si>
     <t>03-02-2026 07:27:31</t>
   </si>
   <si>
     <t>12-02-2026 08:16:52</t>
   </si>
   <si>
-    <t>02-02-2026 14:42:26</t>
-  </si>
-  <si>
-    <t>05-02-2026 18:50:09</t>
-  </si>
-  <si>
-    <t>03-02-2026 07:19:00</t>
-  </si>
-  <si>
-    <t>02-02-2026 16:15:39</t>
-  </si>
-  <si>
     <t>03-02-2026 08:37:42</t>
   </si>
   <si>
-    <t>03-02-2026 17:52:56</t>
-  </si>
-  <si>
-    <t>03-02-2026 13:26:26</t>
-  </si>
-  <si>
-    <t>04-02-2026 20:33:43</t>
-  </si>
-  <si>
-    <t>04-02-2026 19:10:17</t>
-  </si>
-  <si>
-    <t>04-02-2026 08:59:01</t>
+    <t>09-02-2026 17:02:55</t>
+  </si>
+  <si>
+    <t>04-02-2026 15:57:00</t>
   </si>
   <si>
     <t>10-02-2026 16:59:22</t>
   </si>
   <si>
-    <t>04-02-2026 15:57:00</t>
+    <t>10-02-2026 10:11:12</t>
+  </si>
+  <si>
+    <t>10-02-2026 15:40:14</t>
+  </si>
+  <si>
+    <t>09-02-2026 12:51:58</t>
+  </si>
+  <si>
+    <t>09-02-2026 21:06:43</t>
+  </si>
+  <si>
+    <t>12-02-2026 12:53:41</t>
+  </si>
+  <si>
+    <t>10-02-2026 19:53:06</t>
+  </si>
+  <si>
+    <t>11-02-2026 15:30:24</t>
+  </si>
+  <si>
+    <t>12-02-2026 19:42:59</t>
+  </si>
+  <si>
+    <t>13-02-2026 17:16:34</t>
   </si>
   <si>
     <t>10-02-2026 16:55:49</t>
   </si>
   <si>
-    <t>09-02-2026 12:51:58</t>
-  </si>
-  <si>
     <t>05-02-2026 21:13:45</t>
   </si>
   <si>
-    <t>09-02-2026 17:02:55</t>
-  </si>
-  <si>
-    <t>09-02-2026 21:06:43</t>
-  </si>
-  <si>
-    <t>10-02-2026 15:40:14</t>
-  </si>
-  <si>
-    <t>10-02-2026 10:11:12</t>
-  </si>
-  <si>
-    <t>10-02-2026 19:53:06</t>
-  </si>
-  <si>
     <t>09-02-2026 21:01:56</t>
   </si>
   <si>
-    <t>11-02-2026 15:30:24</t>
+    <t>10-02-2026 19:49:44</t>
+  </si>
+  <si>
+    <t>16-02-2026 08:38:13</t>
+  </si>
+  <si>
+    <t>16-02-2026 11:32:22</t>
+  </si>
+  <si>
+    <t>16-02-2026 08:44:12</t>
+  </si>
+  <si>
+    <t>16-02-2026 13:47:19</t>
+  </si>
+  <si>
+    <t>16-02-2026 14:10:44</t>
+  </si>
+  <si>
+    <t>12-02-2026 21:11:55</t>
   </si>
   <si>
     <t>10-02-2026 19:46:13</t>
@@ -1495,19 +1810,13 @@
     <t>10-02-2026 20:04:31</t>
   </si>
   <si>
-    <t>10-02-2026 19:49:44</t>
-  </si>
-  <si>
-    <t>12-02-2026 19:42:59</t>
-  </si>
-  <si>
-    <t>13-02-2026 17:16:34</t>
-  </si>
-  <si>
-    <t>12-02-2026 12:53:41</t>
-  </si>
-  <si>
-    <t>12-02-2026 21:11:55</t>
+    <t>16-02-2026 08:52:04</t>
+  </si>
+  <si>
+    <t>16-02-2026 09:11:41</t>
+  </si>
+  <si>
+    <t>16-02-2026 21:14:42</t>
   </si>
   <si>
     <t>03-03-2026 23:59:59</t>
@@ -1516,27 +1825,30 @@
     <t>02-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>17-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>10-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>04-03-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>05-03-2026 23:59:59</t>
+  </si>
+  <si>
+    <t>03-05-2026 23:59:59</t>
+  </si>
+  <si>
     <t>28-02-2026 23:59:59</t>
   </si>
   <si>
     <t>01-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>04-03-2026 23:59:59</t>
-  </si>
-  <si>
     <t>12-03-2026 23:59:59</t>
   </si>
   <si>
-    <t>05-03-2026 23:59:59</t>
-  </si>
-  <si>
-    <t>03-05-2026 23:59:59</t>
-  </si>
-  <si>
     <t>09-03-2026 23:59:59</t>
   </si>
   <si>
@@ -1549,82 +1861,103 @@
     <t>13-03-2026 23:59:59</t>
   </si>
   <si>
+    <t>16-03-2026 23:59:59</t>
+  </si>
+  <si>
     <t>02-02-2026 20:22:16</t>
   </si>
   <si>
+    <t>17-02-2026 14:13:03</t>
+  </si>
+  <si>
+    <t>02-02-2026 15:47:32</t>
+  </si>
+  <si>
     <t>10-02-2026 16:46:53</t>
   </si>
   <si>
     <t>02-02-2026 14:22:48</t>
   </si>
   <si>
-    <t>02-02-2026 15:47:32</t>
-  </si>
-  <si>
     <t>02-02-2026 17:48:27</t>
   </si>
   <si>
+    <t>02-02-2026 11:00:21</t>
+  </si>
+  <si>
+    <t>04-02-2026 13:53:23</t>
+  </si>
+  <si>
+    <t>02-02-2026 14:45:55</t>
+  </si>
+  <si>
+    <t>02-02-2026 14:40:53</t>
+  </si>
+  <si>
+    <t>05-02-2026 18:49:20</t>
+  </si>
+  <si>
+    <t>02-02-2026 15:54:59</t>
+  </si>
+  <si>
+    <t>03-02-2026 07:18:37</t>
+  </si>
+  <si>
+    <t>04-02-2026 08:57:43</t>
+  </si>
+  <si>
     <t>31-01-2026 14:54:56</t>
   </si>
   <si>
+    <t>02-02-2026 20:16:52</t>
+  </si>
+  <si>
+    <t>04-02-2026 20:33:11</t>
+  </si>
+  <si>
+    <t>02-02-2026 16:14:45</t>
+  </si>
+  <si>
     <t>01-02-2026 12:07:33</t>
   </si>
   <si>
-    <t>02-02-2026 20:16:52</t>
-  </si>
-  <si>
-    <t>02-02-2026 14:45:55</t>
-  </si>
-  <si>
-    <t>02-02-2026 15:54:59</t>
-  </si>
-  <si>
-    <t>02-02-2026 11:00:21</t>
-  </si>
-  <si>
-    <t>04-02-2026 13:53:23</t>
-  </si>
-  <si>
-    <t>02-02-2026 14:40:53</t>
-  </si>
-  <si>
-    <t>05-02-2026 18:49:20</t>
-  </si>
-  <si>
-    <t>03-02-2026 07:18:37</t>
-  </si>
-  <si>
-    <t>02-02-2026 16:14:45</t>
-  </si>
-  <si>
-    <t>04-02-2026 20:33:11</t>
-  </si>
-  <si>
-    <t>04-02-2026 08:57:43</t>
+    <t>09-02-2026 16:59:57</t>
   </si>
   <si>
     <t>10-02-2026 16:58:27</t>
   </si>
   <si>
+    <t>10-02-2026 10:10:28</t>
+  </si>
+  <si>
+    <t>10-02-2026 15:39:43</t>
+  </si>
+  <si>
+    <t>12-02-2026 12:53:05</t>
+  </si>
+  <si>
+    <t>11-02-2026 15:29:47</t>
+  </si>
+  <si>
+    <t>12-02-2026 19:42:26</t>
+  </si>
+  <si>
     <t>10-02-2026 16:54:34</t>
   </si>
   <si>
     <t>05-02-2026 21:13:16</t>
   </si>
   <si>
-    <t>09-02-2026 16:59:57</t>
-  </si>
-  <si>
-    <t>10-02-2026 15:39:43</t>
-  </si>
-  <si>
-    <t>10-02-2026 10:10:28</t>
-  </si>
-  <si>
     <t>09-02-2026 21:01:07</t>
   </si>
   <si>
-    <t>11-02-2026 15:29:47</t>
+    <t>16-02-2026 08:42:55</t>
+  </si>
+  <si>
+    <t>16-02-2026 13:46:36</t>
+  </si>
+  <si>
+    <t>16-02-2026 14:10:01</t>
   </si>
   <si>
     <t>10-02-2026 19:40:58</t>
@@ -1633,10 +1966,13 @@
     <t>10-02-2026 20:04:01</t>
   </si>
   <si>
-    <t>12-02-2026 19:42:26</t>
-  </si>
-  <si>
-    <t>12-02-2026 12:53:05</t>
+    <t>16-02-2026 08:51:31</t>
+  </si>
+  <si>
+    <t>16-02-2026 09:11:13</t>
+  </si>
+  <si>
+    <t>16-02-2026 21:12:23</t>
   </si>
   <si>
     <t>2</t>
@@ -1648,112 +1984,148 @@
     <t>26170522023010001685</t>
   </si>
   <si>
+    <t>26170522429040002526</t>
+  </si>
+  <si>
+    <t>26170522015130001656</t>
+  </si>
+  <si>
     <t>26170522237640002130</t>
   </si>
   <si>
     <t>26170522012560001648</t>
   </si>
   <si>
-    <t>26170522015130001656</t>
-  </si>
-  <si>
     <t>26170522019270001671</t>
   </si>
   <si>
+    <t>26170522006040001630</t>
+  </si>
+  <si>
+    <t>26170522075080001810</t>
+  </si>
+  <si>
+    <t>26170522013390001650</t>
+  </si>
+  <si>
+    <t>26170522013230001649</t>
+  </si>
+  <si>
+    <t>26170522116880001895</t>
+  </si>
+  <si>
+    <t>26170522015420001658</t>
+  </si>
+  <si>
+    <t>26170522051130001755</t>
+  </si>
+  <si>
+    <t>26170522413330002499</t>
+  </si>
+  <si>
+    <t>26170522031900001705</t>
+  </si>
+  <si>
+    <t>26170522039620001735</t>
+  </si>
+  <si>
+    <t>26170522070070001794</t>
+  </si>
+  <si>
+    <t>26170522087360001828</t>
+  </si>
+  <si>
     <t>26170522006780001632</t>
   </si>
   <si>
+    <t>26170522022960001684</t>
+  </si>
+  <si>
+    <t>26170522032040001706</t>
+  </si>
+  <si>
+    <t>26170522089840001847</t>
+  </si>
+  <si>
+    <t>26170522016110001661</t>
+  </si>
+  <si>
     <t>26170521990600001608</t>
   </si>
   <si>
-    <t>26170522022960001684</t>
-  </si>
-  <si>
-    <t>26170522032040001706</t>
-  </si>
-  <si>
-    <t>26170522013390001650</t>
-  </si>
-  <si>
-    <t>26170522015420001658</t>
-  </si>
-  <si>
-    <t>26170522006040001630</t>
-  </si>
-  <si>
-    <t>26170522075080001810</t>
-  </si>
-  <si>
     <t>26170522032100001708</t>
   </si>
   <si>
     <t>26170522288990002257</t>
   </si>
   <si>
-    <t>26170522013230001649</t>
-  </si>
-  <si>
-    <t>26170522116880001895</t>
-  </si>
-  <si>
-    <t>26170522031900001705</t>
-  </si>
-  <si>
-    <t>26170522016110001661</t>
-  </si>
-  <si>
     <t>26170522033950001717</t>
   </si>
   <si>
-    <t>26170522051130001755</t>
-  </si>
-  <si>
-    <t>26170522039620001735</t>
-  </si>
-  <si>
-    <t>26170522089840001847</t>
-  </si>
-  <si>
-    <t>26170522087360001828</t>
-  </si>
-  <si>
-    <t>26170522070070001794</t>
+    <t>26170522200440002040</t>
+  </si>
+  <si>
+    <t>26170522078420001815</t>
   </si>
   <si>
     <t>26170522238110002134</t>
   </si>
   <si>
-    <t>26170522078420001815</t>
+    <t>26170522227920002115</t>
+  </si>
+  <si>
+    <t>26170522235040002127</t>
+  </si>
+  <si>
+    <t>26170522190930002024</t>
+  </si>
+  <si>
+    <t>26170522214560002094</t>
+  </si>
+  <si>
+    <t>26170522292940002271</t>
+  </si>
+  <si>
+    <t>26170522247900002153</t>
+  </si>
+  <si>
+    <t>26170522266490002208</t>
+  </si>
+  <si>
+    <t>26170522305280002308</t>
+  </si>
+  <si>
+    <t>26170522326050002356</t>
   </si>
   <si>
     <t>26170522238010002133</t>
   </si>
   <si>
-    <t>26170522190930002024</t>
-  </si>
-  <si>
     <t>26170522120570001923</t>
   </si>
   <si>
-    <t>26170522200440002040</t>
-  </si>
-  <si>
-    <t>26170522214560002094</t>
-  </si>
-  <si>
-    <t>26170522235040002127</t>
-  </si>
-  <si>
-    <t>26170522227920002115</t>
-  </si>
-  <si>
-    <t>26170522247900002153</t>
-  </si>
-  <si>
     <t>26170522214500002093</t>
   </si>
   <si>
-    <t>26170522266490002208</t>
+    <t>26170522247770002152</t>
+  </si>
+  <si>
+    <t>26170522381280002417</t>
+  </si>
+  <si>
+    <t>26170522385460002427</t>
+  </si>
+  <si>
+    <t>26170522381430002418</t>
+  </si>
+  <si>
+    <t>26170522389180002437</t>
+  </si>
+  <si>
+    <t>26170522389780002438</t>
+  </si>
+  <si>
+    <t>26170522306850002321</t>
   </si>
   <si>
     <t>26170522247630002151</t>
@@ -1762,19 +2134,13 @@
     <t>26170522248340002163</t>
   </si>
   <si>
-    <t>26170522247770002152</t>
-  </si>
-  <si>
-    <t>26170522305280002308</t>
-  </si>
-  <si>
-    <t>26170522326050002356</t>
-  </si>
-  <si>
-    <t>26170522292940002271</t>
-  </si>
-  <si>
-    <t>26170522306850002321</t>
+    <t>26170522381670002419</t>
+  </si>
+  <si>
+    <t>26170522382170002420</t>
+  </si>
+  <si>
+    <t>26170522411380002496</t>
   </si>
   <si>
     <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
@@ -1789,6 +2155,9 @@
     <t>JOSE LUIS  LOPEZ  CORONEL</t>
   </si>
   <si>
+    <t>Mariana Daniela Romero Cruz</t>
+  </si>
+  <si>
     <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
   </si>
   <si>
@@ -1801,10 +2170,10 @@
     <t>Alexa Johana  Haro</t>
   </si>
   <si>
+    <t>Saul  Galeana</t>
+  </si>
+  <si>
     <t>Thannia Lilian Lugo Morales</t>
-  </si>
-  <si>
-    <t>Saul  Galeana</t>
   </si>
   <si>
     <t>Jose Luis Lopez Coronel</t>
@@ -2171,7 +2540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:29">
@@ -2268,76 +2637,76 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="F2" t="s">
-        <v>204</v>
+        <v>243</v>
       </c>
       <c r="G2" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H2" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="I2" t="s">
+        <v>336</v>
+      </c>
+      <c r="J2" t="s">
+        <v>364</v>
+      </c>
+      <c r="K2" t="s">
+        <v>366</v>
+      </c>
+      <c r="L2" t="s">
+        <v>421</v>
+      </c>
+      <c r="M2" t="s">
+        <v>475</v>
+      </c>
+      <c r="N2" t="s">
+        <v>530</v>
+      </c>
+      <c r="O2" t="s">
+        <v>532</v>
+      </c>
+      <c r="P2" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>541</v>
+      </c>
+      <c r="R2" t="s">
+        <v>546</v>
+      </c>
+      <c r="S2" t="s">
+        <v>601</v>
+      </c>
+      <c r="U2" t="s">
         <v>280</v>
-      </c>
-      <c r="J2" t="s">
-        <v>302</v>
-      </c>
-      <c r="K2" t="s">
-        <v>304</v>
-      </c>
-      <c r="L2" t="s">
-        <v>349</v>
-      </c>
-      <c r="M2" t="s">
-        <v>393</v>
-      </c>
-      <c r="N2" t="s">
-        <v>438</v>
-      </c>
-      <c r="O2" t="s">
-        <v>439</v>
-      </c>
-      <c r="P2" t="s">
-        <v>442</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>448</v>
-      </c>
-      <c r="R2" t="s">
-        <v>453</v>
-      </c>
-      <c r="S2" t="s">
-        <v>498</v>
-      </c>
-      <c r="U2" t="s">
-        <v>234</v>
       </c>
       <c r="W2" t="s">
         <v>2</v>
       </c>
       <c r="X2" t="s">
-        <v>542</v>
+        <v>654</v>
       </c>
       <c r="AA2" t="s">
-        <v>448</v>
+        <v>541</v>
       </c>
       <c r="AB2" t="s">
-        <v>593</v>
+        <v>716</v>
       </c>
       <c r="AC2" t="s">
-        <v>598</v>
+        <v>721</v>
       </c>
     </row>
     <row r="3" spans="1:29">
@@ -2345,85 +2714,85 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="E3" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="F3" t="s">
-        <v>205</v>
+        <v>244</v>
       </c>
       <c r="G3" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H3" t="s">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="I3" t="s">
-        <v>281</v>
+        <v>337</v>
       </c>
       <c r="J3" t="s">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="K3" t="s">
-        <v>305</v>
+        <v>367</v>
       </c>
       <c r="L3" t="s">
-        <v>350</v>
+        <v>422</v>
       </c>
       <c r="M3" t="s">
-        <v>394</v>
+        <v>476</v>
       </c>
       <c r="O3" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P3" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="Q3" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R3" t="s">
-        <v>454</v>
+        <v>547</v>
       </c>
       <c r="S3" t="s">
-        <v>499</v>
+        <v>602</v>
       </c>
       <c r="T3" t="s">
-        <v>511</v>
+        <v>616</v>
       </c>
       <c r="U3" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V3" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W3" t="s">
         <v>2</v>
       </c>
       <c r="X3" t="s">
-        <v>543</v>
+        <v>655</v>
       </c>
       <c r="Y3" t="s">
-        <v>587</v>
+        <v>709</v>
       </c>
       <c r="Z3" t="s">
-        <v>589</v>
+        <v>711</v>
       </c>
       <c r="AA3" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB3" t="s">
-        <v>593</v>
+        <v>716</v>
       </c>
       <c r="AC3" t="s">
-        <v>598</v>
+        <v>721</v>
       </c>
     </row>
     <row r="4" spans="1:29">
@@ -2431,82 +2800,82 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="E4" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="F4" t="s">
-        <v>206</v>
+        <v>245</v>
       </c>
       <c r="G4" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H4" t="s">
-        <v>237</v>
+        <v>283</v>
       </c>
       <c r="I4" t="s">
-        <v>282</v>
+        <v>338</v>
       </c>
       <c r="J4" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="K4" t="s">
-        <v>306</v>
+        <v>368</v>
       </c>
       <c r="L4" t="s">
-        <v>351</v>
+        <v>423</v>
       </c>
       <c r="M4" t="s">
-        <v>395</v>
+        <v>477</v>
       </c>
       <c r="N4" t="s">
-        <v>438</v>
+        <v>531</v>
       </c>
       <c r="O4" t="s">
-        <v>441</v>
+        <v>533</v>
       </c>
       <c r="P4" t="s">
-        <v>444</v>
+        <v>536</v>
       </c>
       <c r="Q4" t="s">
-        <v>450</v>
+        <v>542</v>
       </c>
       <c r="R4" t="s">
-        <v>455</v>
+        <v>548</v>
       </c>
       <c r="S4" t="s">
-        <v>500</v>
+        <v>603</v>
       </c>
       <c r="T4" t="s">
-        <v>512</v>
+        <v>617</v>
       </c>
       <c r="U4" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V4" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="W4" t="s">
         <v>2</v>
       </c>
       <c r="X4" t="s">
-        <v>544</v>
+        <v>656</v>
       </c>
       <c r="AA4" t="s">
-        <v>450</v>
+        <v>542</v>
       </c>
       <c r="AB4" t="s">
-        <v>594</v>
+        <v>716</v>
       </c>
       <c r="AC4" t="s">
-        <v>599</v>
+        <v>721</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -2514,79 +2883,79 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="E5" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="F5" t="s">
-        <v>207</v>
+        <v>246</v>
       </c>
       <c r="G5" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H5" t="s">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="I5" t="s">
-        <v>283</v>
+        <v>339</v>
       </c>
       <c r="J5" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="K5" t="s">
-        <v>307</v>
+        <v>369</v>
       </c>
       <c r="L5" t="s">
-        <v>352</v>
+        <v>424</v>
       </c>
       <c r="M5" t="s">
-        <v>396</v>
+        <v>478</v>
       </c>
       <c r="O5" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P5" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="Q5" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R5" t="s">
-        <v>456</v>
+        <v>549</v>
       </c>
       <c r="S5" t="s">
-        <v>499</v>
+        <v>602</v>
       </c>
       <c r="T5" t="s">
-        <v>513</v>
+        <v>618</v>
       </c>
       <c r="U5" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V5" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W5" t="s">
         <v>2</v>
       </c>
       <c r="X5" t="s">
-        <v>545</v>
+        <v>657</v>
       </c>
       <c r="AA5" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB5" t="s">
-        <v>593</v>
+        <v>717</v>
       </c>
       <c r="AC5" t="s">
-        <v>598</v>
+        <v>722</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -2594,79 +2963,82 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="F6" t="s">
-        <v>208</v>
+        <v>247</v>
       </c>
       <c r="G6" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H6" t="s">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="I6" t="s">
-        <v>284</v>
+        <v>340</v>
       </c>
       <c r="J6" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="K6" t="s">
-        <v>308</v>
+        <v>370</v>
       </c>
       <c r="L6" t="s">
-        <v>353</v>
+        <v>425</v>
       </c>
       <c r="M6" t="s">
-        <v>397</v>
+        <v>479</v>
+      </c>
+      <c r="N6" t="s">
+        <v>530</v>
       </c>
       <c r="O6" t="s">
-        <v>440</v>
+        <v>534</v>
       </c>
       <c r="P6" t="s">
-        <v>443</v>
+        <v>537</v>
       </c>
       <c r="Q6" t="s">
-        <v>449</v>
+        <v>543</v>
       </c>
       <c r="R6" t="s">
-        <v>457</v>
+        <v>550</v>
       </c>
       <c r="S6" t="s">
-        <v>499</v>
+        <v>604</v>
       </c>
       <c r="T6" t="s">
-        <v>514</v>
+        <v>619</v>
       </c>
       <c r="U6" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V6" t="s">
-        <v>234</v>
+        <v>653</v>
       </c>
       <c r="W6" t="s">
         <v>2</v>
       </c>
       <c r="X6" t="s">
-        <v>546</v>
+        <v>658</v>
       </c>
       <c r="AA6" t="s">
-        <v>449</v>
+        <v>543</v>
       </c>
       <c r="AB6" t="s">
-        <v>594</v>
+        <v>717</v>
       </c>
       <c r="AC6" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -2674,82 +3046,79 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D7" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="F7" t="s">
-        <v>209</v>
+        <v>248</v>
       </c>
       <c r="G7" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H7" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="I7" t="s">
-        <v>285</v>
+        <v>341</v>
       </c>
       <c r="J7" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="K7" t="s">
-        <v>309</v>
+        <v>371</v>
       </c>
       <c r="L7" t="s">
-        <v>354</v>
+        <v>426</v>
       </c>
       <c r="M7" t="s">
-        <v>398</v>
+        <v>480</v>
       </c>
       <c r="O7" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P7" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="Q7" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R7" t="s">
-        <v>458</v>
+        <v>551</v>
       </c>
       <c r="S7" t="s">
-        <v>499</v>
+        <v>602</v>
       </c>
       <c r="T7" t="s">
-        <v>515</v>
+        <v>620</v>
       </c>
       <c r="U7" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V7" t="s">
-        <v>541</v>
+        <v>280</v>
       </c>
       <c r="W7" t="s">
         <v>2</v>
       </c>
       <c r="X7" t="s">
-        <v>547</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>588</v>
+        <v>659</v>
       </c>
       <c r="AA7" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB7" t="s">
-        <v>594</v>
+        <v>716</v>
       </c>
       <c r="AC7" t="s">
-        <v>599</v>
+        <v>721</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -2757,82 +3126,82 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D8" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="F8" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="G8" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H8" t="s">
-        <v>241</v>
+        <v>287</v>
       </c>
       <c r="I8" t="s">
-        <v>286</v>
+        <v>342</v>
       </c>
       <c r="J8" t="s">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="K8" t="s">
-        <v>310</v>
+        <v>372</v>
       </c>
       <c r="L8" t="s">
-        <v>355</v>
+        <v>427</v>
       </c>
       <c r="M8" t="s">
-        <v>399</v>
+        <v>481</v>
       </c>
       <c r="O8" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P8" t="s">
-        <v>445</v>
+        <v>536</v>
       </c>
       <c r="Q8" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R8" t="s">
-        <v>459</v>
+        <v>552</v>
       </c>
       <c r="S8" t="s">
-        <v>501</v>
+        <v>602</v>
       </c>
       <c r="T8" t="s">
-        <v>516</v>
+        <v>621</v>
       </c>
       <c r="U8" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V8" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="W8" t="s">
         <v>2</v>
       </c>
       <c r="X8" t="s">
-        <v>548</v>
+        <v>660</v>
       </c>
       <c r="Y8" t="s">
-        <v>588</v>
+        <v>710</v>
       </c>
       <c r="AA8" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB8" t="s">
-        <v>594</v>
+        <v>717</v>
       </c>
       <c r="AC8" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -2840,79 +3209,79 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="E9" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="F9" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="G9" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H9" t="s">
-        <v>242</v>
+        <v>288</v>
       </c>
       <c r="I9" t="s">
-        <v>287</v>
+        <v>343</v>
       </c>
       <c r="J9" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="K9" t="s">
-        <v>311</v>
+        <v>373</v>
       </c>
       <c r="L9" t="s">
-        <v>356</v>
+        <v>428</v>
       </c>
       <c r="M9" t="s">
-        <v>400</v>
+        <v>482</v>
       </c>
       <c r="O9" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P9" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="Q9" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R9" t="s">
-        <v>460</v>
+        <v>553</v>
       </c>
       <c r="S9" t="s">
-        <v>502</v>
+        <v>602</v>
       </c>
       <c r="T9" t="s">
-        <v>517</v>
+        <v>622</v>
       </c>
       <c r="U9" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V9" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W9" t="s">
         <v>2</v>
       </c>
       <c r="X9" t="s">
-        <v>549</v>
+        <v>661</v>
       </c>
       <c r="AA9" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB9" t="s">
-        <v>593</v>
+        <v>716</v>
       </c>
       <c r="AC9" t="s">
-        <v>598</v>
+        <v>721</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -2920,85 +3289,85 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="F10" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="G10" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H10" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="I10" t="s">
-        <v>288</v>
+        <v>344</v>
       </c>
       <c r="J10" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="K10" t="s">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="L10" t="s">
-        <v>357</v>
+        <v>429</v>
       </c>
       <c r="M10" t="s">
-        <v>401</v>
+        <v>483</v>
       </c>
       <c r="O10" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P10" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="Q10" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R10" t="s">
-        <v>461</v>
+        <v>554</v>
       </c>
       <c r="S10" t="s">
-        <v>499</v>
+        <v>605</v>
       </c>
       <c r="T10" t="s">
-        <v>518</v>
+        <v>623</v>
       </c>
       <c r="U10" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V10" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W10" t="s">
         <v>2</v>
       </c>
       <c r="X10" t="s">
-        <v>550</v>
+        <v>662</v>
       </c>
       <c r="Y10" t="s">
-        <v>587</v>
+        <v>709</v>
       </c>
       <c r="Z10" t="s">
-        <v>589</v>
+        <v>712</v>
       </c>
       <c r="AA10" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB10" t="s">
-        <v>593</v>
+        <v>718</v>
       </c>
       <c r="AC10" t="s">
-        <v>598</v>
+        <v>722</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -3006,79 +3375,73 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="E11" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="F11" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="G11" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H11" t="s">
-        <v>244</v>
+        <v>290</v>
       </c>
       <c r="J11" t="s">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="K11" t="s">
-        <v>313</v>
-      </c>
-      <c r="L11" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="M11" t="s">
-        <v>402</v>
-      </c>
-      <c r="N11" t="s">
-        <v>438</v>
+        <v>484</v>
       </c>
       <c r="O11" t="s">
-        <v>439</v>
+        <v>533</v>
       </c>
       <c r="P11" t="s">
-        <v>446</v>
+        <v>536</v>
       </c>
       <c r="Q11" t="s">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="R11" t="s">
-        <v>462</v>
+        <v>555</v>
       </c>
       <c r="S11" t="s">
-        <v>498</v>
+        <v>602</v>
+      </c>
+      <c r="T11" t="s">
+        <v>624</v>
       </c>
       <c r="U11" t="s">
-        <v>541</v>
+        <v>653</v>
+      </c>
+      <c r="V11" t="s">
+        <v>280</v>
       </c>
       <c r="W11" t="s">
         <v>2</v>
       </c>
       <c r="X11" t="s">
-        <v>551</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>587</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>590</v>
+        <v>663</v>
       </c>
       <c r="AA11" t="s">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="AB11" t="s">
-        <v>595</v>
+        <v>716</v>
       </c>
       <c r="AC11" t="s">
-        <v>599</v>
+        <v>721</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -3086,73 +3449,79 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="E12" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="F12" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="G12" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H12" t="s">
-        <v>245</v>
+        <v>291</v>
+      </c>
+      <c r="I12" t="s">
+        <v>345</v>
       </c>
       <c r="J12" t="s">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="K12" t="s">
-        <v>314</v>
+        <v>376</v>
+      </c>
+      <c r="L12" t="s">
+        <v>430</v>
       </c>
       <c r="M12" t="s">
-        <v>403</v>
+        <v>485</v>
       </c>
       <c r="O12" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P12" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="Q12" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R12" t="s">
-        <v>463</v>
+        <v>556</v>
       </c>
       <c r="S12" t="s">
-        <v>499</v>
+        <v>602</v>
       </c>
       <c r="T12" t="s">
-        <v>519</v>
+        <v>625</v>
       </c>
       <c r="U12" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V12" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W12" t="s">
         <v>2</v>
       </c>
       <c r="X12" t="s">
-        <v>552</v>
+        <v>664</v>
       </c>
       <c r="AA12" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB12" t="s">
-        <v>593</v>
+        <v>717</v>
       </c>
       <c r="AC12" t="s">
-        <v>598</v>
+        <v>722</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -3160,79 +3529,88 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D13" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="E13" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="F13" t="s">
-        <v>176</v>
+        <v>253</v>
       </c>
       <c r="G13" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H13" t="s">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="I13" t="s">
-        <v>289</v>
+        <v>346</v>
       </c>
       <c r="J13" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="K13" t="s">
-        <v>315</v>
+        <v>377</v>
       </c>
       <c r="L13" t="s">
-        <v>359</v>
+        <v>431</v>
       </c>
       <c r="M13" t="s">
-        <v>404</v>
+        <v>486</v>
+      </c>
+      <c r="N13" t="s">
+        <v>530</v>
       </c>
       <c r="O13" t="s">
-        <v>440</v>
+        <v>534</v>
       </c>
       <c r="P13" t="s">
-        <v>443</v>
+        <v>537</v>
       </c>
       <c r="Q13" t="s">
-        <v>449</v>
+        <v>543</v>
       </c>
       <c r="R13" t="s">
-        <v>464</v>
+        <v>557</v>
       </c>
       <c r="S13" t="s">
-        <v>499</v>
+        <v>606</v>
       </c>
       <c r="T13" t="s">
-        <v>520</v>
+        <v>626</v>
       </c>
       <c r="U13" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V13" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W13" t="s">
         <v>2</v>
       </c>
       <c r="X13" t="s">
-        <v>553</v>
+        <v>665</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>709</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>711</v>
       </c>
       <c r="AA13" t="s">
-        <v>449</v>
+        <v>543</v>
       </c>
       <c r="AB13" t="s">
-        <v>594</v>
+        <v>717</v>
       </c>
       <c r="AC13" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -3240,79 +3618,79 @@
         <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="E14" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="F14" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="G14" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H14" t="s">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="I14" t="s">
-        <v>290</v>
+        <v>347</v>
       </c>
       <c r="J14" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="K14" t="s">
-        <v>316</v>
+        <v>378</v>
       </c>
       <c r="L14" t="s">
-        <v>360</v>
+        <v>432</v>
       </c>
       <c r="M14" t="s">
-        <v>405</v>
+        <v>487</v>
       </c>
       <c r="O14" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P14" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="Q14" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R14" t="s">
-        <v>465</v>
+        <v>558</v>
       </c>
       <c r="S14" t="s">
-        <v>499</v>
+        <v>602</v>
       </c>
       <c r="T14" t="s">
-        <v>521</v>
+        <v>627</v>
       </c>
       <c r="U14" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V14" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W14" t="s">
         <v>2</v>
       </c>
       <c r="X14" t="s">
-        <v>554</v>
+        <v>666</v>
       </c>
       <c r="AA14" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB14" t="s">
-        <v>593</v>
+        <v>717</v>
       </c>
       <c r="AC14" t="s">
-        <v>598</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -3320,85 +3698,73 @@
         <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="E15" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="F15" t="s">
-        <v>214</v>
+        <v>254</v>
       </c>
       <c r="G15" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H15" t="s">
-        <v>248</v>
-      </c>
-      <c r="I15" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="J15" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="K15" t="s">
-        <v>317</v>
+        <v>379</v>
       </c>
       <c r="L15" t="s">
-        <v>361</v>
+        <v>433</v>
       </c>
       <c r="M15" t="s">
-        <v>406</v>
+        <v>488</v>
+      </c>
+      <c r="N15" t="s">
+        <v>530</v>
       </c>
       <c r="O15" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
       <c r="P15" t="s">
-        <v>443</v>
+        <v>538</v>
       </c>
       <c r="Q15" t="s">
-        <v>449</v>
+        <v>544</v>
       </c>
       <c r="R15" t="s">
-        <v>466</v>
+        <v>559</v>
       </c>
       <c r="S15" t="s">
-        <v>503</v>
-      </c>
-      <c r="T15" t="s">
-        <v>522</v>
+        <v>607</v>
       </c>
       <c r="U15" t="s">
-        <v>541</v>
-      </c>
-      <c r="V15" t="s">
-        <v>234</v>
+        <v>653</v>
       </c>
       <c r="W15" t="s">
         <v>2</v>
       </c>
       <c r="X15" t="s">
-        <v>555</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>587</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>590</v>
+        <v>667</v>
       </c>
       <c r="AA15" t="s">
-        <v>449</v>
+        <v>715</v>
       </c>
       <c r="AB15" t="s">
-        <v>596</v>
+        <v>717</v>
       </c>
       <c r="AC15" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -3406,79 +3772,79 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="E16" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="F16" t="s">
-        <v>215</v>
+        <v>255</v>
       </c>
       <c r="G16" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H16" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="J16" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="K16" t="s">
-        <v>318</v>
+        <v>380</v>
       </c>
       <c r="L16" t="s">
-        <v>362</v>
+        <v>434</v>
       </c>
       <c r="M16" t="s">
-        <v>407</v>
+        <v>489</v>
       </c>
       <c r="N16" t="s">
-        <v>438</v>
+        <v>530</v>
       </c>
       <c r="O16" t="s">
-        <v>439</v>
+        <v>532</v>
       </c>
       <c r="P16" t="s">
-        <v>446</v>
+        <v>535</v>
       </c>
       <c r="Q16" t="s">
-        <v>451</v>
+        <v>541</v>
       </c>
       <c r="R16" t="s">
-        <v>467</v>
+        <v>560</v>
       </c>
       <c r="S16" t="s">
-        <v>498</v>
+        <v>603</v>
       </c>
       <c r="U16" t="s">
-        <v>541</v>
+        <v>280</v>
       </c>
       <c r="W16" t="s">
         <v>2</v>
       </c>
       <c r="X16" t="s">
-        <v>556</v>
+        <v>668</v>
       </c>
       <c r="Y16" t="s">
-        <v>587</v>
+        <v>709</v>
       </c>
       <c r="Z16" t="s">
-        <v>590</v>
+        <v>713</v>
       </c>
       <c r="AA16" t="s">
-        <v>451</v>
+        <v>541</v>
       </c>
       <c r="AB16" t="s">
-        <v>596</v>
+        <v>718</v>
       </c>
       <c r="AC16" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -3486,79 +3852,79 @@
         <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="E17" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="F17" t="s">
-        <v>190</v>
+        <v>256</v>
       </c>
       <c r="G17" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H17" t="s">
-        <v>250</v>
+        <v>296</v>
+      </c>
+      <c r="I17" t="s">
+        <v>344</v>
       </c>
       <c r="J17" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="K17" t="s">
-        <v>319</v>
+        <v>381</v>
       </c>
       <c r="L17" t="s">
-        <v>363</v>
+        <v>435</v>
       </c>
       <c r="M17" t="s">
-        <v>408</v>
-      </c>
-      <c r="N17" t="s">
-        <v>438</v>
+        <v>490</v>
       </c>
       <c r="O17" t="s">
-        <v>439</v>
+        <v>533</v>
       </c>
       <c r="P17" t="s">
-        <v>446</v>
+        <v>536</v>
       </c>
       <c r="Q17" t="s">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="R17" t="s">
-        <v>468</v>
+        <v>561</v>
       </c>
       <c r="S17" t="s">
-        <v>504</v>
+        <v>601</v>
+      </c>
+      <c r="T17" t="s">
+        <v>628</v>
       </c>
       <c r="U17" t="s">
-        <v>541</v>
+        <v>653</v>
+      </c>
+      <c r="V17" t="s">
+        <v>280</v>
       </c>
       <c r="W17" t="s">
         <v>2</v>
       </c>
       <c r="X17" t="s">
-        <v>557</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>587</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>590</v>
+        <v>669</v>
       </c>
       <c r="AA17" t="s">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="AB17" t="s">
-        <v>595</v>
+        <v>716</v>
       </c>
       <c r="AC17" t="s">
-        <v>599</v>
+        <v>721</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -3566,79 +3932,73 @@
         <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="E18" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="F18" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="G18" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H18" t="s">
-        <v>251</v>
-      </c>
-      <c r="I18" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="J18" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="K18" t="s">
-        <v>320</v>
+        <v>382</v>
       </c>
       <c r="L18" t="s">
-        <v>364</v>
+        <v>436</v>
       </c>
       <c r="M18" t="s">
-        <v>409</v>
+        <v>491</v>
+      </c>
+      <c r="N18" t="s">
+        <v>530</v>
       </c>
       <c r="O18" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
       <c r="P18" t="s">
-        <v>443</v>
+        <v>539</v>
       </c>
       <c r="Q18" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="R18" t="s">
-        <v>469</v>
+        <v>562</v>
       </c>
       <c r="S18" t="s">
-        <v>499</v>
-      </c>
-      <c r="T18" t="s">
-        <v>523</v>
+        <v>601</v>
       </c>
       <c r="U18" t="s">
-        <v>541</v>
-      </c>
-      <c r="V18" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W18" t="s">
         <v>2</v>
       </c>
       <c r="X18" t="s">
-        <v>558</v>
+        <v>670</v>
       </c>
       <c r="AA18" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="AB18" t="s">
-        <v>594</v>
+        <v>716</v>
       </c>
       <c r="AC18" t="s">
-        <v>599</v>
+        <v>721</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -3646,88 +4006,79 @@
         <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D19" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="E19" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="F19" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="G19" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H19" t="s">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="I19" t="s">
-        <v>292</v>
+        <v>348</v>
       </c>
       <c r="J19" t="s">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="K19" t="s">
-        <v>321</v>
+        <v>383</v>
       </c>
       <c r="L19" t="s">
-        <v>365</v>
+        <v>437</v>
       </c>
       <c r="M19" t="s">
-        <v>410</v>
-      </c>
-      <c r="N19" t="s">
-        <v>438</v>
+        <v>492</v>
       </c>
       <c r="O19" t="s">
-        <v>441</v>
+        <v>533</v>
       </c>
       <c r="P19" t="s">
-        <v>444</v>
+        <v>536</v>
       </c>
       <c r="Q19" t="s">
-        <v>450</v>
+        <v>542</v>
       </c>
       <c r="R19" t="s">
-        <v>470</v>
+        <v>563</v>
       </c>
       <c r="S19" t="s">
-        <v>505</v>
+        <v>605</v>
       </c>
       <c r="T19" t="s">
-        <v>524</v>
+        <v>629</v>
       </c>
       <c r="U19" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V19" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W19" t="s">
         <v>2</v>
       </c>
       <c r="X19" t="s">
-        <v>559</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>587</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>589</v>
+        <v>671</v>
       </c>
       <c r="AA19" t="s">
-        <v>450</v>
+        <v>542</v>
       </c>
       <c r="AB19" t="s">
-        <v>594</v>
+        <v>718</v>
       </c>
       <c r="AC19" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -3735,79 +4086,73 @@
         <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D20" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="E20" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="F20" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="G20" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H20" t="s">
-        <v>253</v>
-      </c>
-      <c r="I20" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="J20" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="K20" t="s">
-        <v>322</v>
+        <v>384</v>
       </c>
       <c r="L20" t="s">
-        <v>366</v>
+        <v>438</v>
       </c>
       <c r="M20" t="s">
-        <v>411</v>
+        <v>493</v>
+      </c>
+      <c r="N20" t="s">
+        <v>530</v>
       </c>
       <c r="O20" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
       <c r="P20" t="s">
-        <v>443</v>
+        <v>539</v>
       </c>
       <c r="Q20" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="R20" t="s">
-        <v>471</v>
+        <v>564</v>
       </c>
       <c r="S20" t="s">
-        <v>498</v>
-      </c>
-      <c r="T20" t="s">
-        <v>525</v>
+        <v>605</v>
       </c>
       <c r="U20" t="s">
-        <v>541</v>
-      </c>
-      <c r="V20" t="s">
-        <v>234</v>
+        <v>653</v>
       </c>
       <c r="W20" t="s">
         <v>2</v>
       </c>
       <c r="X20" t="s">
-        <v>560</v>
+        <v>672</v>
       </c>
       <c r="AA20" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="AB20" t="s">
-        <v>593</v>
+        <v>717</v>
       </c>
       <c r="AC20" t="s">
-        <v>598</v>
+        <v>722</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -3815,79 +4160,82 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D21" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="E21" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="F21" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G21" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H21" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="I21" t="s">
-        <v>293</v>
+        <v>349</v>
       </c>
       <c r="J21" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="K21" t="s">
-        <v>323</v>
+        <v>385</v>
       </c>
       <c r="L21" t="s">
-        <v>367</v>
+        <v>439</v>
       </c>
       <c r="M21" t="s">
-        <v>412</v>
+        <v>494</v>
       </c>
       <c r="O21" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P21" t="s">
-        <v>443</v>
+        <v>540</v>
       </c>
       <c r="Q21" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R21" t="s">
-        <v>472</v>
+        <v>565</v>
       </c>
       <c r="S21" t="s">
-        <v>499</v>
+        <v>608</v>
       </c>
       <c r="T21" t="s">
-        <v>526</v>
+        <v>630</v>
       </c>
       <c r="U21" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V21" t="s">
-        <v>234</v>
+        <v>653</v>
       </c>
       <c r="W21" t="s">
         <v>2</v>
       </c>
       <c r="X21" t="s">
-        <v>561</v>
+        <v>673</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>710</v>
       </c>
       <c r="AA21" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB21" t="s">
-        <v>595</v>
+        <v>717</v>
       </c>
       <c r="AC21" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -3895,73 +4243,85 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D22" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E22" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="F22" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="G22" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H22" t="s">
-        <v>255</v>
+        <v>301</v>
+      </c>
+      <c r="I22" t="s">
+        <v>350</v>
       </c>
       <c r="J22" t="s">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="K22" t="s">
-        <v>324</v>
+        <v>386</v>
       </c>
       <c r="L22" t="s">
-        <v>368</v>
+        <v>440</v>
       </c>
       <c r="M22" t="s">
-        <v>413</v>
-      </c>
-      <c r="N22" t="s">
-        <v>438</v>
+        <v>495</v>
       </c>
       <c r="O22" t="s">
-        <v>439</v>
+        <v>533</v>
       </c>
       <c r="P22" t="s">
-        <v>447</v>
+        <v>536</v>
       </c>
       <c r="Q22" t="s">
-        <v>452</v>
+        <v>542</v>
       </c>
       <c r="R22" t="s">
-        <v>473</v>
+        <v>566</v>
       </c>
       <c r="S22" t="s">
-        <v>506</v>
+        <v>602</v>
+      </c>
+      <c r="T22" t="s">
+        <v>631</v>
       </c>
       <c r="U22" t="s">
-        <v>541</v>
+        <v>653</v>
+      </c>
+      <c r="V22" t="s">
+        <v>280</v>
       </c>
       <c r="W22" t="s">
         <v>2</v>
       </c>
       <c r="X22" t="s">
-        <v>562</v>
+        <v>674</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>709</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>711</v>
       </c>
       <c r="AA22" t="s">
-        <v>592</v>
+        <v>542</v>
       </c>
       <c r="AB22" t="s">
-        <v>596</v>
+        <v>716</v>
       </c>
       <c r="AC22" t="s">
-        <v>599</v>
+        <v>721</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -3969,73 +4329,79 @@
         <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D23" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="E23" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="F23" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="G23" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H23" t="s">
-        <v>256</v>
+        <v>302</v>
       </c>
       <c r="J23" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="K23" t="s">
-        <v>325</v>
+        <v>387</v>
       </c>
       <c r="L23" t="s">
-        <v>369</v>
+        <v>441</v>
       </c>
       <c r="M23" t="s">
-        <v>414</v>
+        <v>496</v>
       </c>
       <c r="N23" t="s">
-        <v>438</v>
+        <v>530</v>
       </c>
       <c r="O23" t="s">
-        <v>439</v>
+        <v>532</v>
       </c>
       <c r="P23" t="s">
-        <v>447</v>
+        <v>539</v>
       </c>
       <c r="Q23" t="s">
-        <v>452</v>
+        <v>545</v>
       </c>
       <c r="R23" t="s">
-        <v>474</v>
+        <v>567</v>
       </c>
       <c r="S23" t="s">
-        <v>506</v>
+        <v>601</v>
       </c>
       <c r="U23" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="W23" t="s">
         <v>2</v>
       </c>
       <c r="X23" t="s">
-        <v>563</v>
+        <v>675</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>709</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>712</v>
       </c>
       <c r="AA23" t="s">
-        <v>592</v>
+        <v>545</v>
       </c>
       <c r="AB23" t="s">
-        <v>594</v>
+        <v>719</v>
       </c>
       <c r="AC23" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -4043,73 +4409,79 @@
         <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="E24" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="F24" t="s">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="G24" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H24" t="s">
-        <v>257</v>
+        <v>303</v>
+      </c>
+      <c r="I24" t="s">
+        <v>351</v>
       </c>
       <c r="J24" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="K24" t="s">
-        <v>326</v>
+        <v>388</v>
       </c>
       <c r="L24" t="s">
-        <v>370</v>
+        <v>442</v>
       </c>
       <c r="M24" t="s">
-        <v>415</v>
-      </c>
-      <c r="N24" t="s">
-        <v>438</v>
+        <v>497</v>
       </c>
       <c r="O24" t="s">
-        <v>439</v>
+        <v>533</v>
       </c>
       <c r="P24" t="s">
-        <v>446</v>
+        <v>536</v>
       </c>
       <c r="Q24" t="s">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="R24" t="s">
-        <v>475</v>
+        <v>568</v>
       </c>
       <c r="S24" t="s">
-        <v>498</v>
+        <v>605</v>
+      </c>
+      <c r="T24" t="s">
+        <v>632</v>
       </c>
       <c r="U24" t="s">
-        <v>234</v>
+        <v>653</v>
+      </c>
+      <c r="V24" t="s">
+        <v>280</v>
       </c>
       <c r="W24" t="s">
         <v>2</v>
       </c>
       <c r="X24" t="s">
-        <v>564</v>
+        <v>676</v>
       </c>
       <c r="AA24" t="s">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="AB24" t="s">
-        <v>593</v>
+        <v>717</v>
       </c>
       <c r="AC24" t="s">
-        <v>598</v>
+        <v>722</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -4117,79 +4489,79 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D25" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="E25" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="F25" t="s">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="G25" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H25" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="I25" t="s">
-        <v>294</v>
+        <v>352</v>
       </c>
       <c r="J25" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="K25" t="s">
-        <v>327</v>
+        <v>389</v>
       </c>
       <c r="L25" t="s">
-        <v>371</v>
+        <v>443</v>
       </c>
       <c r="M25" t="s">
-        <v>416</v>
+        <v>498</v>
       </c>
       <c r="O25" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P25" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="Q25" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R25" t="s">
-        <v>476</v>
+        <v>569</v>
       </c>
       <c r="S25" t="s">
-        <v>503</v>
+        <v>602</v>
       </c>
       <c r="T25" t="s">
-        <v>527</v>
+        <v>633</v>
       </c>
       <c r="U25" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V25" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W25" t="s">
         <v>2</v>
       </c>
       <c r="X25" t="s">
-        <v>565</v>
+        <v>677</v>
       </c>
       <c r="AA25" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB25" t="s">
-        <v>594</v>
+        <v>719</v>
       </c>
       <c r="AC25" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -4197,73 +4569,79 @@
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D26" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="E26" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="F26" t="s">
-        <v>200</v>
+        <v>261</v>
       </c>
       <c r="G26" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H26" t="s">
-        <v>259</v>
+        <v>305</v>
+      </c>
+      <c r="I26" t="s">
+        <v>344</v>
       </c>
       <c r="J26" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="K26" t="s">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="L26" t="s">
-        <v>372</v>
+        <v>444</v>
       </c>
       <c r="M26" t="s">
-        <v>417</v>
-      </c>
-      <c r="N26" t="s">
-        <v>438</v>
+        <v>499</v>
       </c>
       <c r="O26" t="s">
-        <v>439</v>
+        <v>533</v>
       </c>
       <c r="P26" t="s">
-        <v>446</v>
+        <v>536</v>
       </c>
       <c r="Q26" t="s">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="R26" t="s">
-        <v>477</v>
+        <v>570</v>
       </c>
       <c r="S26" t="s">
-        <v>503</v>
+        <v>609</v>
+      </c>
+      <c r="T26" t="s">
+        <v>634</v>
       </c>
       <c r="U26" t="s">
-        <v>541</v>
+        <v>653</v>
+      </c>
+      <c r="V26" t="s">
+        <v>280</v>
       </c>
       <c r="W26" t="s">
         <v>2</v>
       </c>
       <c r="X26" t="s">
-        <v>566</v>
+        <v>678</v>
       </c>
       <c r="AA26" t="s">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="AB26" t="s">
-        <v>594</v>
+        <v>716</v>
       </c>
       <c r="AC26" t="s">
-        <v>599</v>
+        <v>721</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -4271,79 +4649,79 @@
         <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="E27" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="F27" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="G27" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H27" t="s">
-        <v>260</v>
-      </c>
-      <c r="I27" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="J27" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="K27" t="s">
-        <v>329</v>
+        <v>391</v>
       </c>
       <c r="L27" t="s">
-        <v>373</v>
+        <v>445</v>
       </c>
       <c r="M27" t="s">
-        <v>418</v>
+        <v>500</v>
+      </c>
+      <c r="N27" t="s">
+        <v>530</v>
       </c>
       <c r="O27" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
       <c r="P27" t="s">
-        <v>443</v>
+        <v>539</v>
       </c>
       <c r="Q27" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="R27" t="s">
-        <v>478</v>
+        <v>571</v>
       </c>
       <c r="S27" t="s">
-        <v>503</v>
-      </c>
-      <c r="T27" t="s">
-        <v>528</v>
+        <v>601</v>
       </c>
       <c r="U27" t="s">
-        <v>541</v>
-      </c>
-      <c r="V27" t="s">
-        <v>234</v>
+        <v>653</v>
       </c>
       <c r="W27" t="s">
         <v>2</v>
       </c>
       <c r="X27" t="s">
-        <v>567</v>
+        <v>679</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>709</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>712</v>
       </c>
       <c r="AA27" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="AB27" t="s">
-        <v>596</v>
+        <v>718</v>
       </c>
       <c r="AC27" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -4351,85 +4729,79 @@
         <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="E28" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="F28" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="G28" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H28" t="s">
-        <v>261</v>
-      </c>
-      <c r="I28" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="J28" t="s">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="K28" t="s">
-        <v>330</v>
+        <v>392</v>
       </c>
       <c r="L28" t="s">
-        <v>374</v>
+        <v>446</v>
       </c>
       <c r="M28" t="s">
-        <v>419</v>
+        <v>501</v>
+      </c>
+      <c r="N28" t="s">
+        <v>530</v>
       </c>
       <c r="O28" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
       <c r="P28" t="s">
-        <v>443</v>
+        <v>539</v>
       </c>
       <c r="Q28" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="R28" t="s">
-        <v>479</v>
+        <v>572</v>
       </c>
       <c r="S28" t="s">
-        <v>500</v>
-      </c>
-      <c r="T28" t="s">
-        <v>529</v>
+        <v>610</v>
       </c>
       <c r="U28" t="s">
-        <v>541</v>
-      </c>
-      <c r="V28" t="s">
-        <v>234</v>
+        <v>653</v>
       </c>
       <c r="W28" t="s">
         <v>2</v>
       </c>
       <c r="X28" t="s">
-        <v>568</v>
+        <v>680</v>
       </c>
       <c r="Y28" t="s">
-        <v>587</v>
+        <v>709</v>
       </c>
       <c r="Z28" t="s">
-        <v>590</v>
+        <v>712</v>
       </c>
       <c r="AA28" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="AB28" t="s">
-        <v>594</v>
+        <v>719</v>
       </c>
       <c r="AC28" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -4437,73 +4809,73 @@
         <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="E29" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="F29" t="s">
-        <v>200</v>
+        <v>262</v>
       </c>
       <c r="G29" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H29" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="J29" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="K29" t="s">
-        <v>331</v>
+        <v>393</v>
       </c>
       <c r="L29" t="s">
-        <v>375</v>
+        <v>447</v>
       </c>
       <c r="M29" t="s">
-        <v>420</v>
+        <v>502</v>
       </c>
       <c r="N29" t="s">
-        <v>438</v>
+        <v>530</v>
       </c>
       <c r="O29" t="s">
-        <v>439</v>
+        <v>532</v>
       </c>
       <c r="P29" t="s">
-        <v>442</v>
+        <v>538</v>
       </c>
       <c r="Q29" t="s">
-        <v>448</v>
+        <v>544</v>
       </c>
       <c r="R29" t="s">
-        <v>480</v>
+        <v>573</v>
       </c>
       <c r="S29" t="s">
-        <v>503</v>
+        <v>607</v>
       </c>
       <c r="U29" t="s">
-        <v>234</v>
+        <v>653</v>
       </c>
       <c r="W29" t="s">
         <v>2</v>
       </c>
       <c r="X29" t="s">
-        <v>569</v>
+        <v>681</v>
       </c>
       <c r="AA29" t="s">
-        <v>448</v>
+        <v>715</v>
       </c>
       <c r="AB29" t="s">
-        <v>594</v>
+        <v>718</v>
       </c>
       <c r="AC29" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -4511,85 +4883,79 @@
         <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="E30" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="F30" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="G30" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H30" t="s">
-        <v>263</v>
+        <v>309</v>
       </c>
       <c r="I30" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="J30" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="K30" t="s">
-        <v>332</v>
+        <v>394</v>
       </c>
       <c r="L30" t="s">
-        <v>376</v>
+        <v>448</v>
       </c>
       <c r="M30" t="s">
-        <v>421</v>
+        <v>503</v>
       </c>
       <c r="O30" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P30" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="Q30" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R30" t="s">
-        <v>481</v>
+        <v>574</v>
       </c>
       <c r="S30" t="s">
-        <v>500</v>
+        <v>611</v>
       </c>
       <c r="T30" t="s">
-        <v>530</v>
+        <v>635</v>
       </c>
       <c r="U30" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V30" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W30" t="s">
         <v>2</v>
       </c>
       <c r="X30" t="s">
-        <v>570</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>587</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>589</v>
+        <v>682</v>
       </c>
       <c r="AA30" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB30" t="s">
-        <v>594</v>
+        <v>717</v>
       </c>
       <c r="AC30" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -4597,73 +4963,73 @@
         <v>58</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D31" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="E31" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="F31" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="G31" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H31" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
       <c r="J31" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="K31" t="s">
-        <v>333</v>
+        <v>395</v>
       </c>
       <c r="L31" t="s">
-        <v>377</v>
+        <v>449</v>
       </c>
       <c r="M31" t="s">
-        <v>422</v>
+        <v>504</v>
       </c>
       <c r="N31" t="s">
-        <v>438</v>
+        <v>530</v>
       </c>
       <c r="O31" t="s">
-        <v>439</v>
+        <v>532</v>
       </c>
       <c r="P31" t="s">
-        <v>446</v>
+        <v>535</v>
       </c>
       <c r="Q31" t="s">
-        <v>451</v>
+        <v>541</v>
       </c>
       <c r="R31" t="s">
-        <v>482</v>
+        <v>575</v>
       </c>
       <c r="S31" t="s">
-        <v>507</v>
+        <v>605</v>
       </c>
       <c r="U31" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W31" t="s">
         <v>2</v>
       </c>
       <c r="X31" t="s">
-        <v>571</v>
+        <v>683</v>
       </c>
       <c r="AA31" t="s">
-        <v>451</v>
+        <v>541</v>
       </c>
       <c r="AB31" t="s">
-        <v>593</v>
+        <v>717</v>
       </c>
       <c r="AC31" t="s">
-        <v>598</v>
+        <v>722</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -4671,79 +5037,85 @@
         <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="E32" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="F32" t="s">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="G32" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H32" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="I32" t="s">
-        <v>298</v>
+        <v>353</v>
       </c>
       <c r="J32" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="K32" t="s">
-        <v>334</v>
+        <v>396</v>
       </c>
       <c r="L32" t="s">
-        <v>378</v>
+        <v>450</v>
       </c>
       <c r="M32" t="s">
-        <v>423</v>
+        <v>505</v>
       </c>
       <c r="O32" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P32" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="Q32" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R32" t="s">
-        <v>483</v>
+        <v>576</v>
       </c>
       <c r="S32" t="s">
-        <v>505</v>
+        <v>604</v>
       </c>
       <c r="T32" t="s">
-        <v>531</v>
+        <v>636</v>
       </c>
       <c r="U32" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V32" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W32" t="s">
         <v>2</v>
       </c>
       <c r="X32" t="s">
-        <v>572</v>
+        <v>684</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>709</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>712</v>
       </c>
       <c r="AA32" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB32" t="s">
-        <v>594</v>
+        <v>717</v>
       </c>
       <c r="AC32" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -4751,79 +5123,79 @@
         <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="E33" t="s">
-        <v>176</v>
+        <v>222</v>
       </c>
       <c r="F33" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="G33" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H33" t="s">
-        <v>266</v>
+        <v>312</v>
       </c>
       <c r="I33" t="s">
-        <v>287</v>
+        <v>354</v>
       </c>
       <c r="J33" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="K33" t="s">
-        <v>335</v>
+        <v>397</v>
       </c>
       <c r="L33" t="s">
-        <v>379</v>
+        <v>451</v>
       </c>
       <c r="M33" t="s">
-        <v>424</v>
+        <v>506</v>
       </c>
       <c r="O33" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P33" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="Q33" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R33" t="s">
-        <v>484</v>
+        <v>577</v>
       </c>
       <c r="S33" t="s">
-        <v>507</v>
+        <v>604</v>
       </c>
       <c r="T33" t="s">
-        <v>532</v>
+        <v>637</v>
       </c>
       <c r="U33" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V33" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W33" t="s">
         <v>2</v>
       </c>
       <c r="X33" t="s">
-        <v>573</v>
+        <v>685</v>
       </c>
       <c r="AA33" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB33" t="s">
-        <v>594</v>
+        <v>720</v>
       </c>
       <c r="AC33" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -4831,73 +5203,79 @@
         <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D34" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="E34" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="F34" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="G34" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H34" t="s">
-        <v>267</v>
+        <v>313</v>
+      </c>
+      <c r="I34" t="s">
+        <v>344</v>
       </c>
       <c r="J34" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="K34" t="s">
-        <v>336</v>
+        <v>398</v>
       </c>
       <c r="L34" t="s">
-        <v>380</v>
+        <v>452</v>
       </c>
       <c r="M34" t="s">
-        <v>425</v>
-      </c>
-      <c r="N34" t="s">
-        <v>438</v>
+        <v>507</v>
       </c>
       <c r="O34" t="s">
-        <v>439</v>
+        <v>533</v>
       </c>
       <c r="P34" t="s">
-        <v>442</v>
+        <v>536</v>
       </c>
       <c r="Q34" t="s">
-        <v>448</v>
+        <v>542</v>
       </c>
       <c r="R34" t="s">
-        <v>485</v>
+        <v>578</v>
       </c>
       <c r="S34" t="s">
-        <v>507</v>
+        <v>604</v>
+      </c>
+      <c r="T34" t="s">
+        <v>638</v>
       </c>
       <c r="U34" t="s">
-        <v>541</v>
+        <v>653</v>
+      </c>
+      <c r="V34" t="s">
+        <v>280</v>
       </c>
       <c r="W34" t="s">
         <v>2</v>
       </c>
       <c r="X34" t="s">
-        <v>574</v>
+        <v>686</v>
       </c>
       <c r="AA34" t="s">
-        <v>448</v>
+        <v>542</v>
       </c>
       <c r="AB34" t="s">
-        <v>594</v>
+        <v>717</v>
       </c>
       <c r="AC34" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="35" spans="1:29">
@@ -4905,79 +5283,73 @@
         <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C35" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D35" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="E35" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="F35" t="s">
-        <v>227</v>
+        <v>265</v>
       </c>
       <c r="G35" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H35" t="s">
-        <v>268</v>
-      </c>
-      <c r="I35" t="s">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="J35" t="s">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="K35" t="s">
-        <v>337</v>
+        <v>399</v>
       </c>
       <c r="L35" t="s">
-        <v>381</v>
+        <v>453</v>
       </c>
       <c r="M35" t="s">
-        <v>426</v>
+        <v>508</v>
+      </c>
+      <c r="N35" t="s">
+        <v>530</v>
       </c>
       <c r="O35" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
       <c r="P35" t="s">
-        <v>443</v>
+        <v>539</v>
       </c>
       <c r="Q35" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="R35" t="s">
-        <v>486</v>
+        <v>579</v>
       </c>
       <c r="S35" t="s">
-        <v>500</v>
-      </c>
-      <c r="T35" t="s">
-        <v>533</v>
+        <v>611</v>
       </c>
       <c r="U35" t="s">
-        <v>541</v>
-      </c>
-      <c r="V35" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W35" t="s">
         <v>2</v>
       </c>
       <c r="X35" t="s">
-        <v>575</v>
+        <v>687</v>
       </c>
       <c r="AA35" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="AB35" t="s">
-        <v>594</v>
+        <v>716</v>
       </c>
       <c r="AC35" t="s">
-        <v>599</v>
+        <v>721</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -4985,79 +5357,73 @@
         <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C36" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D36" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="E36" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="F36" t="s">
-        <v>166</v>
+        <v>266</v>
       </c>
       <c r="G36" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H36" t="s">
-        <v>269</v>
-      </c>
-      <c r="I36" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="J36" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="K36" t="s">
-        <v>338</v>
+        <v>400</v>
       </c>
       <c r="L36" t="s">
-        <v>382</v>
+        <v>454</v>
       </c>
       <c r="M36" t="s">
-        <v>427</v>
+        <v>509</v>
+      </c>
+      <c r="N36" t="s">
+        <v>530</v>
       </c>
       <c r="O36" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
       <c r="P36" t="s">
-        <v>443</v>
+        <v>535</v>
       </c>
       <c r="Q36" t="s">
-        <v>449</v>
+        <v>541</v>
       </c>
       <c r="R36" t="s">
-        <v>487</v>
+        <v>580</v>
       </c>
       <c r="S36" t="s">
-        <v>500</v>
-      </c>
-      <c r="T36" t="s">
-        <v>534</v>
+        <v>611</v>
       </c>
       <c r="U36" t="s">
-        <v>541</v>
-      </c>
-      <c r="V36" t="s">
-        <v>234</v>
+        <v>653</v>
       </c>
       <c r="W36" t="s">
         <v>2</v>
       </c>
       <c r="X36" t="s">
-        <v>576</v>
+        <v>688</v>
       </c>
       <c r="AA36" t="s">
-        <v>449</v>
+        <v>541</v>
       </c>
       <c r="AB36" t="s">
-        <v>597</v>
+        <v>717</v>
       </c>
       <c r="AC36" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="37" spans="1:29">
@@ -5065,73 +5431,79 @@
         <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C37" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D37" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="E37" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="F37" t="s">
-        <v>166</v>
+        <v>267</v>
       </c>
       <c r="G37" t="s">
-        <v>233</v>
+        <v>280</v>
       </c>
       <c r="H37" t="s">
-        <v>270</v>
+        <v>316</v>
+      </c>
+      <c r="I37" t="s">
+        <v>355</v>
       </c>
       <c r="J37" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="K37" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="L37" t="s">
-        <v>383</v>
+        <v>455</v>
       </c>
       <c r="M37" t="s">
-        <v>428</v>
-      </c>
-      <c r="N37" t="s">
-        <v>438</v>
+        <v>510</v>
       </c>
       <c r="O37" t="s">
-        <v>439</v>
+        <v>533</v>
       </c>
       <c r="P37" t="s">
-        <v>447</v>
+        <v>536</v>
       </c>
       <c r="Q37" t="s">
-        <v>452</v>
+        <v>542</v>
       </c>
       <c r="R37" t="s">
-        <v>488</v>
+        <v>581</v>
       </c>
       <c r="S37" t="s">
-        <v>508</v>
+        <v>610</v>
+      </c>
+      <c r="T37" t="s">
+        <v>639</v>
       </c>
       <c r="U37" t="s">
-        <v>541</v>
+        <v>653</v>
+      </c>
+      <c r="V37" t="s">
+        <v>280</v>
       </c>
       <c r="W37" t="s">
         <v>2</v>
       </c>
       <c r="X37" t="s">
-        <v>577</v>
+        <v>689</v>
       </c>
       <c r="AA37" t="s">
-        <v>592</v>
+        <v>542</v>
       </c>
       <c r="AB37" t="s">
-        <v>594</v>
+        <v>716</v>
       </c>
       <c r="AC37" t="s">
-        <v>599</v>
+        <v>721</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -5139,79 +5511,73 @@
         <v>65</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C38" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D38" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="E38" t="s">
+        <v>226</v>
+      </c>
+      <c r="F38" t="s">
         <v>196</v>
       </c>
-      <c r="F38" t="s">
-        <v>228</v>
-      </c>
       <c r="G38" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H38" t="s">
-        <v>271</v>
-      </c>
-      <c r="I38" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
       <c r="J38" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="K38" t="s">
-        <v>340</v>
+        <v>402</v>
       </c>
       <c r="L38" t="s">
-        <v>384</v>
+        <v>456</v>
       </c>
       <c r="M38" t="s">
-        <v>429</v>
+        <v>511</v>
+      </c>
+      <c r="N38" t="s">
+        <v>530</v>
       </c>
       <c r="O38" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
       <c r="P38" t="s">
-        <v>443</v>
+        <v>538</v>
       </c>
       <c r="Q38" t="s">
-        <v>449</v>
+        <v>544</v>
       </c>
       <c r="R38" t="s">
-        <v>489</v>
+        <v>582</v>
       </c>
       <c r="S38" t="s">
-        <v>507</v>
-      </c>
-      <c r="T38" t="s">
-        <v>535</v>
+        <v>612</v>
       </c>
       <c r="U38" t="s">
-        <v>541</v>
-      </c>
-      <c r="V38" t="s">
-        <v>234</v>
+        <v>653</v>
       </c>
       <c r="W38" t="s">
         <v>2</v>
       </c>
       <c r="X38" t="s">
-        <v>578</v>
+        <v>690</v>
       </c>
       <c r="AA38" t="s">
-        <v>449</v>
+        <v>715</v>
       </c>
       <c r="AB38" t="s">
-        <v>594</v>
+        <v>717</v>
       </c>
       <c r="AC38" t="s">
-        <v>599</v>
+        <v>722</v>
       </c>
     </row>
     <row r="39" spans="1:29">
@@ -5219,79 +5585,79 @@
         <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D39" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="E39" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="F39" t="s">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="G39" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H39" t="s">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="I39" t="s">
-        <v>300</v>
+        <v>356</v>
       </c>
       <c r="J39" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="K39" t="s">
-        <v>341</v>
+        <v>403</v>
       </c>
       <c r="L39" t="s">
-        <v>385</v>
+        <v>457</v>
       </c>
       <c r="M39" t="s">
-        <v>430</v>
+        <v>512</v>
       </c>
       <c r="O39" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P39" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="Q39" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R39" t="s">
-        <v>490</v>
+        <v>583</v>
       </c>
       <c r="S39" t="s">
-        <v>509</v>
+        <v>613</v>
       </c>
       <c r="T39" t="s">
-        <v>536</v>
+        <v>640</v>
       </c>
       <c r="U39" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V39" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W39" t="s">
         <v>2</v>
       </c>
       <c r="X39" t="s">
-        <v>579</v>
+        <v>691</v>
       </c>
       <c r="AA39" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB39" t="s">
-        <v>593</v>
+        <v>716</v>
       </c>
       <c r="AC39" t="s">
-        <v>598</v>
+        <v>721</v>
       </c>
     </row>
     <row r="40" spans="1:29">
@@ -5299,79 +5665,79 @@
         <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D40" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="E40" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="F40" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="G40" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H40" t="s">
-        <v>273</v>
+        <v>319</v>
       </c>
       <c r="I40" t="s">
-        <v>287</v>
+        <v>344</v>
       </c>
       <c r="J40" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="K40" t="s">
-        <v>342</v>
+        <v>404</v>
       </c>
       <c r="L40" t="s">
-        <v>386</v>
+        <v>458</v>
       </c>
       <c r="M40" t="s">
-        <v>431</v>
+        <v>513</v>
       </c>
       <c r="O40" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P40" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="Q40" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R40" t="s">
-        <v>491</v>
+        <v>584</v>
       </c>
       <c r="S40" t="s">
-        <v>500</v>
+        <v>610</v>
       </c>
       <c r="T40" t="s">
-        <v>537</v>
+        <v>641</v>
       </c>
       <c r="U40" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V40" t="s">
-        <v>541</v>
+        <v>280</v>
       </c>
       <c r="W40" t="s">
         <v>2</v>
       </c>
       <c r="X40" t="s">
-        <v>580</v>
+        <v>692</v>
       </c>
       <c r="AA40" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB40" t="s">
-        <v>594</v>
+        <v>716</v>
       </c>
       <c r="AC40" t="s">
-        <v>599</v>
+        <v>721</v>
       </c>
     </row>
     <row r="41" spans="1:29">
@@ -5379,79 +5745,79 @@
         <v>68</v>
       </c>
       <c r="B41" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C41" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D41" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="E41" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="F41" t="s">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="G41" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H41" t="s">
-        <v>274</v>
-      </c>
-      <c r="I41" t="s">
-        <v>287</v>
+        <v>320</v>
       </c>
       <c r="J41" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="K41" t="s">
-        <v>343</v>
+        <v>405</v>
       </c>
       <c r="L41" t="s">
-        <v>387</v>
+        <v>459</v>
       </c>
       <c r="M41" t="s">
-        <v>432</v>
+        <v>514</v>
+      </c>
+      <c r="N41" t="s">
+        <v>530</v>
       </c>
       <c r="O41" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
       <c r="P41" t="s">
-        <v>443</v>
+        <v>539</v>
       </c>
       <c r="Q41" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="R41" t="s">
-        <v>492</v>
+        <v>585</v>
       </c>
       <c r="S41" t="s">
-        <v>500</v>
-      </c>
-      <c r="T41" t="s">
-        <v>538</v>
+        <v>614</v>
       </c>
       <c r="U41" t="s">
-        <v>541</v>
-      </c>
-      <c r="V41" t="s">
-        <v>541</v>
+        <v>280</v>
       </c>
       <c r="W41" t="s">
         <v>2</v>
       </c>
       <c r="X41" t="s">
-        <v>581</v>
+        <v>693</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>709</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>714</v>
       </c>
       <c r="AA41" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="AB41" t="s">
-        <v>594</v>
+        <v>716</v>
       </c>
       <c r="AC41" t="s">
-        <v>599</v>
+        <v>721</v>
       </c>
     </row>
     <row r="42" spans="1:29">
@@ -5459,73 +5825,85 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C42" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D42" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="E42" t="s">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="F42" t="s">
-        <v>203</v>
+        <v>258</v>
       </c>
       <c r="G42" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H42" t="s">
-        <v>275</v>
+        <v>321</v>
+      </c>
+      <c r="I42" t="s">
+        <v>357</v>
       </c>
       <c r="J42" t="s">
-        <v>303</v>
+        <v>364</v>
       </c>
       <c r="K42" t="s">
-        <v>344</v>
+        <v>406</v>
       </c>
       <c r="L42" t="s">
-        <v>388</v>
+        <v>460</v>
       </c>
       <c r="M42" t="s">
-        <v>433</v>
-      </c>
-      <c r="N42" t="s">
-        <v>438</v>
+        <v>515</v>
       </c>
       <c r="O42" t="s">
-        <v>439</v>
+        <v>533</v>
       </c>
       <c r="P42" t="s">
-        <v>446</v>
+        <v>536</v>
       </c>
       <c r="Q42" t="s">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="R42" t="s">
-        <v>493</v>
+        <v>586</v>
       </c>
       <c r="S42" t="s">
-        <v>500</v>
+        <v>604</v>
+      </c>
+      <c r="T42" t="s">
+        <v>642</v>
       </c>
       <c r="U42" t="s">
-        <v>234</v>
+        <v>653</v>
+      </c>
+      <c r="V42" t="s">
+        <v>280</v>
       </c>
       <c r="W42" t="s">
         <v>2</v>
       </c>
       <c r="X42" t="s">
-        <v>582</v>
+        <v>694</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>709</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>711</v>
       </c>
       <c r="AA42" t="s">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="AB42" t="s">
-        <v>593</v>
+        <v>717</v>
       </c>
       <c r="AC42" t="s">
-        <v>598</v>
+        <v>722</v>
       </c>
     </row>
     <row r="43" spans="1:29">
@@ -5533,79 +5911,79 @@
         <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C43" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D43" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="E43" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="F43" t="s">
-        <v>214</v>
+        <v>270</v>
       </c>
       <c r="G43" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H43" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="I43" t="s">
-        <v>287</v>
+        <v>358</v>
       </c>
       <c r="J43" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="K43" t="s">
-        <v>345</v>
+        <v>407</v>
       </c>
       <c r="L43" t="s">
-        <v>389</v>
+        <v>461</v>
       </c>
       <c r="M43" t="s">
-        <v>434</v>
+        <v>516</v>
       </c>
       <c r="O43" t="s">
-        <v>440</v>
+        <v>533</v>
       </c>
       <c r="P43" t="s">
-        <v>443</v>
+        <v>536</v>
       </c>
       <c r="Q43" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="R43" t="s">
-        <v>494</v>
+        <v>587</v>
       </c>
       <c r="S43" t="s">
-        <v>504</v>
+        <v>606</v>
       </c>
       <c r="T43" t="s">
-        <v>539</v>
+        <v>643</v>
       </c>
       <c r="U43" t="s">
-        <v>541</v>
+        <v>653</v>
       </c>
       <c r="V43" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W43" t="s">
         <v>2</v>
       </c>
       <c r="X43" t="s">
-        <v>583</v>
+        <v>695</v>
       </c>
       <c r="AA43" t="s">
-        <v>449</v>
+        <v>542</v>
       </c>
       <c r="AB43" t="s">
-        <v>593</v>
+        <v>717</v>
       </c>
       <c r="AC43" t="s">
-        <v>598</v>
+        <v>722</v>
       </c>
     </row>
     <row r="44" spans="1:29">
@@ -5613,79 +5991,79 @@
         <v>71</v>
       </c>
       <c r="B44" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C44" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D44" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="E44" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="F44" t="s">
-        <v>231</v>
+        <v>271</v>
       </c>
       <c r="G44" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H44" t="s">
-        <v>277</v>
+        <v>323</v>
+      </c>
+      <c r="I44" t="s">
+        <v>344</v>
       </c>
       <c r="J44" t="s">
-        <v>302</v>
+        <v>364</v>
       </c>
       <c r="K44" t="s">
-        <v>346</v>
+        <v>408</v>
       </c>
       <c r="L44" t="s">
-        <v>390</v>
+        <v>462</v>
       </c>
       <c r="M44" t="s">
-        <v>435</v>
-      </c>
-      <c r="N44" t="s">
-        <v>438</v>
+        <v>517</v>
       </c>
       <c r="O44" t="s">
-        <v>439</v>
+        <v>533</v>
       </c>
       <c r="P44" t="s">
-        <v>446</v>
+        <v>536</v>
       </c>
       <c r="Q44" t="s">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="R44" t="s">
-        <v>495</v>
+        <v>588</v>
       </c>
       <c r="S44" t="s">
-        <v>510</v>
+        <v>611</v>
+      </c>
+      <c r="T44" t="s">
+        <v>644</v>
       </c>
       <c r="U44" t="s">
-        <v>234</v>
+        <v>653</v>
+      </c>
+      <c r="V44" t="s">
+        <v>280</v>
       </c>
       <c r="W44" t="s">
         <v>2</v>
       </c>
       <c r="X44" t="s">
-        <v>584</v>
-      </c>
-      <c r="Y44" t="s">
-        <v>587</v>
-      </c>
-      <c r="Z44" t="s">
-        <v>591</v>
+        <v>696</v>
       </c>
       <c r="AA44" t="s">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="AB44" t="s">
-        <v>593</v>
+        <v>717</v>
       </c>
       <c r="AC44" t="s">
-        <v>598</v>
+        <v>722</v>
       </c>
     </row>
     <row r="45" spans="1:29">
@@ -5693,79 +6071,73 @@
         <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C45" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D45" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="E45" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="F45" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="G45" t="s">
-        <v>234</v>
+        <v>279</v>
       </c>
       <c r="H45" t="s">
-        <v>278</v>
-      </c>
-      <c r="I45" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="J45" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="K45" t="s">
-        <v>347</v>
+        <v>409</v>
       </c>
       <c r="L45" t="s">
-        <v>391</v>
+        <v>463</v>
       </c>
       <c r="M45" t="s">
-        <v>436</v>
+        <v>518</v>
+      </c>
+      <c r="N45" t="s">
+        <v>530</v>
       </c>
       <c r="O45" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
       <c r="P45" t="s">
-        <v>443</v>
+        <v>539</v>
       </c>
       <c r="Q45" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="R45" t="s">
-        <v>496</v>
+        <v>589</v>
       </c>
       <c r="S45" t="s">
-        <v>504</v>
-      </c>
-      <c r="T45" t="s">
-        <v>540</v>
+        <v>604</v>
       </c>
       <c r="U45" t="s">
-        <v>541</v>
-      </c>
-      <c r="V45" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W45" t="s">
         <v>2</v>
       </c>
       <c r="X45" t="s">
-        <v>585</v>
+        <v>697</v>
       </c>
       <c r="AA45" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="AB45" t="s">
-        <v>593</v>
+        <v>716</v>
       </c>
       <c r="AC45" t="s">
-        <v>598</v>
+        <v>721</v>
       </c>
     </row>
     <row r="46" spans="1:29">
@@ -5773,73 +6145,879 @@
         <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D46" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E46" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="F46" t="s">
-        <v>174</v>
+        <v>272</v>
       </c>
       <c r="G46" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H46" t="s">
-        <v>279</v>
+        <v>325</v>
       </c>
       <c r="J46" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="K46" t="s">
-        <v>348</v>
+        <v>410</v>
       </c>
       <c r="L46" t="s">
-        <v>392</v>
+        <v>464</v>
       </c>
       <c r="M46" t="s">
-        <v>437</v>
+        <v>519</v>
       </c>
       <c r="N46" t="s">
-        <v>438</v>
+        <v>530</v>
       </c>
       <c r="O46" t="s">
-        <v>439</v>
+        <v>532</v>
       </c>
       <c r="P46" t="s">
-        <v>442</v>
+        <v>539</v>
       </c>
       <c r="Q46" t="s">
-        <v>448</v>
+        <v>545</v>
       </c>
       <c r="R46" t="s">
-        <v>497</v>
+        <v>590</v>
       </c>
       <c r="S46" t="s">
-        <v>504</v>
+        <v>615</v>
       </c>
       <c r="U46" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="W46" t="s">
         <v>2</v>
       </c>
       <c r="X46" t="s">
-        <v>586</v>
+        <v>698</v>
       </c>
       <c r="AA46" t="s">
-        <v>448</v>
+        <v>545</v>
       </c>
       <c r="AB46" t="s">
+        <v>716</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29">
+      <c r="A47" t="s">
+        <v>74</v>
+      </c>
+      <c r="B47" t="s">
+        <v>129</v>
+      </c>
+      <c r="C47" t="s">
+        <v>139</v>
+      </c>
+      <c r="D47" t="s">
+        <v>185</v>
+      </c>
+      <c r="E47" t="s">
+        <v>234</v>
+      </c>
+      <c r="F47" t="s">
+        <v>273</v>
+      </c>
+      <c r="G47" t="s">
+        <v>279</v>
+      </c>
+      <c r="H47" t="s">
+        <v>326</v>
+      </c>
+      <c r="J47" t="s">
+        <v>365</v>
+      </c>
+      <c r="K47" t="s">
+        <v>411</v>
+      </c>
+      <c r="L47" t="s">
+        <v>465</v>
+      </c>
+      <c r="M47" t="s">
+        <v>520</v>
+      </c>
+      <c r="N47" t="s">
+        <v>530</v>
+      </c>
+      <c r="O47" t="s">
+        <v>532</v>
+      </c>
+      <c r="P47" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>541</v>
+      </c>
+      <c r="R47" t="s">
+        <v>591</v>
+      </c>
+      <c r="S47" t="s">
+        <v>615</v>
+      </c>
+      <c r="U47" t="s">
+        <v>280</v>
+      </c>
+      <c r="W47" t="s">
+        <v>2</v>
+      </c>
+      <c r="X47" t="s">
+        <v>699</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>541</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>716</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29">
+      <c r="A48" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" t="s">
+        <v>139</v>
+      </c>
+      <c r="D48" t="s">
+        <v>186</v>
+      </c>
+      <c r="E48" t="s">
+        <v>235</v>
+      </c>
+      <c r="F48" t="s">
+        <v>274</v>
+      </c>
+      <c r="G48" t="s">
+        <v>279</v>
+      </c>
+      <c r="H48" t="s">
+        <v>327</v>
+      </c>
+      <c r="I48" t="s">
+        <v>359</v>
+      </c>
+      <c r="J48" t="s">
+        <v>364</v>
+      </c>
+      <c r="K48" t="s">
+        <v>412</v>
+      </c>
+      <c r="L48" t="s">
+        <v>466</v>
+      </c>
+      <c r="M48" t="s">
+        <v>521</v>
+      </c>
+      <c r="N48" t="s">
+        <v>531</v>
+      </c>
+      <c r="O48" t="s">
+        <v>533</v>
+      </c>
+      <c r="P48" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>542</v>
+      </c>
+      <c r="R48" t="s">
+        <v>592</v>
+      </c>
+      <c r="S48" t="s">
+        <v>615</v>
+      </c>
+      <c r="T48" t="s">
+        <v>645</v>
+      </c>
+      <c r="U48" t="s">
+        <v>653</v>
+      </c>
+      <c r="V48" t="s">
+        <v>653</v>
+      </c>
+      <c r="W48" t="s">
+        <v>2</v>
+      </c>
+      <c r="X48" t="s">
+        <v>700</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>542</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>716</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29">
+      <c r="A49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B49" t="s">
+        <v>131</v>
+      </c>
+      <c r="C49" t="s">
+        <v>139</v>
+      </c>
+      <c r="D49" t="s">
+        <v>187</v>
+      </c>
+      <c r="E49" t="s">
+        <v>236</v>
+      </c>
+      <c r="F49" t="s">
+        <v>275</v>
+      </c>
+      <c r="G49" t="s">
+        <v>279</v>
+      </c>
+      <c r="H49" t="s">
+        <v>328</v>
+      </c>
+      <c r="I49" t="s">
+        <v>360</v>
+      </c>
+      <c r="J49" t="s">
+        <v>364</v>
+      </c>
+      <c r="K49" t="s">
+        <v>413</v>
+      </c>
+      <c r="L49" t="s">
+        <v>467</v>
+      </c>
+      <c r="M49" t="s">
+        <v>522</v>
+      </c>
+      <c r="N49" t="s">
+        <v>531</v>
+      </c>
+      <c r="O49" t="s">
+        <v>533</v>
+      </c>
+      <c r="P49" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>542</v>
+      </c>
+      <c r="R49" t="s">
         <v>593</v>
       </c>
-      <c r="AC46" t="s">
+      <c r="S49" t="s">
+        <v>615</v>
+      </c>
+      <c r="T49" t="s">
+        <v>646</v>
+      </c>
+      <c r="U49" t="s">
+        <v>653</v>
+      </c>
+      <c r="V49" t="s">
+        <v>653</v>
+      </c>
+      <c r="W49" t="s">
+        <v>2</v>
+      </c>
+      <c r="X49" t="s">
+        <v>701</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>542</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>718</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29">
+      <c r="A50" t="s">
+        <v>77</v>
+      </c>
+      <c r="B50" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" t="s">
+        <v>139</v>
+      </c>
+      <c r="D50" t="s">
+        <v>188</v>
+      </c>
+      <c r="E50" t="s">
+        <v>228</v>
+      </c>
+      <c r="F50" t="s">
+        <v>276</v>
+      </c>
+      <c r="G50" t="s">
+        <v>279</v>
+      </c>
+      <c r="H50" t="s">
+        <v>329</v>
+      </c>
+      <c r="I50" t="s">
+        <v>361</v>
+      </c>
+      <c r="J50" t="s">
+        <v>364</v>
+      </c>
+      <c r="K50" t="s">
+        <v>414</v>
+      </c>
+      <c r="L50" t="s">
+        <v>468</v>
+      </c>
+      <c r="M50" t="s">
+        <v>523</v>
+      </c>
+      <c r="N50" t="s">
+        <v>531</v>
+      </c>
+      <c r="O50" t="s">
+        <v>533</v>
+      </c>
+      <c r="P50" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>542</v>
+      </c>
+      <c r="R50" t="s">
+        <v>594</v>
+      </c>
+      <c r="S50" t="s">
+        <v>615</v>
+      </c>
+      <c r="T50" t="s">
+        <v>647</v>
+      </c>
+      <c r="U50" t="s">
+        <v>653</v>
+      </c>
+      <c r="V50" t="s">
+        <v>653</v>
+      </c>
+      <c r="W50" t="s">
+        <v>2</v>
+      </c>
+      <c r="X50" t="s">
+        <v>702</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>542</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>719</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29">
+      <c r="A51" t="s">
+        <v>78</v>
+      </c>
+      <c r="B51" t="s">
+        <v>133</v>
+      </c>
+      <c r="C51" t="s">
+        <v>139</v>
+      </c>
+      <c r="D51" t="s">
+        <v>189</v>
+      </c>
+      <c r="E51" t="s">
+        <v>237</v>
+      </c>
+      <c r="F51" t="s">
+        <v>214</v>
+      </c>
+      <c r="G51" t="s">
+        <v>279</v>
+      </c>
+      <c r="H51" t="s">
+        <v>330</v>
+      </c>
+      <c r="J51" t="s">
+        <v>365</v>
+      </c>
+      <c r="K51" t="s">
+        <v>415</v>
+      </c>
+      <c r="L51" t="s">
+        <v>469</v>
+      </c>
+      <c r="M51" t="s">
+        <v>524</v>
+      </c>
+      <c r="N51" t="s">
+        <v>530</v>
+      </c>
+      <c r="O51" t="s">
+        <v>532</v>
+      </c>
+      <c r="P51" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>541</v>
+      </c>
+      <c r="R51" t="s">
+        <v>595</v>
+      </c>
+      <c r="S51" t="s">
+        <v>610</v>
+      </c>
+      <c r="U51" t="s">
+        <v>280</v>
+      </c>
+      <c r="W51" t="s">
+        <v>2</v>
+      </c>
+      <c r="X51" t="s">
+        <v>703</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>541</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>716</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29">
+      <c r="A52" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" t="s">
+        <v>134</v>
+      </c>
+      <c r="C52" t="s">
+        <v>139</v>
+      </c>
+      <c r="D52" t="s">
+        <v>190</v>
+      </c>
+      <c r="E52" t="s">
+        <v>238</v>
+      </c>
+      <c r="F52" t="s">
+        <v>270</v>
+      </c>
+      <c r="G52" t="s">
+        <v>279</v>
+      </c>
+      <c r="H52" t="s">
+        <v>331</v>
+      </c>
+      <c r="I52" t="s">
+        <v>344</v>
+      </c>
+      <c r="J52" t="s">
+        <v>365</v>
+      </c>
+      <c r="K52" t="s">
+        <v>416</v>
+      </c>
+      <c r="L52" t="s">
+        <v>470</v>
+      </c>
+      <c r="M52" t="s">
+        <v>525</v>
+      </c>
+      <c r="O52" t="s">
+        <v>533</v>
+      </c>
+      <c r="P52" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>542</v>
+      </c>
+      <c r="R52" t="s">
+        <v>596</v>
+      </c>
+      <c r="S52" t="s">
+        <v>604</v>
+      </c>
+      <c r="T52" t="s">
+        <v>648</v>
+      </c>
+      <c r="U52" t="s">
+        <v>653</v>
+      </c>
+      <c r="V52" t="s">
+        <v>653</v>
+      </c>
+      <c r="W52" t="s">
+        <v>2</v>
+      </c>
+      <c r="X52" t="s">
+        <v>704</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>542</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>717</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29">
+      <c r="A53" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" t="s">
+        <v>135</v>
+      </c>
+      <c r="C53" t="s">
+        <v>139</v>
+      </c>
+      <c r="D53" t="s">
+        <v>191</v>
+      </c>
+      <c r="E53" t="s">
+        <v>239</v>
+      </c>
+      <c r="F53" t="s">
+        <v>277</v>
+      </c>
+      <c r="G53" t="s">
+        <v>279</v>
+      </c>
+      <c r="H53" t="s">
+        <v>332</v>
+      </c>
+      <c r="I53" t="s">
+        <v>344</v>
+      </c>
+      <c r="J53" t="s">
+        <v>365</v>
+      </c>
+      <c r="K53" t="s">
+        <v>417</v>
+      </c>
+      <c r="L53" t="s">
+        <v>471</v>
+      </c>
+      <c r="M53" t="s">
+        <v>526</v>
+      </c>
+      <c r="O53" t="s">
+        <v>533</v>
+      </c>
+      <c r="P53" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>542</v>
+      </c>
+      <c r="R53" t="s">
+        <v>597</v>
+      </c>
+      <c r="S53" t="s">
+        <v>604</v>
+      </c>
+      <c r="T53" t="s">
+        <v>649</v>
+      </c>
+      <c r="U53" t="s">
+        <v>653</v>
+      </c>
+      <c r="V53" t="s">
+        <v>653</v>
+      </c>
+      <c r="W53" t="s">
+        <v>2</v>
+      </c>
+      <c r="X53" t="s">
+        <v>705</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>542</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>717</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29">
+      <c r="A54" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54" t="s">
+        <v>139</v>
+      </c>
+      <c r="D54" t="s">
+        <v>192</v>
+      </c>
+      <c r="E54" t="s">
+        <v>240</v>
+      </c>
+      <c r="F54" t="s">
+        <v>196</v>
+      </c>
+      <c r="G54" t="s">
+        <v>279</v>
+      </c>
+      <c r="H54" t="s">
+        <v>333</v>
+      </c>
+      <c r="I54" t="s">
+        <v>362</v>
+      </c>
+      <c r="J54" t="s">
+        <v>364</v>
+      </c>
+      <c r="K54" t="s">
+        <v>418</v>
+      </c>
+      <c r="L54" t="s">
+        <v>472</v>
+      </c>
+      <c r="M54" t="s">
+        <v>527</v>
+      </c>
+      <c r="N54" t="s">
+        <v>531</v>
+      </c>
+      <c r="O54" t="s">
+        <v>533</v>
+      </c>
+      <c r="P54" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>542</v>
+      </c>
+      <c r="R54" t="s">
         <v>598</v>
+      </c>
+      <c r="S54" t="s">
+        <v>615</v>
+      </c>
+      <c r="T54" t="s">
+        <v>650</v>
+      </c>
+      <c r="U54" t="s">
+        <v>653</v>
+      </c>
+      <c r="V54" t="s">
+        <v>653</v>
+      </c>
+      <c r="W54" t="s">
+        <v>2</v>
+      </c>
+      <c r="X54" t="s">
+        <v>706</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>542</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>718</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29">
+      <c r="A55" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" t="s">
+        <v>137</v>
+      </c>
+      <c r="C55" t="s">
+        <v>139</v>
+      </c>
+      <c r="D55" t="s">
+        <v>193</v>
+      </c>
+      <c r="E55" t="s">
+        <v>241</v>
+      </c>
+      <c r="F55" t="s">
+        <v>221</v>
+      </c>
+      <c r="G55" t="s">
+        <v>279</v>
+      </c>
+      <c r="H55" t="s">
+        <v>334</v>
+      </c>
+      <c r="I55" t="s">
+        <v>344</v>
+      </c>
+      <c r="J55" t="s">
+        <v>364</v>
+      </c>
+      <c r="K55" t="s">
+        <v>419</v>
+      </c>
+      <c r="L55" t="s">
+        <v>473</v>
+      </c>
+      <c r="M55" t="s">
+        <v>528</v>
+      </c>
+      <c r="N55" t="s">
+        <v>531</v>
+      </c>
+      <c r="O55" t="s">
+        <v>533</v>
+      </c>
+      <c r="P55" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>542</v>
+      </c>
+      <c r="R55" t="s">
+        <v>599</v>
+      </c>
+      <c r="S55" t="s">
+        <v>615</v>
+      </c>
+      <c r="T55" t="s">
+        <v>651</v>
+      </c>
+      <c r="U55" t="s">
+        <v>653</v>
+      </c>
+      <c r="V55" t="s">
+        <v>280</v>
+      </c>
+      <c r="W55" t="s">
+        <v>2</v>
+      </c>
+      <c r="X55" t="s">
+        <v>707</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>542</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>718</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="56" spans="1:29">
+      <c r="A56" t="s">
+        <v>83</v>
+      </c>
+      <c r="B56" t="s">
+        <v>138</v>
+      </c>
+      <c r="C56" t="s">
+        <v>139</v>
+      </c>
+      <c r="D56" t="s">
+        <v>194</v>
+      </c>
+      <c r="E56" t="s">
+        <v>242</v>
+      </c>
+      <c r="F56" t="s">
+        <v>278</v>
+      </c>
+      <c r="G56" t="s">
+        <v>279</v>
+      </c>
+      <c r="H56" t="s">
+        <v>335</v>
+      </c>
+      <c r="I56" t="s">
+        <v>363</v>
+      </c>
+      <c r="J56" t="s">
+        <v>364</v>
+      </c>
+      <c r="K56" t="s">
+        <v>420</v>
+      </c>
+      <c r="L56" t="s">
+        <v>474</v>
+      </c>
+      <c r="M56" t="s">
+        <v>529</v>
+      </c>
+      <c r="N56" t="s">
+        <v>531</v>
+      </c>
+      <c r="O56" t="s">
+        <v>533</v>
+      </c>
+      <c r="P56" t="s">
+        <v>536</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>542</v>
+      </c>
+      <c r="R56" t="s">
+        <v>600</v>
+      </c>
+      <c r="S56" t="s">
+        <v>615</v>
+      </c>
+      <c r="T56" t="s">
+        <v>652</v>
+      </c>
+      <c r="U56" t="s">
+        <v>653</v>
+      </c>
+      <c r="V56" t="s">
+        <v>280</v>
+      </c>
+      <c r="W56" t="s">
+        <v>2</v>
+      </c>
+      <c r="X56" t="s">
+        <v>708</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>542</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>719</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>722</v>
       </c>
     </row>
   </sheetData>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,12 +991,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>75553</t>
+          <t>118108</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>73366</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DANIEL ALEJANDRO</t>
+          <t>JOSE ANTONIO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROMERO </t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>QUIJADA</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6863466296</t>
+          <t>6865298916</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NERVA 118</t>
+          <t>HACIENDA SAN ROQUE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1041,20 +1041,24 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25-06-2003</t>
+          <t>03-07-1996</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>DANIELQUIJADA2532@GMAIL.COM</t>
+          <t>J.ANTONIO.CRUZ.CARDENAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>28-02-2022 17:04:02</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>23-08-2022 19:27:05</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1072,17 +1076,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-02-2026 14:23:09</t>
+          <t>17-02-2026 14:14:53</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-02-2026 14:22:48</t>
+          <t>17-02-2026 14:13:03</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1092,7 +1096,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1102,7 +1106,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26170522012560001648</t>
+          <t>26170522429040002526</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1126,12 +1130,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>118108</t>
+          <t>183590</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>81097</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1141,17 +1145,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO</t>
+          <t xml:space="preserve">BRIAN </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1161,12 +1165,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6865298916</t>
+          <t>6864295199</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HACIENDA SAN ROQUE</t>
+          <t>GALATEA 245</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1176,24 +1180,20 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>03-07-1996</t>
+          <t>18-12-1993</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>J.ANTONIO.CRUZ.CARDENAS@GMAIL.COM</t>
+          <t>BRIAN.GONZALEZ@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>23-08-2022 19:27:05</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>11-07-2023 17:00:27</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1211,17 +1211,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>17-02-2026 14:14:53</t>
+          <t>02-02-2026 15:48:32</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>17-02-2026 14:13:03</t>
+          <t>02-02-2026 15:47:32</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26170522429040002526</t>
+          <t>26170522015130001656</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1253,24 +1253,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>183590</t>
+          <t>75553</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81097</t>
+          <t>73366</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIAN </t>
+          <t>DANIEL ALEJANDRO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t xml:space="preserve">ROMERO </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>QUIJADA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6864295199</t>
+          <t>6863466296</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GALATEA 245</t>
+          <t>NERVA 118</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1315,17 +1315,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>18-12-1993</t>
+          <t>25-06-2003</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BRIAN.GONZALEZ@UABC.EDU.MX</t>
+          <t>DANIELQUIJADA2532@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>11-07-2023 17:00:27</t>
+          <t>28-02-2022 17:04:02</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-02-2026 15:48:32</t>
+          <t>02-02-2026 14:23:09</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-02-2026 15:47:32</t>
+          <t>02-02-2026 14:22:48</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26170522015130001656</t>
+          <t>26170522012560001648</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1388,24 +1388,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>339800</t>
+          <t>338245</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17618</t>
+          <t>16063</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BRIAN MIGUEL</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AISPURO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t>COSSIO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,75 +1435,67 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6862643137</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6862641454</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>13-12-1998</t>
+          <t>28-07-1999</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PAISPURO1948@GMAIL.COM</t>
+          <t>FM7098082@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>01-02-2026 12:02:45</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>27-01-2026 05:22:15</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>01-02-2026 12:08:41</t>
+          <t>17-02-2026 05:01:55</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>01-02-2026 12:07:33</t>
-        </is>
-      </c>
+          <t>17-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1511,36 +1503,44 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26170521990600001608</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>26170522413330002499</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Mariana Daniela Romero Cruz</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>339895</t>
+          <t>339800</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17713</t>
+          <t>17618</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>JULIO ALEJANDRO</t>
+          <t>BRIAN MIGUEL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>AISPURO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1570,10 +1570,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6867371621</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6862643137</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1581,56 +1585,60 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>04-09-2001</t>
+          <t>13-12-1998</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BEJARANOJULIO10@GMAIL.COM</t>
+          <t>PAISPURO1948@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-02-2026 08:04:32</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>01-02-2026 12:02:45</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-02-2026 07:27:31</t>
+          <t>01-02-2026 12:08:41</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>01-02-2026 12:07:33</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1638,44 +1646,36 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26170522032100001708</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170521990600001608</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>339961</t>
+          <t>339895</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17779</t>
+          <t>17713</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1685,17 +1685,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CELINA</t>
+          <t>JULIO ALEJANDRO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">REYES </t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1705,28 +1705,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6864237570</t>
+          <t>6867371621</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>25-06-1996</t>
+          <t>04-09-2001</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>EYLECELENA25@GMAIL.COM</t>
+          <t>BEJARANOJULIO10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-02-2026 09:30:33</t>
+          <t>02-02-2026 08:04:32</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>12-02-2026 08:16:52</t>
+          <t>03-02-2026 07:27:31</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26170522288990002257</t>
+          <t>26170522032100001708</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1805,12 +1805,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>340035</t>
+          <t>219990</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17853</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1820,17 +1820,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KITZIA AILIME</t>
+          <t xml:space="preserve">DIANA CRISTINA </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MAGALLON</t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t xml:space="preserve">HIGUERA </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1840,14 +1840,10 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6862541870</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>CASA</t>
-        </is>
-      </c>
+          <t>6863372459</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1855,60 +1851,56 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>17-03-2003</t>
+          <t>01-03-1990</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>KITZIAMAGALON@GMAIL.COM</t>
+          <t>DIANA90HIGUERA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-02-2026 10:57:19</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>15-02-2024 09:29:52</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-02-2026 11:00:49</t>
+          <t>20-02-2026 16:08:52</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>02-02-2026 11:00:21</t>
-        </is>
-      </c>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1916,14 +1908,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26170522006040001630</t>
+          <t>26170522529480002736</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1940,12 +1932,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>340108</t>
+          <t>339961</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1955,17 +1947,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t>CELINA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t xml:space="preserve">REYES </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1975,75 +1967,67 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6866740223</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6864237570</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>11-02-2010</t>
+          <t>25-06-1996</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>HIELO12CV@GMAIL.COM</t>
+          <t>EYLECELENA25@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-02-2026 12:53:45</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>02-02-2026 09:30:33</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>04-02-2026 13:54:22</t>
+          <t>12-02-2026 08:16:52</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>04-02-2026 13:53:23</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2051,7 +2035,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26170522075080001810</t>
+          <t>26170522288990002257</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2066,12 +2050,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2083,12 +2067,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>338245</t>
+          <t>340472</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>18290</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2098,17 +2082,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t xml:space="preserve">ELIZABETH </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>COSSIO</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2118,7 +2102,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6862641454</t>
+          <t>6861256955</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2129,17 +2113,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>28-07-1999</t>
+          <t>16-05-1978</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FM7098082@GMAIL.COM</t>
+          <t>ELYMORALESVALENZUELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>27-01-2026 05:22:15</t>
+          <t>03-02-2026 08:35:58</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2154,28 +2138,28 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>17-02-2026 05:01:55</t>
+          <t>03-02-2026 08:37:42</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>03-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -2186,22 +2170,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26170522413330002499</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Mariana Daniela Romero Cruz</t>
-        </is>
-      </c>
+          <t>26170522033950001717</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2218,12 +2194,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340472</t>
+          <t>340249</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18290</t>
+          <t>18067</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2233,17 +2209,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIZABETH </t>
+          <t xml:space="preserve">ANABEL </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t xml:space="preserve">DEARA </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t xml:space="preserve">ARCOS </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2253,67 +2229,75 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6861256955</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>6863957626</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>BONIFACIO AVILES 3133</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>16-05-1978</t>
+          <t>26-01-1995</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ELYMORALESVALENZUELA@GMAIL.COM</t>
+          <t>ANABELDEARA260195@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-02-2026 08:35:58</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 16:10:16</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-02-2026 08:37:42</t>
+          <t>02-02-2026 16:15:39</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:14:45</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2321,19 +2305,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26170522033950001717</t>
+          <t>26170522016110001661</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2345,12 +2329,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>340750</t>
+          <t>339095</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2360,17 +2344,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ARMANDO</t>
+          <t>KARLA ELDA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTIZ </t>
+          <t>ARIZMENDI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2380,67 +2364,75 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6863928150</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6862168895</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>CALLE JAEN ESTE 1637</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>23-02-1988</t>
+          <t>01-08-1984</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>MENTECUERPOYNUTRICION@HOTMAIL.COM</t>
+          <t>KARIZMENDI2902@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-02-2026 17:50:24</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>29-01-2026 17:00:05</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-02-2026 17:52:56</t>
+          <t>02-02-2026 11:21:22</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>28-02-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>31-01-2026 14:54:56</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2448,14 +2440,18 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26170522051130001755</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+          <t>26170522006780001632</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2472,12 +2468,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>340249</t>
+          <t>339521</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18067</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2487,17 +2483,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANABEL </t>
+          <t>LIZY NAILY</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEARA </t>
+          <t>BRICEÑO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARCOS </t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2507,32 +2503,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6863957626</t>
+          <t>6863079480</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>BONIFACIO AVILES 3133</t>
+          <t>CORULLON 193</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>26-01-1995</t>
+          <t>19-10-2002</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ANABELDEARA260195@GMAIL.COM</t>
+          <t>LIZY.NAILY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-02-2026 16:10:16</t>
+          <t>30-01-2026 20:49:36</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2553,7 +2549,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-02-2026 16:15:39</t>
+          <t>02-02-2026 20:17:46</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2563,7 +2559,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-02-2026 16:14:45</t>
+          <t>02-02-2026 20:16:52</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2583,11 +2579,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26170522016110001661</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>26170522022960001684</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>499</t>
@@ -2595,24 +2599,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>339095</t>
+          <t>340181</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>17999</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2622,17 +2626,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KARLA ELDA</t>
+          <t>SAHIRA YOMAHIRA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ARIZMENDI</t>
+          <t xml:space="preserve">BAJO </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PIZANO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2642,12 +2646,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6862168895</t>
+          <t>6862091543</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CALLE JAEN ESTE 1637</t>
+          <t>CASTILLEJA 1818</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2657,17 +2661,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>01-08-1984</t>
+          <t>13-04-2003</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>KARIZMENDI2902@GMAIL.COM</t>
+          <t>CUARTO.SAJIRA@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>29-01-2026 17:00:05</t>
+          <t>02-02-2026 14:35:58</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2678,7 +2682,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2688,17 +2692,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-02-2026 11:21:22</t>
+          <t>02-02-2026 14:42:26</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>31-01-2026 14:54:56</t>
+          <t>02-02-2026 14:40:53</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2708,7 +2712,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2718,14 +2722,10 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26170522006780001632</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26170522013230001649</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2746,12 +2746,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>339521</t>
+          <t>340750</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LIZY NAILY</t>
+          <t>ARMANDO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BRICEÑO</t>
+          <t xml:space="preserve">ORTIZ </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2781,75 +2781,67 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6863079480</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>CORULLON 193</t>
-        </is>
-      </c>
+          <t>6863928150</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19-10-2002</t>
+          <t>23-02-1988</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>LIZY.NAILY@GMAIL.COM</t>
+          <t>MENTECUERPOYNUTRICION@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>30-01-2026 20:49:36</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>03-02-2026 17:50:24</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-02-2026 20:17:46</t>
+          <t>03-02-2026 17:52:56</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>02-02-2026 20:16:52</t>
-        </is>
-      </c>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2857,32 +2849,24 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26170522022960001684</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522051130001755</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3008,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341297</t>
+          <t>340334</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19115</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3039,17 +3023,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NATALIE</t>
+          <t>EMILY SOFIA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ARRIAGA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3059,12 +3043,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6861344365</t>
+          <t>6864702297</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORTALES </t>
+          <t>AV RIOJA 160</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3074,48 +3058,52 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>26-11-2004</t>
+          <t>02-02-2006</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>NATALIE.RODRIGUEZ@UABC.EDU.MX</t>
+          <t>EMILY.ARRIAGA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>05-02-2026 13:00:16</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>02-02-2026 18:06:05</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>10-02-2026 16:55:49</t>
+          <t>05-02-2026 18:50:09</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>10-02-2026 16:54:34</t>
+          <t>05-02-2026 18:49:20</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3135,7 +3123,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26170522238010002133</t>
+          <t>26170522116880001895</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3150,7 +3138,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3167,12 +3155,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>341467</t>
+          <t>341297</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>19115</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3182,17 +3170,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ADOLFO</t>
+          <t>NATALIE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ALBISO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BARAJAS</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3202,32 +3190,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6862300377</t>
+          <t>6861344365</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>NORUEGA 2636</t>
+          <t xml:space="preserve">PORTALES </t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>12-11-1996</t>
+          <t>26-11-2004</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ADOLFO_19962016@HOTMAIL.COM</t>
+          <t>NATALIE.RODRIGUEZ@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>05-02-2026 21:05:50</t>
+          <t>05-02-2026 13:00:16</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3248,17 +3236,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>05-02-2026 21:13:45</t>
+          <t>10-02-2026 16:55:49</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>05-02-2026 21:13:16</t>
+          <t>10-02-2026 16:54:34</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3278,11 +3266,19 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26170522120570001923</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>26170522238010002133</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>499</t>
@@ -3302,12 +3298,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>340181</t>
+          <t>341056</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17999</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3317,17 +3313,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAHIRA YOMAHIRA</t>
+          <t xml:space="preserve">EMMANUEL </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAJO </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PIZANO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3337,75 +3333,67 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6862091543</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>CASTILLEJA 1818</t>
-        </is>
-      </c>
+          <t>6862034611</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13-04-2003</t>
+          <t>03-09-2005</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CUARTO.SAJIRA@ICLOUD.COM</t>
+          <t>EMMANUEL.PEREZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-02-2026 14:35:58</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>04-02-2026 15:54:17</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-02-2026 14:42:26</t>
+          <t>04-02-2026 15:57:00</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>02-02-2026 14:40:53</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3413,14 +3401,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26170522013230001649</t>
+          <t>26170522078420001815</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3437,12 +3425,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>340334</t>
+          <t>341467</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3452,17 +3440,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EMILY SOFIA</t>
+          <t>ADOLFO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ARRIAGA</t>
+          <t>ALBISO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>BARAJAS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3472,57 +3460,53 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6864702297</t>
+          <t>6862300377</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AV RIOJA 160</t>
+          <t>NORUEGA 2636</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>02-02-2006</t>
+          <t>12-11-1996</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>EMILY.ARRIAGA@GMAIL.COM</t>
+          <t>ADOLFO_19962016@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-02-2026 18:06:05</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 21:05:50</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>05-02-2026 18:50:09</t>
+          <t>05-02-2026 21:13:45</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3532,7 +3516,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>05-02-2026 18:49:20</t>
+          <t>05-02-2026 21:13:16</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3552,22 +3536,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26170522116880001895</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522120570001923</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3584,12 +3560,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>340183</t>
+          <t>341189</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18001</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3599,17 +3575,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LEYLANI MIRANDA</t>
+          <t>IVAN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PIZANO</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3619,24 +3595,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6863558685</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>6861965073</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1RA MORELOS 19</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>03-11-2011</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>22-09-2000</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>IVAN.RODRIGUEZ@GMAIL.COM</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>02-02-2026 14:41:17</t>
+          <t>04-02-2026 20:27:47</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3657,17 +3641,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-02-2026 14:46:51</t>
+          <t>04-02-2026 20:33:43</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>02-02-2026 14:45:55</t>
+          <t>04-02-2026 20:33:11</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3687,7 +3671,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26170522013390001650</t>
+          <t>26170522089840001847</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3699,24 +3683,24 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>340231</t>
+          <t>341295</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3726,17 +3710,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ELLIOT SAMUEL</t>
+          <t>FERNANDA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3746,32 +3730,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6866507552</t>
+          <t>6865781520</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AV GOLETA 1807</t>
+          <t>POTALES</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>09-08-1998</t>
+          <t>13-10-2006</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ELLIOT.MORA@UABC.COM.MX</t>
+          <t>FR65671@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-02-2026 15:50:44</t>
+          <t>05-02-2026 12:58:08</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3792,17 +3776,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>02-02-2026 15:56:47</t>
+          <t>10-02-2026 16:59:22</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>02-02-2026 15:54:59</t>
+          <t>10-02-2026 16:58:27</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3822,11 +3806,19 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26170522015420001658</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+          <t>26170522238110002134</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>499</t>
@@ -3846,12 +3838,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>341056</t>
+          <t>322246</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>19185</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3861,17 +3853,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMMANUEL </t>
+          <t>ZAIRA RAMIREZ CASTRO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3881,67 +3873,75 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6862034611</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>6861234537</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LA BARRERA 323 </t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>03-09-2005</t>
+          <t>07-10-1997</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>EMMANUEL.PEREZ@GMAIL.COM</t>
+          <t>ZAIRA071097@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>04-02-2026 15:54:17</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-11-2025 16:07:36</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>04-02-2026 15:57:00</t>
+          <t>02-02-2026 17:50:01</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>02-02-2026 17:48:27</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3949,14 +3949,18 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26170522078420001815</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
+          <t>26170522019270001671</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3973,12 +3977,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>341189</t>
+          <t>340183</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3988,17 +3992,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IVAN</t>
+          <t>LEYLANI MIRANDA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>PIZANO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4008,32 +4012,24 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6861965073</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1RA MORELOS 19</t>
-        </is>
-      </c>
+          <t>6863558685</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>22-09-2000</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>IVAN.RODRIGUEZ@GMAIL.COM</t>
-        </is>
-      </c>
+          <t>03-11-2011</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>04-02-2026 20:27:47</t>
+          <t>02-02-2026 14:41:17</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4054,17 +4050,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>04-02-2026 20:33:43</t>
+          <t>02-02-2026 14:46:51</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>04-02-2026 20:33:11</t>
+          <t>02-02-2026 14:45:55</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4084,7 +4080,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26170522089840001847</t>
+          <t>26170522013390001650</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -4096,24 +4092,24 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>342676</t>
+          <t>340231</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>18049</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4123,17 +4119,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VIVIAN DENIISSE</t>
+          <t>ELLIOT SAMUEL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MELERO</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4143,32 +4139,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6644940465</t>
+          <t>6866507552</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>AV GOLETA 1807</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>19-06-1981</t>
+          <t>09-08-1998</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>VIVIANDEFELIX@GMAIL.COM</t>
+          <t>ELLIOT.MORA@UABC.COM.MX</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>10-02-2026 15:37:05</t>
+          <t>02-02-2026 15:50:44</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4189,17 +4185,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>10-02-2026 15:40:14</t>
+          <t>02-02-2026 15:56:47</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>10-02-2026 15:39:43</t>
+          <t>02-02-2026 15:54:59</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4219,7 +4215,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26170522235040002127</t>
+          <t>26170522015420001658</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4243,12 +4239,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>341295</t>
+          <t>340035</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19113</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4258,17 +4254,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FERNANDA</t>
+          <t>KITZIA AILIME</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>MAGALLON</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4278,12 +4274,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6865781520</t>
+          <t>6862541870</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>POTALES</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4293,17 +4289,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>13-10-2006</t>
+          <t>17-03-2003</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>FR65671@GMAIL.COM</t>
+          <t>KITZIAMAGALON@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>05-02-2026 12:58:08</t>
+          <t>02-02-2026 10:57:19</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4324,17 +4320,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>10-02-2026 16:59:22</t>
+          <t>02-02-2026 11:00:49</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>10-02-2026 16:58:27</t>
+          <t>02-02-2026 11:00:21</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4354,19 +4350,11 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26170522238110002134</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522006040001630</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
           <t>499</t>
@@ -4374,24 +4362,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>341159</t>
+          <t>340108</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>18977</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4401,17 +4389,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DAVID ERNESTO</t>
+          <t>CHRISTIAN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4421,10 +4409,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6863409250</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6866740223</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4432,42 +4424,38 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>28-08-2011</t>
+          <t>11-02-2010</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>DAVID.ERNESTO@GMAIL.COM</t>
+          <t>HIELO12CV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>04-02-2026 19:08:30</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 12:53:45</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>04-02-2026 19:10:17</t>
+          <t>04-02-2026 13:54:22</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4475,13 +4463,21 @@
           <t>04-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>04-02-2026 13:53:23</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4489,19 +4485,27 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26170522087360001828</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
+          <t>26170522075080001810</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4513,12 +4517,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>322246</t>
+          <t>342142</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19185</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4528,17 +4532,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ZAIRA RAMIREZ CASTRO</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4548,14 +4552,10 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6861234537</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LA BARRERA 323 </t>
-        </is>
-      </c>
+          <t>6869453269</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4563,60 +4563,56 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>07-10-1997</t>
+          <t>19-04-2008</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ZAIRA071097@HOTMAIL.COM</t>
+          <t>VALMACIASSA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>05-11-2025 16:07:36</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>09-02-2026 12:49:49</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>02-02-2026 17:50:01</t>
+          <t>09-02-2026 12:51:58</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>02-02-2026 17:48:27</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4624,40 +4620,36 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26170522019270001671</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26170522190930002024</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342843</t>
+          <t>342494</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20660</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4667,17 +4659,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS </t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>TEJADA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BARAJAS</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4687,7 +4679,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6862437298</t>
+          <t>6867291381</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4697,22 +4689,22 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>01-09-1989</t>
+          <t>20-06-2005</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ERREDOS8@GMAIL.COM</t>
+          <t>MIGUELTEJADA317@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10-02-2026 19:36:54</t>
+          <t>09-02-2026 20:58:55</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4733,17 +4725,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>10-02-2026 19:46:13</t>
+          <t>09-02-2026 21:01:56</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>10-02-2026 19:40:58</t>
+          <t>09-02-2026 21:01:07</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4753,7 +4745,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4763,7 +4755,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26170522247630002151</t>
+          <t>26170522214500002093</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4787,12 +4779,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342857</t>
+          <t>342573</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4802,17 +4794,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>LOURDES RENE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">JIMENEZ </t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4822,32 +4814,32 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6861387777</t>
+          <t>6864162086</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>LAGO PAZCUARO SN</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>14-08-1972</t>
+          <t>21-09-1988</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>JORGEJIMENEZSOTO1994@GMAIL.COM</t>
+          <t>CAMPOSLULY0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10-02-2026 19:59:00</t>
+          <t>10-02-2026 10:01:09</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4868,7 +4860,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10-02-2026 20:04:31</t>
+          <t>10-02-2026 10:11:12</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4878,7 +4870,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>10-02-2026 20:04:01</t>
+          <t>10-02-2026 10:10:28</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4888,7 +4880,7 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
@@ -4898,7 +4890,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26170522248340002163</t>
+          <t>26170522227920002115</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4910,7 +4902,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Jose Luis Lopez Coronel</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4922,12 +4914,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342573</t>
+          <t>342851</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>20668</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4937,17 +4929,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LOURDES RENE</t>
+          <t xml:space="preserve">JOSE JAVIE </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">ZEPEDA </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4957,53 +4949,53 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6864162086</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>LAGO PAZCUARO SN</t>
-        </is>
-      </c>
+          <t>6863023309</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>21-09-1988</t>
+          <t>22-08-2003</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CAMPOSLULY0@GMAIL.COM</t>
+          <t>JV220803@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10-02-2026 10:01:09</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>10-02-2026 19:47:49</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>10-02-2026 10:11:12</t>
+          <t>10-02-2026 19:49:44</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -5011,21 +5003,13 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>10-02-2026 10:10:28</t>
-        </is>
-      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5033,36 +5017,36 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26170522227920002115</t>
+          <t>26170522247770002152</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Jose Luis Lopez Coronel</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342494</t>
+          <t>342293</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5072,17 +5056,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TEJADA</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>CORREA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5092,7 +5076,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6867291381</t>
+          <t>6864214771</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -5102,22 +5086,22 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>20-06-2005</t>
+          <t>10-08-2003</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>MIGUELTEJADA317@ICLOUD.COM</t>
+          <t>MORAERNESTO741@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-02-2026 20:58:55</t>
+          <t>09-02-2026 16:57:09</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -5138,7 +5122,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-02-2026 21:01:56</t>
+          <t>09-02-2026 17:02:55</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -5148,7 +5132,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>09-02-2026 21:01:07</t>
+          <t>09-02-2026 16:59:57</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5168,7 +5152,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26170522214500002093</t>
+          <t>26170522200440002040</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5192,12 +5176,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342142</t>
+          <t>342843</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5207,17 +5191,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t xml:space="preserve">CARLOS </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>BARAJAS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5227,67 +5211,75 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6869453269</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>6862437298</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>19-04-2008</t>
+          <t>01-09-1989</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>VALMACIASSA@GMAIL.COM</t>
+          <t>ERREDOS8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>09-02-2026 12:49:49</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 19:36:54</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>09-02-2026 12:51:58</t>
+          <t>10-02-2026 19:46:13</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>10-02-2026 19:40:58</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5295,36 +5287,36 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26170522190930002024</t>
+          <t>26170522247630002151</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>342293</t>
+          <t>343007</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20111</t>
+          <t>20824</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5334,17 +5326,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>SERGIO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>VILLARREAL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CORREA</t>
+          <t>ZEPEDA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5354,12 +5346,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6864214771</t>
+          <t>6864644967</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>DE LAS ESPADAS 61</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5369,17 +5361,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>10-08-2003</t>
+          <t>11-10-2001</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>MORAERNESTO741@GMAIL.COM</t>
+          <t>ZEPEDA111001@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>09-02-2026 16:57:09</t>
+          <t>11-02-2026 15:16:45</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5400,17 +5392,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>09-02-2026 17:02:55</t>
+          <t>11-02-2026 15:30:24</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>09-02-2026 16:59:57</t>
+          <t>11-02-2026 15:29:47</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5430,7 +5422,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26170522200440002040</t>
+          <t>26170522266490002208</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5442,24 +5434,24 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>342851</t>
+          <t>343401</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20668</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5469,17 +5461,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE JAVIE </t>
+          <t>CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t xml:space="preserve">ZEPEDA </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZEPEDA </t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5489,7 +5481,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6863023309</t>
+          <t>6862110739</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5500,17 +5492,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>22-08-2003</t>
+          <t>06-08-1987</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>JV220803@GMAIL.COM</t>
+          <t>ZEPEDACOTAC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>10-02-2026 19:47:49</t>
+          <t>12-02-2026 21:09:33</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5525,22 +5517,22 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>10-02-2026 19:49:44</t>
+          <t>12-02-2026 21:11:55</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -5557,14 +5549,14 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26170522247770002152</t>
+          <t>26170522306850002321</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5581,12 +5573,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>343007</t>
+          <t>341159</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5596,17 +5588,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SERGIO</t>
+          <t>DAVID ERNESTO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>VILLARREAL</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ZEPEDA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5616,14 +5608,10 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6864644967</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>DE LAS ESPADAS 61</t>
-        </is>
-      </c>
+          <t>6863409250</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5631,60 +5619,56 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>11-10-2001</t>
+          <t>28-08-2011</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ZEPEDA111001@GMAIL.COM</t>
+          <t>DAVID.ERNESTO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>11-02-2026 15:16:45</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>04-02-2026 19:08:30</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>11-02-2026 15:30:24</t>
+          <t>04-02-2026 19:10:17</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>11-02-2026 15:29:47</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5692,36 +5676,36 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26170522266490002208</t>
+          <t>26170522087360001828</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>343391</t>
+          <t>342857</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21208</t>
+          <t>20674</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5731,17 +5715,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>JOSE ENRIQUE</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">JIMENEZ </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5751,7 +5735,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6861914185</t>
+          <t>6861387777</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5766,17 +5750,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>02-01-2004</t>
+          <t>14-08-1972</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>JG747801@GMAIL.COM</t>
+          <t>JORGEJIMENEZSOTO1994@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>12-02-2026 19:39:05</t>
+          <t>10-02-2026 19:59:00</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5797,17 +5781,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>12-02-2026 19:42:59</t>
+          <t>10-02-2026 20:04:31</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>12-02-2026 19:42:26</t>
+          <t>10-02-2026 20:04:01</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5817,7 +5801,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5827,7 +5811,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26170522305280002308</t>
+          <t>26170522248340002163</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -5839,24 +5823,24 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>342495</t>
+          <t>340441</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>18259</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5866,17 +5850,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">NELSON </t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MARISCAL</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5886,10 +5870,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6861420567</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>6674121912</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5897,56 +5885,60 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>28-10-1996</t>
+          <t>07-10-2003</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>NELSON.1028@HOTMAIL.COM</t>
+          <t>FELIZLUISFERNANDO3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>09-02-2026 21:04:58</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 07:13:43</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>09-02-2026 21:06:43</t>
+          <t>03-02-2026 07:19:00</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>03-02-2026 07:18:37</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5954,36 +5946,36 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26170522214560002094</t>
+          <t>26170522031900001705</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>343401</t>
+          <t>340564</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21218</t>
+          <t>18382</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5993,17 +5985,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO</t>
+          <t>JOSE MANUEL</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZEPEDA </t>
+          <t>MONTOYA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>REA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6013,7 +6005,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6862110739</t>
+          <t>6865860740</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -6024,17 +6016,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>06-08-1987</t>
+          <t>27-12-1976</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ZEPEDACOTAC@GMAIL.COM</t>
+          <t>REA1628JOSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>12-02-2026 21:09:33</t>
+          <t>03-02-2026 13:24:47</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6049,22 +6041,22 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>12-02-2026 21:11:55</t>
+          <t>03-02-2026 13:26:26</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -6081,14 +6073,14 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26170522306850002321</t>
+          <t>26170522039620001735</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -6105,12 +6097,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>340441</t>
+          <t>343391</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6120,17 +6112,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>JOSE ENRIQUE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6140,7 +6132,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6674121912</t>
+          <t>6861914185</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -6155,17 +6147,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>07-10-2003</t>
+          <t>02-01-2004</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>FELIZLUISFERNANDO3@GMAIL.COM</t>
+          <t>JG747801@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>03-02-2026 07:13:43</t>
+          <t>12-02-2026 19:39:05</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -6186,17 +6178,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>03-02-2026 07:19:00</t>
+          <t>12-02-2026 19:42:59</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>03-02-2026 07:18:37</t>
+          <t>12-02-2026 19:42:26</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6216,7 +6208,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26170522031900001705</t>
+          <t>26170522305280002308</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6240,12 +6232,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>340564</t>
+          <t>340899</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>18717</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6255,17 +6247,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>JOSE MANUEL</t>
+          <t xml:space="preserve">YORLENI </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>REA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6275,67 +6267,75 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6865860740</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>6863226816</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>PRIVADA DUGAN DALI1129</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>27-12-1976</t>
+          <t>09-11-2000</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>REA1628JOSE@GMAIL.COM</t>
+          <t>YORPEREZ073@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>03-02-2026 13:24:47</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 08:51:30</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>03-02-2026 13:26:26</t>
+          <t>04-02-2026 08:59:01</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>04-02-2026 08:57:43</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6343,24 +6343,24 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26170522039620001735</t>
+          <t>26170522070070001794</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>342853</t>
+          <t>344019</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20670</t>
+          <t>21836</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6660,17 +6660,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DAMARIS KATHELEEN</t>
+          <t>ABRHAM ISACC</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>KETCHUL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6861330533</t>
+          <t>6861255888</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6691,17 +6691,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>26-02-2007</t>
+          <t>12-07-1992</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>DAMARISK.SLOPEZ@GMAIL.COM</t>
+          <t>ABRAHAM.SKET1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>10-02-2026 19:51:12</t>
+          <t>16-02-2026 11:31:00</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6716,28 +6716,28 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>10-02-2026 19:53:06</t>
+          <t>16-02-2026 11:32:22</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>10-05-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V47" t="inlineStr"/>
@@ -6748,36 +6748,36 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26170522247900002153</t>
+          <t>26170522385460002427</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>344362</t>
+          <t>342495</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>22179</t>
+          <t>20312</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6787,17 +6787,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDREA MICHELL </t>
+          <t xml:space="preserve">NELSON </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>URIBE</t>
+          <t>MARISCAL</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6807,79 +6807,67 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6863837971</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>HERENCIA 2338</t>
-        </is>
-      </c>
+          <t>6861420567</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>15-08-2000</t>
+          <t>28-10-1996</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ANDREAESTRADA1218@ICLOUD.COM</t>
+          <t>NELSON.1028@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>16-02-2026 21:04:29</t>
+          <t>09-02-2026 21:04:58</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>16-02-2026 21:14:42</t>
+          <t>09-02-2026 21:06:43</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>16-02-2026 21:12:23</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6887,19 +6875,19 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26170522411380002496</t>
+          <t>26170522214560002094</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6911,12 +6899,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>340899</t>
+          <t>344362</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18717</t>
+          <t>22179</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6926,17 +6914,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">YORLENI </t>
+          <t xml:space="preserve">ANDREA MICHELL </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>URIBE</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6946,12 +6934,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6863226816</t>
+          <t>6863837971</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>PRIVADA DUGAN DALI1129</t>
+          <t>HERENCIA 2338</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6961,20 +6949,24 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>09-11-2000</t>
+          <t>15-08-2000</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>YORPEREZ073@GMAIL.COM</t>
+          <t>ANDREAESTRADA1218@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>04-02-2026 08:51:30</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>16-02-2026 21:04:29</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6992,17 +6984,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>04-02-2026 08:59:01</t>
+          <t>16-02-2026 21:14:42</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>04-02-2026 08:57:43</t>
+          <t>16-02-2026 21:12:23</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7022,7 +7014,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26170522070070001794</t>
+          <t>26170522411380002496</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -7034,7 +7026,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7046,12 +7038,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>344864</t>
+          <t>345036</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22681</t>
+          <t>87201</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7061,17 +7053,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ELIAS ABDIEL</t>
+          <t>NORMA ALICIA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">MERCADO </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7081,39 +7073,35 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6865902031</t>
+          <t>6863291327</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>POMONA 2446</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>20-04-2005</t>
+          <t>03-11-1976</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ELIASMORENO052@GMAIL.COM</t>
+          <t>NORMAAGUTIERREZM@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>18-02-2026 16:30:39</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>19-02-2026 11:31:06</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7121,7 +7109,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -7131,17 +7119,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>18-02-2026 16:40:13</t>
+          <t>19-02-2026 12:01:32</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>18-02-2026 16:34:10</t>
+          <t>19-02-2026 11:44:54</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7161,7 +7149,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26170522466910002616</t>
+          <t>26170522492340002663</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7173,24 +7161,24 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>343394</t>
+          <t>342853</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>20670</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7200,17 +7188,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BRIANA NAOMI</t>
+          <t>DAMARIS KATHELEEN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7220,28 +7208,28 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6867481654</t>
+          <t>6861330533</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>05-02-2011</t>
+          <t>26-02-2007</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>NAOMIDOM2011@ICLOUD.COM</t>
+          <t>DAMARISK.SLOPEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>12-02-2026 20:07:03</t>
+          <t>10-02-2026 19:51:12</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7256,28 +7244,28 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>13-02-2026 17:16:34</t>
+          <t>10-02-2026 19:53:06</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
+          <t>10-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V51" t="inlineStr"/>
@@ -7288,44 +7276,36 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26170522326050002356</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170522247900002153</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>343968</t>
+          <t>344864</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21785</t>
+          <t>22681</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7335,17 +7315,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ALEXIS ABRAHAM</t>
+          <t>ELIAS ABDIEL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PINO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7355,32 +7335,32 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6864284152</t>
+          <t>6865902031</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PRIV AUDACIA 2134</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>17-11-2005</t>
+          <t>20-04-2005</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ALEXISARP15@GMAIL.COM</t>
+          <t>ELIASMORENO052@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>16-02-2026 08:36:23</t>
+          <t>18-02-2026 16:30:39</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7405,17 +7385,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>16-02-2026 08:44:12</t>
+          <t>18-02-2026 16:40:13</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>16-02-2026 08:42:55</t>
+          <t>18-02-2026 16:34:10</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7425,7 +7405,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
@@ -7435,7 +7415,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26170522381430002418</t>
+          <t>26170522466910002616</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7447,24 +7427,24 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>344019</t>
+          <t>342676</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7474,17 +7454,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ABRHAM ISACC</t>
+          <t>VIVIAN DENIISSE</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KETCHUL</t>
+          <t>MELERO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7494,67 +7474,75 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6861255888</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>6644940465</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>12-07-1992</t>
+          <t>19-06-1981</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>ABRAHAM.SKET1@GMAIL.COM</t>
+          <t>VIVIANDEFELIX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>16-02-2026 11:31:00</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 15:37:05</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>16-02-2026 11:32:22</t>
+          <t>10-02-2026 15:40:14</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>10-02-2026 15:39:43</t>
+        </is>
+      </c>
       <c r="U53" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7562,36 +7550,36 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26170522385460002427</t>
+          <t>26170522235040002127</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>343240</t>
+          <t>343394</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>21211</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7601,95 +7589,87 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>HECTOR EDUARDO</t>
+          <t>BRIANA NAOMI</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CANALES</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6867481654</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>05-02-2011</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NAOMIDOM2011@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>12-02-2026 20:07:03</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>13-02-2026 17:16:34</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>7602343861</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>C PASEO DEL AGUA 456</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>05-02-1997</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>HECTORCANALESLEYVA@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:48:03</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Forzoso</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>PROMO FEBRERO 12 MESES</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:53:41</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:53:05</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7697,14 +7677,22 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26170522292940002271</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
+          <t>26170522326050002356</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
@@ -7721,12 +7709,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>343969</t>
+          <t>343968</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>21785</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7736,17 +7724,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO</t>
+          <t>ALEXIS ABRAHAM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ALCARAZ</t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>PINO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7756,53 +7744,57 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6462016615</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>6864284152</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>PRIV AUDACIA 2134</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>05-11-2009</t>
+          <t>17-11-2005</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>AR7481660@GMAIL.COM</t>
+          <t>ALEXISARP15@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>16-02-2026 08:36:28</t>
+          <t>16-02-2026 08:36:23</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>16-02-2026 08:38:13</t>
+          <t>16-02-2026 08:44:12</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -7810,13 +7802,21 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:42:55</t>
+        </is>
+      </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7824,14 +7824,14 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26170522381280002417</t>
+          <t>26170522381430002418</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -7848,12 +7848,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>344075</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21892</t>
+          <t>21057</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7863,59 +7863,55 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA </t>
+          <t>HECTOR EDUARDO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t>CANALES</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BACA</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6681446837</t>
+          <t>7602343861</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AV BURGUETE 41</t>
+          <t>C PASEO DEL AGUA 456</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>04-11-1987</t>
+          <t>05-02-1997</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>GABYISA.0104@GMAIL.COM</t>
+          <t>HECTORCANALESLEYVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>16-02-2026 13:40:14</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 12:48:03</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7933,17 +7929,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>16-02-2026 13:47:19</t>
+          <t>12-02-2026 12:53:41</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>16-02-2026 13:46:36</t>
+          <t>12-02-2026 12:53:05</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7953,7 +7949,7 @@
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -7963,7 +7959,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26170522389180002437</t>
+          <t>26170522292940002271</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
@@ -7975,24 +7971,24 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>344087</t>
+          <t>343969</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21904</t>
+          <t>21786</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8002,17 +7998,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ROSARIO GUADALUPE</t>
+          <t>LUIS ALBERTO</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ALCARAZ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8022,57 +8018,53 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6863182471</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>CALLE GILAS1892</t>
-        </is>
-      </c>
+          <t>6462016615</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>06-10-1991</t>
+          <t>05-11-2009</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>GARCIAGUADALUPE7414@HOTMAIL.COM</t>
+          <t>AR7481660@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>16-02-2026 14:05:34</t>
+          <t>16-02-2026 08:36:28</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>16-02-2026 14:10:44</t>
+          <t>16-02-2026 08:38:13</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -8080,21 +8072,13 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>16-02-2026 14:10:01</t>
-        </is>
-      </c>
+      <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8102,36 +8086,36 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26170522389780002438</t>
+          <t>26170522381280002417</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>344869</t>
+          <t>344075</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22686</t>
+          <t>21892</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8141,17 +8125,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEVIN MISAEL </t>
+          <t xml:space="preserve">GABRIELA </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>BACA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8161,12 +8145,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6861053368</t>
+          <t>6681446837</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>AV BURGUETE 41</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8176,17 +8160,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>24-12-2004</t>
+          <t>04-11-1987</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>KEVINRAMIREZ2412@GMAIL.COM</t>
+          <t>GABYISA.0104@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>18-02-2026 16:38:43</t>
+          <t>16-02-2026 13:40:14</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8211,17 +8195,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:20</t>
+          <t>16-02-2026 13:47:19</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>18-02-2026 16:43:02</t>
+          <t>16-02-2026 13:46:36</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8231,7 +8215,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -8241,7 +8225,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26170522467160002617</t>
+          <t>26170522389180002437</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
@@ -8253,10 +8237,288 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
+          <t>Saul  Galeana</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>344087</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>21904</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ROSARIO GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>OCHOA</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>6863182471</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>CALLE GILAS1892</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>06-10-1991</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>GARCIAGUADALUPE7414@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>16-02-2026 14:05:34</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>16-02-2026 14:10:44</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>16-02-2026 14:10:01</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26170522389780002438</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>344869</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>22686</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEVIN MISAEL </t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMIREZ </t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6861053368</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>24-12-2004</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>KEVINRAMIREZ2412@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>18-02-2026 16:38:43</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>18-02-2026 16:45:20</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>18-02-2026 16:43:02</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26170522467160002617</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
           <t>Alexa Johana  Haro</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>con rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,12 +697,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>118108</t>
+          <t>75553</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>73366</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO</t>
+          <t>DANIEL ALEJANDRO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t xml:space="preserve">ROMERO </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>QUIJADA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6865298916</t>
+          <t>6863466296</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HACIENDA SAN ROQUE</t>
+          <t>NERVA 118</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1041,24 +1041,20 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>03-07-1996</t>
+          <t>25-06-2003</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>J.ANTONIO.CRUZ.CARDENAS@GMAIL.COM</t>
+          <t>DANIELQUIJADA2532@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>23-08-2022 19:27:05</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>28-02-2022 17:04:02</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1076,17 +1072,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>17-02-2026 14:14:53</t>
+          <t>02-02-2026 14:23:09</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>17-02-2026 14:13:03</t>
+          <t>02-02-2026 14:22:48</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1096,7 +1092,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1106,7 +1102,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26170522429040002526</t>
+          <t>26170522012560001648</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1118,24 +1114,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>183590</t>
+          <t>118108</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>81097</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1145,17 +1141,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIAN </t>
+          <t>JOSE ANTONIO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1165,12 +1161,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6864295199</t>
+          <t>6865298916</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GALATEA 245</t>
+          <t>HACIENDA SAN ROQUE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1180,20 +1176,24 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>18-12-1993</t>
+          <t>03-07-1996</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>BRIAN.GONZALEZ@UABC.EDU.MX</t>
+          <t>J.ANTONIO.CRUZ.CARDENAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>11-07-2023 17:00:27</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>23-08-2022 19:27:05</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1211,17 +1211,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-02-2026 15:48:32</t>
+          <t>17-02-2026 14:14:53</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-02-2026 15:47:32</t>
+          <t>17-02-2026 14:13:03</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26170522015130001656</t>
+          <t>26170522429040002526</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1265,12 +1265,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>75553</t>
+          <t>183590</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73366</t>
+          <t>81097</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DANIEL ALEJANDRO</t>
+          <t xml:space="preserve">BRIAN </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROMERO </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>QUIJADA</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6863466296</t>
+          <t>6864295199</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NERVA 118</t>
+          <t>GALATEA 245</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1315,17 +1315,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>25-06-2003</t>
+          <t>18-12-1993</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>DANIELQUIJADA2532@GMAIL.COM</t>
+          <t>BRIAN.GONZALEZ@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>28-02-2022 17:04:02</t>
+          <t>11-07-2023 17:00:27</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-02-2026 14:23:09</t>
+          <t>02-02-2026 15:48:32</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-02-2026 14:22:48</t>
+          <t>02-02-2026 15:47:32</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26170522012560001648</t>
+          <t>26170522015130001656</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>219990</t>
+          <t>339961</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1820,17 +1820,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA CRISTINA </t>
+          <t>CELINA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUILAR </t>
+          <t xml:space="preserve">REYES </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIGUERA </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6863372459</t>
+          <t>6864237570</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1851,17 +1851,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>01-03-1990</t>
+          <t>25-06-1996</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>DIANA90HIGUERA@GMAIL.COM</t>
+          <t>EYLECELENA25@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>15-02-2024 09:29:52</t>
+          <t>02-02-2026 09:30:33</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>20-02-2026 16:08:52</t>
+          <t>12-02-2026 08:16:52</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1908,11 +1908,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26170522529480002736</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>26170522288990002257</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>549</t>
@@ -1920,24 +1928,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>339961</t>
+          <t>219990</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17779</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1947,17 +1955,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CELINA</t>
+          <t xml:space="preserve">DIANA CRISTINA </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">REYES </t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">HIGUERA </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1967,7 +1975,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6864237570</t>
+          <t>6863372459</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1978,17 +1986,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>25-06-1996</t>
+          <t>01-03-1990</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>EYLECELENA25@GMAIL.COM</t>
+          <t>DIANA90HIGUERA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-02-2026 09:30:33</t>
+          <t>15-02-2024 09:29:52</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2013,12 +2021,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>12-02-2026 08:16:52</t>
+          <t>20-02-2026 16:08:52</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>20-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2035,19 +2043,11 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26170522288990002257</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522529480002736</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
           <t>549</t>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2194,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340249</t>
+          <t>340750</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18067</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANABEL </t>
+          <t>ARMANDO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEARA </t>
+          <t xml:space="preserve">ORTIZ </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARCOS </t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2229,14 +2229,10 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6863957626</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>BONIFACIO AVILES 3133</t>
-        </is>
-      </c>
+          <t>6863928150</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2244,60 +2240,56 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>26-01-1995</t>
+          <t>23-02-1988</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ANABELDEARA260195@GMAIL.COM</t>
+          <t>MENTECUERPOYNUTRICION@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-02-2026 16:10:16</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>03-02-2026 17:50:24</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-02-2026 16:15:39</t>
+          <t>03-02-2026 17:52:56</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>02-02-2026 16:14:45</t>
-        </is>
-      </c>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2305,19 +2297,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26170522016110001661</t>
+          <t>26170522051130001755</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2611,12 +2603,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340181</t>
+          <t>340249</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17999</t>
+          <t>18067</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2626,17 +2618,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAHIRA YOMAHIRA</t>
+          <t xml:space="preserve">ANABEL </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAJO </t>
+          <t xml:space="preserve">DEARA </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PIZANO</t>
+          <t xml:space="preserve">ARCOS </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2646,32 +2638,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6862091543</t>
+          <t>6863957626</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CASTILLEJA 1818</t>
+          <t>BONIFACIO AVILES 3133</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13-04-2003</t>
+          <t>26-01-1995</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CUARTO.SAJIRA@ICLOUD.COM</t>
+          <t>ANABELDEARA260195@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-02-2026 14:35:58</t>
+          <t>02-02-2026 16:10:16</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2692,7 +2684,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-02-2026 14:42:26</t>
+          <t>02-02-2026 16:15:39</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2702,7 +2694,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-02-2026 14:40:53</t>
+          <t>02-02-2026 16:14:45</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2722,7 +2714,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26170522013230001649</t>
+          <t>26170522016110001661</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2734,7 +2726,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2746,12 +2738,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>340750</t>
+          <t>310670</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2761,17 +2753,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ARMANDO</t>
+          <t xml:space="preserve">OLGA </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTIZ </t>
+          <t>CARLEÑO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2781,28 +2773,28 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6863928150</t>
+          <t>6862097698</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>23-02-1988</t>
+          <t>24-02-1980</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MENTECUERPOYNUTRICION@HOTMAIL.COM</t>
+          <t>OCARLENOHERNANDEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-02-2026 17:50:24</t>
+          <t>22-08-2025 14:08:49</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2827,12 +2819,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-02-2026 17:52:56</t>
+          <t>23-02-2026 14:52:33</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2849,11 +2841,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26170522051130001755</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26170522583230002827</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>1899</t>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>340334</t>
+          <t>340181</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>17999</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3023,17 +3023,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EMILY SOFIA</t>
+          <t>SAHIRA YOMAHIRA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ARRIAGA</t>
+          <t xml:space="preserve">BAJO </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>PIZANO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6864702297</t>
+          <t>6862091543</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AV RIOJA 160</t>
+          <t>CASTILLEJA 1818</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3058,52 +3058,48 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>02-02-2006</t>
+          <t>13-04-2003</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>EMILY.ARRIAGA@GMAIL.COM</t>
+          <t>CUARTO.SAJIRA@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-02-2026 18:06:05</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 14:35:58</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>05-02-2026 18:50:09</t>
+          <t>02-02-2026 14:42:26</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>05-02-2026 18:49:20</t>
+          <t>02-02-2026 14:40:53</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3123,22 +3119,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26170522116880001895</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522013230001649</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3155,12 +3143,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>341297</t>
+          <t>340334</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19115</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3170,17 +3158,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NATALIE</t>
+          <t>EMILY SOFIA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ARRIAGA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3190,12 +3178,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6861344365</t>
+          <t>6864702297</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORTALES </t>
+          <t>AV RIOJA 160</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3205,48 +3193,52 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>26-11-2004</t>
+          <t>02-02-2006</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>NATALIE.RODRIGUEZ@UABC.EDU.MX</t>
+          <t>EMILY.ARRIAGA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>05-02-2026 13:00:16</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>02-02-2026 18:06:05</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>10-02-2026 16:55:49</t>
+          <t>05-02-2026 18:50:09</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>10-02-2026 16:54:34</t>
+          <t>05-02-2026 18:49:20</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3266,7 +3258,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26170522238010002133</t>
+          <t>26170522116880001895</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3281,7 +3273,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3425,12 +3417,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>341467</t>
+          <t>341297</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>19115</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3440,17 +3432,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ADOLFO</t>
+          <t>NATALIE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ALBISO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BARAJAS</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3460,32 +3452,32 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6862300377</t>
+          <t>6861344365</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NORUEGA 2636</t>
+          <t xml:space="preserve">PORTALES </t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>12-11-1996</t>
+          <t>26-11-2004</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ADOLFO_19962016@HOTMAIL.COM</t>
+          <t>NATALIE.RODRIGUEZ@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>05-02-2026 21:05:50</t>
+          <t>05-02-2026 13:00:16</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3506,17 +3498,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>05-02-2026 21:13:45</t>
+          <t>10-02-2026 16:55:49</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>05-02-2026 21:13:16</t>
+          <t>10-02-2026 16:54:34</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3536,11 +3528,19 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26170522120570001923</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+          <t>26170522238010002133</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>499</t>
@@ -3560,12 +3560,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>341189</t>
+          <t>341467</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3575,17 +3575,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>IVAN</t>
+          <t>ADOLFO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>ALBISO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>BARAJAS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6861965073</t>
+          <t>6862300377</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1RA MORELOS 19</t>
+          <t>NORUEGA 2636</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3610,17 +3610,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>22-09-2000</t>
+          <t>12-11-1996</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>IVAN.RODRIGUEZ@GMAIL.COM</t>
+          <t>ADOLFO_19962016@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>04-02-2026 20:27:47</t>
+          <t>05-02-2026 21:05:50</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3641,17 +3641,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>04-02-2026 20:33:43</t>
+          <t>05-02-2026 21:13:45</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>04-02-2026 20:33:11</t>
+          <t>05-02-2026 21:13:16</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26170522089840001847</t>
+          <t>26170522120570001923</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3695,12 +3695,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>341295</t>
+          <t>341189</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19113</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FERNANDA</t>
+          <t>IVAN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3730,32 +3730,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6865781520</t>
+          <t>6861965073</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>POTALES</t>
+          <t>1RA MORELOS 19</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>13-10-2006</t>
+          <t>22-09-2000</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>FR65671@GMAIL.COM</t>
+          <t>IVAN.RODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>05-02-2026 12:58:08</t>
+          <t>04-02-2026 20:27:47</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3776,17 +3776,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>10-02-2026 16:59:22</t>
+          <t>04-02-2026 20:33:43</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>10-02-2026 16:58:27</t>
+          <t>04-02-2026 20:33:11</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3806,19 +3806,11 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26170522238110002134</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522089840001847</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>499</t>
@@ -3838,12 +3830,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>322246</t>
+          <t>341295</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19185</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3853,17 +3845,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ZAIRA RAMIREZ CASTRO</t>
+          <t>FERNANDA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3873,12 +3865,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6861234537</t>
+          <t>6865781520</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">LA BARRERA 323 </t>
+          <t>POTALES</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3888,17 +3880,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>07-10-1997</t>
+          <t>13-10-2006</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ZAIRA071097@HOTMAIL.COM</t>
+          <t>FR65671@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>05-11-2025 16:07:36</t>
+          <t>05-02-2026 12:58:08</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3919,17 +3911,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-02-2026 17:50:01</t>
+          <t>10-02-2026 16:59:22</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>02-02-2026 17:48:27</t>
+          <t>10-02-2026 16:58:27</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3939,7 +3931,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -3949,15 +3941,19 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26170522019270001671</t>
+          <t>26170522238110002134</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>499</t>
@@ -3977,12 +3973,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>340183</t>
+          <t>322246</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>18001</t>
+          <t>19185</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3992,17 +3988,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LEYLANI MIRANDA</t>
+          <t>ZAIRA RAMIREZ CASTRO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PIZANO</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4012,10 +4008,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6863558685</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>6861234537</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LA BARRERA 323 </t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4023,13 +4023,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>03-11-2011</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+          <t>07-10-1997</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>ZAIRA071097@HOTMAIL.COM</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-02-2026 14:41:17</t>
+          <t>05-11-2025 16:07:36</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4050,7 +4054,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-02-2026 14:46:51</t>
+          <t>02-02-2026 17:50:01</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -4060,7 +4064,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>02-02-2026 14:45:55</t>
+          <t>02-02-2026 17:48:27</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4070,7 +4074,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4080,10 +4084,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26170522013390001650</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
+          <t>26170522019270001671</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
@@ -4092,24 +4100,24 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>340231</t>
+          <t>340035</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4119,17 +4127,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ELLIOT SAMUEL</t>
+          <t>KITZIA AILIME</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>MAGALLON</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4139,32 +4147,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6866507552</t>
+          <t>6862541870</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AV GOLETA 1807</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>09-08-1998</t>
+          <t>17-03-2003</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ELLIOT.MORA@UABC.COM.MX</t>
+          <t>KITZIAMAGALON@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>02-02-2026 15:50:44</t>
+          <t>02-02-2026 10:57:19</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4185,7 +4193,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>02-02-2026 15:56:47</t>
+          <t>02-02-2026 11:00:49</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4195,7 +4203,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>02-02-2026 15:54:59</t>
+          <t>02-02-2026 11:00:21</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4215,7 +4223,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26170522015420001658</t>
+          <t>26170522006040001630</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4227,7 +4235,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4239,12 +4247,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>340035</t>
+          <t>340108</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17853</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4254,17 +4262,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KITZIA AILIME</t>
+          <t>CHRISTIAN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MAGALLON</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4274,32 +4282,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6862541870</t>
+          <t>6866740223</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>17-03-2003</t>
+          <t>11-02-2010</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>KITZIAMAGALON@GMAIL.COM</t>
+          <t>HIELO12CV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>02-02-2026 10:57:19</t>
+          <t>02-02-2026 12:53:45</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4320,17 +4328,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>02-02-2026 11:00:49</t>
+          <t>04-02-2026 13:54:22</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>02-02-2026 11:00:21</t>
+          <t>04-02-2026 13:53:23</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4350,11 +4358,19 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26170522006040001630</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+          <t>26170522075080001810</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>499</t>
@@ -4362,24 +4378,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>340108</t>
+          <t>342573</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4389,17 +4405,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t>LOURDES RENE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4409,32 +4425,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6866740223</t>
+          <t>6864162086</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>LAGO PAZCUARO SN</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>11-02-2010</t>
+          <t>21-09-1988</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>HIELO12CV@GMAIL.COM</t>
+          <t>CAMPOSLULY0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>02-02-2026 12:53:45</t>
+          <t>10-02-2026 10:01:09</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4455,17 +4471,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>04-02-2026 13:54:22</t>
+          <t>10-02-2026 10:11:12</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>04-02-2026 13:53:23</t>
+          <t>10-02-2026 10:10:28</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4485,19 +4501,11 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26170522075080001810</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522227920002115</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
           <t>499</t>
@@ -4505,7 +4513,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Jose Luis Lopez Coronel</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4632,24 +4640,24 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>342494</t>
+          <t>343007</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>20824</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4659,17 +4667,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>SERGIO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TEJADA</t>
+          <t>VILLARREAL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>ZEPEDA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4679,32 +4687,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6867291381</t>
+          <t>6864644967</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>DE LAS ESPADAS 61</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>20-06-2005</t>
+          <t>11-10-2001</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>MIGUELTEJADA317@ICLOUD.COM</t>
+          <t>ZEPEDA111001@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>09-02-2026 20:58:55</t>
+          <t>11-02-2026 15:16:45</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4725,17 +4733,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>09-02-2026 21:01:56</t>
+          <t>11-02-2026 15:30:24</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>09-02-2026 21:01:07</t>
+          <t>11-02-2026 15:29:47</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4755,7 +4763,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26170522214500002093</t>
+          <t>26170522266490002208</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -4767,24 +4775,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342573</t>
+          <t>342494</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4794,17 +4802,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LOURDES RENE</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>TEJADA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4814,12 +4822,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6864162086</t>
+          <t>6867291381</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>LAGO PAZCUARO SN</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4829,17 +4837,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>21-09-1988</t>
+          <t>20-06-2005</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CAMPOSLULY0@GMAIL.COM</t>
+          <t>MIGUELTEJADA317@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10-02-2026 10:01:09</t>
+          <t>09-02-2026 20:58:55</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4860,17 +4868,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>10-02-2026 10:11:12</t>
+          <t>09-02-2026 21:01:56</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>10-02-2026 10:10:28</t>
+          <t>09-02-2026 21:01:07</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4890,7 +4898,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26170522227920002115</t>
+          <t>26170522214500002093</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4902,7 +4910,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Jose Luis Lopez Coronel</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4914,12 +4922,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>342851</t>
+          <t>343391</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>20668</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4929,17 +4937,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE JAVIE </t>
+          <t>JOSE ENRIQUE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZEPEDA </t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4949,10 +4957,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6863023309</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>6861914185</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4960,56 +4972,60 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>22-08-2003</t>
+          <t>02-01-2004</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>JV220803@GMAIL.COM</t>
+          <t>JG747801@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10-02-2026 19:47:49</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 19:39:05</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>10-02-2026 19:49:44</t>
+          <t>12-02-2026 19:42:59</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>12-02-2026 19:42:26</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5017,36 +5033,36 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26170522247770002152</t>
+          <t>26170522305280002308</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342293</t>
+          <t>342851</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20111</t>
+          <t>20668</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5056,17 +5072,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t xml:space="preserve">JOSE JAVIE </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CORREA</t>
+          <t xml:space="preserve">ZEPEDA </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5076,14 +5092,10 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6864214771</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6863023309</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5091,60 +5103,56 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>10-08-2003</t>
+          <t>22-08-2003</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>MORAERNESTO741@GMAIL.COM</t>
+          <t>JV220803@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>09-02-2026 16:57:09</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>10-02-2026 19:47:49</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>09-02-2026 17:02:55</t>
+          <t>10-02-2026 19:49:44</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>09-02-2026 16:59:57</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5152,19 +5160,19 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26170522200440002040</t>
+          <t>26170522247770002152</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5311,12 +5319,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>343007</t>
+          <t>340183</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5326,17 +5334,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SERGIO</t>
+          <t>LEYLANI MIRANDA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>VILLARREAL</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ZEPEDA</t>
+          <t>PIZANO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5346,32 +5354,24 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6864644967</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>DE LAS ESPADAS 61</t>
-        </is>
-      </c>
+          <t>6863558685</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>11-10-2001</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>ZEPEDA111001@GMAIL.COM</t>
-        </is>
-      </c>
+          <t>03-11-2011</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>11-02-2026 15:16:45</t>
+          <t>02-02-2026 14:41:17</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5392,17 +5392,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>11-02-2026 15:30:24</t>
+          <t>02-02-2026 14:46:51</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>11-02-2026 15:29:47</t>
+          <t>02-02-2026 14:45:55</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26170522266490002208</t>
+          <t>26170522013390001650</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5446,12 +5446,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>343401</t>
+          <t>340231</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21218</t>
+          <t>18049</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5461,17 +5461,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO</t>
+          <t>ELLIOT SAMUEL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZEPEDA </t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5481,10 +5481,14 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6862110739</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>6866507552</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>AV GOLETA 1807</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5492,56 +5496,60 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>06-08-1987</t>
+          <t>09-08-1998</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ZEPEDACOTAC@GMAIL.COM</t>
+          <t>ELLIOT.MORA@UABC.COM.MX</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>12-02-2026 21:09:33</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 15:50:44</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>12-02-2026 21:11:55</t>
+          <t>02-02-2026 15:56:47</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>02-02-2026 15:54:59</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5549,36 +5557,36 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26170522306850002321</t>
+          <t>26170522015420001658</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>341159</t>
+          <t>342293</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18977</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5588,17 +5596,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DAVID ERNESTO</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CORREA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5608,10 +5616,14 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6863409250</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6864214771</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5619,56 +5631,60 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>28-08-2011</t>
+          <t>10-08-2003</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>DAVID.ERNESTO@GMAIL.COM</t>
+          <t>MORAERNESTO741@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>04-02-2026 19:08:30</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 16:57:09</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>04-02-2026 19:10:17</t>
+          <t>09-02-2026 17:02:55</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>09-02-2026 16:59:57</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5676,14 +5692,14 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26170522087360001828</t>
+          <t>26170522200440002040</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5700,12 +5716,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>342857</t>
+          <t>343401</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5715,17 +5731,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t>CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">JIMENEZ </t>
+          <t xml:space="preserve">ZEPEDA </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5735,14 +5751,10 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6861387777</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6862110739</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5750,60 +5762,56 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>14-08-1972</t>
+          <t>06-08-1987</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>JORGEJIMENEZSOTO1994@GMAIL.COM</t>
+          <t>ZEPEDACOTAC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>10-02-2026 19:59:00</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>12-02-2026 21:09:33</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>10-02-2026 20:04:31</t>
+          <t>12-02-2026 21:11:55</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>10-02-2026 20:04:01</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5811,19 +5819,19 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26170522248340002163</t>
+          <t>26170522306850002321</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5835,12 +5843,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>340441</t>
+          <t>342857</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>20674</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5850,17 +5858,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t xml:space="preserve">JIMENEZ </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5870,7 +5878,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6674121912</t>
+          <t>6861387777</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5885,17 +5893,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>07-10-2003</t>
+          <t>14-08-1972</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>FELIZLUISFERNANDO3@GMAIL.COM</t>
+          <t>JORGEJIMENEZSOTO1994@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>03-02-2026 07:13:43</t>
+          <t>10-02-2026 19:59:00</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5916,17 +5924,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>03-02-2026 07:19:00</t>
+          <t>10-02-2026 20:04:31</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>03-02-2026 07:18:37</t>
+          <t>10-02-2026 20:04:01</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5936,7 +5944,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -5946,7 +5954,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26170522031900001705</t>
+          <t>26170522248340002163</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -5958,24 +5966,24 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>340564</t>
+          <t>340441</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>18259</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5985,17 +5993,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>JOSE MANUEL</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>REA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6005,10 +6013,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6865860740</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>6674121912</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6016,42 +6028,38 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>27-12-1976</t>
+          <t>07-10-2003</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>REA1628JOSE@GMAIL.COM</t>
+          <t>FELIZLUISFERNANDO3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>03-02-2026 13:24:47</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>03-02-2026 07:13:43</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>03-02-2026 13:26:26</t>
+          <t>03-02-2026 07:19:00</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -6059,13 +6067,21 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>03-02-2026 07:18:37</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6073,36 +6089,36 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26170522039620001735</t>
+          <t>26170522031900001705</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>343391</t>
+          <t>340564</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>21208</t>
+          <t>18382</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6112,17 +6128,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>JOSE ENRIQUE</t>
+          <t>JOSE MANUEL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MONTOYA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>REA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6132,14 +6148,10 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6861914185</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6865860740</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6147,60 +6159,56 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>02-01-2004</t>
+          <t>27-12-1976</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>JG747801@GMAIL.COM</t>
+          <t>REA1628JOSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>12-02-2026 19:39:05</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>03-02-2026 13:24:47</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>12-02-2026 19:42:59</t>
+          <t>03-02-2026 13:26:26</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>12-02-2026 19:42:26</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6208,24 +6216,24 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26170522305280002308</t>
+          <t>26170522039620001735</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -6367,12 +6375,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>343975</t>
+          <t>341159</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21792</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6382,17 +6390,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MARIA ISABEL</t>
+          <t>DAVID ERNESTO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PEREYDA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6402,79 +6410,67 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6861945257</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>AVENIDA MONTES DE LEON 2027</t>
-        </is>
-      </c>
+          <t>6863409250</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>24-08-1995</t>
+          <t>28-08-2011</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>ISABELPEREYDA24@GMAIL.COM</t>
+          <t>DAVID.ERNESTO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>16-02-2026 08:43:39</t>
+          <t>04-02-2026 19:08:30</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>16-02-2026 08:52:04</t>
+          <t>04-02-2026 19:10:17</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>16-02-2026 08:51:31</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6482,19 +6478,19 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26170522381670002419</t>
+          <t>26170522087360001828</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6506,12 +6502,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>343982</t>
+          <t>345451</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21799</t>
+          <t>87616</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6521,17 +6517,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">JENNIFER </t>
+          <t>RAMONA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FAVELA</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6541,12 +6537,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6863626144</t>
+          <t>6861238114</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>PORALES</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6556,24 +6552,20 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>11-12-2001</t>
+          <t>02-03-1979</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>FAVELAPEREZVZ11@GMAIL.COM</t>
+          <t>GARENE1976@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>16-02-2026 09:07:20</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>21-02-2026 07:31:03</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6581,7 +6573,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -6591,17 +6583,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>16-02-2026 09:11:41</t>
+          <t>23-02-2026 07:43:05</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>16-02-2026 09:11:13</t>
+          <t>23-02-2026 07:42:26</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6621,11 +6613,19 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26170522382170002420</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
+          <t>26170522572930002811</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>499</t>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6645,12 +6645,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>344019</t>
+          <t>343975</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6660,17 +6660,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ABRHAM ISACC</t>
+          <t>MARIA ISABEL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>PEREYDA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KETCHUL</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6680,53 +6680,57 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6861255888</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>6861945257</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>AVENIDA MONTES DE LEON 2027</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>12-07-1992</t>
+          <t>24-08-1995</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ABRAHAM.SKET1@GMAIL.COM</t>
+          <t>ISABELPEREYDA24@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>16-02-2026 11:31:00</t>
+          <t>16-02-2026 08:43:39</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>16-02-2026 11:32:22</t>
+          <t>16-02-2026 08:52:04</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -6734,13 +6738,21 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr"/>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:51:31</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6748,36 +6760,36 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26170522385460002427</t>
+          <t>26170522381670002419</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>342495</t>
+          <t>343982</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>21799</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6787,17 +6799,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">NELSON </t>
+          <t xml:space="preserve">JENNIFER </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>FAVELA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MARISCAL</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6807,67 +6819,79 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6861420567</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>6863626144</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>28-10-1996</t>
+          <t>11-12-2001</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>NELSON.1028@HOTMAIL.COM</t>
+          <t>FAVELAPEREZVZ11@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>09-02-2026 21:04:58</t>
+          <t>16-02-2026 09:07:20</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>09-02-2026 21:06:43</t>
+          <t>16-02-2026 09:11:41</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>16-02-2026 09:11:13</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6875,19 +6899,19 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26170522214560002094</t>
+          <t>26170522382170002420</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6899,12 +6923,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>344362</t>
+          <t>344019</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22179</t>
+          <t>21836</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6914,17 +6938,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDREA MICHELL </t>
+          <t>ABRHAM ISACC</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>URIBE</t>
+          <t>KETCHUL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6934,57 +6958,53 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6863837971</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>HERENCIA 2338</t>
-        </is>
-      </c>
+          <t>6861255888</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>15-08-2000</t>
+          <t>12-07-1992</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ANDREAESTRADA1218@ICLOUD.COM</t>
+          <t>ABRAHAM.SKET1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>16-02-2026 21:04:29</t>
+          <t>16-02-2026 11:31:00</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>16-02-2026 21:14:42</t>
+          <t>16-02-2026 11:32:22</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -6992,21 +7012,13 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>16-02-2026 21:12:23</t>
-        </is>
-      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7014,14 +7026,14 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26170522411380002496</t>
+          <t>26170522385460002427</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
@@ -7038,12 +7050,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>345036</t>
+          <t>344362</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>87201</t>
+          <t>22179</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7053,17 +7065,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NORMA ALICIA</t>
+          <t xml:space="preserve">ANDREA MICHELL </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">MERCADO </t>
+          <t>URIBE</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7073,12 +7085,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6863291327</t>
+          <t>6863837971</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>POMONA 2446</t>
+          <t>HERENCIA 2338</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7088,20 +7100,24 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>03-11-1976</t>
+          <t>15-08-2000</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>NORMAAGUTIERREZM@HOTMAIL.COM</t>
+          <t>ANDREAESTRADA1218@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>19-02-2026 11:31:06</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>16-02-2026 21:04:29</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7109,7 +7125,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -7119,17 +7135,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>19-02-2026 12:01:32</t>
+          <t>16-02-2026 21:14:42</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>19-02-2026 11:44:54</t>
+          <t>16-02-2026 21:12:23</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7149,7 +7165,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26170522492340002663</t>
+          <t>26170522411380002496</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7161,24 +7177,24 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>342853</t>
+          <t>344524</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20670</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7188,17 +7204,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DAMARIS KATHELEEN</t>
+          <t>GERARDO ANTONIO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t xml:space="preserve">IBAÑEZ </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MANCILLA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7208,10 +7224,14 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6861330533</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>6861832430</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>BASTIA 2595</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7219,56 +7239,60 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>26-02-2007</t>
+          <t>01-02-1966</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>DAMARISK.SLOPEZ@GMAIL.COM</t>
+          <t>GERARDO.ANTONIO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>10-02-2026 19:51:12</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>17-02-2026 15:20:45</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>10-02-2026 19:53:06</t>
+          <t>23-02-2026 16:27:39</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>10-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>23-02-2026 16:25:27</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7276,36 +7300,44 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26170522247900002153</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
+          <t>26170522587090002838</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>344864</t>
+          <t>345036</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22681</t>
+          <t>87201</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7315,17 +7347,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ELIAS ABDIEL</t>
+          <t>NORMA ALICIA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">MERCADO </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7335,39 +7367,35 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6865902031</t>
+          <t>6863291327</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>POMONA 2446</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>20-04-2005</t>
+          <t>03-11-1976</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ELIASMORENO052@GMAIL.COM</t>
+          <t>NORMAAGUTIERREZM@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>18-02-2026 16:30:39</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>19-02-2026 11:31:06</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7375,7 +7403,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -7385,17 +7413,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>18-02-2026 16:40:13</t>
+          <t>19-02-2026 12:01:32</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>18-02-2026 16:34:10</t>
+          <t>19-02-2026 11:44:54</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7415,7 +7443,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26170522466910002616</t>
+          <t>26170522492340002663</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7427,12 +7455,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -7574,12 +7602,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>343394</t>
+          <t>344864</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>22681</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7589,17 +7617,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BRIANA NAOMI</t>
+          <t>ELIAS ABDIEL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7609,67 +7637,79 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6867481654</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>6865902031</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>05-02-2011</t>
+          <t>20-04-2005</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>NAOMIDOM2011@ICLOUD.COM</t>
+          <t>ELIASMORENO052@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>12-02-2026 20:07:03</t>
+          <t>18-02-2026 16:30:39</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>13-02-2026 17:16:34</t>
+          <t>18-02-2026 16:40:13</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr"/>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>18-02-2026 16:34:10</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7677,44 +7717,36 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26170522326050002356</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170522466910002616</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>343968</t>
+          <t>345453</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21785</t>
+          <t>87618</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7724,17 +7756,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ALEXIS ABRAHAM</t>
+          <t>RENE FRANCISCO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PINO</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7744,39 +7776,35 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6864284152</t>
+          <t>6863948826</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>PRIV AUDACIA 2134</t>
+          <t>CASA DIGNA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>17-11-2005</t>
+          <t>17-02-1976</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>ALEXISARP15@GMAIL.COM</t>
+          <t>RENEGARCIA170296@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>16-02-2026 08:36:23</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>21-02-2026 07:40:19</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7784,7 +7812,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
@@ -7794,17 +7822,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>16-02-2026 08:44:12</t>
+          <t>23-02-2026 07:36:13</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>16-02-2026 08:42:55</t>
+          <t>23-02-2026 07:35:10</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7814,7 +7842,7 @@
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -7824,11 +7852,19 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26170522381430002418</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
+          <t>26170522572740002810</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>499</t>
@@ -7836,24 +7872,24 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>343240</t>
+          <t>342495</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>20312</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7863,34 +7899,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HECTOR EDUARDO</t>
+          <t xml:space="preserve">NELSON </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CANALES</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>MARISCAL</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>7602343861</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>C PASEO DEL AGUA 456</t>
-        </is>
-      </c>
+          <t>6861420567</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7898,60 +7930,56 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>05-02-1997</t>
+          <t>28-10-1996</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>HECTORCANALESLEYVA@GMAIL.COM</t>
+          <t>NELSON.1028@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>12-02-2026 12:48:03</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>09-02-2026 21:04:58</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>12-02-2026 12:53:41</t>
+          <t>09-02-2026 21:06:43</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:53:05</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7959,36 +7987,36 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26170522292940002271</t>
+          <t>26170522214560002094</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>343969</t>
+          <t>345849</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>88014</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -7998,17 +8026,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO</t>
+          <t>RUTH ERENDIRA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ALCARAZ</t>
+          <t>SERMEÑO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8018,67 +8046,79 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6462016615</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>6865695069</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>COLUMBUS  1325</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>05-11-2009</t>
+          <t>12-09-1992</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>AR7481660@GMAIL.COM</t>
+          <t>RUTHSERMENO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>16-02-2026 08:36:28</t>
+          <t>23-02-2026 15:50:40</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>16-02-2026 08:38:13</t>
+          <t>23-02-2026 15:54:43</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>23-02-2026 15:54:01</t>
+        </is>
+      </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8086,36 +8126,36 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26170522381280002417</t>
+          <t>26170522585670002834</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>344075</t>
+          <t>345872</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21892</t>
+          <t>88037</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8125,17 +8165,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA </t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t>AMEZQUITA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>BACA</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8145,67 +8185,67 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6681446837</t>
+          <t>6862605035</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>AV BURGUETE 41</t>
+          <t>BOSQUE CIRUELOS 853</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>04-11-1987</t>
+          <t>22-09-2000</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>GABYISA.0104@GMAIL.COM</t>
+          <t>BBMIGUEL28@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>16-02-2026 13:40:14</t>
+          <t>23-02-2026 16:30:33</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>16-02-2026 13:47:19</t>
+          <t>23-02-2026 16:34:54</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>16-02-2026 13:46:36</t>
+          <t>23-02-2026 16:34:22</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8215,7 +8255,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -8225,36 +8265,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26170522389180002437</t>
+          <t>26170522587570002839</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>344087</t>
+          <t>342853</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21904</t>
+          <t>20670</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8264,17 +8304,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ROSARIO GUADALUPE</t>
+          <t>DAMARIS KATHELEEN</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8284,79 +8324,67 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6863182471</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>CALLE GILAS1892</t>
-        </is>
-      </c>
+          <t>6861330533</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>06-10-1991</t>
+          <t>26-02-2007</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>GARCIAGUADALUPE7414@HOTMAIL.COM</t>
+          <t>DAMARISK.SLOPEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>16-02-2026 14:05:34</t>
+          <t>10-02-2026 19:51:12</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>16-02-2026 14:10:44</t>
+          <t>10-02-2026 19:53:06</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>16-02-2026 14:10:01</t>
-        </is>
-      </c>
+          <t>10-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8364,19 +8392,19 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26170522389780002438</t>
+          <t>26170522247900002153</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -8388,12 +8416,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>344869</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22686</t>
+          <t>21057</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8403,59 +8431,55 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEVIN MISAEL </t>
+          <t>HECTOR EDUARDO</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>CANALES</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6861053368</t>
+          <t>7602343861</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>C PASEO DEL AGUA 456</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>24-12-2004</t>
+          <t>05-02-1997</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>KEVINRAMIREZ2412@GMAIL.COM</t>
+          <t>HECTORCANALESLEYVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>18-02-2026 16:38:43</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 12:48:03</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8473,17 +8497,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:20</t>
+          <t>12-02-2026 12:53:41</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>18-02-2026 16:43:02</t>
+          <t>12-02-2026 12:53:05</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8503,7 +8527,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26170522467160002617</t>
+          <t>26170522292940002271</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
@@ -8515,12 +8539,969 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>343394</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>21211</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BRIANA NAOMI</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CAMACHO</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6867481654</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>05-02-2011</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NAOMIDOM2011@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>12-02-2026 20:07:03</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>13-02-2026 17:16:34</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>13-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26170522326050002356</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>343969</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>21786</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LUIS ALBERTO</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ALCARAZ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ROMERO</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6462016615</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>05-11-2009</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>AR7481660@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:36:28</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:38:13</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26170522381280002417</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>344075</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>21892</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA </t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TORRES </t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>BACA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6681446837</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>AV BURGUETE 41</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>04-11-1987</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>GABYISA.0104@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>16-02-2026 13:40:14</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>16-02-2026 13:47:19</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>16-02-2026 13:46:36</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26170522389180002437</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Saul  Galeana</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>343968</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>21785</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ALEXIS ABRAHAM</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMOS </t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>PINO</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6864284152</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>PRIV AUDACIA 2134</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>17-11-2005</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>ALEXISARP15@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:36:23</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:44:12</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:42:55</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26170522381430002418</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>344087</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>21904</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ROSARIO GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>OCHOA</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6863182471</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>CALLE GILAS1892</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>06-10-1991</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>GARCIAGUADALUPE7414@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>16-02-2026 14:05:34</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>16-02-2026 14:10:44</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>16-02-2026 14:10:01</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26170522389780002438</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>344869</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>22686</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEVIN MISAEL </t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMIREZ </t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6861053368</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>24-12-2004</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>KEVINRAMIREZ2412@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>18-02-2026 16:38:43</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>18-02-2026 16:45:20</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>18-02-2026 16:43:02</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26170522467160002617</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
           <t>Alexa Johana  Haro</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
+      <c r="AC66" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>346044</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>88209</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CAMILA</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>VALDEZ</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6863403745</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOSQUE TROPICAL </t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>19-08-2004</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>CAMILA.CONSULTORIOWORK@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:18:53</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:25:35</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:24:56</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26170522601620002882</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1535,12 +1535,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>339800</t>
+          <t>219990</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17618</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1550,17 +1550,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BRIAN MIGUEL</t>
+          <t xml:space="preserve">DIANA CRISTINA </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AISPURO</t>
+          <t xml:space="preserve">AGUILAR </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t xml:space="preserve">HIGUERA </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1570,75 +1570,67 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6862643137</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6863372459</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>13-12-1998</t>
+          <t>01-03-1990</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PAISPURO1948@GMAIL.COM</t>
+          <t>DIANA90HIGUERA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>01-02-2026 12:02:45</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>15-02-2024 09:29:52</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>01-02-2026 12:08:41</t>
+          <t>20-02-2026 16:08:52</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>01-02-2026 12:07:33</t>
-        </is>
-      </c>
+          <t>20-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1646,36 +1638,36 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26170521990600001608</t>
+          <t>26170522529480002736</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>339895</t>
+          <t>340750</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17713</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1685,17 +1677,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JULIO ALEJANDRO</t>
+          <t>ARMANDO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t xml:space="preserve">ORTIZ </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1705,7 +1697,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6867371621</t>
+          <t>6863928150</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1716,17 +1708,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>04-09-2001</t>
+          <t>23-02-1988</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BEJARANOJULIO10@GMAIL.COM</t>
+          <t>MENTECUERPOYNUTRICION@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-02-2026 08:04:32</t>
+          <t>03-02-2026 17:50:24</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1741,22 +1733,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-02-2026 07:27:31</t>
+          <t>03-02-2026 17:52:56</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>03-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1773,27 +1765,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26170522032100001708</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522051130001755</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1805,12 +1789,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>339961</t>
+          <t>340249</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17779</t>
+          <t>18067</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1820,17 +1804,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CELINA</t>
+          <t xml:space="preserve">ANABEL </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">REYES </t>
+          <t xml:space="preserve">DEARA </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">ARCOS </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1840,10 +1824,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6864237570</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6863957626</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BONIFACIO AVILES 3133</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1851,56 +1839,60 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>25-06-1996</t>
+          <t>26-01-1995</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>EYLECELENA25@GMAIL.COM</t>
+          <t>ANABELDEARA260195@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-02-2026 09:30:33</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 16:10:16</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>12-02-2026 08:16:52</t>
+          <t>02-02-2026 16:15:39</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>02-02-2026 16:14:45</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1908,22 +1900,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26170522288990002257</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522016110001661</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1940,12 +1924,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>219990</t>
+          <t>339800</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>17618</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1955,17 +1939,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIANA CRISTINA </t>
+          <t>BRIAN MIGUEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUILAR </t>
+          <t>AISPURO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIGUERA </t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1975,67 +1959,75 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6863372459</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6862643137</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>01-03-1990</t>
+          <t>13-12-1998</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>DIANA90HIGUERA@GMAIL.COM</t>
+          <t>PAISPURO1948@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>15-02-2024 09:29:52</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>01-02-2026 12:02:45</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>20-02-2026 16:08:52</t>
+          <t>01-02-2026 12:08:41</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>20-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>01-02-2026 12:07:33</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2043,36 +2035,36 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26170522529480002736</t>
+          <t>26170521990600001608</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>340472</t>
+          <t>310670</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18290</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2082,17 +2074,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIZABETH </t>
+          <t xml:space="preserve">OLGA </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>CARLEÑO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2102,7 +2094,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6861256955</t>
+          <t>6862097698</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2113,17 +2105,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>16-05-1978</t>
+          <t>24-02-1980</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ELYMORALESVALENZUELA@GMAIL.COM</t>
+          <t>OCARLENOHERNANDEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-02-2026 08:35:58</t>
+          <t>22-08-2025 14:08:49</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2148,12 +2140,12 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-02-2026 08:37:42</t>
+          <t>23-02-2026 14:52:33</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2170,11 +2162,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26170522033950001717</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>26170522583230002827</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>1899</t>
@@ -2182,24 +2182,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>340750</t>
+          <t>339895</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>17713</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ARMANDO</t>
+          <t>JULIO ALEJANDRO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTIZ </t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6863928150</t>
+          <t>6867371621</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2240,17 +2240,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23-02-1988</t>
+          <t>04-09-2001</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>MENTECUERPOYNUTRICION@HOTMAIL.COM</t>
+          <t>BEJARANOJULIO10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-02-2026 17:50:24</t>
+          <t>02-02-2026 08:04:32</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2265,22 +2265,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-02-2026 17:52:56</t>
+          <t>03-02-2026 07:27:31</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2297,19 +2297,27 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26170522051130001755</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>26170522032100001708</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2321,12 +2329,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>339095</t>
+          <t>339961</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2336,17 +2344,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KARLA ELDA</t>
+          <t>CELINA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ARIZMENDI</t>
+          <t xml:space="preserve">REYES </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2356,14 +2364,10 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6862168895</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>CALLE JAEN ESTE 1637</t>
-        </is>
-      </c>
+          <t>6864237570</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2371,60 +2375,56 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>01-08-1984</t>
+          <t>25-06-1996</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>KARIZMENDI2902@GMAIL.COM</t>
+          <t>EYLECELENA25@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>29-01-2026 17:00:05</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>02-02-2026 09:30:33</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-02-2026 11:21:22</t>
+          <t>12-02-2026 08:16:52</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>31-01-2026 14:54:56</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2432,23 +2432,27 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26170522006780001632</t>
+          <t>26170522288990002257</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2460,12 +2464,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>339521</t>
+          <t>340181</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>17999</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2475,17 +2479,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LIZY NAILY</t>
+          <t>SAHIRA YOMAHIRA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BRICEÑO</t>
+          <t xml:space="preserve">BAJO </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>PIZANO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2495,12 +2499,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6863079480</t>
+          <t>6862091543</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CORULLON 193</t>
+          <t>CASTILLEJA 1818</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2510,17 +2514,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19-10-2002</t>
+          <t>13-04-2003</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>LIZY.NAILY@GMAIL.COM</t>
+          <t>CUARTO.SAJIRA@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>30-01-2026 20:49:36</t>
+          <t>02-02-2026 14:35:58</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2541,7 +2545,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-02-2026 20:17:46</t>
+          <t>02-02-2026 14:42:26</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2551,7 +2555,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-02-2026 20:16:52</t>
+          <t>02-02-2026 14:40:53</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2571,19 +2575,11 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26170522022960001684</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522013230001649</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
           <t>499</t>
@@ -2591,24 +2587,24 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340249</t>
+          <t>340334</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18067</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2618,17 +2614,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANABEL </t>
+          <t>EMILY SOFIA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEARA </t>
+          <t>ARRIAGA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARCOS </t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2638,63 +2634,67 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6863957626</t>
+          <t>6864702297</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BONIFACIO AVILES 3133</t>
+          <t>AV RIOJA 160</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>26-01-1995</t>
+          <t>02-02-2006</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ANABELDEARA260195@GMAIL.COM</t>
+          <t>EMILY.ARRIAGA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-02-2026 16:10:16</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>02-02-2026 18:06:05</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-02-2026 16:15:39</t>
+          <t>05-02-2026 18:50:09</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-02-2026 16:14:45</t>
+          <t>05-02-2026 18:49:20</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2714,19 +2714,27 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26170522016110001661</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26170522116880001895</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2738,12 +2746,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>310670</t>
+          <t>340472</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>18290</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2753,17 +2761,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLGA </t>
+          <t xml:space="preserve">ELIZABETH </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CARLEÑO</t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2773,7 +2781,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6862097698</t>
+          <t>6861256955</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2784,17 +2792,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>24-02-1980</t>
+          <t>16-05-1978</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>OCARLENOHERNANDEZ@GMAIL.COM</t>
+          <t>ELYMORALESVALENZUELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>22-08-2025 14:08:49</t>
+          <t>03-02-2026 08:35:58</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2819,12 +2827,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>23-02-2026 14:52:33</t>
+          <t>03-02-2026 08:37:42</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
+          <t>03-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2841,19 +2849,11 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26170522583230002827</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
-        </is>
-      </c>
+          <t>26170522033950001717</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
           <t>1899</t>
@@ -2861,24 +2861,24 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>339898</t>
+          <t>341056</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17716</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NAYLA ALEJANDRA</t>
+          <t xml:space="preserve">EMMANUEL </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2908,28 +2908,28 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6864739006</t>
+          <t>6862034611</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>29-08-2004</t>
+          <t>03-09-2005</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>NAYLITACOTA.CHAVEZ@GMAIL.COM</t>
+          <t>EMMANUEL.PEREZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-02-2026 08:07:50</t>
+          <t>04-02-2026 15:54:17</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2944,28 +2944,28 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>03-02-2026 07:26:19</t>
+          <t>04-02-2026 15:57:00</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -2976,27 +2976,19 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26170522032040001706</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522078420001815</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3008,12 +3000,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>340181</t>
+          <t>341189</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17999</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3023,17 +3015,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SAHIRA YOMAHIRA</t>
+          <t>IVAN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAJO </t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PIZANO</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3043,32 +3035,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6862091543</t>
+          <t>6861965073</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CASTILLEJA 1818</t>
+          <t>1RA MORELOS 19</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13-04-2003</t>
+          <t>22-09-2000</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CUARTO.SAJIRA@ICLOUD.COM</t>
+          <t>IVAN.RODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-02-2026 14:35:58</t>
+          <t>04-02-2026 20:27:47</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3089,17 +3081,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-02-2026 14:42:26</t>
+          <t>04-02-2026 20:33:43</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-02-2026 14:40:53</t>
+          <t>04-02-2026 20:33:11</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3119,7 +3111,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26170522013230001649</t>
+          <t>26170522089840001847</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3143,12 +3135,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>340334</t>
+          <t>341297</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>19115</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3158,17 +3150,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EMILY SOFIA</t>
+          <t>NATALIE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ARRIAGA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3178,12 +3170,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6864702297</t>
+          <t>6861344365</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AV RIOJA 160</t>
+          <t xml:space="preserve">PORTALES </t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3193,52 +3185,48 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>02-02-2006</t>
+          <t>26-11-2004</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>EMILY.ARRIAGA@GMAIL.COM</t>
+          <t>NATALIE.RODRIGUEZ@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-02-2026 18:06:05</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 13:00:16</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>05-02-2026 18:50:09</t>
+          <t>10-02-2026 16:55:49</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>05-02-2026 18:49:20</t>
+          <t>10-02-2026 16:54:34</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3258,7 +3246,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26170522116880001895</t>
+          <t>26170522238010002133</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3273,7 +3261,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3290,12 +3278,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>341056</t>
+          <t>322246</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>19185</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3305,17 +3293,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMMANUEL </t>
+          <t>ZAIRA RAMIREZ CASTRO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3325,67 +3313,75 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6862034611</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6861234537</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LA BARRERA 323 </t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>03-09-2005</t>
+          <t>07-10-1997</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>EMMANUEL.PEREZ@GMAIL.COM</t>
+          <t>ZAIRA071097@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>04-02-2026 15:54:17</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-11-2025 16:07:36</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>04-02-2026 15:57:00</t>
+          <t>02-02-2026 17:50:01</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>02-02-2026 17:48:27</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3393,14 +3389,18 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26170522078420001815</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
+          <t>26170522019270001671</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3417,12 +3417,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>341297</t>
+          <t>340035</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19115</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3432,17 +3432,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NATALIE</t>
+          <t>KITZIA AILIME</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MAGALLON</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6861344365</t>
+          <t>6862541870</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">PORTALES </t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3467,17 +3467,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>26-11-2004</t>
+          <t>17-03-2003</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>NATALIE.RODRIGUEZ@UABC.EDU.MX</t>
+          <t>KITZIAMAGALON@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>05-02-2026 13:00:16</t>
+          <t>02-02-2026 10:57:19</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3498,17 +3498,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>10-02-2026 16:55:49</t>
+          <t>02-02-2026 11:00:49</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>10-02-2026 16:54:34</t>
+          <t>02-02-2026 11:00:21</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3528,19 +3528,11 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26170522238010002133</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522006040001630</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
           <t>499</t>
@@ -3548,7 +3540,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3560,12 +3552,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>341467</t>
+          <t>342573</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3575,17 +3567,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ADOLFO</t>
+          <t>LOURDES RENE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ALBISO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BARAJAS</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3595,32 +3587,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6862300377</t>
+          <t>6864162086</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>NORUEGA 2636</t>
+          <t>LAGO PAZCUARO SN</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>12-11-1996</t>
+          <t>21-09-1988</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ADOLFO_19962016@HOTMAIL.COM</t>
+          <t>CAMPOSLULY0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>05-02-2026 21:05:50</t>
+          <t>10-02-2026 10:01:09</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3641,17 +3633,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>05-02-2026 21:13:45</t>
+          <t>10-02-2026 10:11:12</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>05-02-2026 21:13:16</t>
+          <t>10-02-2026 10:10:28</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3671,7 +3663,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26170522120570001923</t>
+          <t>26170522227920002115</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3683,7 +3675,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Jose Luis Lopez Coronel</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3695,12 +3687,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>341189</t>
+          <t>343007</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>20824</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3710,17 +3702,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IVAN</t>
+          <t>SERGIO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>VILLARREAL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>ZEPEDA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3730,12 +3722,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6861965073</t>
+          <t>6864644967</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1RA MORELOS 19</t>
+          <t>DE LAS ESPADAS 61</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3745,17 +3737,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>22-09-2000</t>
+          <t>11-10-2001</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>IVAN.RODRIGUEZ@GMAIL.COM</t>
+          <t>ZEPEDA111001@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>04-02-2026 20:27:47</t>
+          <t>11-02-2026 15:16:45</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3776,17 +3768,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>04-02-2026 20:33:43</t>
+          <t>11-02-2026 15:30:24</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>04-02-2026 20:33:11</t>
+          <t>11-02-2026 15:29:47</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3806,7 +3798,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26170522089840001847</t>
+          <t>26170522266490002208</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3818,24 +3810,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>341295</t>
+          <t>341467</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19113</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3845,17 +3837,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FERNANDA</t>
+          <t>ADOLFO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>ALBISO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>BARAJAS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3865,32 +3857,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6865781520</t>
+          <t>6862300377</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>POTALES</t>
+          <t>NORUEGA 2636</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>13-10-2006</t>
+          <t>12-11-1996</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>FR65671@GMAIL.COM</t>
+          <t>ADOLFO_19962016@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>05-02-2026 12:58:08</t>
+          <t>05-02-2026 21:05:50</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3911,17 +3903,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>10-02-2026 16:59:22</t>
+          <t>05-02-2026 21:13:45</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>10-02-2026 16:58:27</t>
+          <t>05-02-2026 21:13:16</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3941,19 +3933,11 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26170522238110002134</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522120570001923</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
           <t>499</t>
@@ -3973,12 +3957,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>322246</t>
+          <t>342494</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19185</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3988,17 +3972,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ZAIRA RAMIREZ CASTRO</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>TEJADA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4008,12 +3992,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6861234537</t>
+          <t>6867291381</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">LA BARRERA 323 </t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4023,17 +4007,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>07-10-1997</t>
+          <t>20-06-2005</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ZAIRA071097@HOTMAIL.COM</t>
+          <t>MIGUELTEJADA317@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>05-11-2025 16:07:36</t>
+          <t>09-02-2026 20:58:55</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4054,17 +4038,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-02-2026 17:50:01</t>
+          <t>09-02-2026 21:01:56</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>02-02-2026 17:48:27</t>
+          <t>09-02-2026 21:01:07</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4074,7 +4058,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4084,14 +4068,10 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26170522019270001671</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26170522214500002093</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
@@ -4112,12 +4092,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>340035</t>
+          <t>340108</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17853</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4127,17 +4107,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KITZIA AILIME</t>
+          <t>CHRISTIAN</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MAGALLON</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4147,32 +4127,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6862541870</t>
+          <t>6866740223</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>17-03-2003</t>
+          <t>11-02-2010</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>KITZIAMAGALON@GMAIL.COM</t>
+          <t>HIELO12CV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>02-02-2026 10:57:19</t>
+          <t>02-02-2026 12:53:45</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4193,17 +4173,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>02-02-2026 11:00:49</t>
+          <t>04-02-2026 13:54:22</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>02-02-2026 11:00:21</t>
+          <t>04-02-2026 13:53:23</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4223,11 +4203,19 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26170522006040001630</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
+          <t>26170522075080001810</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>499</t>
@@ -4235,7 +4223,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4247,12 +4235,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>340108</t>
+          <t>343391</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4262,12 +4250,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t>JOSE ENRIQUE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4282,7 +4270,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6866740223</t>
+          <t>6861914185</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4297,17 +4285,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>11-02-2010</t>
+          <t>02-01-2004</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>HIELO12CV@GMAIL.COM</t>
+          <t>JG747801@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>02-02-2026 12:53:45</t>
+          <t>12-02-2026 19:39:05</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4328,17 +4316,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>04-02-2026 13:54:22</t>
+          <t>12-02-2026 19:42:59</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>04-02-2026 13:53:23</t>
+          <t>12-02-2026 19:42:26</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4358,19 +4346,11 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26170522075080001810</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522305280002308</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
           <t>499</t>
@@ -4378,7 +4358,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4390,12 +4370,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342573</t>
+          <t>342293</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4405,17 +4385,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LOURDES RENE</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CORREA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4425,32 +4405,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6864162086</t>
+          <t>6864214771</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LAGO PAZCUARO SN</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>21-09-1988</t>
+          <t>10-08-2003</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CAMPOSLULY0@GMAIL.COM</t>
+          <t>MORAERNESTO741@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10-02-2026 10:01:09</t>
+          <t>09-02-2026 16:57:09</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4471,17 +4451,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>10-02-2026 10:11:12</t>
+          <t>09-02-2026 17:02:55</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>10-02-2026 10:10:28</t>
+          <t>09-02-2026 16:59:57</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4501,7 +4481,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26170522227920002115</t>
+          <t>26170522200440002040</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4513,7 +4493,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Jose Luis Lopez Coronel</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4525,12 +4505,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342142</t>
+          <t>342851</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>20668</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4540,17 +4520,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t xml:space="preserve">JOSE JAVIE </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t xml:space="preserve">ZEPEDA </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4560,28 +4540,28 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6869453269</t>
+          <t>6863023309</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19-04-2008</t>
+          <t>22-08-2003</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>VALMACIASSA@GMAIL.COM</t>
+          <t>JV220803@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>09-02-2026 12:49:49</t>
+          <t>10-02-2026 19:47:49</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4606,12 +4586,12 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>09-02-2026 12:51:58</t>
+          <t>10-02-2026 19:49:44</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -4628,7 +4608,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26170522190930002024</t>
+          <t>26170522247770002152</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4652,12 +4632,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>343007</t>
+          <t>339095</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4667,17 +4647,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SERGIO</t>
+          <t>KARLA ELDA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VILLARREAL</t>
+          <t>ARIZMENDI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ZEPEDA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4687,32 +4667,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6864644967</t>
+          <t>6862168895</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>DE LAS ESPADAS 61</t>
+          <t>CALLE JAEN ESTE 1637</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>11-10-2001</t>
+          <t>01-08-1984</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>ZEPEDA111001@GMAIL.COM</t>
+          <t>KARIZMENDI2902@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>11-02-2026 15:16:45</t>
+          <t>29-01-2026 17:00:05</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4723,7 +4703,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -4733,17 +4713,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>11-02-2026 15:30:24</t>
+          <t>02-02-2026 11:21:22</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>11-02-2026 15:29:47</t>
+          <t>31-01-2026 14:54:56</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4753,7 +4733,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4763,10 +4743,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26170522266490002208</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
+          <t>26170522006780001632</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4775,24 +4759,24 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>342494</t>
+          <t>339521</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4802,17 +4786,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>LIZY NAILY</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TEJADA</t>
+          <t>BRICEÑO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4822,12 +4806,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6867291381</t>
+          <t>6863079480</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>CORULLON 193</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4837,17 +4821,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>20-06-2005</t>
+          <t>19-10-2002</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>MIGUELTEJADA317@ICLOUD.COM</t>
+          <t>LIZY.NAILY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>09-02-2026 20:58:55</t>
+          <t>30-01-2026 20:49:36</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4868,17 +4852,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>09-02-2026 21:01:56</t>
+          <t>02-02-2026 20:17:46</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>09-02-2026 21:01:07</t>
+          <t>02-02-2026 20:16:52</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4898,11 +4882,19 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26170522214500002093</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
+          <t>26170522022960001684</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>499</t>
@@ -4910,24 +4902,24 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>343391</t>
+          <t>339898</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21208</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4937,17 +4929,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>JOSE ENRIQUE</t>
+          <t>NAYLA ALEJANDRA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4957,75 +4949,67 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6861914185</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6864739006</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>02-01-2004</t>
+          <t>29-08-2004</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>JG747801@GMAIL.COM</t>
+          <t>NAYLITACOTA.CHAVEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>12-02-2026 19:39:05</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>02-02-2026 08:07:50</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>12-02-2026 19:42:59</t>
+          <t>03-02-2026 07:26:19</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>12-02-2026 19:42:26</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5033,14 +5017,22 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26170522305280002308</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+          <t>26170522032040001706</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -5057,12 +5049,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>342851</t>
+          <t>340183</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20668</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5072,17 +5064,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE JAVIE </t>
+          <t>LEYLANI MIRANDA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZEPEDA </t>
+          <t>PIZANO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5092,67 +5084,67 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6863023309</t>
+          <t>6863558685</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>22-08-2003</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>JV220803@GMAIL.COM</t>
-        </is>
-      </c>
+          <t>03-11-2011</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>10-02-2026 19:47:49</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 14:41:17</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>10-02-2026 19:49:44</t>
+          <t>02-02-2026 14:46:51</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>02-02-2026 14:45:55</t>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5160,36 +5152,36 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26170522247770002152</t>
+          <t>26170522013390001650</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>342843</t>
+          <t>340231</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20660</t>
+          <t>18049</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5199,17 +5191,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS </t>
+          <t>ELLIOT SAMUEL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ORTIZ</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BARAJAS</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5219,12 +5211,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6862437298</t>
+          <t>6866507552</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>AV GOLETA 1807</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5234,17 +5226,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>01-09-1989</t>
+          <t>09-08-1998</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ERREDOS8@GMAIL.COM</t>
+          <t>ELLIOT.MORA@UABC.COM.MX</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10-02-2026 19:36:54</t>
+          <t>02-02-2026 15:50:44</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5265,17 +5257,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>10-02-2026 19:46:13</t>
+          <t>02-02-2026 15:56:47</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>10-02-2026 19:40:58</t>
+          <t>02-02-2026 15:54:59</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5285,7 +5277,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5295,7 +5287,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26170522247630002151</t>
+          <t>26170522015420001658</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5319,12 +5311,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>340183</t>
+          <t>343401</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18001</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5334,17 +5326,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LEYLANI MIRANDA</t>
+          <t>CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t xml:space="preserve">ZEPEDA </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PIZANO</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5354,67 +5346,67 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6863558685</t>
+          <t>6862110739</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>03-11-2011</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+          <t>06-08-1987</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>ZEPEDACOTAC@GMAIL.COM</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>02-02-2026 14:41:17</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>12-02-2026 21:09:33</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>02-02-2026 14:46:51</t>
+          <t>12-02-2026 21:11:55</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>02-02-2026 14:45:55</t>
-        </is>
-      </c>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5422,36 +5414,36 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26170522013390001650</t>
+          <t>26170522306850002321</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>340231</t>
+          <t>340441</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>18259</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5461,17 +5453,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ELLIOT SAMUEL</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5481,12 +5473,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6866507552</t>
+          <t>6674121912</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AV GOLETA 1807</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5496,17 +5488,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>09-08-1998</t>
+          <t>07-10-2003</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ELLIOT.MORA@UABC.COM.MX</t>
+          <t>FELIZLUISFERNANDO3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>02-02-2026 15:50:44</t>
+          <t>03-02-2026 07:13:43</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5527,17 +5519,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>02-02-2026 15:56:47</t>
+          <t>03-02-2026 07:19:00</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>02-02-2026 15:54:59</t>
+          <t>03-02-2026 07:18:37</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5557,7 +5549,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26170522015420001658</t>
+          <t>26170522031900001705</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5569,7 +5561,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5581,12 +5573,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>342293</t>
+          <t>341159</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20111</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5596,17 +5588,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>DAVID ERNESTO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CORREA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5616,14 +5608,10 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6864214771</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6863409250</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5631,60 +5619,56 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>10-08-2003</t>
+          <t>28-08-2011</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>MORAERNESTO741@GMAIL.COM</t>
+          <t>DAVID.ERNESTO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>09-02-2026 16:57:09</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>04-02-2026 19:08:30</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>09-02-2026 17:02:55</t>
+          <t>04-02-2026 19:10:17</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>09-02-2026 16:59:57</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5692,14 +5676,14 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26170522200440002040</t>
+          <t>26170522087360001828</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5716,12 +5700,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>343401</t>
+          <t>340564</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21218</t>
+          <t>18382</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5731,17 +5715,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO</t>
+          <t>JOSE MANUEL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZEPEDA </t>
+          <t>MONTOYA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>REA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5751,7 +5735,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6862110739</t>
+          <t>6865860740</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5762,17 +5746,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>06-08-1987</t>
+          <t>27-12-1976</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>ZEPEDACOTAC@GMAIL.COM</t>
+          <t>REA1628JOSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>12-02-2026 21:09:33</t>
+          <t>03-02-2026 13:24:47</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5787,22 +5771,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>12-02-2026 21:11:55</t>
+          <t>03-02-2026 13:26:26</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -5819,14 +5803,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26170522306850002321</t>
+          <t>26170522039620001735</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5843,12 +5827,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>342857</t>
+          <t>342843</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5858,17 +5842,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>JORGE</t>
+          <t xml:space="preserve">CARLOS </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">JIMENEZ </t>
+          <t>ORTIZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>BARAJAS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5878,7 +5862,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6861387777</t>
+          <t>6862437298</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5893,17 +5877,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>14-08-1972</t>
+          <t>01-09-1989</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>JORGEJIMENEZSOTO1994@GMAIL.COM</t>
+          <t>ERREDOS8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>10-02-2026 19:59:00</t>
+          <t>10-02-2026 19:36:54</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5924,7 +5908,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>10-02-2026 20:04:31</t>
+          <t>10-02-2026 19:46:13</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5934,7 +5918,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>10-02-2026 20:04:01</t>
+          <t>10-02-2026 19:40:58</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5954,7 +5938,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26170522248340002163</t>
+          <t>26170522247630002151</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -5978,12 +5962,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>340441</t>
+          <t>342857</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>20674</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5993,17 +5977,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>JORGE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t xml:space="preserve">JIMENEZ </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6013,7 +5997,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6674121912</t>
+          <t>6861387777</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -6028,17 +6012,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>07-10-2003</t>
+          <t>14-08-1972</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>FELIZLUISFERNANDO3@GMAIL.COM</t>
+          <t>JORGEJIMENEZSOTO1994@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>03-02-2026 07:13:43</t>
+          <t>10-02-2026 19:59:00</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -6059,17 +6043,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>03-02-2026 07:19:00</t>
+          <t>10-02-2026 20:04:31</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>03-02-2026 07:18:37</t>
+          <t>10-02-2026 20:04:01</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6079,7 +6063,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -6089,7 +6073,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26170522031900001705</t>
+          <t>26170522248340002163</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6101,7 +6085,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -6113,12 +6097,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>340564</t>
+          <t>341295</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6128,17 +6112,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>JOSE MANUEL</t>
+          <t>FERNANDA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>REA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6148,67 +6132,75 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6865860740</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>6865781520</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>POTALES</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>27-12-1976</t>
+          <t>13-10-2006</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>REA1628JOSE@GMAIL.COM</t>
+          <t>FR65671@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>03-02-2026 13:24:47</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 12:58:08</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>03-02-2026 13:26:26</t>
+          <t>10-02-2026 16:59:22</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>10-02-2026 16:58:27</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6216,19 +6208,27 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26170522039620001735</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
+          <t>26170522238110002134</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6375,12 +6375,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>341159</t>
+          <t>345451</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>18977</t>
+          <t>87616</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6390,17 +6390,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DAVID ERNESTO</t>
+          <t>RAMONA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6410,67 +6410,75 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6863409250</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>6861238114</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>PORALES</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>28-08-2011</t>
+          <t>02-03-1979</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>DAVID.ERNESTO@GMAIL.COM</t>
+          <t>GARENE1976@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>04-02-2026 19:08:30</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>21-02-2026 07:31:03</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>04-02-2026 19:10:17</t>
+          <t>23-02-2026 07:43:05</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>23-02-2026 07:42:26</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6478,19 +6486,27 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26170522087360001828</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
+          <t>26170522572930002811</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6502,12 +6518,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>345451</t>
+          <t>342142</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>87616</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6517,17 +6533,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>RAMONA</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6537,14 +6553,10 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6861238114</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>PORALES</t>
-        </is>
-      </c>
+          <t>6869453269</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6552,60 +6564,56 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>02-03-1979</t>
+          <t>19-04-2008</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>GARENE1976@GMAIL.COM</t>
+          <t>VALMACIASSA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>21-02-2026 07:31:03</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>09-02-2026 12:49:49</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>23-02-2026 07:43:05</t>
+          <t>09-02-2026 12:51:58</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>23-02-2026 07:42:26</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6613,22 +6621,14 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26170522572930002811</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170522190930002024</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
@@ -6645,12 +6645,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>343975</t>
+          <t>344019</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21792</t>
+          <t>21836</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6660,17 +6660,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MARIA ISABEL</t>
+          <t>ABRHAM ISACC</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PEREYDA</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>KETCHUL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6680,57 +6680,53 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6861945257</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>AVENIDA MONTES DE LEON 2027</t>
-        </is>
-      </c>
+          <t>6861255888</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>24-08-1995</t>
+          <t>12-07-1992</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ISABELPEREYDA24@GMAIL.COM</t>
+          <t>ABRAHAM.SKET1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>16-02-2026 08:43:39</t>
+          <t>16-02-2026 11:31:00</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>16-02-2026 08:52:04</t>
+          <t>16-02-2026 11:32:22</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -6738,21 +6734,13 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>16-02-2026 08:51:31</t>
-        </is>
-      </c>
+      <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6760,19 +6748,19 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26170522381670002419</t>
+          <t>26170522385460002427</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6784,12 +6772,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>343982</t>
+          <t>343975</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21799</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6799,17 +6787,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">JENNIFER </t>
+          <t>MARIA ISABEL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FAVELA</t>
+          <t>PEREYDA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6819,12 +6807,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6863626144</t>
+          <t>6861945257</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>AVENIDA MONTES DE LEON 2027</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6834,17 +6822,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>11-12-2001</t>
+          <t>24-08-1995</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>FAVELAPEREZVZ11@GMAIL.COM</t>
+          <t>ISABELPEREYDA24@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>16-02-2026 09:07:20</t>
+          <t>16-02-2026 08:43:39</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -6869,7 +6857,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>16-02-2026 09:11:41</t>
+          <t>16-02-2026 08:52:04</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -6879,7 +6867,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>16-02-2026 09:11:13</t>
+          <t>16-02-2026 08:51:31</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -6889,7 +6877,7 @@
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
@@ -6899,7 +6887,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26170522382170002420</t>
+          <t>26170522381670002419</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -6923,12 +6911,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>344019</t>
+          <t>343982</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>21799</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6938,17 +6926,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ABRHAM ISACC</t>
+          <t xml:space="preserve">JENNIFER </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>FAVELA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KETCHUL</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6958,53 +6946,57 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6861255888</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>6863626144</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>12-07-1992</t>
+          <t>11-12-2001</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>ABRAHAM.SKET1@GMAIL.COM</t>
+          <t>FAVELAPEREZVZ11@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>16-02-2026 11:31:00</t>
+          <t>16-02-2026 09:07:20</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>16-02-2026 11:32:22</t>
+          <t>16-02-2026 09:11:41</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -7012,13 +7004,21 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>16-02-2026 09:11:13</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7026,19 +7026,19 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26170522385460002427</t>
+          <t>26170522382170002420</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7050,12 +7050,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>344362</t>
+          <t>342676</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22179</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7065,17 +7065,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDREA MICHELL </t>
+          <t>VIVIAN DENIISSE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>URIBE</t>
+          <t>MELERO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6863837971</t>
+          <t>6644940465</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>HERENCIA 2338</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7100,24 +7100,20 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>15-08-2000</t>
+          <t>19-06-1981</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>ANDREAESTRADA1218@ICLOUD.COM</t>
+          <t>VIVIANDEFELIX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>16-02-2026 21:04:29</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 15:37:05</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7135,17 +7131,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>16-02-2026 21:14:42</t>
+          <t>10-02-2026 15:40:14</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>16-02-2026 21:12:23</t>
+          <t>10-02-2026 15:39:43</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7165,7 +7161,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26170522411380002496</t>
+          <t>26170522235040002127</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7177,7 +7173,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7189,12 +7185,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>344524</t>
+          <t>342495</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22341</t>
+          <t>20312</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7204,17 +7200,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>GERARDO ANTONIO</t>
+          <t xml:space="preserve">NELSON </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBAÑEZ </t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MANCILLA</t>
+          <t>MARISCAL</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7224,14 +7220,10 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6861832430</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>BASTIA 2595</t>
-        </is>
-      </c>
+          <t>6861420567</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7239,60 +7231,56 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>01-02-1966</t>
+          <t>28-10-1996</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>GERARDO.ANTONIO@GMAIL.COM</t>
+          <t>NELSON.1028@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>17-02-2026 15:20:45</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>09-02-2026 21:04:58</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>23-02-2026 16:27:39</t>
+          <t>09-02-2026 21:06:43</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>23-02-2026 16:25:27</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7300,44 +7288,36 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26170522587090002838</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522214560002094</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>345036</t>
+          <t>344362</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>87201</t>
+          <t>22179</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7347,17 +7327,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NORMA ALICIA</t>
+          <t xml:space="preserve">ANDREA MICHELL </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">MERCADO </t>
+          <t>URIBE</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7367,12 +7347,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6863291327</t>
+          <t>6863837971</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>POMONA 2446</t>
+          <t>HERENCIA 2338</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7382,20 +7362,24 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>03-11-1976</t>
+          <t>15-08-2000</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>NORMAAGUTIERREZM@HOTMAIL.COM</t>
+          <t>ANDREAESTRADA1218@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>19-02-2026 11:31:06</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>16-02-2026 21:04:29</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7403,7 +7387,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
@@ -7413,17 +7397,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>19-02-2026 12:01:32</t>
+          <t>16-02-2026 21:14:42</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>19-02-2026 11:44:54</t>
+          <t>16-02-2026 21:12:23</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7443,7 +7427,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26170522492340002663</t>
+          <t>26170522411380002496</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7455,24 +7439,24 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>342676</t>
+          <t>344524</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7482,17 +7466,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VIVIAN DENIISSE</t>
+          <t>GERARDO ANTONIO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t xml:space="preserve">IBAÑEZ </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MELERO</t>
+          <t>MANCILLA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7502,32 +7486,32 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6644940465</t>
+          <t>6861832430</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>BASTIA 2595</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>19-06-1981</t>
+          <t>01-02-1966</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>VIVIANDEFELIX@GMAIL.COM</t>
+          <t>GERARDO.ANTONIO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>10-02-2026 15:37:05</t>
+          <t>17-02-2026 15:20:45</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -7538,7 +7522,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -7548,17 +7532,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10-02-2026 15:40:14</t>
+          <t>23-02-2026 16:27:39</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>10-02-2026 15:39:43</t>
+          <t>23-02-2026 16:25:27</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7578,11 +7562,19 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26170522235040002127</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
+          <t>26170522587090002838</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>499</t>
@@ -7590,24 +7582,24 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>344864</t>
+          <t>345849</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22681</t>
+          <t>88014</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7617,17 +7609,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ELIAS ABDIEL</t>
+          <t>RUTH ERENDIRA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>SERMEÑO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7637,32 +7629,32 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6865902031</t>
+          <t>6865695069</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>COLUMBUS  1325</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>20-04-2005</t>
+          <t>12-09-1992</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>ELIASMORENO052@GMAIL.COM</t>
+          <t>RUTHSERMENO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>18-02-2026 16:30:39</t>
+          <t>23-02-2026 15:50:40</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7687,17 +7679,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>18-02-2026 16:40:13</t>
+          <t>23-02-2026 15:54:43</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>18-02-2026 16:34:10</t>
+          <t>23-02-2026 15:54:01</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7707,7 +7699,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7717,7 +7709,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26170522466910002616</t>
+          <t>26170522585670002834</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
@@ -7741,12 +7733,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>345453</t>
+          <t>345872</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>87618</t>
+          <t>88037</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7756,17 +7748,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>RENE FRANCISCO</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>AMEZQUITA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7776,12 +7768,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6863948826</t>
+          <t>6862605035</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CASA DIGNA</t>
+          <t>BOSQUE CIRUELOS 853</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7791,38 +7783,42 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>17-02-1976</t>
+          <t>22-09-2000</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>RENEGARCIA170296@GMAIL.COM</t>
+          <t>BBMIGUEL28@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>21-02-2026 07:40:19</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>23-02-2026 16:30:33</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>23-02-2026 07:36:13</t>
+          <t>23-02-2026 16:34:54</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -7832,7 +7828,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>23-02-2026 07:35:10</t>
+          <t>23-02-2026 16:34:22</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7852,44 +7848,36 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26170522572740002810</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170522587570002839</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>342495</t>
+          <t>342853</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>20670</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7899,17 +7887,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">NELSON </t>
+          <t>DAMARIS KATHELEEN</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MARISCAL</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7919,7 +7907,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6861420567</t>
+          <t>6861330533</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7930,17 +7918,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>28-10-1996</t>
+          <t>26-02-2007</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>NELSON.1028@HOTMAIL.COM</t>
+          <t>DAMARISK.SLOPEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>09-02-2026 21:04:58</t>
+          <t>10-02-2026 19:51:12</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -7955,22 +7943,22 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>09-02-2026 21:06:43</t>
+          <t>10-02-2026 19:53:06</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>10-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -7987,14 +7975,14 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26170522214560002094</t>
+          <t>26170522247900002153</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -8011,12 +7999,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>345849</t>
+          <t>344864</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>88014</t>
+          <t>22681</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8026,17 +8014,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>RUTH ERENDIRA</t>
+          <t>ELIAS ABDIEL</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SERMEÑO</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8046,32 +8034,32 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6865695069</t>
+          <t>6865902031</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>COLUMBUS  1325</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>12-09-1992</t>
+          <t>20-04-2005</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>RUTHSERMENO@GMAIL.COM</t>
+          <t>ELIASMORENO052@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>23-02-2026 15:50:40</t>
+          <t>18-02-2026 16:30:39</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8096,17 +8084,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>23-02-2026 15:54:43</t>
+          <t>18-02-2026 16:40:13</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>23-02-2026 15:54:01</t>
+          <t>18-02-2026 16:34:10</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8116,7 +8104,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -8126,7 +8114,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26170522585670002834</t>
+          <t>26170522466910002616</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
@@ -8150,12 +8138,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>345872</t>
+          <t>345453</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>88037</t>
+          <t>87618</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8165,17 +8153,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>RENE FRANCISCO</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AMEZQUITA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8185,12 +8173,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6862605035</t>
+          <t>6863948826</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>BOSQUE CIRUELOS 853</t>
+          <t>CASA DIGNA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8200,42 +8188,38 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>22-09-2000</t>
+          <t>17-02-1976</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BBMIGUEL28@GMAIL.COM</t>
+          <t>RENEGARCIA170296@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>23-02-2026 16:30:33</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>21-02-2026 07:40:19</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>23-02-2026 16:34:54</t>
+          <t>23-02-2026 07:36:13</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -8245,7 +8229,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>23-02-2026 16:34:22</t>
+          <t>23-02-2026 07:35:10</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8265,36 +8249,44 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26170522587570002839</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
+          <t>26170522572740002810</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>342853</t>
+          <t>346065</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20670</t>
+          <t>88230</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8304,17 +8296,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DAMARIS KATHELEEN</t>
+          <t xml:space="preserve">LUZ ELENA </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t xml:space="preserve">BERNAL </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8324,67 +8316,79 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6861330533</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>6861751473</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>C ISLAS ORCADAS 1927</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>26-02-2007</t>
+          <t>06-09-1973</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>DAMARISK.SLOPEZ@GMAIL.COM</t>
+          <t>PDGA.LUZVERNAL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>10-02-2026 19:51:12</t>
+          <t>24-02-2026 06:11:46</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>10-02-2026 19:53:06</t>
+          <t>25-02-2026 06:08:41</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>10-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr"/>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>25-02-2026 06:07:15</t>
+        </is>
+      </c>
       <c r="U59" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W59" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8392,19 +8396,27 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26170522247900002153</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
+          <t>26170522640790002973</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -8416,12 +8428,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>343240</t>
+          <t>346148</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>88313</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8431,95 +8443,99 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>HECTOR EDUARDO</t>
+          <t xml:space="preserve">LINDA PATRICIA </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CANALES</t>
+          <t xml:space="preserve">PERAZA </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6692315071</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>PASEO DEL REAL 455</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>25-10-1986</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>LPPERAZG@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>24-02-2026 13:10:41</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>24-02-2026 13:17:17</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>24-02-2026 13:15:52</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>7602343861</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>C PASEO DEL AGUA 456</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>05-02-1997</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>HECTORCANALESLEYVA@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:48:03</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Forzoso</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>PROMO FEBRERO 12 MESES</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:53:41</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:53:05</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="W60" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8527,7 +8543,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26170522292940002271</t>
+          <t>26170522618830002912</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
@@ -8539,24 +8555,24 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>343394</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>21057</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8566,87 +8582,95 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BRIANA NAOMI</t>
+          <t>HECTOR EDUARDO</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>CANALES</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6867481654</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>7602343861</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>C PASEO DEL AGUA 456</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>05-02-2011</t>
+          <t>05-02-1997</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>NAOMIDOM2011@ICLOUD.COM</t>
+          <t>HECTORCANALESLEYVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>12-02-2026 20:07:03</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 12:48:03</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>13-02-2026 17:16:34</t>
+          <t>12-02-2026 12:53:41</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>12-02-2026 12:53:05</t>
+        </is>
+      </c>
       <c r="U61" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8654,22 +8678,14 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26170522326050002356</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170522292940002271</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
@@ -8686,12 +8702,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>343969</t>
+          <t>343394</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>21211</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8701,17 +8717,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO</t>
+          <t>BRIANA NAOMI</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ALCARAZ</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8721,28 +8737,28 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6462016615</t>
+          <t>6867481654</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>05-11-2009</t>
+          <t>05-02-2011</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>AR7481660@GMAIL.COM</t>
+          <t>NAOMIDOM2011@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>16-02-2026 08:36:28</t>
+          <t>12-02-2026 20:07:03</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -8767,12 +8783,12 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>16-02-2026 08:38:13</t>
+          <t>13-02-2026 17:16:34</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -8789,11 +8805,19 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26170522381280002417</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
+          <t>26170522326050002356</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>549</t>
@@ -8813,12 +8837,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>344075</t>
+          <t>343969</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21892</t>
+          <t>21786</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8828,17 +8852,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA </t>
+          <t>LUIS ALBERTO</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t>ALCARAZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BACA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8848,57 +8872,53 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6681446837</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>AV BURGUETE 41</t>
-        </is>
-      </c>
+          <t>6462016615</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>04-11-1987</t>
+          <t>05-11-2009</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>GABYISA.0104@GMAIL.COM</t>
+          <t>AR7481660@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>16-02-2026 13:40:14</t>
+          <t>16-02-2026 08:36:28</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>16-02-2026 13:47:19</t>
+          <t>16-02-2026 08:38:13</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -8906,21 +8926,13 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>16-02-2026 13:46:36</t>
-        </is>
-      </c>
+      <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8928,19 +8940,19 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26170522389180002437</t>
+          <t>26170522381280002417</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -9091,12 +9103,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>344087</t>
+          <t>345036</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21904</t>
+          <t>87201</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9106,17 +9118,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ROSARIO GUADALUPE</t>
+          <t>NORMA ALICIA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t xml:space="preserve">MERCADO </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9126,12 +9138,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6863182471</t>
+          <t>6863291327</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CALLE GILAS1892</t>
+          <t>POMONA 2446</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -9141,24 +9153,20 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>06-10-1991</t>
+          <t>03-11-1976</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>GARCIAGUADALUPE7414@HOTMAIL.COM</t>
+          <t>NORMAAGUTIERREZM@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>16-02-2026 14:05:34</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>19-02-2026 11:31:06</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9166,7 +9174,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -9176,17 +9184,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>16-02-2026 14:10:44</t>
+          <t>19-02-2026 12:01:32</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>16-02-2026 14:10:01</t>
+          <t>19-02-2026 11:44:54</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9196,7 +9204,7 @@
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -9206,7 +9214,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26170522389780002438</t>
+          <t>26170522492340002663</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
@@ -9218,24 +9226,24 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>344869</t>
+          <t>344075</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22686</t>
+          <t>21892</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9245,17 +9253,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEVIN MISAEL </t>
+          <t xml:space="preserve">GABRIELA </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>BACA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9265,12 +9273,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6861053368</t>
+          <t>6681446837</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>AV BURGUETE 41</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -9280,17 +9288,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>24-12-2004</t>
+          <t>04-11-1987</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>KEVINRAMIREZ2412@GMAIL.COM</t>
+          <t>GABYISA.0104@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>18-02-2026 16:38:43</t>
+          <t>16-02-2026 13:40:14</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9315,17 +9323,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:20</t>
+          <t>16-02-2026 13:47:19</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>18-02-2026 16:43:02</t>
+          <t>16-02-2026 13:46:36</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -9335,7 +9343,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -9345,7 +9353,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26170522467160002617</t>
+          <t>26170522389180002437</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
@@ -9357,7 +9365,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -9369,12 +9377,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>346044</t>
+          <t>344087</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>88209</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9384,17 +9392,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CAMILA</t>
+          <t>ROSARIO GUADALUPE</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9404,12 +9412,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6863403745</t>
+          <t>6863182471</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSQUE TROPICAL </t>
+          <t>CALLE GILAS1892</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9419,17 +9427,17 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>19-08-2004</t>
+          <t>06-10-1991</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CAMILA.CONSULTORIOWORK@GMAIL.COM</t>
+          <t>GARCIAGUADALUPE7414@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>23-02-2026 20:18:53</t>
+          <t>16-02-2026 14:05:34</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -9454,17 +9462,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>23-02-2026 20:25:35</t>
+          <t>16-02-2026 14:10:44</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>23-02-2026 20:24:56</t>
+          <t>16-02-2026 14:10:01</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -9474,7 +9482,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -9484,7 +9492,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26170522601620002882</t>
+          <t>26170522389780002438</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
@@ -9496,12 +9504,723 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>346035</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>88200</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>MUÑOZ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>HERRERA</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>6861618654</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GERONIMO 2675 </t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>08-08-1994</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>ALEJANDRO.MUNOZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:51:28</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>24-02-2026 20:10:23</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>24-02-2026 20:09:41</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>26170522636500002957</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
+      <c r="AC68" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>344869</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>22686</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEVIN MISAEL </t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMIREZ </t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>6861053368</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>24-12-2004</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>KEVINRAMIREZ2412@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>18-02-2026 16:38:43</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>18-02-2026 16:45:20</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>18-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>18-02-2026 16:43:02</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>26170522467160002617</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>Alexa Johana  Haro</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>345642</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>87807</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LUIS</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>COVARRUBIAS</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>TELLEZ</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>6865705647</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>TAXQUEÑA 1135</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>11-08-1999</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>LTELLEZ945@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>23-02-2026 05:17:04</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>25-02-2026 07:13:43</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>25-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>25-02-2026 07:11:39</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>26170522645430002976</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Saul  Galeana</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>345689</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>87854</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>BRAYAN ALEXIS</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>GUZMAN</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6861096516</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>NOTREDAME OESTE 295</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>27-09-1995</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>DECKSARIA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>23-02-2026 09:56:35</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>24-02-2026 10:26:50</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>24-02-2026 10:26:08</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>26170522615550002903</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Saul  Galeana</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>346044</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>88209</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>CAMILA</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>VALDEZ</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6863403745</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOSQUE TROPICAL </t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>19-08-2004</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>CAMILA.CONSULTORIOWORK@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:18:53</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:25:35</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>23-02-2026 20:24:56</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>26170522601620002882</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Alexa Johana  Haro</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,12 +852,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>134792</t>
+          <t>75553</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32440</t>
+          <t>73366</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -867,17 +867,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRANCISCO ALEXANDER </t>
+          <t>DANIEL ALEJANDRO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOTO </t>
+          <t xml:space="preserve">ROMERO </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VILLAMAN</t>
+          <t>QUIJADA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6863847095</t>
+          <t>6863466296</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AV. PINILLO 2898</t>
+          <t>NERVA 118</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -902,52 +902,48 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>26-06-2003</t>
+          <t>25-06-2003</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ALEXANDERVILLAMAN@HOTMAIL.COM</t>
+          <t>DANIELQUIJADA2532@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>14-11-2022 21:53:57</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>28-02-2022 17:04:02</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>10-02-2026 16:48:07</t>
+          <t>02-02-2026 14:23:09</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>10-02-2026 16:46:53</t>
+          <t>02-02-2026 14:22:48</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -957,7 +953,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -967,19 +963,19 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26170522237640002130</t>
+          <t>26170522012560001648</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -991,12 +987,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>75553</t>
+          <t>134792</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>73366</t>
+          <t>32440</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +1002,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DANIEL ALEJANDRO</t>
+          <t xml:space="preserve">FRANCISCO ALEXANDER </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROMERO </t>
+          <t xml:space="preserve">SOTO </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>QUIJADA</t>
+          <t>VILLAMAN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,12 +1022,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6863466296</t>
+          <t>6863847095</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NERVA 118</t>
+          <t>AV. PINILLO 2898</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1041,48 +1037,52 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25-06-2003</t>
+          <t>26-06-2003</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>DANIELQUIJADA2532@GMAIL.COM</t>
+          <t>ALEXANDERVILLAMAN@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>28-02-2022 17:04:02</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>14-11-2022 21:53:57</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-02-2026 14:23:09</t>
+          <t>10-02-2026 16:48:07</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-02-2026 14:22:48</t>
+          <t>10-02-2026 16:46:53</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1102,19 +1102,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26170522012560001648</t>
+          <t>26170522237640002130</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1126,12 +1126,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>118108</t>
+          <t>44694</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>42557</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1141,17 +1141,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO</t>
+          <t>ARMANDO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t xml:space="preserve">GAONA </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6865298916</t>
+          <t>6863670678</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HACIENDA SAN ROQUE</t>
+          <t>DESTREZA 2781</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1176,24 +1176,20 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>03-07-1996</t>
+          <t>03-03-2001</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>J.ANTONIO.CRUZ.CARDENAS@GMAIL.COM</t>
+          <t>GAONA03@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>23-08-2022 19:27:05</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>16-08-2021 18:26:38</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1201,7 +1197,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1211,17 +1207,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>17-02-2026 14:14:53</t>
+          <t>26-02-2026 15:54:17</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>17-02-2026 14:13:03</t>
+          <t>26-02-2026 15:53:42</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1241,7 +1237,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26170522429040002526</t>
+          <t>26170522685730003058</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1253,24 +1249,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>183590</t>
+          <t>118108</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81097</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1280,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIAN </t>
+          <t>JOSE ANTONIO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1300,12 +1296,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6864295199</t>
+          <t>6865298916</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GALATEA 245</t>
+          <t>HACIENDA SAN ROQUE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1315,20 +1311,24 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>18-12-1993</t>
+          <t>03-07-1996</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BRIAN.GONZALEZ@UABC.EDU.MX</t>
+          <t>J.ANTONIO.CRUZ.CARDENAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>11-07-2023 17:00:27</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>23-08-2022 19:27:05</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-02-2026 15:48:32</t>
+          <t>17-02-2026 14:14:53</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-02-2026 15:47:32</t>
+          <t>17-02-2026 14:13:03</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26170522015130001656</t>
+          <t>26170522429040002526</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1400,12 +1400,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>338245</t>
+          <t>183590</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>81097</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MARIA FERNANDA</t>
+          <t xml:space="preserve">BRIAN </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>COSSIO</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,67 +1435,75 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6862641454</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6864295199</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>GALATEA 245</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>28-07-1999</t>
+          <t>18-12-1993</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FM7098082@GMAIL.COM</t>
+          <t>BRIAN.GONZALEZ@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>27-01-2026 05:22:15</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-07-2023 17:00:27</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>17-02-2026 05:01:55</t>
+          <t>02-02-2026 15:48:32</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>17-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>02-02-2026 15:47:32</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1503,27 +1511,19 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26170522413330002499</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Mariana Daniela Romero Cruz</t>
-        </is>
-      </c>
+          <t>26170522015130001656</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1662,12 +1662,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>340750</t>
+          <t>338245</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>16063</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ARMANDO</t>
+          <t>MARIA FERNANDA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTIZ </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>COSSIO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1697,28 +1697,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6863928150</t>
+          <t>6862641454</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>23-02-1988</t>
+          <t>28-07-1999</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>MENTECUERPOYNUTRICION@HOTMAIL.COM</t>
+          <t>FM7098082@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>03-02-2026 17:50:24</t>
+          <t>27-01-2026 05:22:15</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1733,28 +1733,28 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-02-2026 17:52:56</t>
+          <t>17-02-2026 05:01:55</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
+          <t>17-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1765,19 +1765,27 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26170522051130001755</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26170522413330002499</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Mariana Daniela Romero Cruz</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1789,12 +1797,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>340249</t>
+          <t>339800</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18067</t>
+          <t>17618</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,17 +1812,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANABEL </t>
+          <t>BRIAN MIGUEL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DEARA </t>
+          <t>AISPURO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ARCOS </t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1824,32 +1832,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6863957626</t>
+          <t>6862643137</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>BONIFACIO AVILES 3133</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>26-01-1995</t>
+          <t>13-12-1998</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ANABELDEARA260195@GMAIL.COM</t>
+          <t>PAISPURO1948@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-02-2026 16:10:16</t>
+          <t>01-02-2026 12:02:45</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1870,17 +1878,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-02-2026 16:15:39</t>
+          <t>01-02-2026 12:08:41</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>01-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>02-02-2026 16:14:45</t>
+          <t>01-02-2026 12:07:33</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1900,7 +1908,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26170522016110001661</t>
+          <t>26170521990600001608</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1924,12 +1932,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>339800</t>
+          <t>339895</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17618</t>
+          <t>17713</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1939,17 +1947,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BRIAN MIGUEL</t>
+          <t>JULIO ALEJANDRO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AISPURO</t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1959,14 +1967,10 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6862643137</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6867371621</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1974,60 +1978,56 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>13-12-1998</t>
+          <t>04-09-2001</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PAISPURO1948@GMAIL.COM</t>
+          <t>BEJARANOJULIO10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>01-02-2026 12:02:45</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>02-02-2026 08:04:32</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>01-02-2026 12:08:41</t>
+          <t>03-02-2026 07:27:31</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>01-02-2026 12:07:33</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2035,19 +2035,27 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26170521990600001608</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>26170522032100001708</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2059,12 +2067,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>310670</t>
+          <t>339961</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2074,17 +2082,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLGA </t>
+          <t>CELINA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CARLEÑO</t>
+          <t xml:space="preserve">REYES </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2094,7 +2102,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6862097698</t>
+          <t>6864237570</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2105,17 +2113,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>24-02-1980</t>
+          <t>25-06-1996</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>OCARLENOHERNANDEZ@GMAIL.COM</t>
+          <t>EYLECELENA25@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>22-08-2025 14:08:49</t>
+          <t>02-02-2026 09:30:33</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2130,22 +2138,22 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>23-02-2026 14:52:33</t>
+          <t>12-02-2026 08:16:52</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2162,7 +2170,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26170522583230002827</t>
+          <t>26170522288990002257</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2172,34 +2180,34 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>339895</t>
+          <t>340181</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17713</t>
+          <t>17999</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2209,17 +2217,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JULIO ALEJANDRO</t>
+          <t>SAHIRA YOMAHIRA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t xml:space="preserve">BAJO </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>PIZANO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2229,67 +2237,75 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6867371621</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>6862091543</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>CASTILLEJA 1818</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>04-09-2001</t>
+          <t>13-04-2003</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>BEJARANOJULIO10@GMAIL.COM</t>
+          <t>CUARTO.SAJIRA@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-02-2026 08:04:32</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 14:35:58</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-02-2026 07:27:31</t>
+          <t>02-02-2026 14:42:26</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>02-02-2026 14:40:53</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2297,27 +2313,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26170522032100001708</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522013230001649</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2329,12 +2337,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>339961</t>
+          <t>340334</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17779</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2344,17 +2352,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CELINA</t>
+          <t>EMILY SOFIA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">REYES </t>
+          <t>ARRIAGA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2364,10 +2372,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6864237570</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6864702297</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>AV RIOJA 160</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2375,17 +2387,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>25-06-1996</t>
+          <t>02-02-2006</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>EYLECELENA25@GMAIL.COM</t>
+          <t>EMILY.ARRIAGA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-02-2026 09:30:33</t>
+          <t>02-02-2026 18:06:05</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2395,36 +2407,44 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>12-02-2026 08:16:52</t>
+          <t>05-02-2026 18:50:09</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>05-02-2026 18:49:20</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2432,7 +2452,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26170522288990002257</t>
+          <t>26170522116880001895</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2442,17 +2462,17 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2464,12 +2484,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>340181</t>
+          <t>340472</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17999</t>
+          <t>18290</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2479,17 +2499,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SAHIRA YOMAHIRA</t>
+          <t xml:space="preserve">ELIZABETH </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAJO </t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PIZANO</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2499,14 +2519,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6862091543</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>CASTILLEJA 1818</t>
-        </is>
-      </c>
+          <t>6861256955</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2514,60 +2530,56 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>13-04-2003</t>
+          <t>16-05-1978</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CUARTO.SAJIRA@ICLOUD.COM</t>
+          <t>ELYMORALESVALENZUELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-02-2026 14:35:58</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>03-02-2026 08:35:58</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-02-2026 14:42:26</t>
+          <t>03-02-2026 08:37:42</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>02-02-2026 14:40:53</t>
-        </is>
-      </c>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2575,19 +2587,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26170522013230001649</t>
+          <t>26170522033950001717</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2599,12 +2611,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340334</t>
+          <t>340249</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>18067</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2614,17 +2626,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EMILY SOFIA</t>
+          <t xml:space="preserve">ANABEL </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ARRIAGA</t>
+          <t xml:space="preserve">DEARA </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t xml:space="preserve">ARCOS </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2634,12 +2646,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6864702297</t>
+          <t>6863957626</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AV RIOJA 160</t>
+          <t>BONIFACIO AVILES 3133</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2649,52 +2661,48 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>02-02-2006</t>
+          <t>26-01-1995</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>EMILY.ARRIAGA@GMAIL.COM</t>
+          <t>ANABELDEARA260195@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-02-2026 18:06:05</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 16:10:16</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>05-02-2026 18:50:09</t>
+          <t>02-02-2026 16:15:39</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>05-02-2026 18:49:20</t>
+          <t>02-02-2026 16:14:45</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2714,27 +2722,19 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26170522116880001895</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522016110001661</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2746,12 +2746,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>340472</t>
+          <t>310670</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18290</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2761,17 +2761,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIZABETH </t>
+          <t xml:space="preserve">OLGA </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t>CARLEÑO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6861256955</t>
+          <t>6862097698</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2792,17 +2792,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>16-05-1978</t>
+          <t>24-02-1980</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ELYMORALESVALENZUELA@GMAIL.COM</t>
+          <t>OCARLENOHERNANDEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-02-2026 08:35:58</t>
+          <t>22-08-2025 14:08:49</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-02-2026 08:37:42</t>
+          <t>23-02-2026 14:52:33</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2849,11 +2849,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26170522033950001717</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>26170522583230002827</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>1899</t>
@@ -2861,12 +2869,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3008,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>341189</t>
+          <t>341297</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>19115</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3015,17 +3023,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IVAN</t>
+          <t>NATALIE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3035,32 +3043,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6861965073</t>
+          <t>6861344365</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1RA MORELOS 19</t>
+          <t xml:space="preserve">PORTALES </t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>22-09-2000</t>
+          <t>26-11-2004</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>IVAN.RODRIGUEZ@GMAIL.COM</t>
+          <t>NATALIE.RODRIGUEZ@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>04-02-2026 20:27:47</t>
+          <t>05-02-2026 13:00:16</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3081,17 +3089,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>04-02-2026 20:33:43</t>
+          <t>10-02-2026 16:55:49</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>04-02-2026 20:33:11</t>
+          <t>10-02-2026 16:54:34</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3111,11 +3119,19 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26170522089840001847</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+          <t>26170522238010002133</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>499</t>
@@ -3135,12 +3151,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>341297</t>
+          <t>340750</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19115</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3150,17 +3166,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NATALIE</t>
+          <t>ARMANDO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">ORTIZ </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3170,75 +3186,67 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6861344365</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PORTALES </t>
-        </is>
-      </c>
+          <t>6863928150</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>26-11-2004</t>
+          <t>23-02-1988</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>NATALIE.RODRIGUEZ@UABC.EDU.MX</t>
+          <t>MENTECUERPOYNUTRICION@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>05-02-2026 13:00:16</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>03-02-2026 17:50:24</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>10-02-2026 16:55:49</t>
+          <t>03-02-2026 17:52:56</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>10-02-2026 16:54:34</t>
-        </is>
-      </c>
+          <t>03-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3246,22 +3254,14 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26170522238010002133</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522051130001755</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342573</t>
+          <t>341467</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3567,17 +3567,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LOURDES RENE</t>
+          <t>ADOLFO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>ALBISO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>BARAJAS</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3587,32 +3587,32 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6864162086</t>
+          <t>6862300377</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LAGO PAZCUARO SN</t>
+          <t>NORUEGA 2636</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>21-09-1988</t>
+          <t>12-11-1996</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CAMPOSLULY0@GMAIL.COM</t>
+          <t>ADOLFO_19962016@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10-02-2026 10:01:09</t>
+          <t>05-02-2026 21:05:50</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3633,17 +3633,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>10-02-2026 10:11:12</t>
+          <t>05-02-2026 21:13:45</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>10-02-2026 10:10:28</t>
+          <t>05-02-2026 21:13:16</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26170522227920002115</t>
+          <t>26170522120570001923</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Jose Luis Lopez Coronel</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3687,12 +3687,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>343007</t>
+          <t>339095</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3702,17 +3702,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SERGIO</t>
+          <t>KARLA ELDA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VILLARREAL</t>
+          <t>ARIZMENDI</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ZEPEDA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6864644967</t>
+          <t>6862168895</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>DE LAS ESPADAS 61</t>
+          <t>CALLE JAEN ESTE 1637</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>11-10-2001</t>
+          <t>01-08-1984</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ZEPEDA111001@GMAIL.COM</t>
+          <t>KARIZMENDI2902@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>11-02-2026 15:16:45</t>
+          <t>29-01-2026 17:00:05</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3768,17 +3768,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>11-02-2026 15:30:24</t>
+          <t>02-02-2026 11:21:22</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>11-02-2026 15:29:47</t>
+          <t>31-01-2026 14:54:56</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3798,10 +3798,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26170522266490002208</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
+          <t>26170522006780001632</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3810,24 +3814,24 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>341467</t>
+          <t>339521</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3837,17 +3841,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ADOLFO</t>
+          <t>LIZY NAILY</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ALBISO</t>
+          <t>BRICEÑO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BARAJAS</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3857,32 +3861,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6862300377</t>
+          <t>6863079480</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NORUEGA 2636</t>
+          <t>CORULLON 193</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>12-11-1996</t>
+          <t>19-10-2002</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>ADOLFO_19962016@HOTMAIL.COM</t>
+          <t>LIZY.NAILY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>05-02-2026 21:05:50</t>
+          <t>30-01-2026 20:49:36</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3903,17 +3907,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>05-02-2026 21:13:45</t>
+          <t>02-02-2026 20:17:46</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>05-02-2026 21:13:16</t>
+          <t>02-02-2026 20:16:52</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3933,11 +3937,19 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26170522120570001923</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+          <t>26170522022960001684</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>499</t>
@@ -3945,24 +3957,24 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342494</t>
+          <t>339898</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3972,17 +3984,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>NAYLA ALEJANDRA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TEJADA</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3992,14 +4004,10 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6867291381</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6864739006</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4007,60 +4015,56 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>20-06-2005</t>
+          <t>29-08-2004</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>MIGUELTEJADA317@ICLOUD.COM</t>
+          <t>NAYLITACOTA.CHAVEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>09-02-2026 20:58:55</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>02-02-2026 08:07:50</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>09-02-2026 21:01:56</t>
+          <t>03-02-2026 07:26:19</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>09-02-2026 21:01:07</t>
-        </is>
-      </c>
+          <t>03-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4068,19 +4072,27 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26170522214500002093</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
+          <t>26170522032040001706</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4235,12 +4247,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>343391</t>
+          <t>340183</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21208</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4250,17 +4262,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JOSE ENRIQUE</t>
+          <t>LEYLANI MIRANDA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>PIZANO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4270,32 +4282,24 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6861914185</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6863558685</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>02-01-2004</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>JG747801@GMAIL.COM</t>
-        </is>
-      </c>
+          <t>03-11-2011</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>12-02-2026 19:39:05</t>
+          <t>02-02-2026 14:41:17</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4316,17 +4320,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>12-02-2026 19:42:59</t>
+          <t>02-02-2026 14:46:51</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>12-02-2026 19:42:26</t>
+          <t>02-02-2026 14:45:55</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4346,7 +4350,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26170522305280002308</t>
+          <t>26170522013390001650</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4358,24 +4362,24 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>342293</t>
+          <t>340231</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20111</t>
+          <t>18049</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4385,7 +4389,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>ELLIOT SAMUEL</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4395,7 +4399,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CORREA</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4405,12 +4409,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6864214771</t>
+          <t>6866507552</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>AV GOLETA 1807</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4420,17 +4424,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>10-08-2003</t>
+          <t>09-08-1998</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>MORAERNESTO741@GMAIL.COM</t>
+          <t>ELLIOT.MORA@UABC.COM.MX</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>09-02-2026 16:57:09</t>
+          <t>02-02-2026 15:50:44</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4451,17 +4455,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>09-02-2026 17:02:55</t>
+          <t>02-02-2026 15:56:47</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>09-02-2026 16:59:57</t>
+          <t>02-02-2026 15:54:59</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4481,7 +4485,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26170522200440002040</t>
+          <t>26170522015420001658</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4505,12 +4509,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>342851</t>
+          <t>341189</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20668</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4520,17 +4524,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE JAVIE </t>
+          <t>IVAN</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZEPEDA </t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4540,10 +4544,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6863023309</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>6861965073</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1RA MORELOS 19</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4551,56 +4559,60 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>22-08-2003</t>
+          <t>22-09-2000</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>JV220803@GMAIL.COM</t>
+          <t>IVAN.RODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10-02-2026 19:47:49</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 20:27:47</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>10-02-2026 19:49:44</t>
+          <t>04-02-2026 20:33:43</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>04-02-2026 20:33:11</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4608,19 +4620,19 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26170522247770002152</t>
+          <t>26170522089840001847</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4632,12 +4644,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>339095</t>
+          <t>342494</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4647,17 +4659,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KARLA ELDA</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ARIZMENDI</t>
+          <t>TEJADA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4667,12 +4679,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6862168895</t>
+          <t>6867291381</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CALLE JAEN ESTE 1637</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4682,17 +4694,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>01-08-1984</t>
+          <t>20-06-2005</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>KARIZMENDI2902@GMAIL.COM</t>
+          <t>MIGUELTEJADA317@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>29-01-2026 17:00:05</t>
+          <t>09-02-2026 20:58:55</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4703,7 +4715,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -4713,17 +4725,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>02-02-2026 11:21:22</t>
+          <t>09-02-2026 21:01:56</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>31-01-2026 14:54:56</t>
+          <t>09-02-2026 21:01:07</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4733,7 +4745,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4743,14 +4755,10 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26170522006780001632</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26170522214500002093</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
@@ -4771,12 +4779,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>339521</t>
+          <t>340441</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>18259</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4786,17 +4794,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LIZY NAILY</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BRICEÑO</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4806,32 +4814,32 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6863079480</t>
+          <t>6674121912</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>CORULLON 193</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19-10-2002</t>
+          <t>07-10-2003</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>LIZY.NAILY@GMAIL.COM</t>
+          <t>FELIZLUISFERNANDO3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>30-01-2026 20:49:36</t>
+          <t>03-02-2026 07:13:43</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4852,17 +4860,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>02-02-2026 20:17:46</t>
+          <t>03-02-2026 07:19:00</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>02-02-2026 20:16:52</t>
+          <t>03-02-2026 07:18:37</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4882,19 +4890,11 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26170522022960001684</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522031900001705</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
           <t>499</t>
@@ -4902,24 +4902,24 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>339898</t>
+          <t>340564</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>17716</t>
+          <t>18382</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4929,17 +4929,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NAYLA ALEJANDRA</t>
+          <t>JOSE MANUEL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>MONTOYA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>REA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4949,28 +4949,28 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6864739006</t>
+          <t>6865860740</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>29-08-2004</t>
+          <t>27-12-1976</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>NAYLITACOTA.CHAVEZ@GMAIL.COM</t>
+          <t>REA1628JOSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>02-02-2026 08:07:50</t>
+          <t>03-02-2026 13:24:47</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>03-02-2026 07:26:19</t>
+          <t>03-02-2026 13:26:26</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -5006,7 +5006,7 @@
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V34" t="inlineStr"/>
@@ -5017,19 +5017,11 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26170522032040001706</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522039620001735</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
           <t>549</t>
@@ -5049,12 +5041,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>340183</t>
+          <t>342851</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18001</t>
+          <t>20668</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5064,17 +5056,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LEYLANI MIRANDA</t>
+          <t xml:space="preserve">JOSE JAVIE </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PIZANO</t>
+          <t xml:space="preserve">ZEPEDA </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5084,67 +5076,67 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6863558685</t>
+          <t>6863023309</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>03-11-2011</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+          <t>22-08-2003</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>JV220803@GMAIL.COM</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>02-02-2026 14:41:17</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>10-02-2026 19:47:49</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>02-02-2026 14:46:51</t>
+          <t>10-02-2026 19:49:44</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>02-02-2026 14:45:55</t>
-        </is>
-      </c>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5152,36 +5144,36 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26170522013390001650</t>
+          <t>26170522247770002152</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>340231</t>
+          <t>341159</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5191,17 +5183,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ELLIOT SAMUEL</t>
+          <t>DAVID ERNESTO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5211,14 +5203,10 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6866507552</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>AV GOLETA 1807</t>
-        </is>
-      </c>
+          <t>6863409250</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5226,60 +5214,56 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>09-08-1998</t>
+          <t>28-08-2011</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ELLIOT.MORA@UABC.COM.MX</t>
+          <t>DAVID.ERNESTO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>02-02-2026 15:50:44</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>04-02-2026 19:08:30</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>02-02-2026 15:56:47</t>
+          <t>04-02-2026 19:10:17</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>02-02-2026 15:54:59</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5287,14 +5271,14 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26170522015420001658</t>
+          <t>26170522087360001828</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
@@ -5311,12 +5295,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>343401</t>
+          <t>342293</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21218</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5326,17 +5310,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZEPEDA </t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>CORREA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5346,10 +5330,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6862110739</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6864214771</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5357,56 +5345,60 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>06-08-1987</t>
+          <t>10-08-2003</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>ZEPEDACOTAC@GMAIL.COM</t>
+          <t>MORAERNESTO741@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>12-02-2026 21:09:33</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>09-02-2026 16:57:09</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>12-02-2026 21:11:55</t>
+          <t>09-02-2026 17:02:55</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>09-02-2026 16:59:57</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5414,19 +5406,19 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26170522306850002321</t>
+          <t>26170522200440002040</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5438,12 +5430,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>340441</t>
+          <t>341295</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5453,17 +5445,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>FERNANDA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5473,32 +5465,32 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6674121912</t>
+          <t>6865781520</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>POTALES</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>07-10-2003</t>
+          <t>13-10-2006</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>FELIZLUISFERNANDO3@GMAIL.COM</t>
+          <t>FR65671@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>03-02-2026 07:13:43</t>
+          <t>05-02-2026 12:58:08</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5519,17 +5511,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>03-02-2026 07:19:00</t>
+          <t>10-02-2026 16:59:22</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>03-02-2026 07:18:37</t>
+          <t>10-02-2026 16:58:27</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5549,11 +5541,19 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26170522031900001705</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
+          <t>26170522238110002134</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>499</t>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5573,12 +5573,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>341159</t>
+          <t>340899</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18977</t>
+          <t>18717</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DAVID ERNESTO</t>
+          <t xml:space="preserve">YORLENI </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5608,53 +5608,53 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6863409250</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>6863226816</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>PRIVADA DUGAN DALI1129</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>28-08-2011</t>
+          <t>09-11-2000</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>DAVID.ERNESTO@GMAIL.COM</t>
+          <t>YORPEREZ073@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>04-02-2026 19:08:30</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 08:51:30</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>04-02-2026 19:10:17</t>
+          <t>04-02-2026 08:59:01</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -5662,13 +5662,21 @@
           <t>04-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>04-02-2026 08:57:43</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5676,19 +5684,19 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26170522087360001828</t>
+          <t>26170522070070001794</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5700,12 +5708,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>340564</t>
+          <t>343401</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5715,17 +5723,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>JOSE MANUEL</t>
+          <t>CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t xml:space="preserve">ZEPEDA </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>REA</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5735,7 +5743,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6865860740</t>
+          <t>6862110739</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5746,17 +5754,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>27-12-1976</t>
+          <t>06-08-1987</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>REA1628JOSE@GMAIL.COM</t>
+          <t>ZEPEDACOTAC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>03-02-2026 13:24:47</t>
+          <t>12-02-2026 21:09:33</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5771,22 +5779,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>03-02-2026 13:26:26</t>
+          <t>12-02-2026 21:11:55</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -5803,14 +5811,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26170522039620001735</t>
+          <t>26170522306850002321</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -6097,12 +6105,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>341295</t>
+          <t>342142</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19113</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6112,17 +6120,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>FERNANDA</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>MACIAS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6132,14 +6140,10 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6865781520</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>POTALES</t>
-        </is>
-      </c>
+          <t>6869453269</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6147,60 +6151,56 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>13-10-2006</t>
+          <t>19-04-2008</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>FR65671@GMAIL.COM</t>
+          <t>VALMACIASSA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>05-02-2026 12:58:08</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>09-02-2026 12:49:49</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>10-02-2026 16:59:22</t>
+          <t>09-02-2026 12:51:58</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>10-02-2026 16:58:27</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6208,27 +6208,19 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26170522238110002134</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522190930002024</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -6240,12 +6232,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>340899</t>
+          <t>342495</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18717</t>
+          <t>20312</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6255,17 +6247,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">YORLENI </t>
+          <t xml:space="preserve">NELSON </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MARISCAL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6275,75 +6267,67 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6863226816</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>PRIVADA DUGAN DALI1129</t>
-        </is>
-      </c>
+          <t>6861420567</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>09-11-2000</t>
+          <t>28-10-1996</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>YORPEREZ073@GMAIL.COM</t>
+          <t>NELSON.1028@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>04-02-2026 08:51:30</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>09-02-2026 21:04:58</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>04-02-2026 08:59:01</t>
+          <t>09-02-2026 21:06:43</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>04-02-2026 08:57:43</t>
-        </is>
-      </c>
+          <t>09-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6351,19 +6335,19 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26170522070070001794</t>
+          <t>26170522214560002094</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -6375,12 +6359,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>345451</t>
+          <t>343975</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>87616</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6390,17 +6374,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>RAMONA</t>
+          <t>MARIA ISABEL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>PEREYDA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6410,12 +6394,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6861238114</t>
+          <t>6861945257</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PORALES</t>
+          <t>AVENIDA MONTES DE LEON 2027</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6425,20 +6409,24 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>02-03-1979</t>
+          <t>24-08-1995</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>GARENE1976@GMAIL.COM</t>
+          <t>ISABELPEREYDA24@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>21-02-2026 07:31:03</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>16-02-2026 08:43:39</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -6446,7 +6434,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -6456,17 +6444,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>23-02-2026 07:43:05</t>
+          <t>16-02-2026 08:52:04</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>23-02-2026 07:42:26</t>
+          <t>16-02-2026 08:51:31</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6476,7 +6464,7 @@
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -6486,19 +6474,11 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26170522572930002811</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170522381670002419</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
           <t>499</t>
@@ -6506,7 +6486,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6518,12 +6498,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>342142</t>
+          <t>343982</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19960</t>
+          <t>21799</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6533,17 +6513,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t xml:space="preserve">JENNIFER </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MACIAS</t>
+          <t>FAVELA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6553,10 +6533,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6869453269</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>6863626144</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -6564,56 +6548,64 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>19-04-2008</t>
+          <t>11-12-2001</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>VALMACIASSA@GMAIL.COM</t>
+          <t>FAVELAPEREZVZ11@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>09-02-2026 12:49:49</t>
+          <t>16-02-2026 09:07:20</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>09-02-2026 12:51:58</t>
+          <t>16-02-2026 09:11:41</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>16-02-2026 09:11:13</t>
+        </is>
+      </c>
       <c r="U46" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6621,19 +6613,19 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26170522190930002024</t>
+          <t>26170522382170002420</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -6645,12 +6637,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>344019</t>
+          <t>342676</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6660,17 +6652,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ABRHAM ISACC</t>
+          <t>VIVIAN DENIISSE</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KETCHUL</t>
+          <t>MELERO</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6680,67 +6672,75 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6861255888</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>6644940465</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>12-07-1992</t>
+          <t>19-06-1981</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ABRAHAM.SKET1@GMAIL.COM</t>
+          <t>VIVIANDEFELIX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>16-02-2026 11:31:00</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>10-02-2026 15:37:05</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>16-02-2026 11:32:22</t>
+          <t>10-02-2026 15:40:14</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr"/>
+          <t>10-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>10-02-2026 15:39:43</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6748,19 +6748,19 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26170522385460002427</t>
+          <t>26170522235040002127</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -6772,12 +6772,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>343975</t>
+          <t>342853</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21792</t>
+          <t>20670</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6787,12 +6787,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MARIA ISABEL</t>
+          <t>DAMARIS KATHELEEN</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PEREYDA</t>
+          <t>SALGADO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6807,79 +6807,67 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6861945257</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>AVENIDA MONTES DE LEON 2027</t>
-        </is>
-      </c>
+          <t>6861330533</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>24-08-1995</t>
+          <t>26-02-2007</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>ISABELPEREYDA24@GMAIL.COM</t>
+          <t>DAMARISK.SLOPEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>16-02-2026 08:43:39</t>
+          <t>10-02-2026 19:51:12</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>16-02-2026 08:52:04</t>
+          <t>10-02-2026 19:53:06</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>16-02-2026 08:51:31</t>
-        </is>
-      </c>
+          <t>10-05-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6887,19 +6875,19 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26170522381670002419</t>
+          <t>26170522247900002153</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6911,12 +6899,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>343982</t>
+          <t>344019</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21799</t>
+          <t>21836</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6926,17 +6914,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">JENNIFER </t>
+          <t>ABRHAM ISACC</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FAVELA</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>KETCHUL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6946,57 +6934,53 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6863626144</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6861255888</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>11-12-2001</t>
+          <t>12-07-1992</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>FAVELAPEREZVZ11@GMAIL.COM</t>
+          <t>ABRAHAM.SKET1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>16-02-2026 09:07:20</t>
+          <t>16-02-2026 11:31:00</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>inscripcion promo 199</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>16-02-2026 09:11:41</t>
+          <t>16-02-2026 11:32:22</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -7004,21 +6988,13 @@
           <t>16-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>16-02-2026 09:11:13</t>
-        </is>
-      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7026,19 +7002,19 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26170522382170002420</t>
+          <t>26170522385460002427</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7050,12 +7026,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>342676</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>21057</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7065,52 +7041,52 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VIVIAN DENIISSE</t>
+          <t>HECTOR EDUARDO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>CANALES</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MELERO</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6644940465</t>
+          <t>7602343861</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>C PASEO DEL AGUA 456</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>19-06-1981</t>
+          <t>05-02-1997</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>VIVIANDEFELIX@GMAIL.COM</t>
+          <t>HECTORCANALESLEYVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>10-02-2026 15:37:05</t>
+          <t>12-02-2026 12:48:03</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -7131,17 +7107,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10-02-2026 15:40:14</t>
+          <t>12-02-2026 12:53:41</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>10-02-2026 15:39:43</t>
+          <t>12-02-2026 12:53:05</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7161,7 +7137,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26170522235040002127</t>
+          <t>26170522292940002271</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7173,7 +7149,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -7185,12 +7161,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>342495</t>
+          <t>343394</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>21211</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7200,17 +7176,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">NELSON </t>
+          <t>BRIANA NAOMI</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MIRANDA</t>
+          <t>DOMINGUEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MARISCAL</t>
+          <t>CAMACHO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7220,28 +7196,28 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6861420567</t>
+          <t>6867481654</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>28-10-1996</t>
+          <t>05-02-2011</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>NELSON.1028@HOTMAIL.COM</t>
+          <t>NAOMIDOM2011@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>09-02-2026 21:04:58</t>
+          <t>12-02-2026 20:07:03</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7256,28 +7232,28 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>09-02-2026 21:06:43</t>
+          <t>13-02-2026 17:16:34</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>13-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V51" t="inlineStr"/>
@@ -7288,19 +7264,27 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26170522214560002094</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
+          <t>26170522326050002356</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7312,12 +7296,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>344362</t>
+          <t>342573</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22179</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7327,17 +7311,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDREA MICHELL </t>
+          <t>LOURDES RENE</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>URIBE</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7347,12 +7331,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6863837971</t>
+          <t>6864162086</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>HERENCIA 2338</t>
+          <t>LAGO PAZCUARO SN</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7362,24 +7346,20 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>15-08-2000</t>
+          <t>21-09-1988</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ANDREAESTRADA1218@ICLOUD.COM</t>
+          <t>CAMPOSLULY0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>16-02-2026 21:04:29</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 10:01:09</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7397,17 +7377,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>16-02-2026 21:14:42</t>
+          <t>10-02-2026 10:11:12</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>16-02-2026 21:12:23</t>
+          <t>10-02-2026 10:10:28</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7427,7 +7407,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26170522411380002496</t>
+          <t>26170522227920002115</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7439,7 +7419,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Jose Luis Lopez Coronel</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -7451,12 +7431,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>344524</t>
+          <t>343969</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22341</t>
+          <t>21786</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7466,17 +7446,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GERARDO ANTONIO</t>
+          <t>LUIS ALBERTO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBAÑEZ </t>
+          <t>ALCARAZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MANCILLA</t>
+          <t>ROMERO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7486,14 +7466,10 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6861832430</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>BASTIA 2595</t>
-        </is>
-      </c>
+          <t>6462016615</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7501,60 +7477,56 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>01-02-1966</t>
+          <t>05-11-2009</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>GERARDO.ANTONIO@GMAIL.COM</t>
+          <t>AR7481660@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>17-02-2026 15:20:45</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>16-02-2026 08:36:28</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>23-02-2026 16:27:39</t>
+          <t>16-02-2026 08:38:13</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>23-02-2026 16:25:27</t>
-        </is>
-      </c>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7562,44 +7534,36 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26170522587090002838</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522381280002417</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>345849</t>
+          <t>344362</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>88014</t>
+          <t>22179</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7609,17 +7573,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>RUTH ERENDIRA</t>
+          <t xml:space="preserve">ANDREA MICHELL </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SERMEÑO</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ALBA</t>
+          <t>URIBE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7629,12 +7593,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6865695069</t>
+          <t>6863837971</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COLUMBUS  1325</t>
+          <t>HERENCIA 2338</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7644,17 +7608,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>12-09-1992</t>
+          <t>15-08-2000</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>RUTHSERMENO@GMAIL.COM</t>
+          <t>ANDREAESTRADA1218@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>23-02-2026 15:50:40</t>
+          <t>16-02-2026 21:04:29</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7679,17 +7643,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>23-02-2026 15:54:43</t>
+          <t>16-02-2026 21:14:42</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>23-02-2026 15:54:01</t>
+          <t>16-02-2026 21:12:23</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7699,7 +7663,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7709,7 +7673,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26170522585670002834</t>
+          <t>26170522411380002496</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr"/>
@@ -7721,7 +7685,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -7733,12 +7697,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>345872</t>
+          <t>344524</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>88037</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7748,17 +7712,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>GERARDO ANTONIO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AMEZQUITA</t>
+          <t xml:space="preserve">IBAÑEZ </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>MANCILLA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7768,12 +7732,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6862605035</t>
+          <t>6861832430</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>BOSQUE CIRUELOS 853</t>
+          <t>BASTIA 2595</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7783,42 +7747,38 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>22-09-2000</t>
+          <t>01-02-1966</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>BBMIGUEL28@GMAIL.COM</t>
+          <t>GERARDO.ANTONIO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>23-02-2026 16:30:33</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>17-02-2026 15:20:45</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>23-02-2026 16:34:54</t>
+          <t>23-02-2026 16:27:39</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -7828,7 +7788,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>23-02-2026 16:34:22</t>
+          <t>23-02-2026 16:25:27</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7848,14 +7808,22 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26170522587570002839</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
+          <t>26170522587090002838</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -7872,12 +7840,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>342853</t>
+          <t>343968</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>20670</t>
+          <t>21785</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7887,17 +7855,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>DAMARIS KATHELEEN</t>
+          <t>ALEXIS ABRAHAM</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SALGADO</t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>PINO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7907,67 +7875,79 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6861330533</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>6864284152</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>PRIV AUDACIA 2134</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>26-02-2007</t>
+          <t>17-11-2005</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>DAMARISK.SLOPEZ@GMAIL.COM</t>
+          <t>ALEXISARP15@GMAIL.COM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>10-02-2026 19:51:12</t>
+          <t>16-02-2026 08:36:23</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>inscripcion promo 199</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>10-02-2026 19:53:06</t>
+          <t>16-02-2026 08:44:12</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>10-05-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr"/>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>16-02-2026 08:42:55</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W56" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7975,19 +7955,19 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>26170522247900002153</t>
+          <t>26170522381430002418</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -7999,12 +7979,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>344864</t>
+          <t>346122</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22681</t>
+          <t>88287</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8014,17 +7994,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ELIAS ABDIEL</t>
+          <t xml:space="preserve">MERCEDALIA </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t xml:space="preserve">CORONA </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>RUSILES</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8034,32 +8014,32 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6865902031</t>
+          <t>6861102643</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>CALLE ISLA MALTA 80</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>20-04-2005</t>
+          <t>04-11-1979</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>ELIASMORENO052@GMAIL.COM</t>
+          <t>MERCEDALIA.CABANILLAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>18-02-2026 16:30:39</t>
+          <t>24-02-2026 11:35:51</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8084,17 +8064,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>18-02-2026 16:40:13</t>
+          <t>26-02-2026 10:37:21</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>18-02-2026 16:34:10</t>
+          <t>26-02-2026 10:36:38</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -8104,7 +8084,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -8114,7 +8094,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>26170522466910002616</t>
+          <t>26170522679710003051</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr"/>
@@ -8126,24 +8106,24 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>345453</t>
+          <t>344075</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>87618</t>
+          <t>21892</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8153,17 +8133,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>RENE FRANCISCO</t>
+          <t xml:space="preserve">GABRIELA </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">TORRES </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t>BACA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8173,35 +8153,39 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6863948826</t>
+          <t>6681446837</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CASA DIGNA</t>
+          <t>AV BURGUETE 41</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>17-02-1976</t>
+          <t>04-11-1987</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>RENEGARCIA170296@GMAIL.COM</t>
+          <t>GABYISA.0104@GMAIL.COM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>21-02-2026 07:40:19</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>16-02-2026 13:40:14</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8209,7 +8193,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -8219,17 +8203,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>23-02-2026 07:36:13</t>
+          <t>16-02-2026 13:47:19</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>23-02-2026 07:35:10</t>
+          <t>16-02-2026 13:46:36</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -8239,7 +8223,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -8249,19 +8233,11 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>26170522572740002810</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170522389180002437</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
           <t>499</t>
@@ -8269,7 +8245,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -8281,12 +8257,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>346065</t>
+          <t>344087</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>88230</t>
+          <t>21904</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8296,17 +8272,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUZ ELENA </t>
+          <t>ROSARIO GUADALUPE</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERNAL </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>OCHOA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8316,12 +8292,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6861751473</t>
+          <t>6863182471</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>C ISLAS ORCADAS 1927</t>
+          <t>CALLE GILAS1892</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -8331,17 +8307,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>06-09-1973</t>
+          <t>06-10-1991</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>PDGA.LUZVERNAL@HOTMAIL.COM</t>
+          <t>GARCIAGUADALUPE7414@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>24-02-2026 06:11:46</t>
+          <t>16-02-2026 14:05:34</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -8366,17 +8342,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>25-02-2026 06:08:41</t>
+          <t>16-02-2026 14:10:44</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>25-02-2026 06:07:15</t>
+          <t>16-02-2026 14:10:01</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8396,19 +8372,11 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26170522640790002973</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170522389780002438</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
           <t>499</t>
@@ -8416,7 +8384,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
@@ -8428,12 +8396,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>346148</t>
+          <t>345849</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>88313</t>
+          <t>88014</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8443,17 +8411,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINDA PATRICIA </t>
+          <t>RUTH ERENDIRA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">PERAZA </t>
+          <t>SERMEÑO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ALBA</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8463,12 +8431,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>6692315071</t>
+          <t>6865695069</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>PASEO DEL REAL 455</t>
+          <t>COLUMBUS  1325</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8478,17 +8446,17 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>25-10-1986</t>
+          <t>12-09-1992</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>LPPERAZG@GMAIL.COM</t>
+          <t>RUTHSERMENO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>24-02-2026 13:10:41</t>
+          <t>23-02-2026 15:50:40</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -8513,17 +8481,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>24-02-2026 13:17:17</t>
+          <t>23-02-2026 15:54:43</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>24-02-2026 13:15:52</t>
+          <t>23-02-2026 15:54:01</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -8533,7 +8501,7 @@
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -8543,7 +8511,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26170522618830002912</t>
+          <t>26170522585670002834</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
@@ -8555,24 +8523,24 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>343240</t>
+          <t>345872</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>88037</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8582,95 +8550,99 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>HECTOR EDUARDO</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CANALES</t>
+          <t>AMEZQUITA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6862605035</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>BOSQUE CIRUELOS 853</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>22-09-2000</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>BBMIGUEL28@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>23-02-2026 16:30:33</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>23-02-2026 16:34:54</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>23-02-2026 16:34:22</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>7602343861</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>C PASEO DEL AGUA 456</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>05-02-1997</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>HECTORCANALESLEYVA@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:48:03</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>Forzoso</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>PROMO FEBRERO 12 MESES</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:53:41</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:53:05</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="W61" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8678,36 +8650,36 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26170522292940002271</t>
+          <t>26170522587570002839</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>343394</t>
+          <t>343007</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>20824</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8717,17 +8689,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BRIANA NAOMI</t>
+          <t>SERGIO</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>DOMINGUEZ</t>
+          <t>VILLARREAL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CAMACHO</t>
+          <t>ZEPEDA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8737,67 +8709,75 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6867481654</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>6864644967</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>DE LAS ESPADAS 61</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>05-02-2011</t>
+          <t>11-10-2001</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>NAOMIDOM2011@ICLOUD.COM</t>
+          <t>ZEPEDA111001@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>12-02-2026 20:07:03</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>11-02-2026 15:16:45</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>13-02-2026 17:16:34</t>
+          <t>11-02-2026 15:30:24</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>13-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr"/>
+          <t>11-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>11-02-2026 15:29:47</t>
+        </is>
+      </c>
       <c r="U62" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8805,44 +8785,36 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26170522326050002356</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170522266490002208</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>343969</t>
+          <t>343391</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8852,17 +8824,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO</t>
+          <t>JOSE ENRIQUE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ALCARAZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ROMERO</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8872,10 +8844,14 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6462016615</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>6861914185</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8883,56 +8859,60 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>05-11-2009</t>
+          <t>02-01-2004</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>AR7481660@GMAIL.COM</t>
+          <t>JG747801@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>16-02-2026 08:36:28</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>12-02-2026 19:39:05</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>16-02-2026 08:38:13</t>
+          <t>12-02-2026 19:42:59</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr"/>
+          <t>12-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>12-02-2026 19:42:26</t>
+        </is>
+      </c>
       <c r="U63" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8940,14 +8920,14 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26170522381280002417</t>
+          <t>26170522305280002308</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
@@ -8964,12 +8944,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>343968</t>
+          <t>346065</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21785</t>
+          <t>88230</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8979,17 +8959,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ALEXIS ABRAHAM</t>
+          <t xml:space="preserve">LUZ ELENA </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t xml:space="preserve">BERNAL </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PINO</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8999,12 +8979,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6864284152</t>
+          <t>6861751473</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>PRIV AUDACIA 2134</t>
+          <t>C ISLAS ORCADAS 1927</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -9014,17 +8994,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>17-11-2005</t>
+          <t>06-09-1973</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>ALEXISARP15@GMAIL.COM</t>
+          <t>PDGA.LUZVERNAL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>16-02-2026 08:36:23</t>
+          <t>24-02-2026 06:11:46</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9049,17 +9029,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>16-02-2026 08:44:12</t>
+          <t>25-02-2026 06:08:41</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>16-02-2026 08:42:55</t>
+          <t>25-02-2026 06:07:15</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -9079,11 +9059,19 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26170522381430002418</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
+          <t>26170522640790002973</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>499</t>
@@ -9091,7 +9079,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -9103,12 +9091,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>345036</t>
+          <t>346148</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>87201</t>
+          <t>88313</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9118,17 +9106,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NORMA ALICIA</t>
+          <t xml:space="preserve">LINDA PATRICIA </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t xml:space="preserve">PERAZA </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">MERCADO </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -9138,12 +9126,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>6863291327</t>
+          <t>6692315071</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>POMONA 2446</t>
+          <t>PASEO DEL REAL 455</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -9153,20 +9141,24 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>03-11-1976</t>
+          <t>25-10-1986</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>NORMAAGUTIERREZM@HOTMAIL.COM</t>
+          <t>LPPERAZG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>19-02-2026 11:31:06</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>24-02-2026 13:10:41</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9174,7 +9166,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -9184,17 +9176,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>19-02-2026 12:01:32</t>
+          <t>24-02-2026 13:17:17</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>19-02-2026 11:44:54</t>
+          <t>24-02-2026 13:15:52</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -9214,7 +9206,7 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>26170522492340002663</t>
+          <t>26170522618830002912</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr"/>
@@ -9238,12 +9230,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>344075</t>
+          <t>344869</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21892</t>
+          <t>22686</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9253,17 +9245,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA </t>
+          <t xml:space="preserve">KEVIN MISAEL </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">TORRES </t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BACA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9273,12 +9265,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6681446837</t>
+          <t>6861053368</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>AV BURGUETE 41</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -9288,17 +9280,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>04-11-1987</t>
+          <t>24-12-2004</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>GABYISA.0104@GMAIL.COM</t>
+          <t>KEVINRAMIREZ2412@GMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>16-02-2026 13:40:14</t>
+          <t>18-02-2026 16:38:43</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -9323,17 +9315,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>16-02-2026 13:47:19</t>
+          <t>18-02-2026 16:45:20</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>16-02-2026 13:46:36</t>
+          <t>18-02-2026 16:43:02</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -9343,7 +9335,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -9353,7 +9345,7 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26170522389180002437</t>
+          <t>26170522467160002617</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr"/>
@@ -9365,7 +9357,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
@@ -9377,12 +9369,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>344087</t>
+          <t>345036</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>21904</t>
+          <t>87201</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9392,17 +9384,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ROSARIO GUADALUPE</t>
+          <t>NORMA ALICIA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>OCHOA</t>
+          <t xml:space="preserve">MERCADO </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9412,12 +9404,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6863182471</t>
+          <t>6863291327</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>CALLE GILAS1892</t>
+          <t>POMONA 2446</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9427,24 +9419,20 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>06-10-1991</t>
+          <t>03-11-1976</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>GARCIAGUADALUPE7414@HOTMAIL.COM</t>
+          <t>NORMAAGUTIERREZM@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>16-02-2026 14:05:34</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>19-02-2026 11:31:06</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9452,7 +9440,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -9462,17 +9450,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>16-02-2026 14:10:44</t>
+          <t>19-02-2026 12:01:32</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>16-02-2026 14:10:01</t>
+          <t>19-02-2026 11:44:54</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -9482,7 +9470,7 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -9492,7 +9480,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26170522389780002438</t>
+          <t>26170522492340002663</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
@@ -9504,24 +9492,24 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>346035</t>
+          <t>346742</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>88200</t>
+          <t>88907</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9531,17 +9519,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>INGRID MONSERRAT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -9551,39 +9539,35 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>6861618654</t>
+          <t>6863236007</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">GERONIMO 2675 </t>
+          <t>DESTREZA 2781</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>08-08-1994</t>
+          <t>19-08-2002</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>ALEJANDRO.MUNOZ@GMAIL.COM</t>
+          <t>INGRID.MONSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>23-02-2026 19:51:28</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>26-02-2026 15:56:12</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9591,7 +9575,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -9601,17 +9585,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>24-02-2026 20:10:23</t>
+          <t>26-02-2026 15:59:45</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>24-02-2026 20:09:41</t>
+          <t>26-02-2026 15:59:06</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -9631,7 +9615,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>26170522636500002957</t>
+          <t>26170522685900003059</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr"/>
@@ -9655,12 +9639,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>344869</t>
+          <t>345642</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22686</t>
+          <t>87807</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9670,17 +9654,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEVIN MISAEL </t>
+          <t>LUIS</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>COVARRUBIAS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>TELLEZ</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9690,32 +9674,32 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>6861053368</t>
+          <t>6865705647</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>TAXQUEÑA 1135</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>24-12-2004</t>
+          <t>11-08-1999</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>KEVINRAMIREZ2412@GMAIL.COM</t>
+          <t>LTELLEZ945@GMAIL.COM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>18-02-2026 16:38:43</t>
+          <t>23-02-2026 05:17:04</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -9740,17 +9724,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:20</t>
+          <t>25-02-2026 07:13:43</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>18-02-2026 16:43:02</t>
+          <t>25-02-2026 07:11:39</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -9760,7 +9744,7 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -9770,11 +9754,19 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>26170522467160002617</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
+          <t>26170522645430002976</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>499</t>
@@ -9782,7 +9774,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
@@ -9794,12 +9786,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>345642</t>
+          <t>345689</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>87807</t>
+          <t>87854</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9809,17 +9801,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LUIS</t>
+          <t>BRAYAN ALEXIS</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>COVARRUBIAS</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TELLEZ</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9829,12 +9821,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6865705647</t>
+          <t>6861096516</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TAXQUEÑA 1135</t>
+          <t>NOTREDAME OESTE 295</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9844,17 +9836,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>11-08-1999</t>
+          <t>27-09-1995</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>LTELLEZ945@GMAIL.COM</t>
+          <t>DECKSARIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>23-02-2026 05:17:04</t>
+          <t>23-02-2026 09:56:35</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -9879,17 +9871,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>25-02-2026 07:13:43</t>
+          <t>24-02-2026 10:26:50</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>25-02-2026 07:11:39</t>
+          <t>24-02-2026 10:26:08</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -9899,7 +9891,7 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -9909,7 +9901,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26170522645430002976</t>
+          <t>26170522615550002903</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -9941,12 +9933,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>345689</t>
+          <t>344864</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>87854</t>
+          <t>22681</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -9956,17 +9948,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BRAYAN ALEXIS</t>
+          <t>ELIAS ABDIEL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9976,12 +9968,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>6861096516</t>
+          <t>6865902031</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>NOTREDAME OESTE 295</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9991,17 +9983,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>27-09-1995</t>
+          <t>20-04-2005</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>DECKSARIA@GMAIL.COM</t>
+          <t>ELIASMORENO052@GMAIL.COM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>23-02-2026 09:56:35</t>
+          <t>18-02-2026 16:30:39</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -10026,17 +10018,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>24-02-2026 10:26:50</t>
+          <t>18-02-2026 16:40:13</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>24-02-2026 10:26:08</t>
+          <t>18-02-2026 16:34:10</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -10056,19 +10048,11 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>26170522615550002903</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170522466910002616</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
           <t>499</t>
@@ -10076,7 +10060,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -10088,139 +10072,711 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>345453</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>87618</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RENE FRANCISCO</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>SOTO</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6863948826</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>CASA DIGNA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>17-02-1976</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>RENEGARCIA170296@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>21-02-2026 07:40:19</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>23-02-2026 07:36:13</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>23-02-2026 07:35:10</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>26170522572740002810</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>346044</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>88209</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>VILLAS DEL REY</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>MEDINA</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>VALDEZ</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>6863403745</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">BOSQUE TROPICAL </t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>Femenino</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>19-08-2004</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>CAMILA.CONSULTORIOWORK@GMAIL.COM</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>23-02-2026 20:18:53</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>inscripcion promo 199</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>Forzoso</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>23-02-2026 20:25:35</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>23-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="T73" t="inlineStr">
         <is>
           <t>23-02-2026 20:24:56</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="U73" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="V73" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="W73" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>26170522601620002882</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
-      <c r="AA72" t="inlineStr">
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>Alexa Johana  Haro</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
+      <c r="AC73" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>346035</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>88200</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>MUÑOZ</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>HERRERA</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>6861618654</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GERONIMO 2675 </t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>08-08-1994</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>ALEJANDRO.MUNOZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>23-02-2026 19:51:28</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>24-02-2026 20:10:23</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>24-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>24-02-2026 20:09:41</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>26170522636500002957</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>345451</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>87616</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RAMONA</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>NUÑEZ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6861238114</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>PORALES</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>02-03-1979</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>GARENE1976@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>21-02-2026 07:31:03</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>23-02-2026 07:43:05</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>23-02-2026 07:42:26</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>26170522572930002811</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>346601</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>88766</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDA </t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>PIO</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>6863843373</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>BAHIA BLANCA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>14-07-2001</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>FERNANDA.FLORES@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>25-02-2026 19:55:13</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>PROMO FEBRERO 12 MESES</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>26-02-2026 20:33:13</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>26-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>26-02-2026 20:32:40</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>26170522696820003084</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
@@ -2059,12 +2059,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>339800</t>
+          <t>341056</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17618</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2074,17 +2074,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BRIAN MIGUEL</t>
+          <t xml:space="preserve">EMMANUEL </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AISPURO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CORTEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2094,14 +2094,10 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6862643137</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6862034611</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2109,60 +2105,56 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>13-12-1998</t>
+          <t>03-09-2005</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PAISPURO1948@GMAIL.COM</t>
+          <t>EMMANUEL.PEREZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>01-02-2026 12:02:45</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>04-02-2026 15:54:17</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>01-02-2026 12:08:41</t>
+          <t>04-02-2026 15:57:00</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>01-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>01-02-2026 12:07:33</t>
-        </is>
-      </c>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2170,19 +2162,19 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26170521990600001608</t>
+          <t>26170522078420001815</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2194,12 +2186,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>341056</t>
+          <t>339800</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18874</t>
+          <t>17618</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2209,17 +2201,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMMANUEL </t>
+          <t>BRIAN MIGUEL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>AISPURO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>CORTEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2229,10 +2221,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6862034611</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>6862643137</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2240,56 +2236,60 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>03-09-2005</t>
+          <t>13-12-1998</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>EMMANUEL.PEREZ@GMAIL.COM</t>
+          <t>PAISPURO1948@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>04-02-2026 15:54:17</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>01-02-2026 12:02:45</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>04-02-2026 15:57:00</t>
+          <t>01-02-2026 12:08:41</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>01-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>01-02-2026 12:07:33</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2297,19 +2297,19 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26170522078420001815</t>
+          <t>26170521990600001608</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2321,12 +2321,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>339895</t>
+          <t>310670</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17713</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JULIO ALEJANDRO</t>
+          <t xml:space="preserve">OLGA </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BEJARANO</t>
+          <t>CARLEÑO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2356,28 +2356,28 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6867371621</t>
+          <t>6862097698</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>04-09-2001</t>
+          <t>24-02-1980</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>BEJARANOJULIO10@GMAIL.COM</t>
+          <t>OCARLENOHERNANDEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-02-2026 08:04:32</t>
+          <t>22-08-2025 14:08:49</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2392,22 +2392,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-02-2026 07:27:31</t>
+          <t>23-02-2026 14:52:33</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
+          <t>23-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26170522032100001708</t>
+          <t>26170522583230002827</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2456,12 +2456,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>339961</t>
+          <t>339895</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17779</t>
+          <t>17713</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2471,17 +2471,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CELINA</t>
+          <t>JULIO ALEJANDRO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">REYES </t>
+          <t>BEJARANO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2491,28 +2491,28 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6864237570</t>
+          <t>6867371621</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>25-06-1996</t>
+          <t>04-09-2001</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>EYLECELENA25@GMAIL.COM</t>
+          <t>BEJARANOJULIO10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-02-2026 09:30:33</t>
+          <t>02-02-2026 08:04:32</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>12-02-2026 08:16:52</t>
+          <t>03-02-2026 07:27:31</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26170522288990002257</t>
+          <t>26170522032100001708</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2591,12 +2591,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>340472</t>
+          <t>339961</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18290</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2606,17 +2606,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIZABETH </t>
+          <t>CELINA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">MORALES </t>
+          <t xml:space="preserve">REYES </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">VALENZUELA </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6861256955</t>
+          <t>6864237570</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2637,17 +2637,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>16-05-1978</t>
+          <t>25-06-1996</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ELYMORALESVALENZUELA@GMAIL.COM</t>
+          <t>EYLECELENA25@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-02-2026 08:35:58</t>
+          <t>02-02-2026 09:30:33</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2662,22 +2662,22 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-02-2026 08:37:42</t>
+          <t>12-02-2026 08:16:52</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-05-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2694,19 +2694,27 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26170522033950001717</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26170522288990002257</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2718,12 +2726,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>310670</t>
+          <t>340472</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8169</t>
+          <t>18290</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2733,17 +2741,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">OLGA </t>
+          <t xml:space="preserve">ELIZABETH </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CARLEÑO</t>
+          <t xml:space="preserve">MORALES </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">VALENZUELA </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2753,7 +2761,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6862097698</t>
+          <t>6861256955</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2764,17 +2772,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>24-02-1980</t>
+          <t>16-05-1978</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>OCARLENOHERNANDEZ@GMAIL.COM</t>
+          <t>ELYMORALESVALENZUELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>22-08-2025 14:08:49</t>
+          <t>03-02-2026 08:35:58</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2799,12 +2807,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>23-02-2026 14:52:33</t>
+          <t>03-02-2026 08:37:42</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>23-05-2026 23:59:59</t>
+          <t>03-05-2026 23:59:59</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2821,19 +2829,11 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26170522583230002827</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
-        </is>
-      </c>
+          <t>26170522033950001717</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
           <t>1899</t>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2853,12 +2853,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>342494</t>
+          <t>340035</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2868,17 +2868,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MIGUEL ANGEL</t>
+          <t>KITZIA AILIME</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TEJADA</t>
+          <t>MAGALLON</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HURTADO</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6867291381</t>
+          <t>6862541870</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>CASA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2903,17 +2903,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20-06-2005</t>
+          <t>17-03-2003</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MIGUELTEJADA317@ICLOUD.COM</t>
+          <t>KITZIAMAGALON@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>09-02-2026 20:58:55</t>
+          <t>02-02-2026 10:57:19</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2934,17 +2934,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>09-02-2026 21:01:56</t>
+          <t>02-02-2026 11:00:49</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>09-02-2026 21:01:07</t>
+          <t>02-02-2026 11:00:21</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26170522214500002093</t>
+          <t>26170522006040001630</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3127,12 +3127,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>340035</t>
+          <t>342494</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17853</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3142,17 +3142,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KITZIA AILIME</t>
+          <t>MIGUEL ANGEL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MAGALLON</t>
+          <t>TEJADA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>HURTADO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6862541870</t>
+          <t>6867291381</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CASA</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3177,17 +3177,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>17-03-2003</t>
+          <t>20-06-2005</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>KITZIAMAGALON@GMAIL.COM</t>
+          <t>MIGUELTEJADA317@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-02-2026 10:57:19</t>
+          <t>09-02-2026 20:58:55</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3208,17 +3208,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-02-2026 11:00:49</t>
+          <t>09-02-2026 21:01:56</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>02-02-2026 11:00:21</t>
+          <t>09-02-2026 21:01:07</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26170522006040001630</t>
+          <t>26170522214500002093</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3262,12 +3262,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>340181</t>
+          <t>340108</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17999</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAHIRA YOMAHIRA</t>
+          <t>CHRISTIAN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">BAJO </t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PIZANO</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6862091543</t>
+          <t>6866740223</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CASTILLEJA 1818</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13-04-2003</t>
+          <t>11-02-2010</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CUARTO.SAJIRA@ICLOUD.COM</t>
+          <t>HIELO12CV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-02-2026 14:35:58</t>
+          <t>02-02-2026 12:53:45</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3343,17 +3343,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-02-2026 14:42:26</t>
+          <t>04-02-2026 13:54:22</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>04-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>02-02-2026 14:40:53</t>
+          <t>04-02-2026 13:53:23</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3373,11 +3373,19 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26170522013230001649</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+          <t>26170522075080001810</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>499</t>
@@ -3385,7 +3393,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3397,12 +3405,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>340334</t>
+          <t>340181</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18152</t>
+          <t>17999</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3412,17 +3420,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EMILY SOFIA</t>
+          <t>SAHIRA YOMAHIRA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ARRIAGA</t>
+          <t xml:space="preserve">BAJO </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>PIZANO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3432,12 +3440,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6864702297</t>
+          <t>6862091543</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AV RIOJA 160</t>
+          <t>CASTILLEJA 1818</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3447,52 +3455,48 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>02-02-2006</t>
+          <t>13-04-2003</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>EMILY.ARRIAGA@GMAIL.COM</t>
+          <t>CUARTO.SAJIRA@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-02-2026 18:06:05</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-02-2026 14:35:58</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>05-02-2026 18:50:09</t>
+          <t>02-02-2026 14:42:26</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>05-02-2026 18:49:20</t>
+          <t>02-02-2026 14:40:53</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3512,22 +3516,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26170522116880001895</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522013230001649</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3544,12 +3540,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>342573</t>
+          <t>340334</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3559,17 +3555,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LOURDES RENE</t>
+          <t>EMILY SOFIA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>ARRIAGA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3579,12 +3575,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6864162086</t>
+          <t>6864702297</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LAGO PAZCUARO SN</t>
+          <t>AV RIOJA 160</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3594,48 +3590,52 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>21-09-1988</t>
+          <t>02-02-2006</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CAMPOSLULY0@GMAIL.COM</t>
+          <t>EMILY.ARRIAGA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10-02-2026 10:01:09</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>02-02-2026 18:06:05</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>10-02-2026 10:11:12</t>
+          <t>05-02-2026 18:50:09</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>05-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>10-02-2026 10:10:28</t>
+          <t>05-02-2026 18:49:20</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3655,19 +3655,27 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26170522227920002115</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+          <t>26170522116880001895</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Jose Luis Lopez Coronel</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3679,12 +3687,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>340108</t>
+          <t>342573</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3694,17 +3702,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CHRISTIAN</t>
+          <t>LOURDES RENE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3714,32 +3722,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6866740223</t>
+          <t>6864162086</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>LAGO PAZCUARO SN</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>11-02-2010</t>
+          <t>21-09-1988</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>HIELO12CV@GMAIL.COM</t>
+          <t>CAMPOSLULY0@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-02-2026 12:53:45</t>
+          <t>10-02-2026 10:01:09</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3760,17 +3768,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>04-02-2026 13:54:22</t>
+          <t>10-02-2026 10:11:12</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>04-02-2026 13:53:23</t>
+          <t>10-02-2026 10:10:28</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3790,19 +3798,11 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26170522075080001810</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522227920002115</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>499</t>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Jose Luis Lopez Coronel</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3822,12 +3822,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>340183</t>
+          <t>343007</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>18001</t>
+          <t>20824</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3837,17 +3837,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LEYLANI MIRANDA</t>
+          <t>SERGIO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>VILLARREAL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PIZANO</t>
+          <t>ZEPEDA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3857,24 +3857,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6863558685</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>6864644967</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>DE LAS ESPADAS 61</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>03-11-2011</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+          <t>11-10-2001</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>ZEPEDA111001@GMAIL.COM</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-02-2026 14:41:17</t>
+          <t>11-02-2026 15:16:45</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3895,17 +3903,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-02-2026 14:46:51</t>
+          <t>11-02-2026 15:30:24</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>11-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>02-02-2026 14:45:55</t>
+          <t>11-02-2026 15:29:47</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3925,7 +3933,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26170522013390001650</t>
+          <t>26170522266490002208</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3949,12 +3957,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>340231</t>
+          <t>343391</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3964,17 +3972,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ELLIOT SAMUEL</t>
+          <t>JOSE ENRIQUE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3984,12 +3992,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6866507552</t>
+          <t>6861914185</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AV GOLETA 1807</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3999,17 +4007,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>09-08-1998</t>
+          <t>02-01-2004</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ELLIOT.MORA@UABC.COM.MX</t>
+          <t>JG747801@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-02-2026 15:50:44</t>
+          <t>12-02-2026 19:39:05</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4030,17 +4038,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-02-2026 15:56:47</t>
+          <t>12-02-2026 19:42:59</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>02-02-2026 15:54:59</t>
+          <t>12-02-2026 19:42:26</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4060,7 +4068,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26170522015420001658</t>
+          <t>26170522305280002308</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -4072,7 +4080,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -4084,12 +4092,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>343007</t>
+          <t>340183</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4099,17 +4107,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SERGIO</t>
+          <t>LEYLANI MIRANDA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VILLARREAL</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ZEPEDA</t>
+          <t>PIZANO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4119,32 +4127,24 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6864644967</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>DE LAS ESPADAS 61</t>
-        </is>
-      </c>
+          <t>6863558685</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>11-10-2001</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>ZEPEDA111001@GMAIL.COM</t>
-        </is>
-      </c>
+          <t>03-11-2011</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>11-02-2026 15:16:45</t>
+          <t>02-02-2026 14:41:17</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4165,17 +4165,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>11-02-2026 15:30:24</t>
+          <t>02-02-2026 14:46:51</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>11-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>11-02-2026 15:29:47</t>
+          <t>02-02-2026 14:45:55</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26170522266490002208</t>
+          <t>26170522013390001650</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4219,12 +4219,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>343391</t>
+          <t>340231</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21208</t>
+          <t>18049</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4234,17 +4234,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>JOSE ENRIQUE</t>
+          <t>ELLIOT SAMUEL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6861914185</t>
+          <t>6866507552</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>AV GOLETA 1807</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4269,17 +4269,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>02-01-2004</t>
+          <t>09-08-1998</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>JG747801@GMAIL.COM</t>
+          <t>ELLIOT.MORA@UABC.COM.MX</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>12-02-2026 19:39:05</t>
+          <t>02-02-2026 15:50:44</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4300,17 +4300,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>12-02-2026 19:42:59</t>
+          <t>02-02-2026 15:56:47</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>12-03-2026 23:59:59</t>
+          <t>02-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>12-02-2026 19:42:26</t>
+          <t>02-02-2026 15:54:59</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26170522305280002308</t>
+          <t>26170522015420001658</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4354,12 +4354,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>339095</t>
+          <t>340605</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>18423</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KARLA ELDA</t>
+          <t xml:space="preserve">SANDRA </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ARIZMENDI</t>
+          <t>ARAUJO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4389,75 +4389,67 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6862168895</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>CALLE JAEN ESTE 1637</t>
-        </is>
-      </c>
+          <t>6861472474</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>01-08-1984</t>
+          <t>17-01-1989</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>KARIZMENDI2902@GMAIL.COM</t>
+          <t>SANDRAARAUJO66@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>29-01-2026 17:00:05</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>03-02-2026 14:49:56</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PROMO ENERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>02-02-2026 11:21:22</t>
+          <t>27-02-2026 14:57:21</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>28-02-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>31-01-2026 14:54:56</t>
-        </is>
-      </c>
+          <t>27-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4465,28 +4457,32 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26170522006780001632</t>
+          <t>26170522713580003104</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4565,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -4615,7 +4611,7 @@
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4632,12 +4628,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>339521</t>
+          <t>339095</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4647,17 +4643,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LIZY NAILY</t>
+          <t>KARLA ELDA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BRICEÑO</t>
+          <t>ARIZMENDI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RAMOS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4667,12 +4663,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6863079480</t>
+          <t>6862168895</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>CORULLON 193</t>
+          <t>CALLE JAEN ESTE 1637</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4682,17 +4678,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>19-10-2002</t>
+          <t>01-08-1984</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>LIZY.NAILY@GMAIL.COM</t>
+          <t>KARIZMENDI2902@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>30-01-2026 20:49:36</t>
+          <t>29-01-2026 17:00:05</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4703,27 +4699,27 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PROMO ENERO 12 MESES</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>02-02-2026 20:17:46</t>
+          <t>02-02-2026 11:21:22</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>02-03-2026 23:59:59</t>
+          <t>28-02-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>02-02-2026 20:16:52</t>
+          <t>31-01-2026 14:54:56</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4733,7 +4729,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -4743,44 +4739,40 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26170522022960001684</t>
+          <t>26170522006780001632</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>339898</t>
+          <t>339521</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17716</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4790,17 +4782,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NAYLA ALEJANDRA</t>
+          <t>LIZY NAILY</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>COTA</t>
+          <t>BRICEÑO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>RAMOS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4810,10 +4802,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6864739006</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>6863079480</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>CORULLON 193</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4821,56 +4817,60 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>29-08-2004</t>
+          <t>19-10-2002</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>NAYLITACOTA.CHAVEZ@GMAIL.COM</t>
+          <t>LIZY.NAILY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>02-02-2026 08:07:50</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>30-01-2026 20:49:36</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>03-02-2026 07:26:19</t>
+          <t>02-02-2026 20:17:46</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
+          <t>02-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>02-02-2026 20:16:52</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26170522032040001706</t>
+          <t>26170522022960001684</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4888,34 +4888,34 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>340605</t>
+          <t>339898</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18423</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4925,17 +4925,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANDRA </t>
+          <t>NAYLA ALEJANDRA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ARAUJO</t>
+          <t>COTA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4945,33 +4945,33 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6861472474</t>
+          <t>6864739006</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>17-01-1989</t>
+          <t>29-08-2004</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>SANDRAARAUJO66@GMAIL.COM</t>
+          <t>NAYLITACOTA.CHAVEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>03-02-2026 14:49:56</t>
+          <t>02-02-2026 08:07:50</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -4991,18 +4991,18 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>27-02-2026 14:57:21</t>
+          <t>03-02-2026 07:26:19</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V34" t="inlineStr"/>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26170522713580003104</t>
+          <t>26170522032040001706</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -5033,24 +5033,24 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>341297</t>
+          <t>342851</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19115</t>
+          <t>20668</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5060,17 +5060,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NATALIE</t>
+          <t xml:space="preserve">JOSE JAVIE </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>VALENZUELA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t xml:space="preserve">ZEPEDA </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5080,53 +5080,53 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6861344365</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PORTALES </t>
-        </is>
-      </c>
+          <t>6863023309</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>26-11-2004</t>
+          <t>22-08-2003</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>NATALIE.RODRIGUEZ@UABC.EDU.MX</t>
+          <t>JV220803@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>05-02-2026 13:00:16</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>10-02-2026 19:47:49</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>10-02-2026 16:55:49</t>
+          <t>10-02-2026 19:49:44</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -5134,21 +5134,13 @@
           <t>10-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>10-02-2026 16:54:34</t>
-        </is>
-      </c>
+      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5156,27 +5148,19 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26170522238010002133</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522247770002152</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -5188,12 +5172,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>341467</t>
+          <t>341297</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>19115</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5203,17 +5187,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ADOLFO</t>
+          <t>NATALIE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ALBISO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BARAJAS</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5223,32 +5207,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6862300377</t>
+          <t>6861344365</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>NORUEGA 2636</t>
+          <t xml:space="preserve">PORTALES </t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>12-11-1996</t>
+          <t>26-11-2004</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ADOLFO_19962016@HOTMAIL.COM</t>
+          <t>NATALIE.RODRIGUEZ@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>05-02-2026 21:05:50</t>
+          <t>05-02-2026 13:00:16</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5269,17 +5253,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>05-02-2026 21:13:45</t>
+          <t>10-02-2026 16:55:49</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>05-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>05-02-2026 21:13:16</t>
+          <t>10-02-2026 16:54:34</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5299,11 +5283,19 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26170522120570001923</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
+          <t>26170522238010002133</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>499</t>
@@ -5323,12 +5315,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>342851</t>
+          <t>341467</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20668</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5338,17 +5330,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE JAVIE </t>
+          <t>ADOLFO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>VALENZUELA</t>
+          <t>ALBISO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZEPEDA </t>
+          <t>BARAJAS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5358,10 +5350,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6863023309</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6862300377</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>NORUEGA 2636</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5369,56 +5365,60 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>22-08-2003</t>
+          <t>12-11-1996</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>JV220803@GMAIL.COM</t>
+          <t>ADOLFO_19962016@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>10-02-2026 19:47:49</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>05-02-2026 21:05:50</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>10-02-2026 19:49:44</t>
+          <t>05-02-2026 21:13:45</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>05-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>05-02-2026 21:13:16</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5426,19 +5426,19 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26170522247770002152</t>
+          <t>26170522120570001923</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -5577,12 +5577,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>341189</t>
+          <t>340441</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>18259</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5592,17 +5592,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IVAN</t>
+          <t>LUIS FERNANDO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">RODRIGUEZ </t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6861965073</t>
+          <t>6674121912</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1RA MORELOS 19</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5627,17 +5627,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>22-09-2000</t>
+          <t>07-10-2003</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>IVAN.RODRIGUEZ@GMAIL.COM</t>
+          <t>FELIZLUISFERNANDO3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>04-02-2026 20:27:47</t>
+          <t>03-02-2026 07:13:43</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5658,17 +5658,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>04-02-2026 20:33:43</t>
+          <t>03-02-2026 07:19:00</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>04-03-2026 23:59:59</t>
+          <t>03-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>04-02-2026 20:33:11</t>
+          <t>03-02-2026 07:18:37</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26170522089840001847</t>
+          <t>26170522031900001705</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -5712,12 +5712,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>340441</t>
+          <t>340564</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>18382</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5727,17 +5727,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LUIS FERNANDO</t>
+          <t>JOSE MANUEL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>MONTOYA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t>REA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5747,14 +5747,10 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6674121912</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6865860740</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5762,38 +5758,42 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>07-10-2003</t>
+          <t>27-12-1976</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>FELIZLUISFERNANDO3@GMAIL.COM</t>
+          <t>REA1628JOSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>03-02-2026 07:13:43</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>03-02-2026 13:24:47</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>03-02-2026 07:19:00</t>
+          <t>03-02-2026 13:26:26</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5801,21 +5801,13 @@
           <t>03-03-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>03-02-2026 07:18:37</t>
-        </is>
-      </c>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5823,14 +5815,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26170522031900001705</t>
+          <t>26170522039620001735</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5847,12 +5839,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>340564</t>
+          <t>341189</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5862,17 +5854,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>JOSE MANUEL</t>
+          <t>IVAN</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MONTOYA</t>
+          <t xml:space="preserve">RODRIGUEZ </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>REA</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5882,10 +5874,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6865860740</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>6861965073</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1RA MORELOS 19</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5893,56 +5889,60 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>27-12-1976</t>
+          <t>22-09-2000</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>REA1628JOSE@GMAIL.COM</t>
+          <t>IVAN.RODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>03-02-2026 13:24:47</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>04-02-2026 20:27:47</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>03-02-2026 13:26:26</t>
+          <t>04-02-2026 20:33:43</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>03-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr"/>
+          <t>04-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>04-02-2026 20:33:11</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5950,19 +5950,19 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26170522039620001735</t>
+          <t>26170522089840001847</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -6379,12 +6379,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>342293</t>
+          <t>345451</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20111</t>
+          <t>87616</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ERNESTO</t>
+          <t>RAMONA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MORA</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CORREA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6414,32 +6414,32 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6864214771</t>
+          <t>6861238114</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>PORALES</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>10-08-2003</t>
+          <t>02-03-1979</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>MORAERNESTO741@GMAIL.COM</t>
+          <t>GARENE1976@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>09-02-2026 16:57:09</t>
+          <t>21-02-2026 07:31:03</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
@@ -6460,17 +6460,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>09-02-2026 17:02:55</t>
+          <t>23-02-2026 07:43:05</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>09-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>09-02-2026 16:59:57</t>
+          <t>23-02-2026 07:42:26</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -6490,11 +6490,19 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26170522200440002040</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
+          <t>26170522572930002811</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>499</t>
@@ -6502,7 +6510,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -6514,12 +6522,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>345451</t>
+          <t>342293</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>87616</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6529,17 +6537,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>RAMONA</t>
+          <t>ERNESTO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>CORREA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6549,32 +6557,32 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6861238114</t>
+          <t>6864214771</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PORALES</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>02-03-1979</t>
+          <t>10-08-2003</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>GARENE1976@GMAIL.COM</t>
+          <t>MORAERNESTO741@GMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>21-02-2026 07:31:03</t>
+          <t>09-02-2026 16:57:09</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6585,7 +6593,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -6595,17 +6603,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>23-02-2026 07:43:05</t>
+          <t>09-02-2026 17:02:55</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>09-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>23-02-2026 07:42:26</t>
+          <t>09-02-2026 16:59:57</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6625,19 +6633,11 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26170522572930002811</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170522200440002040</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
           <t>499</t>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -7181,12 +7181,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>343975</t>
+          <t>342676</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21792</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7196,17 +7196,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MARIA ISABEL</t>
+          <t>VIVIAN DENIISSE</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PEREYDA</t>
+          <t>FELIX</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>MELERO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6861945257</t>
+          <t>6644940465</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AVENIDA MONTES DE LEON 2027</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7231,24 +7231,20 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>24-08-1995</t>
+          <t>19-06-1981</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>ISABELPEREYDA24@GMAIL.COM</t>
+          <t>VIVIANDEFELIX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>16-02-2026 08:43:39</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>10-02-2026 15:37:05</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7266,17 +7262,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>16-02-2026 08:52:04</t>
+          <t>10-02-2026 15:40:14</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>10-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>16-02-2026 08:51:31</t>
+          <t>10-02-2026 15:39:43</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7286,7 +7282,7 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -7296,7 +7292,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26170522381670002419</t>
+          <t>26170522235040002127</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
@@ -7308,7 +7304,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
@@ -7320,12 +7316,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>343982</t>
+          <t>346601</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21799</t>
+          <t>88766</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7335,17 +7331,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">JENNIFER </t>
+          <t xml:space="preserve">FERNANDA </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FAVELA</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PIO</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7355,12 +7351,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6863626144</t>
+          <t>6863843373</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>BAHIA BLANCA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7370,17 +7366,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>11-12-2001</t>
+          <t>14-07-2001</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>FAVELAPEREZVZ11@GMAIL.COM</t>
+          <t>FERNANDA.FLORES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>16-02-2026 09:07:20</t>
+          <t>25-02-2026 19:55:13</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7405,17 +7401,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>16-02-2026 09:11:41</t>
+          <t>26-02-2026 20:33:13</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>16-02-2026 09:11:13</t>
+          <t>26-02-2026 20:32:40</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7435,11 +7431,19 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26170522382170002420</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
+          <t>26170522696820003084</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>499</t>
@@ -7447,24 +7451,24 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>342676</t>
+          <t>346603</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>88768</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7474,17 +7478,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VIVIAN DENIISSE</t>
+          <t>BRYAN ALEJANDRO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>BACHO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MELERO</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7494,35 +7498,39 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>6644940465</t>
+          <t>6863400672</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>MONTES DE TOLEDO 152</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>19-06-1981</t>
+          <t>22-08-2003</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>VIVIANDEFELIX@GMAIL.COM</t>
+          <t>ALEBACHO2003@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>10-02-2026 15:37:05</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>25-02-2026 19:57:16</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O53" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -7540,17 +7548,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>10-02-2026 15:40:14</t>
+          <t>27-02-2026 20:47:17</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>10-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>10-02-2026 15:39:43</t>
+          <t>27-02-2026 20:46:20</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7570,10 +7578,14 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26170522235040002127</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr"/>
+          <t>26170522726120003130</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
@@ -7582,24 +7594,24 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>346601</t>
+          <t>343975</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>88766</t>
+          <t>21792</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7609,17 +7621,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDA </t>
+          <t>MARIA ISABEL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>PEREYDA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>PIO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -7629,12 +7641,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>6863843373</t>
+          <t>6861945257</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>BAHIA BLANCA</t>
+          <t>AVENIDA MONTES DE LEON 2027</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7644,17 +7656,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>14-07-2001</t>
+          <t>24-08-1995</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>FERNANDA.FLORES@GMAIL.COM</t>
+          <t>ISABELPEREYDA24@GMAIL.COM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>25-02-2026 19:55:13</t>
+          <t>16-02-2026 08:43:39</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -7679,17 +7691,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>26-02-2026 20:33:13</t>
+          <t>16-02-2026 08:52:04</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>26-02-2026 20:32:40</t>
+          <t>16-02-2026 08:51:31</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -7699,7 +7711,7 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -7709,19 +7721,11 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>26170522696820003084</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522381670002419</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
           <t>499</t>
@@ -7729,24 +7733,24 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>346603</t>
+          <t>343982</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>88768</t>
+          <t>21799</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7756,17 +7760,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BRYAN ALEJANDRO</t>
+          <t xml:space="preserve">JENNIFER </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>BACHO</t>
+          <t>FAVELA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -7776,32 +7780,32 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6863400672</t>
+          <t>6863626144</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>MONTES DE TOLEDO 152</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>22-08-2003</t>
+          <t>11-12-2001</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>ALEBACHO2003@GMAIL.COM</t>
+          <t>FAVELAPEREZVZ11@GMAIL.COM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>25-02-2026 19:57:16</t>
+          <t>16-02-2026 09:07:20</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -7826,17 +7830,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>27-02-2026 20:47:17</t>
+          <t>16-02-2026 09:11:41</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>27-02-2026 20:46:20</t>
+          <t>16-02-2026 09:11:13</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7856,14 +7860,10 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>26170522726120003130</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26170522382170002420</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
@@ -7872,12 +7872,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -8285,12 +8285,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>344362</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22179</t>
+          <t>21057</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8300,59 +8300,55 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDREA MICHELL </t>
+          <t>HECTOR EDUARDO</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>CANALES</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>URIBE</t>
+          <t>LEYVA</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6863837971</t>
+          <t>7602343861</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>HERENCIA 2338</t>
+          <t>C PASEO DEL AGUA 456</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>15-08-2000</t>
+          <t>05-02-1997</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>ANDREAESTRADA1218@ICLOUD.COM</t>
+          <t>HECTORCANALESLEYVA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>16-02-2026 21:04:29</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>12-02-2026 12:48:03</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8370,17 +8366,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>16-02-2026 21:14:42</t>
+          <t>12-02-2026 12:53:41</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>12-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>16-02-2026 21:12:23</t>
+          <t>12-02-2026 12:53:05</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -8400,7 +8396,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>26170522411380002496</t>
+          <t>26170522292940002271</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr"/>
@@ -8424,12 +8420,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>343240</t>
+          <t>344019</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>21836</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -8439,95 +8435,87 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>HECTOR EDUARDO</t>
+          <t>ABRHAM ISACC</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CANALES</t>
+          <t>SUAREZ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LEYVA</t>
+          <t>KETCHUL</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6861255888</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>12-07-1992</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>ABRAHAM.SKET1@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>16-02-2026 11:31:00</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>16-02-2026 11:32:22</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>16-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>7602343861</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>C PASEO DEL AGUA 456</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Masculino</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>05-02-1997</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>HECTORCANALESLEYVA@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:48:03</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Forzoso</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>PROMO FEBRERO 12 MESES</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:53:41</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>12-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>12-02-2026 12:53:05</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8535,14 +8523,14 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>26170522292940002271</t>
+          <t>26170522385460002427</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
@@ -8559,12 +8547,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>344524</t>
+          <t>344362</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22341</t>
+          <t>22179</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8574,17 +8562,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>GERARDO ANTONIO</t>
+          <t xml:space="preserve">ANDREA MICHELL </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">IBAÑEZ </t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MANCILLA</t>
+          <t>URIBE</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8594,35 +8582,39 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6861832430</t>
+          <t>6863837971</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>BASTIA 2595</t>
+          <t>HERENCIA 2338</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>01-02-1966</t>
+          <t>15-08-2000</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>GERARDO.ANTONIO@GMAIL.COM</t>
+          <t>ANDREAESTRADA1218@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>17-02-2026 15:20:45</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+          <t>16-02-2026 21:04:29</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -8630,7 +8622,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
@@ -8640,17 +8632,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>23-02-2026 16:27:39</t>
+          <t>16-02-2026 21:14:42</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>23-02-2026 16:25:27</t>
+          <t>16-02-2026 21:12:23</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -8670,19 +8662,11 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>26170522587090002838</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522411380002496</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
           <t>499</t>
@@ -8690,24 +8674,24 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>344019</t>
+          <t>344524</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8717,17 +8701,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ABRHAM ISACC</t>
+          <t>GERARDO ANTONIO</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SUAREZ</t>
+          <t xml:space="preserve">IBAÑEZ </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KETCHUL</t>
+          <t>MANCILLA</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8737,10 +8721,14 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6861255888</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>6861832430</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>BASTIA 2595</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -8748,56 +8736,60 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>12-07-1992</t>
+          <t>01-02-1966</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>ABRAHAM.SKET1@GMAIL.COM</t>
+          <t>GERARDO.ANTONIO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>16-02-2026 11:31:00</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>17-02-2026 15:20:45</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>16-02-2026 11:32:22</t>
+          <t>23-02-2026 16:27:39</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr"/>
+          <t>23-03-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>23-02-2026 16:25:27</t>
+        </is>
+      </c>
       <c r="U62" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -8805,36 +8797,44 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>26170522385460002427</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
+          <t>26170522587090002838</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>344864</t>
+          <t>343968</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22681</t>
+          <t>21785</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8844,17 +8844,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ELIAS ABDIEL</t>
+          <t>ALEXIS ABRAHAM</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t xml:space="preserve">RAMOS </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>PINO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8864,32 +8864,32 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6865902031</t>
+          <t>6864284152</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>PRIV AUDACIA 2134</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>20-04-2005</t>
+          <t>17-11-2005</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>ELIASMORENO052@GMAIL.COM</t>
+          <t>ALEXISARP15@GMAIL.COM</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>18-02-2026 16:30:39</t>
+          <t>16-02-2026 08:36:23</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -8914,17 +8914,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>18-02-2026 16:40:13</t>
+          <t>16-02-2026 08:44:12</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>16-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>18-02-2026 16:34:10</t>
+          <t>16-02-2026 08:42:55</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>26170522466910002616</t>
+          <t>26170522381430002418</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr"/>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -8968,12 +8968,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>343968</t>
+          <t>345508</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21785</t>
+          <t>87673</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8983,17 +8983,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ALEXIS ABRAHAM</t>
+          <t>EMILI RUBY</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMOS </t>
+          <t>VALDEZ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PINO</t>
+          <t>CARDENAS</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6864284152</t>
+          <t>6861328502</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>PRIV AUDACIA 2134</t>
+          <t>CONSTANTINOPLA 396</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -9018,24 +9018,20 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>17-11-2005</t>
+          <t>06-01-2010</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>ALEXISARP15@GMAIL.COM</t>
+          <t>EMILI.RUBY@GMAIL.COM</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>16-02-2026 08:36:23</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>21-02-2026 11:00:05</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9043,7 +9039,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -9053,17 +9049,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>16-02-2026 08:44:12</t>
+          <t>27-02-2026 22:18:25</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>16-03-2026 23:59:59</t>
+          <t>27-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>16-02-2026 08:42:55</t>
+          <t>27-02-2026 22:16:49</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -9073,7 +9069,7 @@
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -9083,11 +9079,19 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>26170522381430002418</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
+          <t>26170522726580003133</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>499</t>
@@ -9095,12 +9099,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -9234,12 +9238,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>345453</t>
+          <t>345036</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>87618</t>
+          <t>87201</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9249,17 +9253,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>RENE FRANCISCO</t>
+          <t>NORMA ALICIA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">GUTIERREZ </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SOTO</t>
+          <t xml:space="preserve">MERCADO </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -9269,32 +9273,32 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6863948826</t>
+          <t>6863291327</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CASA DIGNA</t>
+          <t>POMONA 2446</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>17-02-1976</t>
+          <t>03-11-1976</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>RENEGARCIA170296@GMAIL.COM</t>
+          <t>NORMAAGUTIERREZM@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>21-02-2026 07:40:19</t>
+          <t>19-02-2026 11:31:06</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -9315,17 +9319,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>23-02-2026 07:36:13</t>
+          <t>19-02-2026 12:01:32</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>23-03-2026 23:59:59</t>
+          <t>19-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>23-02-2026 07:35:10</t>
+          <t>19-02-2026 11:44:54</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -9345,19 +9349,11 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>26170522572740002810</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170522492340002663</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
           <t>499</t>
@@ -9365,24 +9361,24 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>345036</t>
+          <t>344864</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>87201</t>
+          <t>22681</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9392,17 +9388,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NORMA ALICIA</t>
+          <t>ELIAS ABDIEL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">GUTIERREZ </t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">MERCADO </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -9412,35 +9408,39 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>6863291327</t>
+          <t>6865902031</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>POMONA 2446</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>03-11-1976</t>
+          <t>20-04-2005</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>NORMAAGUTIERREZM@HOTMAIL.COM</t>
+          <t>ELIASMORENO052@GMAIL.COM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>19-02-2026 11:31:06</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>18-02-2026 16:30:39</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -9458,17 +9458,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>19-02-2026 12:01:32</t>
+          <t>18-02-2026 16:40:13</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>19-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>19-02-2026 11:44:54</t>
+          <t>18-02-2026 16:34:10</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>26170522492340002663</t>
+          <t>26170522466910002616</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
@@ -9500,12 +9500,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -9790,12 +9790,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>345508</t>
+          <t>345453</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>87673</t>
+          <t>87618</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9805,17 +9805,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EMILI RUBY</t>
+          <t>RENE FRANCISCO</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>VALDEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CARDENAS</t>
+          <t>SOTO</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9825,32 +9825,32 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>6861328502</t>
+          <t>6863948826</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>CONSTANTINOPLA 396</t>
+          <t>CASA DIGNA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>06-01-2010</t>
+          <t>17-02-1976</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>EMILI.RUBY@GMAIL.COM</t>
+          <t>RENEGARCIA170296@GMAIL.COM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>21-02-2026 11:00:05</t>
+          <t>21-02-2026 07:40:19</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>BORRON Y CUENTA NUEVA 12 MESES $499</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
@@ -9871,17 +9871,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>27-02-2026 22:18:25</t>
+          <t>23-02-2026 07:36:13</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>27-03-2026 23:59:59</t>
+          <t>23-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>27-02-2026 22:16:49</t>
+          <t>23-02-2026 07:35:10</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>26170522726580003133</t>
+          <t>26170522572740002810</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -10211,12 +10211,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>344869</t>
+          <t>346742</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22686</t>
+          <t>88907</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">KEVIN MISAEL </t>
+          <t>INGRID MONSERRAT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>CASTELLANOS</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>6861053368</t>
+          <t>6863236007</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>DESTREZA 2781</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -10261,24 +10261,20 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>24-12-2004</t>
+          <t>19-08-2002</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>KEVINRAMIREZ2412@GMAIL.COM</t>
+          <t>INGRID.MONSE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>18-02-2026 16:38:43</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>inscripcion promo 199</t>
-        </is>
-      </c>
+          <t>26-02-2026 15:56:12</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -10286,7 +10282,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>PROMO FEBRERO 12 MESES</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -10296,17 +10292,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>18-02-2026 16:45:20</t>
+          <t>26-02-2026 15:59:45</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>18-03-2026 23:59:59</t>
+          <t>26-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>18-02-2026 16:43:02</t>
+          <t>26-02-2026 15:59:06</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -10316,7 +10312,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -10326,7 +10322,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>26170522467160002617</t>
+          <t>26170522685900003059</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr"/>
@@ -10338,24 +10334,24 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>345689</t>
+          <t>346065</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>87854</t>
+          <t>88230</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10365,17 +10361,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BRAYAN ALEXIS</t>
+          <t xml:space="preserve">LUZ ELENA </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t xml:space="preserve">BERNAL </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -10385,32 +10381,32 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6861096516</t>
+          <t>6861751473</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>NOTREDAME OESTE 295</t>
+          <t>C ISLAS ORCADAS 1927</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>27-09-1995</t>
+          <t>06-09-1973</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>DECKSARIA@GMAIL.COM</t>
+          <t>PDGA.LUZVERNAL@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>23-02-2026 09:56:35</t>
+          <t>24-02-2026 06:11:46</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -10435,17 +10431,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>24-02-2026 10:26:50</t>
+          <t>25-02-2026 06:08:41</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>24-03-2026 23:59:59</t>
+          <t>25-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>24-02-2026 10:26:08</t>
+          <t>25-02-2026 06:07:15</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -10455,7 +10451,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -10465,7 +10461,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>26170522615550002903</t>
+          <t>26170522640790002973</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
@@ -10497,12 +10493,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>346035</t>
+          <t>346148</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>88200</t>
+          <t>88313</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10512,17 +10508,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t xml:space="preserve">LINDA PATRICIA </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t xml:space="preserve">PERAZA </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -10532,32 +10528,32 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>6861618654</t>
+          <t>6692315071</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">GERONIMO 2675 </t>
+          <t>PASEO DEL REAL 455</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>08-08-1994</t>
+          <t>25-10-1986</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>ALEJANDRO.MUNOZ@GMAIL.COM</t>
+          <t>LPPERAZG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>23-02-2026 19:51:28</t>
+          <t>24-02-2026 13:10:41</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -10582,7 +10578,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>24-02-2026 20:10:23</t>
+          <t>24-02-2026 13:17:17</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -10592,7 +10588,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>24-02-2026 20:09:41</t>
+          <t>24-02-2026 13:15:52</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -10602,7 +10598,7 @@
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -10612,7 +10608,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>26170522636500002957</t>
+          <t>26170522618830002912</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr"/>
@@ -10636,12 +10632,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>346065</t>
+          <t>344869</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>88230</t>
+          <t>22686</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10651,17 +10647,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUZ ELENA </t>
+          <t xml:space="preserve">KEVIN MISAEL </t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">BERNAL </t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -10671,12 +10667,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>6861751473</t>
+          <t>6861053368</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>C ISLAS ORCADAS 1927</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -10686,17 +10682,17 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>06-09-1973</t>
+          <t>24-12-2004</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>PDGA.LUZVERNAL@HOTMAIL.COM</t>
+          <t>KEVINRAMIREZ2412@GMAIL.COM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>24-02-2026 06:11:46</t>
+          <t>18-02-2026 16:38:43</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -10721,17 +10717,17 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>25-02-2026 06:08:41</t>
+          <t>18-02-2026 16:45:20</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>25-03-2026 23:59:59</t>
+          <t>18-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>25-02-2026 06:07:15</t>
+          <t>18-02-2026 16:43:02</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -10741,7 +10737,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -10751,19 +10747,11 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>26170522640790002973</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170522467160002617</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
           <t>499</t>
@@ -10771,7 +10759,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>Saul  Galeana</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -10783,12 +10771,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>346148</t>
+          <t>346035</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>88313</t>
+          <t>88200</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10798,17 +10786,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINDA PATRICIA </t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">PERAZA </t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -10818,32 +10806,32 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>6692315071</t>
+          <t>6861618654</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>PASEO DEL REAL 455</t>
+          <t xml:space="preserve">GERONIMO 2675 </t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>25-10-1986</t>
+          <t>08-08-1994</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>LPPERAZG@GMAIL.COM</t>
+          <t>ALEJANDRO.MUNOZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>24-02-2026 13:10:41</t>
+          <t>23-02-2026 19:51:28</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -10868,7 +10856,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>24-02-2026 13:17:17</t>
+          <t>24-02-2026 20:10:23</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -10878,7 +10866,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>24-02-2026 13:15:52</t>
+          <t>24-02-2026 20:09:41</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -10888,7 +10876,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -10898,7 +10886,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>26170522618830002912</t>
+          <t>26170522636500002957</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr"/>
@@ -10922,12 +10910,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>346742</t>
+          <t>345689</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>88907</t>
+          <t>87854</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -10937,17 +10925,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>INGRID MONSERRAT</t>
+          <t>BRAYAN ALEXIS</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -10957,35 +10945,39 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>6863236007</t>
+          <t>6861096516</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>DESTREZA 2781</t>
+          <t>NOTREDAME OESTE 295</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>19-08-2002</t>
+          <t>27-09-1995</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>INGRID.MONSE@GMAIL.COM</t>
+          <t>DECKSARIA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>26-02-2026 15:56:12</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
+          <t>23-02-2026 09:56:35</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>inscripcion promo 199</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -10993,7 +10985,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>PROMO FEBRERO 12 MESES</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -11003,17 +10995,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>26-02-2026 15:59:45</t>
+          <t>24-02-2026 10:26:50</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>26-03-2026 23:59:59</t>
+          <t>24-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>26-02-2026 15:59:06</t>
+          <t>24-02-2026 10:26:08</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -11023,7 +11015,7 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
@@ -11033,11 +11025,19 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>26170522685900003059</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
+          <t>26170522615550002903</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>499</t>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Saul  Galeana</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,12 +856,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347710</t>
+          <t>309174</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89875</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KEVIN URIEL</t>
+          <t>CAMILA ANAHI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ALCALA</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>LANDEROS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6865258242</t>
+          <t>6862447701</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -901,57 +901,57 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>25-04-2004</t>
+          <t>10-04-2010</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>KEVINALCALA224@GMAIL.COM</t>
+          <t>CAMILAANAHI1010@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 16:52:40</t>
+          <t>12-08-2025 19:31:30</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 16:59:11</t>
+          <t>03-03-2026 17:23:07</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>02-03-2026 16:58:32</t>
+          <t>03-03-2026 17:22:43</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -971,36 +971,44 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26170522804230003223</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+          <t>26170522850510003334</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>YATZENI ALEXANDRA MORENO QUINTERO</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347903</t>
+          <t>309170</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90068</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1010,17 +1018,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">EREYLI KIAVETH </t>
+          <t>LUZ HEREYDA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>LANDEROS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">MILLAN </t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1030,12 +1038,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6863621801</t>
+          <t>6864056242</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HAVIENDA LA ESTANCIA 9</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1045,17 +1053,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>15-08-1995</t>
+          <t>14-10-1976</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>EREYLI.KIAVENTH@GMAIL.COM</t>
+          <t>LUZ_HLANDEROS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 20:32:15</t>
+          <t>12-08-2025 19:24:04</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1080,17 +1088,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 20:37:43</t>
+          <t>03-03-2026 17:18:00</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 20:36:54</t>
+          <t>03-03-2026 17:16:23</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1100,7 +1108,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1110,11 +1118,19 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26170522819910003279</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>26170522850020003332</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>549</t>
@@ -1122,24 +1138,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347910</t>
+          <t>347859</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90075</t>
+          <t>90024</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1149,17 +1165,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PAULETT NICOLE</t>
+          <t>ERIKA LILIANA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AVENDAÑO</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CARRERA</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1169,10 +1185,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6861005692</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>6861090195</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>DAMIANAS 988</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1180,32 +1200,32 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>08-02-2011</t>
+          <t>20-12-1983</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PAVENDANO@EDUBC.COM.MX</t>
+          <t>ERIKA.MUOZ.H@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 21:00:40</t>
+          <t>02-03-2026 19:00:26</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1215,21 +1235,29 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 21:01:59</t>
+          <t>03-03-2026 20:07:42</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:07:01</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1237,11 +1265,19 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26170522820430003283</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26170522860450003370</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>549</t>
@@ -1261,12 +1297,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347878</t>
+          <t>347710</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90043</t>
+          <t>89875</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1312,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OMAR SALVADOR</t>
+          <t>KEVIN URIEL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BECERRA</t>
+          <t>ALCALA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BARBA</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,7 +1332,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6866066983</t>
+          <t>6865258242</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1311,42 +1347,42 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>09-03-2005</t>
+          <t>25-04-2004</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BARBAOMAR68@GMAIL.COM</t>
+          <t>KEVINALCALA224@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 19:43:58</t>
+          <t>02-03-2026 16:52:40</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 19:50:24</t>
+          <t>02-03-2026 16:59:11</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1356,7 +1392,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-03-2026 19:49:48</t>
+          <t>02-03-2026 16:58:32</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1376,22 +1412,1098 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26170522818050003264</t>
+          <t>26170522804230003223</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>347933</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>90098</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEONEL FAUSTINO </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CHAVEZ</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6864205790</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>26-03-2012</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>LEONELMARTINEZ@COLEGIOVASCONCELOS.NET</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:24:46</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>549</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>03-03-2026 05:26:34</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>26170522823240003292</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>348140</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>90305</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BRENDA JUDITH</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>HERNADEZ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CANTERO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4423654832</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>30-06-1994</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>JUDITHDZCANT@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:56:54</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:01:30</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:00:48</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>26170522848940003330</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>347878</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OMAR SALVADOR</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BECERRA</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BARBA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6866066983</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>09-03-2005</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>BARBAOMAR68@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:43:58</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:50:24</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:49:48</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>26170522818050003264</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>348264</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>90429</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GISSELA GUADALUPE </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CASTRO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAYAN </t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6862343891</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>06-12-1996</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>CASTROGISSELA2@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:24:27</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:26:23</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>26170522858740003362</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>347903</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>90068</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EREYLI KIAVETH </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PEREZ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MILLAN </t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6863621801</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>HAVIENDA LA ESTANCIA 9</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>15-08-1995</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>EREYLI.KIAVENTH@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:32:15</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:37:43</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>02-03-2026 20:36:54</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>26170522819910003279</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>347974</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>90139</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ARIANA DENISSE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLEGAS </t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PONCE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6863922841</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>CASA  GRANDE 1908</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>02-01-1997</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>A.PONCE@OULOCK.COM</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:47:41</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:54:52</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:53:26</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>26170522834130003305</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>348254</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>90419</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JULIO CESAR </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SILVA </t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DEL CID</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6861501383</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MILANO 1122</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>22-11-1977</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>JULIODELCID@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:07:08</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:12:13</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:11:36</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>26170522857870003357</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>347910</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>90075</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PAULETT NICOLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AVENDAÑO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CARRERA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6861005692</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>08-02-2011</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PAVENDANO@EDUBC.COM.MX</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>02-03-2026 21:00:40</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>02-03-2026 21:01:59</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>26170522820430003283</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347517</t>
+          <t>309170</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89682</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DIEGO ADRIAN</t>
+          <t>LUZ HEREYDA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>LANDEROS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,32 +613,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6863085535</t>
+          <t>6864056242</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>VALOR 1199</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>04-09-2002</t>
+          <t>14-10-1976</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>DIEGOG5531@GMAIL.COM</t>
+          <t>LUZ_HLANDEROS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 11:51:43</t>
+          <t>12-08-2025 19:24:04</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 12:00:33</t>
+          <t>03-03-2026 17:18:00</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>02-03-2026 11:58:53</t>
+          <t>03-03-2026 17:16:23</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -693,11 +693,19 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26170522790100003195</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>26170522850020003332</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>549</t>
@@ -705,24 +713,24 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347527</t>
+          <t>347552</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89692</t>
+          <t>89717</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +740,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HECTOR DANIEL</t>
+          <t xml:space="preserve">VICTOR </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VASCONCELOS</t>
+          <t xml:space="preserve">ORTIZ </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ARAGON</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,12 +760,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6863386463</t>
+          <t>6862684016</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LA PALMITA 1965</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -767,17 +775,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>02-05-2004</t>
+          <t>22-09-1999</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ARAGOND158@GMAIL.COM</t>
+          <t>VICTOR-OP15@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 12:07:31</t>
+          <t>02-03-2026 13:01:26</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -802,17 +810,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 12:18:44</t>
+          <t>04-03-2026 12:34:41</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>02-03-2026 12:13:55</t>
+          <t>04-03-2026 12:33:08</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -832,7 +840,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26170522790830003198</t>
+          <t>26170522880700003393</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -856,12 +864,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>309174</t>
+          <t>347859</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>90024</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,17 +879,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CAMILA ANAHI</t>
+          <t>ERIKA LILIANA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LANDEROS</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -891,12 +899,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6862447701</t>
+          <t>6861090195</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>DAMIANAS 988</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -906,17 +914,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>10-04-2010</t>
+          <t>20-12-1983</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CAMILAANAHI1010@GMAIL.COM</t>
+          <t>ERIKA.MUOZ.H@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12-08-2025 19:31:30</t>
+          <t>02-03-2026 19:00:26</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -941,7 +949,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-03-2026 17:23:07</t>
+          <t>03-03-2026 20:07:42</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -951,7 +959,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>03-03-2026 17:22:43</t>
+          <t>03-03-2026 20:07:01</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -971,7 +979,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26170522850510003334</t>
+          <t>26170522860450003370</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -981,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>YATZENI ALEXANDRA MORENO QUINTERO</t>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,24 +999,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>309170</t>
+          <t>347517</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>89682</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1018,17 +1026,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LUZ HEREYDA</t>
+          <t>DIEGO ADRIAN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LANDEROS</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1038,32 +1046,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6864056242</t>
+          <t>6863085535</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>VALOR 1199</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>14-10-1976</t>
+          <t>04-09-2002</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>LUZ_HLANDEROS@HOTMAIL.COM</t>
+          <t>DIEGOG5531@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12-08-2025 19:24:04</t>
+          <t>02-03-2026 11:51:43</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1088,17 +1096,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>03-03-2026 17:18:00</t>
+          <t>02-03-2026 12:00:33</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>03-03-2026 17:16:23</t>
+          <t>02-03-2026 11:58:53</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1108,7 +1116,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1118,19 +1126,11 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26170522850020003332</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
-        </is>
-      </c>
+          <t>26170522790100003195</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>549</t>
@@ -1138,24 +1138,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347859</t>
+          <t>347527</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90024</t>
+          <t>89692</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ERIKA LILIANA</t>
+          <t>HECTOR DANIEL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>VASCONCELOS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>ARAGON</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1185,32 +1185,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6861090195</t>
+          <t>6863386463</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DAMIANAS 988</t>
+          <t>LA PALMITA 1965</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>20-12-1983</t>
+          <t>02-05-2004</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ERIKA.MUOZ.H@GMAIL.COM</t>
+          <t>ARAGOND158@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 19:00:26</t>
+          <t>02-03-2026 12:07:31</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1235,17 +1235,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 20:07:42</t>
+          <t>02-03-2026 12:18:44</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>03-03-2026 20:07:01</t>
+          <t>02-03-2026 12:13:55</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1265,19 +1265,11 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26170522860450003370</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522790830003198</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
           <t>549</t>
@@ -1424,24 +1416,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347933</t>
+          <t>348264</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90098</t>
+          <t>90429</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1451,17 +1443,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEONEL FAUSTINO </t>
+          <t xml:space="preserve">GISSELA GUADALUPE </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t xml:space="preserve">PAYAN </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1471,33 +1463,33 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6864205790</t>
+          <t>6862343891</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>26-03-2012</t>
+          <t>06-12-1996</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>LEONELMARTINEZ@COLEGIOVASCONCELOS.NET</t>
+          <t>CASTROGISSELA2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-03-2026 05:24:46</t>
+          <t>03-03-2026 19:24:27</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1507,17 +1499,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 05:26:34</t>
+          <t>03-03-2026 19:26:23</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1539,14 +1531,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26170522823240003292</t>
+          <t>26170522858740003362</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1563,12 +1555,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>348140</t>
+          <t>309174</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90305</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1578,17 +1570,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BRENDA JUDITH</t>
+          <t>CAMILA ANAHI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HERNADEZ</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CANTERO</t>
+          <t>LANDEROS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1598,7 +1590,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4423654832</t>
+          <t>6862447701</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1613,42 +1605,42 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>30-06-1994</t>
+          <t>10-04-2010</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>JUDITHDZCANT@GMAIL.COM</t>
+          <t>CAMILAANAHI1010@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>03-03-2026 16:56:54</t>
+          <t>12-08-2025 19:31:30</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 17:01:30</t>
+          <t>03-03-2026 17:23:07</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1658,7 +1650,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>03-03-2026 17:00:48</t>
+          <t>03-03-2026 17:22:43</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1678,36 +1670,44 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26170522848940003330</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26170522850510003334</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>YATZENI ALEXANDRA MORENO QUINTERO</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347878</t>
+          <t>347903</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90043</t>
+          <t>90068</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1717,17 +1717,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OMAR SALVADOR</t>
+          <t xml:space="preserve">EREYLI KIAVETH </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BECERRA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BARBA</t>
+          <t xml:space="preserve">MILLAN </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1737,32 +1737,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6866066983</t>
+          <t>6863621801</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>HAVIENDA LA ESTANCIA 9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>09-03-2005</t>
+          <t>15-08-1995</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BARBAOMAR68@GMAIL.COM</t>
+          <t>EREYLI.KIAVENTH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 19:43:58</t>
+          <t>02-03-2026 20:32:15</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 19:50:24</t>
+          <t>02-03-2026 20:37:43</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>02-03-2026 19:49:48</t>
+          <t>02-03-2026 20:36:54</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26170522818050003264</t>
+          <t>26170522819910003279</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1829,24 +1829,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>348264</t>
+          <t>347974</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90429</t>
+          <t>90139</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">GISSELA GUADALUPE </t>
+          <t>ARIANA DENISSE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">VILLEGAS </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAYAN </t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1876,10 +1876,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6862343891</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6863922841</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CASA  GRANDE 1908</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1887,42 +1891,42 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>06-12-1996</t>
+          <t>02-01-1997</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CASTROGISSELA2@GMAIL.COM</t>
+          <t>A.PONCE@OULOCK.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 19:24:27</t>
+          <t>03-03-2026 08:47:41</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 19:26:23</t>
+          <t>03-03-2026 08:54:52</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1930,13 +1934,21 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:53:26</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1944,14 +1956,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26170522858740003362</t>
+          <t>26170522834130003305</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1968,12 +1980,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347903</t>
+          <t>347878</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90068</t>
+          <t>90043</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1983,17 +1995,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">EREYLI KIAVETH </t>
+          <t>OMAR SALVADOR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>BECERRA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MILLAN </t>
+          <t>BARBA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2003,32 +2015,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6863621801</t>
+          <t>6866066983</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>HAVIENDA LA ESTANCIA 9</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>15-08-1995</t>
+          <t>09-03-2005</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>EREYLI.KIAVENTH@GMAIL.COM</t>
+          <t>BARBAOMAR68@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 20:32:15</t>
+          <t>02-03-2026 19:43:58</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2053,7 +2065,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 20:37:43</t>
+          <t>02-03-2026 19:50:24</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2063,7 +2075,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>02-03-2026 20:36:54</t>
+          <t>02-03-2026 19:49:48</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2083,7 +2095,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26170522819910003279</t>
+          <t>26170522818050003264</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2095,24 +2107,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347974</t>
+          <t>347910</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90139</t>
+          <t>90075</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2122,17 +2134,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ARIANA DENISSE</t>
+          <t>PAULETT NICOLE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLEGAS </t>
+          <t>AVENDAÑO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>CARRERA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2142,14 +2154,10 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6863922841</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CASA  GRANDE 1908</t>
-        </is>
-      </c>
+          <t>6861005692</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2157,32 +2165,32 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>02-01-1997</t>
+          <t>08-02-2011</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>A.PONCE@OULOCK.COM</t>
+          <t>PAVENDANO@EDUBC.COM.MX</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 08:47:41</t>
+          <t>02-03-2026 21:00:40</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2192,29 +2200,21 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 08:54:52</t>
+          <t>02-03-2026 21:01:59</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>03-03-2026 08:53:26</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26170522834130003305</t>
+          <t>26170522820430003283</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -2385,12 +2385,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347910</t>
+          <t>347933</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90075</t>
+          <t>90098</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2400,17 +2400,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PAULETT NICOLE</t>
+          <t xml:space="preserve">LEONEL FAUSTINO </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AVENDAÑO</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CARRERA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2420,28 +2420,28 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6861005692</t>
+          <t>6864205790</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>08-02-2011</t>
+          <t>26-03-2012</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PAVENDANO@EDUBC.COM.MX</t>
+          <t>LEONELMARTINEZ@COLEGIOVASCONCELOS.NET</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 21:00:40</t>
+          <t>03-03-2026 05:24:46</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2466,18 +2466,18 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 21:01:59</t>
+          <t>03-03-2026 05:26:34</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26170522820430003283</t>
+          <t>26170522823240003292</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2506,6 +2506,423 @@
       <c r="AC15" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>348456</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>90621</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>JAVIER BERNARDO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ANDRADE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6861358156</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>TORRE LAS ARCAS 2061</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>09-12-1992</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>FRANXYS_BARAJAS018@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:10:42</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:17:23</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:16:44</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>26170522884760003398</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>348800</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>90965</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NANCY FERNANDA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6861440730</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BOSQUE ZORZAL 775</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>08-08-1991</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>FERNANDA9189@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:20:03</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:26:02</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:25:30</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>26170522929400003484</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>348140</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>90305</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BRENDA JUDITH</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>HERNADEZ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CANTERO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4423654832</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>30-06-1994</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>JUDITHDZCANT@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:56:54</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:01:30</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:00:48</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26170522848940003330</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>309170</t>
+          <t>309174</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,19 +593,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LUZ HEREYDA</t>
+          <t>CAMILA ANAHI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>LANDEROS</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>BARRERA</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>52</t>
@@ -613,7 +613,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6864056242</t>
+          <t>6862447701</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -628,17 +628,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>14-10-1976</t>
+          <t>10-04-2010</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>LUZ_HLANDEROS@HOTMAIL.COM</t>
+          <t>CAMILAANAHI1010@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>12-08-2025 19:24:04</t>
+          <t>12-08-2025 19:31:30</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>03-03-2026 17:18:00</t>
+          <t>03-03-2026 17:23:07</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>03-03-2026 17:16:23</t>
+          <t>03-03-2026 17:22:43</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26170522850020003332</t>
+          <t>26170522850510003334</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
+          <t>YATZENI ALEXANDRA MORENO QUINTERO</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -725,12 +725,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347552</t>
+          <t>309170</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89717</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -740,17 +740,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR </t>
+          <t>LUZ HEREYDA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTIZ </t>
+          <t>LANDEROS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6862684016</t>
+          <t>6864056242</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -770,22 +770,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>22-09-1999</t>
+          <t>14-10-1976</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>VICTOR-OP15@HOTMAIL.COM</t>
+          <t>LUZ_HLANDEROS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 13:01:26</t>
+          <t>12-08-2025 19:24:04</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -810,17 +810,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>04-03-2026 12:34:41</t>
+          <t>03-03-2026 17:18:00</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>04-03-2026 12:33:08</t>
+          <t>03-03-2026 17:16:23</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -840,11 +840,19 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26170522880700003393</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>26170522850020003332</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>549</t>
@@ -852,24 +860,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347859</t>
+          <t>347517</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>90024</t>
+          <t>89682</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -879,17 +887,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ERIKA LILIANA</t>
+          <t>DIEGO ADRIAN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -899,32 +907,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6861090195</t>
+          <t>6863085535</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DAMIANAS 988</t>
+          <t>VALOR 1199</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20-12-1983</t>
+          <t>04-09-2002</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ERIKA.MUOZ.H@GMAIL.COM</t>
+          <t>DIEGOG5531@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 19:00:26</t>
+          <t>02-03-2026 11:51:43</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -949,17 +957,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-03-2026 20:07:42</t>
+          <t>02-03-2026 12:00:33</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>03-03-2026 20:07:01</t>
+          <t>02-03-2026 11:58:53</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -969,7 +977,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -979,19 +987,11 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26170522860450003370</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522790100003195</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>549</t>
@@ -1011,12 +1011,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347517</t>
+          <t>347527</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89682</t>
+          <t>89692</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1026,17 +1026,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DIEGO ADRIAN</t>
+          <t>HECTOR DANIEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>VASCONCELOS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>ARAGON</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6863085535</t>
+          <t>6863386463</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>VALOR 1199</t>
+          <t>LA PALMITA 1965</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>04-09-2002</t>
+          <t>02-05-2004</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>DIEGOG5531@GMAIL.COM</t>
+          <t>ARAGOND158@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 11:51:43</t>
+          <t>02-03-2026 12:07:31</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1096,17 +1096,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 12:00:33</t>
+          <t>02-03-2026 12:18:44</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 11:58:53</t>
+          <t>02-03-2026 12:13:55</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26170522790100003195</t>
+          <t>26170522790830003198</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1150,12 +1150,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347527</t>
+          <t>347710</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89692</t>
+          <t>89875</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HECTOR DANIEL</t>
+          <t>KEVIN URIEL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VASCONCELOS</t>
+          <t>ALCALA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ARAGON</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6863386463</t>
+          <t>6865258242</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LA PALMITA 1965</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1200,52 +1200,52 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>02-05-2004</t>
+          <t>25-04-2004</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ARAGOND158@GMAIL.COM</t>
+          <t>KEVINALCALA224@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 12:07:31</t>
+          <t>02-03-2026 16:52:40</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 12:18:44</t>
+          <t>02-03-2026 16:59:11</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 12:13:55</t>
+          <t>02-03-2026 16:58:32</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1265,36 +1265,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26170522790830003198</t>
+          <t>26170522804230003223</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347710</t>
+          <t>347933</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89875</t>
+          <t>90098</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KEVIN URIEL</t>
+          <t xml:space="preserve">LEONEL FAUSTINO </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ALCALA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1324,14 +1324,10 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6865258242</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6864205790</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -1339,42 +1335,42 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>25-04-2004</t>
+          <t>26-03-2012</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>KEVINALCALA224@GMAIL.COM</t>
+          <t>LEONELMARTINEZ@COLEGIOVASCONCELOS.NET</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 16:52:40</t>
+          <t>03-03-2026 05:24:46</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 16:59:11</t>
+          <t>03-03-2026 05:26:34</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1382,21 +1378,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:58:32</t>
-        </is>
-      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1404,36 +1392,36 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26170522804230003223</t>
+          <t>26170522823240003292</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>348264</t>
+          <t>348140</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90429</t>
+          <t>90305</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1443,17 +1431,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">GISSELA GUADALUPE </t>
+          <t>BRENDA JUDITH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t>HERNADEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAYAN </t>
+          <t>CANTERO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1463,10 +1451,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6862343891</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>4423654832</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1474,17 +1466,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>06-12-1996</t>
+          <t>30-06-1994</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CASTROGISSELA2@GMAIL.COM</t>
+          <t>JUDITHDZCANT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-03-2026 19:24:27</t>
+          <t>03-03-2026 16:56:54</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1494,36 +1486,44 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 19:26:23</t>
+          <t>03-03-2026 17:01:30</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:00:48</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1531,36 +1531,36 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26170522858740003362</t>
+          <t>26170522848940003330</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>309174</t>
+          <t>347910</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>90075</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1570,17 +1570,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CAMILA ANAHI</t>
+          <t>PAULETT NICOLE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>AVENDAÑO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LANDEROS</t>
+          <t>CARRERA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1590,14 +1590,10 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6862447701</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6861005692</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1605,32 +1601,32 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>10-04-2010</t>
+          <t>08-02-2011</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CAMILAANAHI1010@GMAIL.COM</t>
+          <t>PAVENDANO@EDUBC.COM.MX</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>12-08-2025 19:31:30</t>
+          <t>02-03-2026 21:00:40</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1640,29 +1636,21 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>03-03-2026 17:23:07</t>
+          <t>02-03-2026 21:01:59</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:22:43</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1670,19 +1658,11 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26170522850510003334</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>YATZENI ALEXANDRA MORENO QUINTERO</t>
-        </is>
-      </c>
+          <t>26170522820430003283</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>549</t>
@@ -1702,12 +1682,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347903</t>
+          <t>347878</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90068</t>
+          <t>90043</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1717,17 +1697,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">EREYLI KIAVETH </t>
+          <t>OMAR SALVADOR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>BECERRA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">MILLAN </t>
+          <t>BARBA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1737,32 +1717,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6863621801</t>
+          <t>6866066983</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>HAVIENDA LA ESTANCIA 9</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>15-08-1995</t>
+          <t>09-03-2005</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>EREYLI.KIAVENTH@GMAIL.COM</t>
+          <t>BARBAOMAR68@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 20:32:15</t>
+          <t>02-03-2026 19:43:58</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1787,17 +1767,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 20:37:43</t>
+          <t>02-03-2026 19:50:24</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>02-03-2026 20:36:54</t>
+          <t>02-03-2026 19:49:48</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1817,7 +1797,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26170522819910003279</t>
+          <t>26170522818050003264</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1829,24 +1809,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347974</t>
+          <t>347903</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90139</t>
+          <t>90068</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1856,17 +1836,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ARIANA DENISSE</t>
+          <t xml:space="preserve">EREYLI KIAVETH </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLEGAS </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t xml:space="preserve">MILLAN </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1876,12 +1856,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6863922841</t>
+          <t>6863621801</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CASA  GRANDE 1908</t>
+          <t>HAVIENDA LA ESTANCIA 9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1891,17 +1871,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>02-01-1997</t>
+          <t>15-08-1995</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>A.PONCE@OULOCK.COM</t>
+          <t>EREYLI.KIAVENTH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 08:47:41</t>
+          <t>02-03-2026 20:32:15</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1926,17 +1906,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 08:54:52</t>
+          <t>02-03-2026 20:37:43</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>03-03-2026 08:53:26</t>
+          <t>02-03-2026 20:36:54</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1956,7 +1936,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26170522834130003305</t>
+          <t>26170522819910003279</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1968,24 +1948,24 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347878</t>
+          <t>347974</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90043</t>
+          <t>90139</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1995,17 +1975,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OMAR SALVADOR</t>
+          <t>ARIANA DENISSE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BECERRA</t>
+          <t xml:space="preserve">VILLEGAS </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BARBA</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2015,32 +1995,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6866066983</t>
+          <t>6863922841</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>CASA  GRANDE 1908</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>09-03-2005</t>
+          <t>02-01-1997</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>BARBAOMAR68@GMAIL.COM</t>
+          <t>A.PONCE@OULOCK.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 19:43:58</t>
+          <t>03-03-2026 08:47:41</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2065,7 +2045,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 19:50:24</t>
+          <t>03-03-2026 08:54:52</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2075,7 +2055,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>02-03-2026 19:49:48</t>
+          <t>03-03-2026 08:53:26</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2095,7 +2075,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26170522818050003264</t>
+          <t>26170522834130003305</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2119,12 +2099,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347910</t>
+          <t>347552</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90075</t>
+          <t>89717</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2134,17 +2114,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PAULETT NICOLE</t>
+          <t xml:space="preserve">VICTOR </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AVENDAÑO</t>
+          <t xml:space="preserve">ORTIZ </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CARRERA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2154,43 +2134,47 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6861005692</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>6862684016</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>08-02-2011</t>
+          <t>22-09-1999</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>PAVENDANO@EDUBC.COM.MX</t>
+          <t>VICTOR-OP15@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 21:00:40</t>
+          <t>02-03-2026 13:01:26</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2200,21 +2184,29 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 21:01:59</t>
+          <t>04-03-2026 12:34:41</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>04-03-2026 12:33:08</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2222,7 +2214,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26170522820430003283</t>
+          <t>26170522880700003393</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2234,24 +2226,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348254</t>
+          <t>348456</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90419</t>
+          <t>90621</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2261,17 +2253,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">JULIO CESAR </t>
+          <t>JAVIER BERNARDO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVA </t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DEL CID</t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2281,32 +2273,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6861501383</t>
+          <t>6861358156</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MILANO 1122</t>
+          <t>TORRE LAS ARCAS 2061</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22-11-1977</t>
+          <t>09-12-1992</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>JULIODELCID@GMAIL.COM</t>
+          <t>FRANXYS_BARAJAS018@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>03-03-2026 19:07:08</t>
+          <t>04-03-2026 15:10:42</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2331,7 +2323,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>03-03-2026 19:12:13</t>
+          <t>04-03-2026 15:17:23</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2341,7 +2333,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>03-03-2026 19:11:36</t>
+          <t>04-03-2026 15:16:44</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2361,7 +2353,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26170522857870003357</t>
+          <t>26170522884760003398</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2373,24 +2365,24 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Raymundo Cardenas Real</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347933</t>
+          <t>348264</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90098</t>
+          <t>90429</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2400,17 +2392,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEONEL FAUSTINO </t>
+          <t xml:space="preserve">GISSELA GUADALUPE </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t xml:space="preserve">PAYAN </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2420,33 +2412,33 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6864205790</t>
+          <t>6862343891</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>26-03-2012</t>
+          <t>06-12-1996</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>LEONELMARTINEZ@COLEGIOVASCONCELOS.NET</t>
+          <t>CASTROGISSELA2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 05:24:46</t>
+          <t>03-03-2026 19:24:27</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2456,22 +2448,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 05:26:34</t>
+          <t>03-03-2026 19:26:23</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2488,14 +2480,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26170522823240003292</t>
+          <t>26170522858740003362</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2512,12 +2504,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348456</t>
+          <t>348254</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90621</t>
+          <t>90419</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2527,17 +2519,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>JAVIER BERNARDO</t>
+          <t xml:space="preserve">JULIO CESAR </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t xml:space="preserve">SILVA </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>DEL CID</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2547,32 +2539,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6861358156</t>
+          <t>6861501383</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TORRE LAS ARCAS 2061</t>
+          <t>MILANO 1122</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>09-12-1992</t>
+          <t>22-11-1977</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>FRANXYS_BARAJAS018@HOTMAIL.COM</t>
+          <t>JULIODELCID@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>04-03-2026 15:10:42</t>
+          <t>03-03-2026 19:07:08</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2597,17 +2589,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>04-03-2026 15:17:23</t>
+          <t>03-03-2026 19:12:13</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>04-03-2026 15:16:44</t>
+          <t>03-03-2026 19:11:36</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2627,7 +2619,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26170522884760003398</t>
+          <t>26170522857870003357</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2639,12 +2631,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Raymundo Cardenas Real</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2733,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2790,12 +2782,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>348140</t>
+          <t>347859</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90305</t>
+          <t>90024</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2805,17 +2797,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BRENDA JUDITH</t>
+          <t>ERIKA LILIANA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HERNADEZ</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CANTERO</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2825,12 +2817,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4423654832</t>
+          <t>6861090195</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>DAMIANAS 988</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2840,89 +2832,224 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>30-06-1994</t>
+          <t>20-12-1983</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>JUDITHDZCANT@GMAIL.COM</t>
+          <t>ERIKA.MUOZ.H@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>03-03-2026 16:56:54</t>
+          <t>02-03-2026 19:00:26</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:07:42</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:07:01</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>26170522860450003370</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>348847</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>91012</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSCAR </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SERNA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>MAPULA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6866069985</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>31-10-1991</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>OSCAR.SERNA18@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>06-03-2026 08:03:53</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t>Tarifas 2026 LE</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>No Forzoso</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>RECURRENTE $649 LE</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:01:30</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:00:48</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>06-03-2026 08:05:18</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>26170522848940003330</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Thannia Lilian Lugo Morales</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>con rutina</t>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>26170522944050003508</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>309174</t>
+          <t>308413</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CAMILA ANAHI</t>
+          <t>SAID ISMAEL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t xml:space="preserve">ROMAN </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LANDEROS</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,47 +613,43 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6862447701</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6862454233</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>10-04-2010</t>
+          <t>12-03-2010</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CAMILAANAHI1010@GMAIL.COM</t>
+          <t>RSAIDISMAEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>12-08-2025 19:31:30</t>
+          <t>08-08-2025 13:06:57</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -663,29 +659,21 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>03-03-2026 17:23:07</t>
+          <t>09-03-2026 20:15:54</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:22:43</t>
-        </is>
-      </c>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -693,7 +681,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26170522850510003334</t>
+          <t>26170523030910003658</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -703,7 +691,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>YATZENI ALEXANDRA MORENO QUINTERO</t>
+          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -713,7 +701,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -725,12 +713,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>309170</t>
+          <t>309174</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -740,19 +728,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LUZ HEREYDA</t>
+          <t>CAMILA ANAHI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>LANDEROS</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>BARRERA</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>52</t>
@@ -760,7 +748,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6864056242</t>
+          <t>6862447701</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -775,17 +763,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>14-10-1976</t>
+          <t>10-04-2010</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>LUZ_HLANDEROS@HOTMAIL.COM</t>
+          <t>CAMILAANAHI1010@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12-08-2025 19:24:04</t>
+          <t>12-08-2025 19:31:30</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -810,7 +798,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 17:18:00</t>
+          <t>03-03-2026 17:23:07</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -820,7 +808,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>03-03-2026 17:16:23</t>
+          <t>03-03-2026 17:22:43</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -840,7 +828,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26170522850020003332</t>
+          <t>26170522850510003334</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -850,7 +838,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
+          <t>YATZENI ALEXANDRA MORENO QUINTERO</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +860,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347517</t>
+          <t>127830</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89682</t>
+          <t>25503</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -887,17 +875,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DIEGO ADRIAN</t>
+          <t>BRYAN ALAN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">LUNA </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -907,12 +895,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6863085535</t>
+          <t>6866024630</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>VALOR 1199</t>
+          <t>TAMAULIPAS 440</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -922,32 +910,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>04-09-2002</t>
+          <t>23-12-1996</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>DIEGOG5531@GMAIL.COM</t>
+          <t>BRYANLUNAGLEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 11:51:43</t>
+          <t>05-10-2022 17:20:12</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -957,29 +945,21 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 12:00:33</t>
+          <t>09-03-2026 14:49:12</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>02-03-2026 11:58:53</t>
-        </is>
-      </c>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -987,7 +967,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26170522790100003195</t>
+          <t>26010523009900006038</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -999,24 +979,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347527</t>
+          <t>212091</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89692</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1026,17 +1006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HECTOR DANIEL</t>
+          <t>YAMILETH MARISOL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VASCONCELOS</t>
+          <t>ARREDONDO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ARAGON</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1046,32 +1026,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6863386463</t>
+          <t>5627748663</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LA PALMITA 1965</t>
+          <t>ORGULLO 2242</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>02-05-2004</t>
+          <t>05-04-2005</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ARAGOND158@GMAIL.COM</t>
+          <t>YAMILETHMARISELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 12:07:31</t>
+          <t>30-12-2023 13:26:00</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1096,17 +1076,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 12:18:44</t>
+          <t>16-03-2026 19:53:36</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 12:13:55</t>
+          <t>16-03-2026 19:52:04</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1126,7 +1106,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26170522790830003198</t>
+          <t>26170523234130003979</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1150,12 +1130,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347710</t>
+          <t>333353</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89875</t>
+          <t>17220</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1165,17 +1145,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KEVIN URIEL</t>
+          <t xml:space="preserve">DIEGO ALEJANDRO </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ALCALA</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>AVILES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1185,12 +1165,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6865258242</t>
+          <t>6866194136</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>HACIENDA SAN BERNARDO 60</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1200,52 +1180,52 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>25-04-2004</t>
+          <t>02-02-2010</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>KEVINALCALA224@GMAIL.COM</t>
+          <t>DIEGO.ALEJANDROO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 16:52:40</t>
+          <t>09-01-2026 16:23:37</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 16:59:11</t>
+          <t>16-03-2026 18:09:21</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 16:58:32</t>
+          <t>16-03-2026 18:08:51</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1265,36 +1245,44 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26170522804230003223</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>26170523230230003968</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347933</t>
+          <t>309170</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90098</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1304,17 +1292,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEONEL FAUSTINO </t>
+          <t>LUZ HEREYDA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>LANDEROS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1324,43 +1312,47 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6864205790</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6864056242</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>26-03-2012</t>
+          <t>14-10-1976</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>LEONELMARTINEZ@COLEGIOVASCONCELOS.NET</t>
+          <t>LUZ_HLANDEROS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>03-03-2026 05:24:46</t>
+          <t>12-08-2025 19:24:04</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1370,7 +1362,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 05:26:34</t>
+          <t>03-03-2026 17:18:00</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1378,13 +1370,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:16:23</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1392,11 +1392,19 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26170522823240003292</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26170522850020003332</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>549</t>
@@ -1404,24 +1412,24 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Raymundo Cardenas Real</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>348140</t>
+          <t>347710</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90305</t>
+          <t>89875</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1431,17 +1439,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BRENDA JUDITH</t>
+          <t>KEVIN URIEL</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HERNADEZ</t>
+          <t>ALCALA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CANTERO</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1451,7 +1459,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4423654832</t>
+          <t>6865258242</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1461,22 +1469,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30-06-1994</t>
+          <t>25-04-2004</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>JUDITHDZCANT@GMAIL.COM</t>
+          <t>KEVINALCALA224@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-03-2026 16:56:54</t>
+          <t>02-03-2026 16:52:40</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1501,17 +1509,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 17:01:30</t>
+          <t>02-03-2026 16:59:11</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>03-03-2026 17:00:48</t>
+          <t>02-03-2026 16:58:32</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1521,7 +1529,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1531,7 +1539,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26170522848940003330</t>
+          <t>26170522804230003223</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1543,7 +1551,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1555,12 +1563,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347910</t>
+          <t>347517</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90075</t>
+          <t>89682</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1570,17 +1578,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PAULETT NICOLE</t>
+          <t>DIEGO ADRIAN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AVENDAÑO</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CARRERA</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1590,43 +1598,47 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6861005692</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>6863085535</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>VALOR 1199</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>08-02-2011</t>
+          <t>04-09-2002</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PAVENDANO@EDUBC.COM.MX</t>
+          <t>DIEGOG5531@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 21:00:40</t>
+          <t>02-03-2026 11:51:43</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1636,7 +1648,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 21:01:59</t>
+          <t>02-03-2026 12:00:33</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1644,13 +1656,21 @@
           <t>01-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>02-03-2026 11:58:53</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1658,7 +1678,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26170522820430003283</t>
+          <t>26170522790100003195</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1670,7 +1690,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Raymundo Cardenas Real</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1682,12 +1702,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347878</t>
+          <t>347527</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90043</t>
+          <t>89692</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1697,17 +1717,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>OMAR SALVADOR</t>
+          <t>HECTOR DANIEL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BECERRA</t>
+          <t>VASCONCELOS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BARBA</t>
+          <t>ARAGON</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1717,12 +1737,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6866066983</t>
+          <t>6863386463</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>LA PALMITA 1965</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1732,17 +1752,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>09-03-2005</t>
+          <t>02-05-2004</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>BARBAOMAR68@GMAIL.COM</t>
+          <t>ARAGOND158@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 19:43:58</t>
+          <t>02-03-2026 12:07:31</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1767,7 +1787,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 19:50:24</t>
+          <t>02-03-2026 12:18:44</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1777,7 +1797,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>02-03-2026 19:49:48</t>
+          <t>02-03-2026 12:13:55</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1797,7 +1817,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26170522818050003264</t>
+          <t>26170522790830003198</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1809,24 +1829,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347903</t>
+          <t>347933</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90068</t>
+          <t>90098</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1836,17 +1856,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">EREYLI KIAVETH </t>
+          <t xml:space="preserve">LEONEL FAUSTINO </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MILLAN </t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1856,47 +1876,43 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6863621801</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>HAVIENDA LA ESTANCIA 9</t>
-        </is>
-      </c>
+          <t>6864205790</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15-08-1995</t>
+          <t>26-03-2012</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>EREYLI.KIAVENTH@GMAIL.COM</t>
+          <t>LEONELMARTINEZ@COLEGIOVASCONCELOS.NET</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 20:32:15</t>
+          <t>03-03-2026 05:24:46</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1906,29 +1922,21 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 20:37:43</t>
+          <t>03-03-2026 05:26:34</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>02-03-2026 20:36:54</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1936,7 +1944,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26170522819910003279</t>
+          <t>26170522823240003292</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1960,12 +1968,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347974</t>
+          <t>347903</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90139</t>
+          <t>90068</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1975,17 +1983,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ARIANA DENISSE</t>
+          <t xml:space="preserve">EREYLI KIAVETH </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLEGAS </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t xml:space="preserve">MILLAN </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1995,12 +2003,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6863922841</t>
+          <t>6863621801</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CASA  GRANDE 1908</t>
+          <t>HAVIENDA LA ESTANCIA 9</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2010,17 +2018,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>02-01-1997</t>
+          <t>15-08-1995</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>A.PONCE@OULOCK.COM</t>
+          <t>EREYLI.KIAVENTH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>03-03-2026 08:47:41</t>
+          <t>02-03-2026 20:32:15</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2045,17 +2053,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>03-03-2026 08:54:52</t>
+          <t>02-03-2026 20:37:43</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>03-03-2026 08:53:26</t>
+          <t>02-03-2026 20:36:54</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2075,7 +2083,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26170522834130003305</t>
+          <t>26170522819910003279</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2087,24 +2095,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347552</t>
+          <t>347974</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89717</t>
+          <t>90139</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2114,17 +2122,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICTOR </t>
+          <t>ARIANA DENISSE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORTIZ </t>
+          <t xml:space="preserve">VILLEGAS </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2134,32 +2142,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6862684016</t>
+          <t>6863922841</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>CASA  GRANDE 1908</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22-09-1999</t>
+          <t>02-01-1997</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>VICTOR-OP15@HOTMAIL.COM</t>
+          <t>A.PONCE@OULOCK.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 13:01:26</t>
+          <t>03-03-2026 08:47:41</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2184,17 +2192,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>04-03-2026 12:34:41</t>
+          <t>03-03-2026 08:54:52</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>04-03-2026 12:33:08</t>
+          <t>03-03-2026 08:53:26</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2214,7 +2222,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26170522880700003393</t>
+          <t>26170522834130003305</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2226,24 +2234,24 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>348456</t>
+          <t>347878</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90621</t>
+          <t>90043</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2253,17 +2261,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>JAVIER BERNARDO</t>
+          <t>OMAR SALVADOR</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>BECERRA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>BARBA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2273,12 +2281,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6861358156</t>
+          <t>6866066983</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TORRE LAS ARCAS 2061</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2288,17 +2296,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>09-12-1992</t>
+          <t>09-03-2005</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>FRANXYS_BARAJAS018@HOTMAIL.COM</t>
+          <t>BARBAOMAR68@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>04-03-2026 15:10:42</t>
+          <t>02-03-2026 19:43:58</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2323,17 +2331,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>04-03-2026 15:17:23</t>
+          <t>02-03-2026 19:50:24</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>04-03-2026 15:16:44</t>
+          <t>02-03-2026 19:49:48</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2343,7 +2351,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2353,7 +2361,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26170522884760003398</t>
+          <t>26170522818050003264</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2365,7 +2373,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Raymundo Cardenas Real</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2377,12 +2385,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348264</t>
+          <t>347552</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90429</t>
+          <t>89717</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2392,17 +2400,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">GISSELA GUADALUPE </t>
+          <t xml:space="preserve">VICTOR </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CASTRO</t>
+          <t xml:space="preserve">ORTIZ </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAYAN </t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2412,67 +2420,79 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6862343891</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>6862684016</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>06-12-1996</t>
+          <t>22-09-1999</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CASTROGISSELA2@GMAIL.COM</t>
+          <t>VICTOR-OP15@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 19:24:27</t>
+          <t>02-03-2026 13:01:26</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 19:26:23</t>
+          <t>04-03-2026 12:34:41</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>04-03-2026 12:33:08</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2480,36 +2500,36 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26170522858740003362</t>
+          <t>26170522880700003393</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348254</t>
+          <t>348140</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90419</t>
+          <t>90305</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2519,17 +2539,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">JULIO CESAR </t>
+          <t>BRENDA JUDITH</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVA </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DEL CID</t>
+          <t>CANTERO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2539,12 +2559,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6861501383</t>
+          <t>4423654832</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MILANO 1122</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2554,42 +2574,42 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>22-11-1977</t>
+          <t>30-06-1994</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>JULIODELCID@GMAIL.COM</t>
+          <t>JUDITHDZCANT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 19:07:08</t>
+          <t>03-03-2026 16:56:54</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 19:12:13</t>
+          <t>03-03-2026 17:01:30</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2599,7 +2619,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>03-03-2026 19:11:36</t>
+          <t>03-03-2026 17:00:48</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2619,36 +2639,36 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26170522857870003357</t>
+          <t>26170522848940003330</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348800</t>
+          <t>348254</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90965</t>
+          <t>90419</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2658,17 +2678,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NANCY FERNANDA</t>
+          <t xml:space="preserve">JULIO CESAR </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t xml:space="preserve">SILVA </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>DEL CID</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2678,12 +2698,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6861440730</t>
+          <t>6861501383</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>BOSQUE ZORZAL 775</t>
+          <t>MILANO 1122</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2693,17 +2713,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>08-08-1991</t>
+          <t>22-11-1977</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>FERNANDA9189@OUTLOOK.COM</t>
+          <t>JULIODELCID@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>05-03-2026 19:20:03</t>
+          <t>03-03-2026 19:07:08</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2728,17 +2748,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>05-03-2026 19:26:02</t>
+          <t>03-03-2026 19:12:13</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>05-03-2026 19:25:30</t>
+          <t>03-03-2026 19:11:36</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2758,7 +2778,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26170522929400003484</t>
+          <t>26170522857870003357</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2770,24 +2790,24 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347859</t>
+          <t>347910</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90024</t>
+          <t>90075</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2797,17 +2817,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ERIKA LILIANA</t>
+          <t>PAULETT NICOLE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t>AVENDAÑO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>CARRERA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2817,14 +2837,10 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6861090195</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>DAMIANAS 988</t>
-        </is>
-      </c>
+          <t>6861005692</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2832,32 +2848,32 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>20-12-1983</t>
+          <t>08-02-2011</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ERIKA.MUOZ.H@GMAIL.COM</t>
+          <t>PAVENDANO@EDUBC.COM.MX</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 19:00:26</t>
+          <t>02-03-2026 21:00:40</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2867,29 +2883,21 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>03-03-2026 20:07:42</t>
+          <t>02-03-2026 21:01:59</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>03-03-2026 20:07:01</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2897,19 +2905,11 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26170522860450003370</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522820430003283</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
           <t>549</t>
@@ -2917,24 +2917,24 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>348847</t>
+          <t>348264</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>91012</t>
+          <t>90429</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCAR </t>
+          <t xml:space="preserve">GISSELA GUADALUPE </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SERNA</t>
+          <t>CASTRO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MAPULA</t>
+          <t xml:space="preserve">PAYAN </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2964,28 +2964,28 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6866069985</t>
+          <t>6862343891</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31-10-1991</t>
+          <t>06-12-1996</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>OSCAR.SERNA18@GMAIL.COM</t>
+          <t>CASTROGISSELA2@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>06-03-2026 08:03:53</t>
+          <t>03-03-2026 19:24:27</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3010,18 +3010,18 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>06-03-2026 08:05:18</t>
+          <t>03-03-2026 19:26:23</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26170522944050003508</t>
+          <t>26170522858740003362</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3044,12 +3044,4503 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
+          <t>Alexa Johana  Haro</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>347859</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>90024</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ERIKA LILIANA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MUÑOZ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>HERRERA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6861090195</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>DAMIANAS 988</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>20-12-1983</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>ERIKA.MUOZ.H@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:00:26</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:07:42</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:07:01</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>26170522860450003370</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>348847</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>91012</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSCAR </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SERNA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MAPULA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6866069985</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>31-10-1991</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>OSCAR.SERNA18@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>06-03-2026 08:03:53</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>06-03-2026 08:05:18</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>26170522944050003508</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>349196</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>91361</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PABLO ADRIAN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>HERALDEZ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>QUINTERO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6861550495</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>C FORMALIDAD 1159</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>28-12-1992</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PABLO-ADRIAN25@OULOOK.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>08-03-2026 10:30:34</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>09-03-2026 09:24:05</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>09-03-2026 09:22:59</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26170523001910003595</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>349195</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>91360</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANA KAREN </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GARCIA </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NUÑEZ</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6863547771</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>C HACIENDA ZAUDIN 1997</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>19-08-1999</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>ANA1.KAREN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>08-03-2026 10:28:43</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>09-03-2026 09:31:58</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>09-03-2026 09:31:24</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26170523002050003596</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>349029</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>91194</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ROCIO ISABEL</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEPULVEDA </t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6861887054</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PORTLA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>12-07-1990</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>SEPULVEDA_D910@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>06-03-2026 18:57:17</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>09-03-2026 17:00:54</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>09-03-2026 16:59:33</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26170523015820003620</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>348456</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>90621</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>JAVIER BERNARDO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ANDRADE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6861358156</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TORRE LAS ARCAS 2061</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>09-12-1992</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>FRANXYS_BARAJAS018@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:10:42</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:17:23</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>04-03-2026 15:16:44</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26170522884760003398</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>348800</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>90965</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NANCY FERNANDA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MEZA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6861440730</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>BOSQUE ZORZAL 775</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>08-08-1991</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>FERNANDA9189@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:20:03</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:26:02</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>05-03-2026 19:25:30</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26170522929400003484</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Alexa Johana  Haro</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>349692</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>91857</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>JONATHAN  MAURICIO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>CARRERA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6863487217</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>21-10-2003</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>JONRODRI2110@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:49:28</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:54:41</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:53:41</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26170523029500003649</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>349761</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>91926</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>JUANA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>GATICA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>BAUTISTA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6862453198</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>10-03-1983</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>GATICAJUANA308@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>10-03-2026 08:07:14</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>14-03-2026 08:44:32</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>13-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>14-03-2026 08:43:57</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26170523178290003905</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>349902</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>92067</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>RAFAEL</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>VELASCO</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>MOLINA</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6865241165</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>21-10-2009</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>RAFAELVM2110@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>10-03-2026 17:28:40</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>anualidad LE 300</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>ANUALIDAD + MES REGALO $5,999</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>461.46</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>10-03-2026 17:47:46</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>09-04-2027 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26170523061190003705</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>5999</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>349961</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>92126</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NAOMI </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ESPINAL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>HINOJOSA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6862353187</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>AV DE LAS TORONJAS 456</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>27-03-2006</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>HINOJOSANAOMI79@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:43:29</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:50:23</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>10-03-2026 18:48:32</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26170523065660003716</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>349980</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>92145</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUIS </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PERALTA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6867425304</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>23-02-2006</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>LUIS.FER@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:11:58</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:13:13</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26170523067280003721</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>350353</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>92517</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>GERARDO YAEL</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>MOLINO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6863318956</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>05-08-2006</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>GERAYAMOFLO05@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>12-03-2026 14:59:21</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>12-03-2026 15:01:01</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>11-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26170523124250003820</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>351335</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>93499</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TANIA PATRICIA </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LOYA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6863834080</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL DEL REY 47</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>13-11-1990</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>TLOYAMTZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:17:43</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:25:46</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:25:12</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26170523233010003973</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>349699</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>91864</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>RUBEN FIDEL</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>GALVAN</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6862410652</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>05-12-2005</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>RUBEN3NGALVAN@ICLOUD.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>09-03-2026 19:59:01</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:05:04</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:04:18</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26170523030160003654</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>350634</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>92798</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>JOSE ENRIQUE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESCOBAR </t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6862137528</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>15-11-2011</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>JOSE.ENRIQUE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>13-03-2026 17:27:31</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>13-03-2026 17:29:29</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26170523158710003881</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>350483</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>92647</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIANEY </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SARMIENTO </t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6863354738</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ISLAS MINDANAO 849</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>21-07-2001</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>VSARMIENTOHERNANDEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>12-03-2026 20:14:08</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>13-03-2026 17:18:08</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>13-03-2026 17:17:26</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26170523158300003880</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>349978</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>92143</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DEREMI ARMANDO</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PERALTA </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6678706306</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>08-05-2010</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>VA.PERALTA.RAMIREZ@CBATIS140.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:09:33</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>10-03-2026 19:12:05</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26170523067130003720</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>351358</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>93522</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AMY ELIZABETH </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>CARRERA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6863070739</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>FUENTE DE HORACIO 2650</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>30-08-2008</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>AMY.ELI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:55:36</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>16-03-2026 20:00:23</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:59:35</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26170523234310003980</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>351369</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>93533</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDA </t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OLIVARES </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>LEON</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6863456907</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>CASANOVA 1345</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>31-07-1995</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>FERNANDA.LEON@GAMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>16-03-2026 20:16:37</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>16-03-2026 20:21:12</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>16-03-2026 20:20:46</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26170523234920003985</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>350717</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>92881</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>JULIO JARED</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASTILLO </t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>QUINTANA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6865891061</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>03-07-2001</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>JULIOCASTILLOQ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>14-03-2026 06:54:32</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>17-03-2026 07:52:31</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26170523245690004008</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>352002</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>94166</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELIZABETH </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>BETANCOURT</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6863405423</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>GUARACHA 2233</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>02-06-1998</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>ELII.BETA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:21:27</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:26:33</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:25:55</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26170523309720004111</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Alexa Johana  Haro</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>352226</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>94390</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LANDA</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>VASQUEZ</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6862415445</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>13-08-1992</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>ALEJANDRO.LANDAV@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:24:37</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:29:59</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:29:03</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26170523344240004172</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>351315</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>93479</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERICKA </t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>AGUILAR</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6861118944</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>CHIGNA HUAPAN 608</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>20-12-1994</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>ERICKA123@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>16-03-2026 18:51:25</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>16-03-2026 18:57:24</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>16-03-2026 18:56:54</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26170523231780003971</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>351745</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>93909</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAYMUNDO </t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMIREZ </t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ZAMORA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6864690491</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>BENEVENTO1215</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>20-10-1999</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>ARQ.RAYMUNDO.RAMIREZ20@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>18-03-2026 06:19:02</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>18-03-2026 06:26:31</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>18-03-2026 06:25:44</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26170523283380004070</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>351420</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>93584</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HECTOR  YAEL </t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>TURRUBIARTES</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6863465753</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>03-11-2008</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>YR200166@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>17-03-2026 08:10:52</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>17-03-2026 08:12:41</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>16-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26170523246280004009</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>351136</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>93300</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUAN </t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>HARO</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>CHAVEZ</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6861808524</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>23-10-1991</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>JUANC.HAROC@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>16-03-2026 12:10:33</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>16-03-2026 12:19:43</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26170523218710003945</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>351726</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>93890</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MAYRA LOURDES</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARRERA </t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6867480211</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>11-02-1993</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>MAYRA_PAULETT13@OULOOK.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>17-03-2026 21:07:50</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>17-03-2026 21:09:26</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26170523275240004061</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>351870</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>94034</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ELDA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>FLORES</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>NUÑEZ</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6862591116</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>PORTSLR</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>31-08-1958</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>GREEEKFACE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>18-03-2026 16:21:23</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>PLAN RECURRENTE PAGO INCIAL $1,449 LE</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>19-03-2026 19:02:02</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>19-03-2026 19:00:28</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26170523339900004153</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>351341</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>93505</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LUIS FRANCISCO</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>VILLA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>GUZMAN</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6861873597</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV SOLLER 47 </t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>11-02-1991</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>UVG.LUISFRANCISCO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:27:38</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:31:07</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:30:15</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26170523233270003974</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Alexa Johana  Haro</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>352233</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>94397</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>STEFANY YERALDI</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REYES </t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>VILLAREAL</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>6383809898</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>06-12-1993</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>FANYBLUE93@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:33:35</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:37:28</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:36:21</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26170523344570004175</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>351859</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>94023</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>RAFAEL</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ENCISO</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6861989778</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>25-10-1989</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>RELZX89PER@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>18-03-2026 15:58:55</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>19-03-2026 15:51:19</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26170523331510004134</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>352149</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>94313</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>RAQUEL YUREM</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>CASTELLANOS</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>CAMPOS</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>6863894647</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>28-06-1992</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>CASTELLANOSR@UABC.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>19-03-2026 17:22:50</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>19-03-2026 17:24:06</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>18-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26170523334750004144</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>con rutina</t>
         </is>
       </c>
     </row>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__VILLAS DEL REY.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>308413</t>
+          <t>137315</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>34957</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAID ISMAEL</t>
+          <t>EDUARDO ANDREY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ROMAN </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,10 +613,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6862454233</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>6862833229</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>HUASTECA 93</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -624,32 +628,32 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>12-03-2010</t>
+          <t>02-03-1987</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>RSAIDISMAEL@GMAIL.COM</t>
+          <t>ANDREYG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>08-08-2025 13:06:57</t>
+          <t>05-12-2022 12:34:57</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -659,21 +663,29 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>09-03-2026 20:15:54</t>
+          <t>25-03-2026 09:35:01</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>25-03-2026 09:32:53</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -681,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26170523030910003658</t>
+          <t>26160523497170004074</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -691,7 +703,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
+          <t>ANDREA PATRICIA ACUÑA PERALTA</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -701,7 +713,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Ricardo Alexis Alvarez Camarena</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -713,12 +725,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>309174</t>
+          <t>212091</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -728,17 +740,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CAMILA ANAHI</t>
+          <t>YAMILETH MARISOL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>ARREDONDO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LANDEROS</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -748,12 +760,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6862447701</t>
+          <t>5627748663</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>ORGULLO 2242</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -763,17 +775,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>10-04-2010</t>
+          <t>05-04-2005</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CAMILAANAHI1010@GMAIL.COM</t>
+          <t>YAMILETHMARISELA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12-08-2025 19:31:30</t>
+          <t>30-12-2023 13:26:00</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -798,17 +810,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 17:23:07</t>
+          <t>16-03-2026 19:53:36</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>03-03-2026 17:22:43</t>
+          <t>16-03-2026 19:52:04</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -818,7 +830,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -828,19 +840,11 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26170522850510003334</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>YATZENI ALEXANDRA MORENO QUINTERO</t>
-        </is>
-      </c>
+          <t>26170523234130003979</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
           <t>549</t>
@@ -848,24 +852,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>127830</t>
+          <t>216593</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25503</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -875,17 +879,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BRYAN ALAN</t>
+          <t xml:space="preserve">EDUARDO </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUNA </t>
+          <t>ESCALANTE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ZARATE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,12 +899,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6866024630</t>
+          <t>6861966619</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TAMAULIPAS 440</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -910,32 +914,32 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>23-12-1996</t>
+          <t>25-06-1995</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>BRYANLUNAGLEZ@GMAIL.COM</t>
+          <t>EDESCALANTEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>05-10-2022 17:20:12</t>
+          <t>23-01-2024 20:34:30</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -945,21 +949,29 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>09-03-2026 14:49:12</t>
+          <t>23-03-2026 22:01:29</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
+          <t>22-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>23-03-2026 22:00:58</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -967,7 +979,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26010523009900006038</t>
+          <t>26170523450840004348</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -979,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Raymundo Cardenas Real</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -991,12 +1003,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>212091</t>
+          <t>127830</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>25503</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1006,17 +1018,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>YAMILETH MARISOL</t>
+          <t>BRYAN ALAN</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ARREDONDO</t>
+          <t xml:space="preserve">LUNA </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1026,47 +1038,47 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5627748663</t>
+          <t>6866024630</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ORGULLO 2242</t>
+          <t>TAMAULIPAS 440</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>05-04-2005</t>
+          <t>23-12-1996</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>YAMILETHMARISELA@GMAIL.COM</t>
+          <t>BRYANLUNAGLEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>30-12-2023 13:26:00</t>
+          <t>05-10-2022 17:20:12</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1076,29 +1088,21 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>16-03-2026 19:53:36</t>
+          <t>09-03-2026 14:49:12</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>16-03-2026 19:52:04</t>
-        </is>
-      </c>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1106,7 +1110,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26170523234130003979</t>
+          <t>26010523009900006038</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1118,24 +1122,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>333353</t>
+          <t>216590</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1145,17 +1149,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIEGO ALEJANDRO </t>
+          <t>JOSELYN KARINA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>ZAMORA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AVILES</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1165,32 +1169,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6866194136</t>
+          <t>6864053266</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HACIENDA SAN BERNARDO 60</t>
+          <t>PORTSLES</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>02-02-2010</t>
+          <t>20-12-1994</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>DIEGO.ALEJANDROO@GMAIL.COM</t>
+          <t>KZANIHZ94@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>09-01-2026 16:23:37</t>
+          <t>23-01-2024 20:32:18</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1215,17 +1219,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>16-03-2026 18:09:21</t>
+          <t>23-03-2026 22:03:53</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
+          <t>22-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>16-03-2026 18:08:51</t>
+          <t>23-03-2026 22:03:35</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1245,19 +1249,11 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26170523230230003968</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170523450870004349</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
           <t>549</t>
@@ -1265,24 +1261,24 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Raymundo Cardenas Real</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>309170</t>
+          <t>308413</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1292,17 +1288,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LUZ HEREYDA</t>
+          <t>SAID ISMAEL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LANDEROS</t>
+          <t xml:space="preserve">ROMAN </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BARRERA</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1312,47 +1308,43 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6864056242</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>PORTALES</t>
-        </is>
-      </c>
+          <t>6862454233</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>14-10-1976</t>
+          <t>12-03-2010</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>LUZ_HLANDEROS@HOTMAIL.COM</t>
+          <t>RSAIDISMAEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12-08-2025 19:24:04</t>
+          <t>08-08-2025 13:06:57</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1362,29 +1354,21 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 17:18:00</t>
+          <t>09-03-2026 20:15:54</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:16:23</t>
-        </is>
-      </c>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1392,7 +1376,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26170522850020003332</t>
+          <t>26170523030910003658</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1412,7 +1396,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Raymundo Cardenas Real</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1424,12 +1408,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347710</t>
+          <t>107015</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89875</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1439,17 +1423,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KEVIN URIEL</t>
+          <t xml:space="preserve">ANGEL ALFONSO </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ALCALA</t>
+          <t>BRAVO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>AGUIRRE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1459,12 +1443,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6865258242</t>
+          <t>6861947303</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>ZIMONTES DE TOLEDO 2000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1474,64 +1458,56 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>25-04-2004</t>
+          <t>06-01-2008</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>KEVINALCALA224@GMAIL.COM</t>
+          <t>BEA637018@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 16:52:40</t>
+          <t>11-07-2022 08:24:38</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 16:59:11</t>
+          <t>30-03-2026 14:41:27</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:58:32</t>
-        </is>
-      </c>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1539,36 +1515,36 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26170522804230003223</t>
+          <t>26170523630560004668</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347517</t>
+          <t>309174</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89682</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1578,17 +1554,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DIEGO ADRIAN</t>
+          <t>CAMILA ANAHI</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>LANDEROS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1598,32 +1574,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6863085535</t>
+          <t>6862447701</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>VALOR 1199</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>04-09-2002</t>
+          <t>10-04-2010</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>DIEGOG5531@GMAIL.COM</t>
+          <t>CAMILAANAHI1010@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 11:51:43</t>
+          <t>12-08-2025 19:31:30</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1648,17 +1624,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 12:00:33</t>
+          <t>03-03-2026 17:23:07</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 11:58:53</t>
+          <t>03-03-2026 17:22:43</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1668,7 +1644,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1678,11 +1654,19 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26170522790100003195</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>26170522850510003334</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>YATZENI ALEXANDRA MORENO QUINTERO</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>549</t>
@@ -1690,7 +1674,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Raymundo Cardenas Real</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1702,12 +1686,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347527</t>
+          <t>333353</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89692</t>
+          <t>17220</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1717,17 +1701,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HECTOR DANIEL</t>
+          <t xml:space="preserve">DIEGO ALEJANDRO </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VASCONCELOS</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ARAGON</t>
+          <t>AVILES</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1737,12 +1721,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6863386463</t>
+          <t>6866194136</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LA PALMITA 1965</t>
+          <t>HACIENDA SAN BERNARDO 60</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1752,17 +1736,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>02-05-2004</t>
+          <t>02-02-2010</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ARAGOND158@GMAIL.COM</t>
+          <t>DIEGO.ALEJANDROO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 12:07:31</t>
+          <t>09-01-2026 16:23:37</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1787,17 +1771,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 12:18:44</t>
+          <t>16-03-2026 18:09:21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>02-03-2026 12:13:55</t>
+          <t>16-03-2026 18:08:51</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1817,11 +1801,19 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26170522790830003198</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>26170523230230003968</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>549</t>
@@ -1829,24 +1821,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347933</t>
+          <t>309170</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90098</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1856,17 +1848,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LEONEL FAUSTINO </t>
+          <t>LUZ HEREYDA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>LANDEROS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>BARRERA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1876,43 +1868,47 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6864205790</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6864056242</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>26-03-2012</t>
+          <t>14-10-1976</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>LEONELMARTINEZ@COLEGIOVASCONCELOS.NET</t>
+          <t>LUZ_HLANDEROS@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 05:24:46</t>
+          <t>12-08-2025 19:24:04</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1922,7 +1918,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 05:26:34</t>
+          <t>03-03-2026 17:18:00</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1930,13 +1926,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:16:23</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1944,11 +1948,19 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26170522823240003292</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>26170522850020003332</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISAIRIS  FLORES  VERDUGO </t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>549</t>
@@ -1956,7 +1968,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Raymundo Cardenas Real</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1968,12 +1980,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347903</t>
+          <t>347517</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>90068</t>
+          <t>89682</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1983,17 +1995,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">EREYLI KIAVETH </t>
+          <t>DIEGO ADRIAN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MILLAN </t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2003,32 +2015,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6863621801</t>
+          <t>6863085535</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>HAVIENDA LA ESTANCIA 9</t>
+          <t>VALOR 1199</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>15-08-1995</t>
+          <t>04-09-2002</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>EREYLI.KIAVENTH@GMAIL.COM</t>
+          <t>DIEGOG5531@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 20:32:15</t>
+          <t>02-03-2026 11:51:43</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2053,7 +2065,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 20:37:43</t>
+          <t>02-03-2026 12:00:33</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2063,7 +2075,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>02-03-2026 20:36:54</t>
+          <t>02-03-2026 11:58:53</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2083,7 +2095,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26170522819910003279</t>
+          <t>26170522790100003195</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2095,7 +2107,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Raymundo Cardenas Real</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2107,12 +2119,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347974</t>
+          <t>347527</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>90139</t>
+          <t>89692</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2122,17 +2134,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ARIANA DENISSE</t>
+          <t>HECTOR DANIEL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLEGAS </t>
+          <t>VASCONCELOS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PONCE</t>
+          <t>ARAGON</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2142,32 +2154,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6863922841</t>
+          <t>6863386463</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CASA  GRANDE 1908</t>
+          <t>LA PALMITA 1965</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>02-01-1997</t>
+          <t>02-05-2004</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>A.PONCE@OULOCK.COM</t>
+          <t>ARAGOND158@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>03-03-2026 08:47:41</t>
+          <t>02-03-2026 12:07:31</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2192,17 +2204,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>03-03-2026 08:54:52</t>
+          <t>02-03-2026 12:18:44</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>03-03-2026 08:53:26</t>
+          <t>02-03-2026 12:13:55</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2222,7 +2234,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26170522834130003305</t>
+          <t>26170522790830003198</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2524,12 +2536,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>348140</t>
+          <t>347859</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90305</t>
+          <t>90024</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2539,17 +2551,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BRENDA JUDITH</t>
+          <t>ERIKA LILIANA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CANTERO</t>
+          <t>HERRERA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2559,12 +2571,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4423654832</t>
+          <t>6861090195</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>DAMIANAS 988</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2574,42 +2586,42 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30-06-1994</t>
+          <t>20-12-1983</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>JUDITHDZCANT@GMAIL.COM</t>
+          <t>ERIKA.MUOZ.H@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 16:56:54</t>
+          <t>02-03-2026 19:00:26</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 17:01:30</t>
+          <t>03-03-2026 20:07:42</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2619,7 +2631,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>03-03-2026 17:00:48</t>
+          <t>03-03-2026 20:07:01</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2639,14 +2651,22 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26170522848940003330</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>26170522860450003370</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2663,12 +2683,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348254</t>
+          <t>347933</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90419</t>
+          <t>90098</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2678,17 +2698,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">JULIO CESAR </t>
+          <t xml:space="preserve">LEONEL FAUSTINO </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SILVA </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DEL CID</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2698,47 +2718,43 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6861501383</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>MILANO 1122</t>
-        </is>
-      </c>
+          <t>6864205790</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22-11-1977</t>
+          <t>26-03-2012</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>JULIODELCID@GMAIL.COM</t>
+          <t>LEONELMARTINEZ@COLEGIOVASCONCELOS.NET</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-03-2026 19:07:08</t>
+          <t>03-03-2026 05:24:46</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2748,7 +2764,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-03-2026 19:12:13</t>
+          <t>03-03-2026 05:26:34</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2756,21 +2772,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>03-03-2026 19:11:36</t>
-        </is>
-      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2778,7 +2786,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26170522857870003357</t>
+          <t>26170522823240003292</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2802,12 +2810,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347910</t>
+          <t>348140</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90075</t>
+          <t>90305</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2817,17 +2825,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PAULETT NICOLE</t>
+          <t>BRENDA JUDITH</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AVENDAÑO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CARRERA</t>
+          <t>CANTERO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2837,10 +2845,14 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6861005692</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>4423654832</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2848,56 +2860,64 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>08-02-2011</t>
+          <t>30-06-1994</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PAVENDANO@EDUBC.COM.MX</t>
+          <t>JUDITHDZCANT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 21:00:40</t>
+          <t>03-03-2026 16:56:54</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 21:01:59</t>
+          <t>03-03-2026 17:01:30</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:00:48</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2905,19 +2925,19 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26170522820430003283</t>
+          <t>26170522848940003330</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -3056,12 +3076,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347859</t>
+          <t>348254</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90024</t>
+          <t>90419</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3071,17 +3091,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ERIKA LILIANA</t>
+          <t xml:space="preserve">JULIO CESAR </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MUÑOZ</t>
+          <t xml:space="preserve">SILVA </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HERRERA</t>
+          <t>DEL CID</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3091,12 +3111,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6861090195</t>
+          <t>6861501383</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DAMIANAS 988</t>
+          <t>MILANO 1122</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3106,17 +3126,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>20-12-1983</t>
+          <t>22-11-1977</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ERIKA.MUOZ.H@GMAIL.COM</t>
+          <t>JULIODELCID@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 19:00:26</t>
+          <t>03-03-2026 19:07:08</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3141,7 +3161,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03-03-2026 20:07:42</t>
+          <t>03-03-2026 19:12:13</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3151,7 +3171,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>03-03-2026 20:07:01</t>
+          <t>03-03-2026 19:11:36</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3171,19 +3191,11 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26170522860450003370</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170522857870003357</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
           <t>549</t>
@@ -3330,12 +3342,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>349196</t>
+          <t>347910</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>91361</t>
+          <t>90075</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3345,17 +3357,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PABLO ADRIAN</t>
+          <t>PAULETT NICOLE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HERALDEZ</t>
+          <t>AVENDAÑO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>QUINTERO</t>
+          <t>CARRERA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3365,75 +3377,67 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6861550495</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>C FORMALIDAD 1159</t>
-        </is>
-      </c>
+          <t>6861005692</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>28-12-1992</t>
+          <t>08-02-2011</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>PABLO-ADRIAN25@OULOOK.COM</t>
+          <t>PAVENDANO@EDUBC.COM.MX</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>08-03-2026 10:30:34</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>02-03-2026 21:00:40</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>09-03-2026 09:24:05</t>
+          <t>02-03-2026 21:01:59</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>09-03-2026 09:22:59</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3441,27 +3445,19 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26170523001910003595</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>26170522820430003283</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Raymundo Cardenas Real</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3473,12 +3469,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>349195</t>
+          <t>349029</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>91360</t>
+          <t>91194</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3488,17 +3484,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANA KAREN </t>
+          <t>ROCIO ISABEL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">GARCIA </t>
+          <t xml:space="preserve">SEPULVEDA </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NUÑEZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3508,12 +3504,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6863547771</t>
+          <t>6861887054</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C HACIENDA ZAUDIN 1997</t>
+          <t>PORTLA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3523,20 +3519,24 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>19-08-1999</t>
+          <t>12-07-1990</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ANA1.KAREN@GMAIL.COM</t>
+          <t>SEPULVEDA_D910@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>08-03-2026 10:28:43</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>06-03-2026 18:57:17</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3544,17 +3544,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>PLAN FAMILIA / AMIGOS X $499</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>09-03-2026 09:31:58</t>
+          <t>09-03-2026 17:00:54</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>09-03-2026 09:31:24</t>
+          <t>09-03-2026 16:59:33</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3584,22 +3584,18 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26170523002050003596</t>
+          <t>26170523015820003620</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>ARLET ORIANA MARTINEZ ARAGON</t>
-        </is>
-      </c>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3616,12 +3612,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>349029</t>
+          <t>349195</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>91194</t>
+          <t>91360</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3631,17 +3627,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ROCIO ISABEL</t>
+          <t xml:space="preserve">ANA KAREN </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEPULVEDA </t>
+          <t xml:space="preserve">GARCIA </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>NUÑEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3651,12 +3647,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6861887054</t>
+          <t>6863547771</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PORTLA</t>
+          <t>C HACIENDA ZAUDIN 1997</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3666,24 +3662,20 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>12-07-1990</t>
+          <t>19-08-1999</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>SEPULVEDA_D910@HOTMAIL.COM</t>
+          <t>ANA1.KAREN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>06-03-2026 18:57:17</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>08-03-2026 10:28:43</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3691,17 +3683,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>09-03-2026 17:00:54</t>
+          <t>09-03-2026 09:31:58</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3711,7 +3703,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>09-03-2026 16:59:33</t>
+          <t>09-03-2026 09:31:24</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3721,7 +3713,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3731,18 +3723,22 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26170523015820003620</t>
+          <t>26170523002050003596</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr"/>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3759,12 +3755,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>348456</t>
+          <t>349692</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90621</t>
+          <t>91857</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3774,17 +3770,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>JAVIER BERNARDO</t>
+          <t>JONATHAN  MAURICIO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>CARRERA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ANDRADE</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3794,12 +3790,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6861358156</t>
+          <t>6863487217</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TORRE LAS ARCAS 2061</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3809,17 +3805,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>09-12-1992</t>
+          <t>21-10-2003</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>FRANXYS_BARAJAS018@HOTMAIL.COM</t>
+          <t>JONRODRI2110@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>04-03-2026 15:10:42</t>
+          <t>09-03-2026 19:49:28</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3844,17 +3840,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>04-03-2026 15:17:23</t>
+          <t>09-03-2026 19:54:41</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>08-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>04-03-2026 15:16:44</t>
+          <t>09-03-2026 19:53:41</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3864,7 +3860,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3874,7 +3870,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26170522884760003398</t>
+          <t>26170523029500003649</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3898,12 +3894,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>348800</t>
+          <t>347710</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90965</t>
+          <t>89875</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3913,17 +3909,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NANCY FERNANDA</t>
+          <t>KEVIN URIEL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MEZA</t>
+          <t>ALCALA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3933,67 +3929,67 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6861440730</t>
+          <t>6865258242</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>BOSQUE ZORZAL 775</t>
+          <t>PORTALES</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>08-08-1991</t>
+          <t>25-04-2004</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>FERNANDA9189@OUTLOOK.COM</t>
+          <t>KEVINALCALA224@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>05-03-2026 19:20:03</t>
+          <t>02-03-2026 16:52:40</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>05-03-2026 19:26:02</t>
+          <t>02-03-2026 16:59:11</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>05-03-2026 19:25:30</t>
+          <t>02-03-2026 16:58:32</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4003,7 +3999,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -4013,14 +4009,14 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26170522929400003484</t>
+          <t>26170522804230003223</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -4037,12 +4033,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>349692</t>
+          <t>348456</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>91857</t>
+          <t>90621</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4052,17 +4048,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JONATHAN  MAURICIO</t>
+          <t>JAVIER BERNARDO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CARRERA</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ANDRADE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4072,12 +4068,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6863487217</t>
+          <t>6861358156</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>TORRE LAS ARCAS 2061</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4087,17 +4083,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>21-10-2003</t>
+          <t>09-12-1992</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>JONRODRI2110@GMAIL.COM</t>
+          <t>FRANXYS_BARAJAS018@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>09-03-2026 19:49:28</t>
+          <t>04-03-2026 15:10:42</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4122,17 +4118,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>09-03-2026 19:54:41</t>
+          <t>04-03-2026 15:17:23</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>09-03-2026 19:53:41</t>
+          <t>04-03-2026 15:16:44</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4142,7 +4138,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4152,7 +4148,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26170523029500003649</t>
+          <t>26170522884760003398</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -4176,12 +4172,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>349761</t>
+          <t>348800</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>91926</t>
+          <t>90965</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4191,17 +4187,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JUANA</t>
+          <t>NANCY FERNANDA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GATICA</t>
+          <t>MEZA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4211,12 +4207,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6862453198</t>
+          <t>6861440730</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>BOSQUE ZORZAL 775</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4226,17 +4222,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>10-03-1983</t>
+          <t>08-08-1991</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>GATICAJUANA308@GMAIL.COM</t>
+          <t>FERNANDA9189@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>10-03-2026 08:07:14</t>
+          <t>05-03-2026 19:20:03</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4261,17 +4257,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>14-03-2026 08:44:32</t>
+          <t>05-03-2026 19:26:02</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>13-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>14-03-2026 08:43:57</t>
+          <t>05-03-2026 19:25:30</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4281,7 +4277,7 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -4291,19 +4287,11 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26170523178290003905</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
-        </is>
-      </c>
+          <t>26170522929400003484</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
           <t>549</t>
@@ -4311,7 +4299,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Thannia Lilian Lugo Morales</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4716,12 +4704,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>350353</t>
+          <t>349196</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>92517</t>
+          <t>91361</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4731,17 +4719,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GERARDO YAEL</t>
+          <t>PABLO ADRIAN</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MOLINO</t>
+          <t>HERALDEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>QUINTERO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4751,10 +4739,14 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6863318956</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6861550495</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>C FORMALIDAD 1159</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -4762,56 +4754,60 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>05-08-2006</t>
+          <t>28-12-1992</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>GERAYAMOFLO05@ICLOUD.COM</t>
+          <t>PABLO-ADRIAN25@OULOOK.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>12-03-2026 14:59:21</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>08-03-2026 10:30:34</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>PLAN FAMILIA / AMIGOS X $499</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>499</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>12-03-2026 15:01:01</t>
+          <t>09-03-2026 09:24:05</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>11-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>09-03-2026 09:22:59</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4819,36 +4815,44 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26170523124250003820</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+          <t>26170523001910003595</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>ARLET ORIANA MARTINEZ ARAGON</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>499</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Raymundo Cardenas Real</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>351335</t>
+          <t>347903</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>93499</t>
+          <t>90068</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4858,17 +4862,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">TANIA PATRICIA </t>
+          <t xml:space="preserve">EREYLI KIAVETH </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LOYA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t xml:space="preserve">MILLAN </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4878,12 +4882,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6863834080</t>
+          <t>6863621801</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>RESIDENCIAL DEL REY 47</t>
+          <t>HAVIENDA LA ESTANCIA 9</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4893,17 +4897,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>13-11-1990</t>
+          <t>15-08-1995</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>TLOYAMTZ@GMAIL.COM</t>
+          <t>EREYLI.KIAVENTH@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>16-03-2026 19:17:43</t>
+          <t>02-03-2026 20:32:15</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4928,17 +4932,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>16-03-2026 19:25:46</t>
+          <t>02-03-2026 20:37:43</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>16-03-2026 19:25:12</t>
+          <t>02-03-2026 20:36:54</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4958,7 +4962,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26170523233010003973</t>
+          <t>26170522819910003279</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4970,7 +4974,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Raymundo Cardenas Real</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4982,12 +4986,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>349699</t>
+          <t>347974</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>91864</t>
+          <t>90139</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4997,17 +5001,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>RUBEN FIDEL</t>
+          <t>ARIANA DENISSE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GALVAN</t>
+          <t xml:space="preserve">VILLEGAS </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>PONCE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5017,32 +5021,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6862410652</t>
+          <t>6863922841</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>CASA  GRANDE 1908</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>05-12-2005</t>
+          <t>02-01-1997</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>RUBEN3NGALVAN@ICLOUD.COM</t>
+          <t>A.PONCE@OULOCK.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>09-03-2026 19:59:01</t>
+          <t>03-03-2026 08:47:41</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5067,17 +5071,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>09-03-2026 20:05:04</t>
+          <t>03-03-2026 08:54:52</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>08-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>09-03-2026 20:04:18</t>
+          <t>03-03-2026 08:53:26</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5097,7 +5101,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26170523030160003654</t>
+          <t>26170522834130003305</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -5109,7 +5113,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>Raymundo Cardenas Real</t>
+          <t>Thannia Lilian Lugo Morales</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -5121,12 +5125,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>350634</t>
+          <t>349699</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>92798</t>
+          <t>91864</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5136,17 +5140,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>JOSE ENRIQUE</t>
+          <t>RUBEN FIDEL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>GALVAN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">ESCOBAR </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5156,43 +5160,47 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6862137528</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>6862410652</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>15-11-2011</t>
+          <t>05-12-2005</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>JOSE.ENRIQUE@GMAIL.COM</t>
+          <t>RUBEN3NGALVAN@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>13-03-2026 17:27:31</t>
+          <t>09-03-2026 19:59:01</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -5202,21 +5210,29 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>13-03-2026 17:29:29</t>
+          <t>09-03-2026 20:05:04</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>12-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr"/>
+          <t>08-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>09-03-2026 20:04:18</t>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5224,7 +5240,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26170523158710003881</t>
+          <t>26170523030160003654</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5248,12 +5264,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>350483</t>
+          <t>350634</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>92647</t>
+          <t>92798</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5263,17 +5279,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIANEY </t>
+          <t>JOSE ENRIQUE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">SARMIENTO </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t xml:space="preserve">ESCOBAR </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5283,14 +5299,10 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6863354738</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>ISLAS MINDANAO 849</t>
-        </is>
-      </c>
+          <t>6862137528</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5298,32 +5310,32 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>21-07-2001</t>
+          <t>15-11-2011</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>VSARMIENTOHERNANDEZ@GMAIL.COM</t>
+          <t>JOSE.ENRIQUE@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>12-03-2026 20:14:08</t>
+          <t>13-03-2026 17:27:31</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -5333,7 +5345,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>13-03-2026 17:18:08</t>
+          <t>13-03-2026 17:29:29</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -5341,21 +5353,13 @@
           <t>12-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>13-03-2026 17:17:26</t>
-        </is>
-      </c>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5363,7 +5367,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26170523158300003880</t>
+          <t>26170523158710003881</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5387,12 +5391,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>349978</t>
+          <t>351335</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>92143</t>
+          <t>93499</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5402,17 +5406,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DEREMI ARMANDO</t>
+          <t xml:space="preserve">TANIA PATRICIA </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">PERALTA </t>
+          <t>LOYA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5422,43 +5426,47 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6678706306</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>6863834080</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL DEL REY 47</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>08-05-2010</t>
+          <t>13-11-1990</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>VA.PERALTA.RAMIREZ@CBATIS140.EDU.MX</t>
+          <t>TLOYAMTZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>10-03-2026 19:09:33</t>
+          <t>16-03-2026 19:17:43</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -5468,21 +5476,29 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>10-03-2026 19:12:05</t>
+          <t>16-03-2026 19:25:46</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>09-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:25:12</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5490,7 +5506,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26170523067130003720</t>
+          <t>26170523233010003973</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5792,12 +5808,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>350717</t>
+          <t>351420</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>92881</t>
+          <t>93584</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5807,17 +5823,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>JULIO JARED</t>
+          <t xml:space="preserve">HECTOR  YAEL </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASTILLO </t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>QUINTANA</t>
+          <t>TURRUBIARTES</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5827,7 +5843,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6865891061</t>
+          <t>6863465753</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5838,17 +5854,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>03-07-2001</t>
+          <t>03-11-2008</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>JULIOCASTILLOQ@GMAIL.COM</t>
+          <t>YR200166@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>14-03-2026 06:54:32</t>
+          <t>17-03-2026 08:10:52</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5863,28 +5879,28 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>17-03-2026 07:52:31</t>
+          <t>17-03-2026 08:12:41</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>16-04-2026 23:59:59</t>
+          <t>16-06-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -5895,14 +5911,14 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26170523245690004008</t>
+          <t>26170523246280004009</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5919,12 +5935,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>352002</t>
+          <t>350717</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>94166</t>
+          <t>92881</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5934,17 +5950,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELIZABETH </t>
+          <t>JULIO JARED</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>BETANCOURT</t>
+          <t xml:space="preserve">CASTILLO </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>QUINTANA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5954,79 +5970,67 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6863405423</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>GUARACHA 2233</t>
-        </is>
-      </c>
+          <t>6865891061</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>02-06-1998</t>
+          <t>03-07-2001</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ELII.BETA@GMAIL.COM</t>
+          <t>JULIOCASTILLOQ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>18-03-2026 20:21:27</t>
+          <t>14-03-2026 06:54:32</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>18-03-2026 20:26:33</t>
+          <t>17-03-2026 07:52:31</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>18-03-2026 20:25:55</t>
-        </is>
-      </c>
+          <t>16-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6034,36 +6038,36 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26170523309720004111</t>
+          <t>26170523245690004008</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>352226</t>
+          <t>351745</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>94390</t>
+          <t>93909</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6073,17 +6077,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t xml:space="preserve">RAYMUNDO </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>LANDA</t>
+          <t xml:space="preserve">RAMIREZ </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>VASQUEZ</t>
+          <t>ZAMORA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6093,12 +6097,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6862415445</t>
+          <t>6864690491</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PORTALES</t>
+          <t>BENEVENTO1215</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6108,17 +6112,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>13-08-1992</t>
+          <t>20-10-1999</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>ALEJANDRO.LANDAV@HOTMAIL.COM</t>
+          <t>ARQ.RAYMUNDO.RAMIREZ20@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>19-03-2026 20:24:37</t>
+          <t>18-03-2026 06:19:02</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6143,17 +6147,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>19-03-2026 20:29:59</t>
+          <t>18-03-2026 06:26:31</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
+          <t>17-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>19-03-2026 20:29:03</t>
+          <t>18-03-2026 06:25:44</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6173,7 +6177,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26170523344240004172</t>
+          <t>26170523283380004070</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6197,12 +6201,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>351315</t>
+          <t>350353</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>93479</t>
+          <t>92517</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6212,17 +6216,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERICKA </t>
+          <t>GERARDO YAEL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>MOLINO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AGUILAR</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6232,79 +6236,67 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6861118944</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>CHIGNA HUAPAN 608</t>
-        </is>
-      </c>
+          <t>6863318956</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>20-12-1994</t>
+          <t>05-08-2006</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>ERICKA123@GMAIL.COM</t>
+          <t>GERAYAMOFLO05@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>16-03-2026 18:51:25</t>
+          <t>12-03-2026 14:59:21</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>3 MESES $1,899</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>633</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>16-03-2026 18:57:24</t>
+          <t>12-03-2026 15:01:01</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>16-03-2026 18:56:54</t>
-        </is>
-      </c>
+          <t>11-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6312,36 +6304,36 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26170523231780003971</t>
+          <t>26170523124250003820</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Raymundo Cardenas Real</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>351745</t>
+          <t>351315</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>93909</t>
+          <t>93479</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6351,17 +6343,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAYMUNDO </t>
+          <t xml:space="preserve">ERICKA </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">RAMIREZ </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ZAMORA</t>
+          <t>AGUILAR</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6371,32 +6363,32 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6864690491</t>
+          <t>6861118944</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>BENEVENTO1215</t>
+          <t>CHIGNA HUAPAN 608</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>20-10-1999</t>
+          <t>20-12-1994</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ARQ.RAYMUNDO.RAMIREZ20@GMAIL.COM</t>
+          <t>ERICKA123@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>18-03-2026 06:19:02</t>
+          <t>16-03-2026 18:51:25</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6421,17 +6413,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>18-03-2026 06:26:31</t>
+          <t>16-03-2026 18:57:24</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>17-04-2026 23:59:59</t>
+          <t>15-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>18-03-2026 06:25:44</t>
+          <t>16-03-2026 18:56:54</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6451,7 +6443,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26170523283380004070</t>
+          <t>26170523231780003971</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
@@ -6463,24 +6455,24 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Raymundo Cardenas Real</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>351420</t>
+          <t>352002</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>93584</t>
+          <t>94166</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6490,17 +6482,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">HECTOR  YAEL </t>
+          <t xml:space="preserve">ELIZABETH </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>BETANCOURT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TURRUBIARTES</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -6510,67 +6502,79 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6863465753</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>6863405423</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>GUARACHA 2233</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>03-11-2008</t>
+          <t>02-06-1998</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>YR200166@GMAIL.COM</t>
+          <t>ELII.BETA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>17-03-2026 08:10:52</t>
+          <t>18-03-2026 20:21:27</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>17-03-2026 08:12:41</t>
+          <t>18-03-2026 20:26:33</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>16-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr"/>
+          <t>17-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>18-03-2026 20:25:55</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6578,36 +6582,36 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26170523246280004009</t>
+          <t>26170523309720004111</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>351136</t>
+          <t>352226</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>93300</t>
+          <t>94390</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6617,17 +6621,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN </t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HARO</t>
+          <t>LANDA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>VASQUEZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6637,10 +6641,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6861808524</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>6862415445</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -6648,32 +6656,32 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>23-10-1991</t>
+          <t>13-08-1992</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>JUANC.HAROC@GMAIL.COM</t>
+          <t>ALEJANDRO.LANDAV@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>16-03-2026 12:10:33</t>
+          <t>19-03-2026 20:24:37</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>convenio 300</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -6683,21 +6691,29 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>16-03-2026 12:19:43</t>
+          <t>19-03-2026 20:29:59</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr"/>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:29:03</t>
+        </is>
+      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6705,14 +6721,10 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26170523218710003945</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>PASE RECORRIDO</t>
-        </is>
-      </c>
+          <t>26170523344240004172</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
@@ -6721,12 +6733,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -6995,24 +7007,24 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>351341</t>
+          <t>349978</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>93505</t>
+          <t>92143</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7022,17 +7034,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LUIS FRANCISCO</t>
+          <t>DEREMI ARMANDO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>VILLA</t>
+          <t xml:space="preserve">PERALTA </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7042,14 +7054,10 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6861873597</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AV SOLLER 47 </t>
-        </is>
-      </c>
+          <t>6678706306</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -7057,32 +7065,32 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>11-02-1991</t>
+          <t>08-05-2010</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>UVG.LUISFRANCISCO@GMAIL.COM</t>
+          <t>VA.PERALTA.RAMIREZ@CBATIS140.EDU.MX</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>16-03-2026 19:27:38</t>
+          <t>10-03-2026 19:09:33</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>convenio 300</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -7092,29 +7100,21 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>16-03-2026 19:31:07</t>
+          <t>10-03-2026 19:12:05</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>15-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>16-03-2026 19:30:15</t>
-        </is>
-      </c>
+          <t>09-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26170523233270003974</t>
+          <t>26170523067130003720</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Alexa Johana  Haro</t>
+          <t>Raymundo Cardenas Real</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
@@ -7146,12 +7146,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>352233</t>
+          <t>352789</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>94397</t>
+          <t>94953</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7161,17 +7161,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>STEFANY YERALDI</t>
+          <t>JOANA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">REYES </t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>VILLAREAL</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6383809898</t>
+          <t>6863400587</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -7196,17 +7196,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>06-12-1993</t>
+          <t>05-02-2005</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>FANYBLUE93@HOTMAIL.COM</t>
+          <t>JH020588898@GMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>19-03-2026 20:33:35</t>
+          <t>23-03-2026 15:17:49</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7231,17 +7231,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>19-03-2026 20:37:28</t>
+          <t>23-03-2026 15:21:16</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
+          <t>22-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>19-03-2026 20:36:21</t>
+          <t>23-03-2026 15:20:39</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26170523344570004175</t>
+          <t>26170523429500004276</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7285,12 +7285,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>351859</t>
+          <t>353463</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>94023</t>
+          <t>95627</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7300,17 +7300,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>RAFAEL</t>
+          <t>JESSICA ABYGAIL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ENCISO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CONTRERAS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7320,28 +7320,32 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>6861989778</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>6688364208</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>25-10-1989</t>
+          <t>01-03-1996</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>RELZX89PER@GMAIL.COM</t>
+          <t>ABYCONTRERAS77@GMAIL.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>18-03-2026 15:58:55</t>
+          <t>25-03-2026 20:02:03</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7351,36 +7355,44 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>19-03-2026 15:51:19</t>
+          <t>25-03-2026 20:07:45</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>18-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr"/>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>25-03-2026 20:07:02</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7388,44 +7400,36 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26170523331510004134</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>JOSE LUIS  LOPEZ  CORONEL</t>
-        </is>
-      </c>
+          <t>26170523517220004490</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Alexa Johana  Haro</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>352149</t>
+          <t>352233</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>94313</t>
+          <t>94397</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7435,17 +7439,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>RAQUEL YUREM</t>
+          <t>STEFANY YERALDI</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CASTELLANOS</t>
+          <t xml:space="preserve">REYES </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>VILLAREAL</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7455,10 +7459,14 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>6863894647</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>6383809898</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -7466,56 +7474,64 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>28-06-1992</t>
+          <t>06-12-1993</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CASTELLANOSR@UABC.EDU.MX</t>
+          <t>FANYBLUE93@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>19-03-2026 17:22:50</t>
+          <t>19-03-2026 20:33:35</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>3 MESES $1,899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>19-03-2026 17:24:06</t>
+          <t>19-03-2026 20:37:28</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>18-06-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr"/>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>19-03-2026 20:36:21</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -7523,24 +7539,4312 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26170523334750004144</t>
+          <t>26170523344570004175</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Alexa Johana  Haro</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>353464</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>95628</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VALERIA </t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>AMAVIZCA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6864205317</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>10-07-1996</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>VALEDONS10@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>25-03-2026 20:04:18</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>25-03-2026 20:07:45</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26170523517220004490</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Alexa Johana  Haro</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>354207</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>96371</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KEYSI XIOMARA </t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COVARRUBIAS </t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ANDRADE</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6864226393</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>18-02-2006</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>COBARRUBIASKYSI@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>30-03-2026 13:44:32</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>30-03-2026 13:47:14</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26170523628730004664</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>353627</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>95791</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ANNIE LUUE</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>BUENROSTRO</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>CORTEZ</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>6861363924</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>09-10-2005</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>CORTEZANNIE24@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>26-03-2026 18:50:34</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>26-03-2026 18:54:55</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>26-03-2026 18:53:57</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26170523544460004540</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>353647</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>95811</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LUIS DANIEL</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>CAMACHO</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>6863477259</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>02-02-2006</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>DANIELWERO403@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>26-03-2026 19:55:42</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>26-03-2026 19:56:59</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26170523547490004555</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Alexa Johana  Haro</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>353649</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>95813</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>JOSE LUIS</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MALDONADO </t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>RAMIREZ</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>6863309802</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>16-05-2005</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>JOSE10LUISMR@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>26-03-2026 19:58:42</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>26-03-2026 19:59:36</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26170523547670004557</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>Alexa Johana  Haro</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>354306</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>96470</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LUIS RODRIGO</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PEREA</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>QUIROZ</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>6863544962</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>24-11-2001</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>ROPEREA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:07:09</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:12:22</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:11:41</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26170523636760004682</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>353025</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>95189</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GABRIELA </t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REYES </t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>7851038682</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>POIRTALES</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>18-10-1992</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>GABYREYEZHERNANDEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>24-03-2026 08:15:51</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>26-03-2026 19:48:57</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>26-03-2026 19:44:56</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26170523547170004554</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>353116</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>95280</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ANGEL JAHAZIEL</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>BRIZ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DORAME</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6867276601</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>SAN MARCOS</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>25-07-1985</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>ANGEL.J.BRIZ.D@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>24-03-2026 15:16:09</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>25-03-2026 16:29:56</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>25-03-2026 16:28:23</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26170523505740004459</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>353392</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>95556</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AXEL</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6865868266</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>29-08-2011</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>AXELITOGONZALEZATG35@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>25-03-2026 17:11:21</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>25-03-2026 17:13:27</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26170523507750004467</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>353209</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>95373</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>JUAN PABLO</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>BARBA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>BALLESTEROS</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6863152986</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>07-01-1972</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>PABLOBARBA72@HOTMNAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>24-03-2026 19:15:49</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>24-03-2026 19:23:48</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>24-03-2026 19:23:17</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26170523482180004406</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>353927</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>96091</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANGELICA ESTEFANIA </t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DOMINGUEZ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>JARAMILLO</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6863640620</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>06-01-2004</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>JARAMILLOANGELICA7906@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>28-03-2026 12:08:25</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>28-03-2026 12:10:52</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>27-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>26170523594350004629</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Alexa Johana  Haro</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>354329</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>96493</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CYNTHIA </t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CUEVAS</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6863575906</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>PORTL</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>13-11-1981</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>CYNTHIALCUEVAS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:39:54</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:42:36</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:41:54</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>26170523638680004687</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>353551</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>95715</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JHOVANNY ISRAEL </t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ORDOÑEZ </t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>BUSTOS</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6863309270</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>AV DESICION 2363</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>29-05-1997</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>JHOVANNYOB29@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>26-03-2026 13:33:37</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>26-03-2026 13:42:01</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>26-03-2026 13:41:11</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>26170523533940004519</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>353843</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>96007</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EMANUEL</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>SANDOVAL</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6862289829</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>09-05-2005</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>SERBROGENEV@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>27-03-2026 21:37:43</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>27-03-2026 21:40:06</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>26-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>26170523577120004620</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>353553</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>95717</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRENDA </t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RAMOS </t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>AUYON</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6863531869</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>26-05-1993</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>26-03-2026 13:37:49</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>26-03-2026 13:42:01</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>25-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>26170523533940004519</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>353611</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>95775</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EFRAIN </t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SALAS</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>REYES</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>6865492944</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>07-08-2006</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>EFRAINSALASJR1@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>26-03-2026 17:44:15</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>27-03-2026 17:49:57</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>26-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>26170523570810004599</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>351136</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>93300</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUAN </t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>HARO</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>CHAVEZ</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>6861808524</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>23-10-1991</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>JUANC.HAROC@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>16-03-2026 12:10:33</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>16-03-2026 12:19:43</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>26170523218710003945</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>PASE RECORRIDO</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>354464</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>96628</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EDUARDO ALEXANDER</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ESCALANTE</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ZAMORA</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>6864216961</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>PORETALES</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>27-02-2014</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>EAEZ2702@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>30-03-2026 21:22:56</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>30-03-2026 21:30:30</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>30-03-2026 21:28:53</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>26170523652380004754</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>349761</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>91926</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>JUANA</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>GATICA</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>BAUTISTA</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6862453198</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>10-03-1983</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>GATICAJUANA308@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>10-03-2026 08:07:14</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>14-03-2026 08:44:32</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>13-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>14-03-2026 08:43:57</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>26170523178290003905</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>Thannia Lilian Lugo Morales</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>351341</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>93505</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LUIS FRANCISCO</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>VILLA</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>GUZMAN</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6861873597</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AV SOLLER 47 </t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>11-02-1991</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>UVG.LUISFRANCISCO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:27:38</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:31:07</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>15-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>16-03-2026 19:30:15</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>26170523233270003974</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Alexa Johana  Haro</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>350483</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>92647</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIANEY </t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SARMIENTO </t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>6863354738</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>ISLAS MINDANAO 849</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>21-07-2001</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>VSARMIENTOHERNANDEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>12-03-2026 20:14:08</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>13-03-2026 17:18:08</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>12-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>13-03-2026 17:17:26</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>26170523158300003880</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>351859</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>94023</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RAFAEL</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>ENCISO</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>6861989778</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>25-10-1989</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>RELZX89PER@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>18-03-2026 15:58:55</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>19-03-2026 15:51:19</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>18-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>26170523331510004134</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>JOSE LUIS  LOPEZ  CORONEL</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>352149</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>94313</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RAQUEL YUREM</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>CASTELLANOS</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>CAMPOS</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6863894647</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>28-06-1992</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>CASTELLANOSR@UABC.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>19-03-2026 17:22:50</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>19-03-2026 17:24:06</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>18-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>26170523334750004144</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr">
+        <is>
           <t>1899</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>Raymundo Cardenas Real</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
+      <c r="AC75" t="inlineStr">
         <is>
           <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>352484</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>94648</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MAXIMILIANO </t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>SILVA</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>MORALES</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>6866059485</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>PORTLES</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>21-08-2011</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>SILVAMORALES2022@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>21-03-2026 10:05:56</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:13:50</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:12:08</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>26170523646060004709</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>352630</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>94794</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>KATZARA</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>VERDEJA ESQUER</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>VERDEJA ESQUER</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>6862482816</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>BARCELONA, PACIFICA RESIDENCIAL</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>30-08-2005</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>KATZARAV@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>22-03-2026 22:22:41</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>22-03-2026 22:22:41</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>21-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>22-03-2026 22:22:41</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>26170523407940004250</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>353256</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>95420</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>JORGE IVAN</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SALAZAR</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>6861128183</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>10-10-1979</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>RDZJI@YAHOO.COM</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>24-03-2026 21:35:23</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>3 MESES $1,899</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>30-03-2026 20:42:44</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>29-06-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>26170523651010004746</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANAILY AVILA RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>354172</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>96336</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>MARIA ANTONIETA</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>JEREZ</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>6861572616</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>CERRADA DE LA CARICA 437</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>08-02-1966</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>TONYLOGE66@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>30-03-2026 12:10:35</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>30-03-2026 12:19:22</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>30-03-2026 12:18:43</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>26170523625980004661</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>353119</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>95283</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>GERARDO EZEQUIEL</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>OROZCO</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ORTIZ</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>6531017520</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>30-11-2005</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>GERARDOEZEQUELOROZCOORTIZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>24-03-2026 15:26:32</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>24-03-2026 15:28:17</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>23-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>26170523469500004371</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Raymundo Cardenas Real</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>353390</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>95554</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LUIS ANGEL</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>SOLANO</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>RIOS</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>6861694464</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>25-12-2005</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>RUISZZZ592@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>25-03-2026 17:05:28</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>25-03-2026 17:07:15</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>24-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>26170523507400004466</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>354103</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>96267</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROSA JANETH </t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OLMEDA </t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>ESTRADA</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>6864206094</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>MONTES DE LEON 39</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>13-05-1988</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>ROSAJANETHOLMEDA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>30-03-2026 08:56:38</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (ADULTO + ADULTO)</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>30-03-2026 09:08:19</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>30-03-2026 09:05:39</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>26170523621100004655</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>354312</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>96476</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ROGELIO</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>RIVERA</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>6625531140</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>13-10-2010</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>ROGERM.RIVERA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:14:50</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>convenio 300</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>30-03-2026 17:16:20</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>26170523637050004684</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>354417</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>96581</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>VILLAS DEL REY</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELENA </t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>ESCOBAR</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>6864296610</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>PORTALES</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>22-07-1975</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>PATIMARTINEZESCOBAR@OUTLOOK.ES</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:20:21</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:22:52</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>29-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>30-03-2026 19:22:14</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>26170523646890004715</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
